--- a/Results/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Ammonia/ammonia resource use fossils results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.38637711722365</v>
+        <v>35.38637711722358</v>
       </c>
       <c r="C2" t="n">
-        <v>39.56457782970472</v>
+        <v>39.56457782970475</v>
       </c>
       <c r="D2" t="n">
-        <v>36.92083881005444</v>
+        <v>36.92083881005443</v>
       </c>
       <c r="E2" t="n">
-        <v>41.42462648574185</v>
+        <v>41.42462648574184</v>
       </c>
       <c r="F2" t="n">
-        <v>37.23455260568202</v>
+        <v>37.234552605682</v>
       </c>
       <c r="G2" t="n">
-        <v>37.0973780330044</v>
+        <v>37.09737803300438</v>
       </c>
       <c r="H2" t="n">
-        <v>44.05961174057666</v>
+        <v>44.05961174057669</v>
       </c>
       <c r="I2" t="n">
         <v>35.70534228953645</v>
       </c>
       <c r="J2" t="n">
-        <v>48.73437416941217</v>
+        <v>48.73437416941216</v>
       </c>
       <c r="K2" t="n">
-        <v>38.5493456913513</v>
+        <v>38.54934569135133</v>
       </c>
       <c r="L2" t="n">
-        <v>41.82462817766542</v>
+        <v>41.82462817766544</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.01088013006086</v>
+        <v>40.0108801300609</v>
       </c>
       <c r="C3" t="n">
-        <v>44.23618762552476</v>
+        <v>44.23618762552474</v>
       </c>
       <c r="D3" t="n">
-        <v>41.7758289395984</v>
+        <v>41.77582893959842</v>
       </c>
       <c r="E3" t="n">
         <v>46.09720485732934</v>
       </c>
       <c r="F3" t="n">
-        <v>41.90713097726948</v>
+        <v>41.90713097726951</v>
       </c>
       <c r="G3" t="n">
-        <v>41.97888561598078</v>
+        <v>41.97888561598073</v>
       </c>
       <c r="H3" t="n">
-        <v>49.98802245249212</v>
+        <v>49.98802245249211</v>
       </c>
       <c r="I3" t="n">
-        <v>40.37848981689169</v>
+        <v>40.37848981689168</v>
       </c>
       <c r="J3" t="n">
-        <v>54.25469321077522</v>
+        <v>54.25469321077517</v>
       </c>
       <c r="K3" t="n">
-        <v>43.39923394076222</v>
+        <v>43.39923394076216</v>
       </c>
       <c r="L3" t="n">
-        <v>47.41606001949937</v>
+        <v>47.41606001949941</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.49514243083445</v>
+        <v>5.824555706130798</v>
       </c>
       <c r="C4" t="n">
-        <v>11.5240295504233</v>
+        <v>5.986415281912107</v>
       </c>
       <c r="D4" t="n">
-        <v>12.4073148865649</v>
+        <v>6.736728161861281</v>
       </c>
       <c r="E4" t="n">
-        <v>11.64408607520378</v>
+        <v>6.007545955334663</v>
       </c>
       <c r="F4" t="n">
-        <v>11.64408607520378</v>
+        <v>6.007545955334668</v>
       </c>
       <c r="G4" t="n">
-        <v>12.51379228049887</v>
+        <v>6.84194293524467</v>
       </c>
       <c r="H4" t="n">
-        <v>16.64950498207981</v>
+        <v>10.9789182573762</v>
       </c>
       <c r="I4" t="n">
-        <v>11.69518329772608</v>
+        <v>6.016353056575388</v>
       </c>
       <c r="J4" t="n">
-        <v>15.04041089658937</v>
+        <v>9.369824171885758</v>
       </c>
       <c r="K4" t="n">
-        <v>12.38712376006561</v>
+        <v>6.716537035361984</v>
       </c>
       <c r="L4" t="n">
-        <v>15.32169897985559</v>
+        <v>9.65111225515199</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>415.0048301805547</v>
+        <v>76.84226036526377</v>
       </c>
       <c r="C5" t="n">
-        <v>438.3133982416695</v>
+        <v>81.10134376455304</v>
       </c>
       <c r="D5" t="n">
-        <v>522.4692198746087</v>
+        <v>96.50762295332392</v>
       </c>
       <c r="E5" t="n">
-        <v>438.3133991217368</v>
+        <v>81.10134464462072</v>
       </c>
       <c r="F5" t="n">
-        <v>438.3133991217368</v>
+        <v>81.10134464462072</v>
       </c>
       <c r="G5" t="n">
-        <v>545.8585651186607</v>
+        <v>100.7106224461238</v>
       </c>
       <c r="H5" t="n">
-        <v>1087.424568500395</v>
+        <v>199.4353284154292</v>
       </c>
       <c r="I5" t="n">
-        <v>438.3131733815983</v>
+        <v>81.10111890448201</v>
       </c>
       <c r="J5" t="n">
-        <v>841.7938398591941</v>
+        <v>154.8784268808505</v>
       </c>
       <c r="K5" t="n">
-        <v>520.3161691240175</v>
+        <v>96.11204853501839</v>
       </c>
       <c r="L5" t="n">
-        <v>962.284625028132</v>
+        <v>60.25458774974938</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>882.7867499835252</v>
+        <v>133.5928877198341</v>
       </c>
       <c r="C6" t="n">
-        <v>737.5199563272108</v>
+        <v>133.761697702263</v>
       </c>
       <c r="D6" t="n">
-        <v>738.4459941732071</v>
+        <v>134.5195363662912</v>
       </c>
       <c r="E6" t="n">
-        <v>665.374593818178</v>
+        <v>121.0641146946522</v>
       </c>
       <c r="F6" t="n">
-        <v>737.6941182283923</v>
+        <v>133.7923509218805</v>
       </c>
       <c r="G6" t="n">
-        <v>883.8053998331892</v>
+        <v>160.1892650335897</v>
       </c>
       <c r="H6" t="n">
-        <v>888.76511748813</v>
+        <v>164.471265226727</v>
       </c>
       <c r="I6" t="n">
-        <v>882.9867908504167</v>
+        <v>133.7846850702788</v>
       </c>
       <c r="J6" t="n">
-        <v>778.187663396443</v>
+        <v>143.683739884066</v>
       </c>
       <c r="K6" t="n">
-        <v>738.4208875752201</v>
+        <v>134.4984787744294</v>
       </c>
       <c r="L6" t="n">
-        <v>741.4671431561195</v>
+        <v>137.4527097376681</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.25245600605266</v>
+        <v>7.189842887971294</v>
       </c>
       <c r="C7" t="n">
-        <v>19.45272173301538</v>
+        <v>7.381865098486912</v>
       </c>
       <c r="D7" t="n">
-        <v>20.16454289978262</v>
+        <v>8.102000284789735</v>
       </c>
       <c r="E7" t="n">
-        <v>19.45529849519577</v>
+        <v>7.382319333803898</v>
       </c>
       <c r="F7" t="n">
-        <v>19.45529849519577</v>
+        <v>7.382319333803898</v>
       </c>
       <c r="G7" t="n">
-        <v>20.27110585571711</v>
+        <v>8.207230117085134</v>
       </c>
       <c r="H7" t="n">
-        <v>24.40681855729805</v>
+        <v>12.34420543921666</v>
       </c>
       <c r="I7" t="n">
-        <v>19.4524968729443</v>
+        <v>7.381640238415844</v>
       </c>
       <c r="J7" t="n">
-        <v>22.79772447180761</v>
+        <v>10.73511135372622</v>
       </c>
       <c r="K7" t="n">
-        <v>20.14443733528383</v>
+        <v>8.081824217202438</v>
       </c>
       <c r="L7" t="n">
-        <v>23.07901255507382</v>
+        <v>11.01639943699245</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.6233666837125</v>
+        <v>7.783123164024673</v>
       </c>
       <c r="C8" t="n">
-        <v>31.25921454687363</v>
+        <v>9.459807822466415</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71528323149113</v>
+        <v>10.48693057024744</v>
       </c>
       <c r="E8" t="n">
-        <v>28.95290256874812</v>
+        <v>9.053897641691485</v>
       </c>
       <c r="F8" t="n">
-        <v>23.09248434708012</v>
+        <v>8.022464040266849</v>
       </c>
       <c r="G8" t="n">
-        <v>32.07344831972321</v>
+        <v>10.28444237949462</v>
       </c>
       <c r="H8" t="n">
-        <v>36.20916102130702</v>
+        <v>14.42141770162665</v>
       </c>
       <c r="I8" t="n">
-        <v>31.2548393369504</v>
+        <v>9.458852500825317</v>
       </c>
       <c r="J8" t="n">
-        <v>34.60172394173446</v>
+        <v>12.81261524917617</v>
       </c>
       <c r="K8" t="n">
-        <v>23.35872983986085</v>
+        <v>8.647539694942612</v>
       </c>
       <c r="L8" t="n">
-        <v>43.68869053355013</v>
+        <v>14.64370274154936</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.69891979464648</v>
+        <v>11.49242049144986</v>
       </c>
       <c r="C9" t="n">
-        <v>53.39754519167734</v>
+        <v>13.35615399483912</v>
       </c>
       <c r="D9" t="n">
-        <v>54.109454134652</v>
+        <v>14.07630462975436</v>
       </c>
       <c r="E9" t="n">
-        <v>64.35843809197907</v>
+        <v>15.28527186001479</v>
       </c>
       <c r="F9" t="n">
-        <v>53.3975335574537</v>
+        <v>13.35615267239145</v>
       </c>
       <c r="G9" t="n">
-        <v>54.21592931437907</v>
+        <v>14.18151901343733</v>
       </c>
       <c r="H9" t="n">
-        <v>58.35164201596007</v>
+        <v>18.31849433556886</v>
       </c>
       <c r="I9" t="n">
-        <v>53.39732033160632</v>
+        <v>13.35592913476805</v>
       </c>
       <c r="J9" t="n">
-        <v>56.7425479304696</v>
+        <v>16.70940025007843</v>
       </c>
       <c r="K9" t="n">
-        <v>42.12912994425072</v>
+        <v>13.08751718905331</v>
       </c>
       <c r="L9" t="n">
-        <v>57.0238360137358</v>
+        <v>16.99068833334466</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.38681955985926</v>
+        <v>28.38681955985925</v>
       </c>
       <c r="C2" t="n">
-        <v>34.11806238391608</v>
+        <v>34.11806238391606</v>
       </c>
       <c r="D2" t="n">
-        <v>31.92924727835531</v>
+        <v>31.92924727835528</v>
       </c>
       <c r="E2" t="n">
-        <v>35.9264329141733</v>
+        <v>35.92643291417328</v>
       </c>
       <c r="F2" t="n">
-        <v>31.89115563641192</v>
+        <v>31.89115563641193</v>
       </c>
       <c r="G2" t="n">
-        <v>31.5495560982179</v>
+        <v>31.54955609821791</v>
       </c>
       <c r="H2" t="n">
-        <v>31.00498812744912</v>
+        <v>31.00498812744911</v>
       </c>
       <c r="I2" t="n">
-        <v>30.46930664205258</v>
+        <v>30.46930664205257</v>
       </c>
       <c r="J2" t="n">
-        <v>42.41996105870042</v>
+        <v>42.41996105870039</v>
       </c>
       <c r="K2" t="n">
-        <v>31.22668510206056</v>
+        <v>31.22668510206057</v>
       </c>
       <c r="L2" t="n">
-        <v>31.12986278111054</v>
+        <v>31.12986278111052</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.93596837271098</v>
+        <v>31.93596837271097</v>
       </c>
       <c r="C3" t="n">
-        <v>37.9792901227332</v>
+        <v>37.97929012273315</v>
       </c>
       <c r="D3" t="n">
-        <v>36.01049406067268</v>
+        <v>36.01049406067265</v>
       </c>
       <c r="E3" t="n">
-        <v>39.78854221231541</v>
+        <v>39.7885422123154</v>
       </c>
       <c r="F3" t="n">
-        <v>35.75326493455406</v>
+        <v>35.75326493455403</v>
       </c>
       <c r="G3" t="n">
-        <v>35.57377055072365</v>
+        <v>35.57377055072362</v>
       </c>
       <c r="H3" t="n">
-        <v>34.9481015880591</v>
+        <v>34.94810158805911</v>
       </c>
       <c r="I3" t="n">
-        <v>34.33141619621509</v>
+        <v>34.33141619621505</v>
       </c>
       <c r="J3" t="n">
-        <v>47.02956200534028</v>
+        <v>47.0295620053402</v>
       </c>
       <c r="K3" t="n">
         <v>35.00722704579658</v>
       </c>
       <c r="L3" t="n">
-        <v>35.09110183392132</v>
+        <v>35.09110183392133</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.771041198810378</v>
+        <v>1.244126713048688</v>
       </c>
       <c r="C4" t="n">
-        <v>5.758493653159487</v>
+        <v>2.438497048399755</v>
       </c>
       <c r="D4" t="n">
-        <v>6.876864372060767</v>
+        <v>3.349949886299086</v>
       </c>
       <c r="E4" t="n">
-        <v>5.837441762246407</v>
+        <v>2.452393127290685</v>
       </c>
       <c r="F4" t="n">
-        <v>5.837441762246411</v>
+        <v>2.452393127290689</v>
       </c>
       <c r="G4" t="n">
-        <v>6.653613688818438</v>
+        <v>3.124672464251723</v>
       </c>
       <c r="H4" t="n">
-        <v>6.327626213724957</v>
+        <v>2.800711727963269</v>
       </c>
       <c r="I4" t="n">
-        <v>6.02509008402387</v>
+        <v>2.485271998463304</v>
       </c>
       <c r="J4" t="n">
-        <v>8.967871116610047</v>
+        <v>5.440956630848363</v>
       </c>
       <c r="K4" t="n">
-        <v>5.686799283052709</v>
+        <v>2.159884797291026</v>
       </c>
       <c r="L4" t="n">
-        <v>6.401904784890113</v>
+        <v>2.874990299128426</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.97889765930186</v>
+        <v>3.744709436545521</v>
       </c>
       <c r="C5" t="n">
-        <v>124.1775164018555</v>
+        <v>23.28024493923708</v>
       </c>
       <c r="D5" t="n">
-        <v>195.1446217261575</v>
+        <v>36.48507500107404</v>
       </c>
       <c r="E5" t="n">
-        <v>124.1775178724464</v>
+        <v>23.28024640982802</v>
       </c>
       <c r="F5" t="n">
-        <v>124.1775178724464</v>
+        <v>23.28024640982802</v>
       </c>
       <c r="G5" t="n">
-        <v>184.2757289302598</v>
+        <v>34.38616457735224</v>
       </c>
       <c r="H5" t="n">
-        <v>171.0090719249037</v>
+        <v>31.78464601607826</v>
       </c>
       <c r="I5" t="n">
-        <v>124.17733919128</v>
+        <v>23.28006772866162</v>
       </c>
       <c r="J5" t="n">
-        <v>420.812633637981</v>
+        <v>77.92563444184381</v>
       </c>
       <c r="K5" t="n">
-        <v>93.06698396288212</v>
+        <v>17.53879721760877</v>
       </c>
       <c r="L5" t="n">
-        <v>99.92508222370584</v>
+        <v>35.20540133908856</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>761.0543742497873</v>
+        <v>134.3499926087727</v>
       </c>
       <c r="C6" t="n">
-        <v>637.5834865495065</v>
+        <v>113.6396951956017</v>
       </c>
       <c r="D6" t="n">
-        <v>638.6394056876715</v>
+        <v>136.4869008777443</v>
       </c>
       <c r="E6" t="n">
-        <v>574.7740737592783</v>
+        <v>102.585239816188</v>
       </c>
       <c r="F6" t="n">
-        <v>637.7040730793649</v>
+        <v>113.6609196365085</v>
       </c>
       <c r="G6" t="n">
-        <v>762.9369467397955</v>
+        <v>114.29816812626</v>
       </c>
       <c r="H6" t="n">
-        <v>763.2002754860202</v>
+        <v>136.0102972780772</v>
       </c>
       <c r="I6" t="n">
-        <v>637.6926824954636</v>
+        <v>113.6587676604715</v>
       </c>
       <c r="J6" t="n">
-        <v>765.6231678664747</v>
+        <v>138.6122881372218</v>
       </c>
       <c r="K6" t="n">
-        <v>637.2469647717666</v>
+        <v>113.3144733210018</v>
       </c>
       <c r="L6" t="n">
-        <v>638.1205081593681</v>
+        <v>114.0574638905829</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.591598097517416</v>
+        <v>2.092544722623881</v>
       </c>
       <c r="C7" t="n">
-        <v>10.84582419330635</v>
+        <v>3.333867218613948</v>
       </c>
       <c r="D7" t="n">
-        <v>11.69741681949834</v>
+        <v>4.198367112450859</v>
       </c>
       <c r="E7" t="n">
-        <v>10.80620802956901</v>
+        <v>3.326895985600877</v>
       </c>
       <c r="F7" t="n">
-        <v>10.80620802956901</v>
+        <v>3.326895985600877</v>
       </c>
       <c r="G7" t="n">
-        <v>11.47417058752547</v>
+        <v>3.973090473826915</v>
       </c>
       <c r="H7" t="n">
-        <v>11.148183112432</v>
+        <v>3.649129737538465</v>
       </c>
       <c r="I7" t="n">
-        <v>10.84564698273091</v>
+        <v>3.333690008038496</v>
       </c>
       <c r="J7" t="n">
-        <v>13.78842801531709</v>
+        <v>6.289374640423553</v>
       </c>
       <c r="K7" t="n">
-        <v>10.50735618175974</v>
+        <v>3.008302806866219</v>
       </c>
       <c r="L7" t="n">
-        <v>11.22246168359715</v>
+        <v>3.723408308703622</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.91431483603428</v>
+        <v>2.325342867341408</v>
       </c>
       <c r="C8" t="n">
-        <v>16.73602545949342</v>
+        <v>4.370542635845529</v>
       </c>
       <c r="D8" t="n">
-        <v>18.5794520837531</v>
+        <v>5.409605312396469</v>
       </c>
       <c r="E8" t="n">
-        <v>15.48072743274098</v>
+        <v>4.149611396101175</v>
       </c>
       <c r="F8" t="n">
-        <v>12.29086783651791</v>
+        <v>3.588196110208</v>
       </c>
       <c r="G8" t="n">
-        <v>17.40142128820397</v>
+        <v>5.016286591493663</v>
       </c>
       <c r="H8" t="n">
-        <v>17.0754338131198</v>
+        <v>4.692325855206846</v>
       </c>
       <c r="I8" t="n">
-        <v>16.77289768340941</v>
+        <v>4.376886125705242</v>
       </c>
       <c r="J8" t="n">
-        <v>19.71658363235051</v>
+        <v>7.332730023367908</v>
       </c>
       <c r="K8" t="n">
-        <v>11.74454133852415</v>
+        <v>3.226047393276881</v>
       </c>
       <c r="L8" t="n">
-        <v>21.95953312657047</v>
+        <v>5.613132872427248</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.16468897548286</v>
+        <v>3.777408708016183</v>
       </c>
       <c r="C9" t="n">
-        <v>24.7047333809615</v>
+        <v>5.77303522242436</v>
       </c>
       <c r="D9" t="n">
-        <v>25.5563347878294</v>
+        <v>6.637536661660226</v>
       </c>
       <c r="E9" t="n">
-        <v>29.65047972052933</v>
+        <v>6.64348778523858</v>
       </c>
       <c r="F9" t="n">
-        <v>24.70473285149679</v>
+        <v>5.773036341005484</v>
       </c>
       <c r="G9" t="n">
-        <v>25.33307977518061</v>
+        <v>6.412258477637334</v>
       </c>
       <c r="H9" t="n">
-        <v>25.00709230008709</v>
+        <v>6.088297741348883</v>
       </c>
       <c r="I9" t="n">
-        <v>24.70455617038606</v>
+        <v>5.77285801184891</v>
       </c>
       <c r="J9" t="n">
-        <v>27.64733720297223</v>
+        <v>8.728542644233967</v>
       </c>
       <c r="K9" t="n">
-        <v>21.88304723000482</v>
+        <v>5.01042442050864</v>
       </c>
       <c r="L9" t="n">
-        <v>25.08137087125228</v>
+        <v>6.162576312514037</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.33786235871407</v>
+        <v>33.33786235871408</v>
       </c>
       <c r="C2" t="n">
-        <v>32.2903104447925</v>
+        <v>32.29031044479255</v>
       </c>
       <c r="D2" t="n">
-        <v>35.79842461537146</v>
+        <v>35.79842461537221</v>
       </c>
       <c r="E2" t="n">
-        <v>34.02041293627797</v>
+        <v>34.02041293627796</v>
       </c>
       <c r="F2" t="n">
-        <v>34.02041293627797</v>
+        <v>34.02041293627796</v>
       </c>
       <c r="G2" t="n">
-        <v>35.69229028829417</v>
+        <v>35.69229028829412</v>
       </c>
       <c r="H2" t="n">
-        <v>38.37021054213562</v>
+        <v>38.37021054213558</v>
       </c>
       <c r="I2" t="n">
-        <v>34.95683857904697</v>
+        <v>34.95683857904696</v>
       </c>
       <c r="J2" t="n">
-        <v>40.4541365762146</v>
+        <v>40.45413657621465</v>
       </c>
       <c r="K2" t="n">
-        <v>36.24888377846313</v>
+        <v>36.24888377846293</v>
       </c>
       <c r="L2" t="n">
-        <v>34.71861746945857</v>
+        <v>34.71861746945855</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.4873292393552</v>
+        <v>37.48732923935518</v>
       </c>
       <c r="C3" t="n">
-        <v>36.43043268145238</v>
+        <v>36.43043268145245</v>
       </c>
       <c r="D3" t="n">
-        <v>40.31748553844843</v>
+        <v>40.31748553844798</v>
       </c>
       <c r="E3" t="n">
-        <v>38.41323768631709</v>
+        <v>38.41323768631706</v>
       </c>
       <c r="F3" t="n">
-        <v>38.41323768631709</v>
+        <v>38.41323768631706</v>
       </c>
       <c r="G3" t="n">
-        <v>40.19540907664879</v>
+        <v>40.19540907664857</v>
       </c>
       <c r="H3" t="n">
-        <v>43.27668260828555</v>
+        <v>43.27668260828552</v>
       </c>
       <c r="I3" t="n">
-        <v>39.3504962714252</v>
+        <v>39.35049627142519</v>
       </c>
       <c r="J3" t="n">
         <v>45.44883425669848</v>
       </c>
       <c r="K3" t="n">
-        <v>40.71637609349008</v>
+        <v>40.71637609349013</v>
       </c>
       <c r="L3" t="n">
-        <v>39.07560081205222</v>
+        <v>39.07560081205218</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.765824840639573</v>
+        <v>3.193974122904979</v>
       </c>
       <c r="C4" t="n">
-        <v>7.326911703455545</v>
+        <v>3.089111490883501</v>
       </c>
       <c r="D4" t="n">
-        <v>9.228524839355167</v>
+        <v>4.656674121621076</v>
       </c>
       <c r="E4" t="n">
-        <v>8.624770114655711</v>
+        <v>4.138750767931356</v>
       </c>
       <c r="F4" t="n">
-        <v>8.624770114655702</v>
+        <v>4.138750767931356</v>
       </c>
       <c r="G4" t="n">
-        <v>9.157732518192732</v>
+        <v>4.592226568336041</v>
       </c>
       <c r="H4" t="n">
-        <v>10.75681399475308</v>
+        <v>6.184963277018488</v>
       </c>
       <c r="I4" t="n">
-        <v>8.676939993007556</v>
+        <v>4.147822532044172</v>
       </c>
       <c r="J4" t="n">
-        <v>11.11089794219917</v>
+        <v>6.539047224464577</v>
       </c>
       <c r="K4" t="n">
-        <v>9.024437667307518</v>
+        <v>4.45258694957283</v>
       </c>
       <c r="L4" t="n">
-        <v>8.587093257643339</v>
+        <v>4.015242539908722</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>181.5095441143293</v>
+        <v>33.77286854937943</v>
       </c>
       <c r="C5" t="n">
-        <v>177.2601620141098</v>
+        <v>32.99736338349761</v>
       </c>
       <c r="D5" t="n">
-        <v>317.6902835680816</v>
+        <v>58.9459433637077</v>
       </c>
       <c r="E5" t="n">
-        <v>271.8895242349926</v>
+        <v>50.47334724204194</v>
       </c>
       <c r="F5" t="n">
-        <v>271.8895242349926</v>
+        <v>50.47334724204194</v>
       </c>
       <c r="G5" t="n">
-        <v>320.7683662479826</v>
+        <v>59.43569780760392</v>
       </c>
       <c r="H5" t="n">
-        <v>526.9967470767687</v>
+        <v>97.04319100712836</v>
       </c>
       <c r="I5" t="n">
-        <v>271.8893905767072</v>
+        <v>50.47321358375645</v>
       </c>
       <c r="J5" t="n">
-        <v>526.369629591623</v>
+        <v>97.22458350337433</v>
       </c>
       <c r="K5" t="n">
-        <v>299.1257173833485</v>
+        <v>55.51041190293629</v>
       </c>
       <c r="L5" t="n">
-        <v>294.4116022416785</v>
+        <v>54.32035584851553</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>807.7648735045537</v>
+        <v>120.6419424506911</v>
       </c>
       <c r="C6" t="n">
-        <v>674.7489484021816</v>
+        <v>120.555389313356</v>
       </c>
       <c r="D6" t="n">
-        <v>676.610839658801</v>
+        <v>122.1159597119773</v>
       </c>
       <c r="E6" t="n">
-        <v>609.5536468123315</v>
+        <v>109.9022324936318</v>
       </c>
       <c r="F6" t="n">
-        <v>676.0198745530587</v>
+        <v>121.6002885126127</v>
       </c>
       <c r="G6" t="n">
-        <v>809.1567811821062</v>
+        <v>145.3920583702463</v>
       </c>
       <c r="H6" t="n">
-        <v>811.741346409954</v>
+        <v>147.1582402182158</v>
       </c>
       <c r="I6" t="n">
-        <v>808.6759886569207</v>
+        <v>144.9476543339545</v>
       </c>
       <c r="J6" t="n">
-        <v>811.5456534057104</v>
+        <v>147.4155634226884</v>
       </c>
       <c r="K6" t="n">
-        <v>676.3628378004067</v>
+        <v>121.9041447365704</v>
       </c>
       <c r="L6" t="n">
-        <v>675.9337547570207</v>
+        <v>121.4682543273678</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.1658561111448</v>
+        <v>4.320379620410344</v>
       </c>
       <c r="C7" t="n">
-        <v>14.1211086157945</v>
+        <v>4.284890140975702</v>
       </c>
       <c r="D7" t="n">
-        <v>15.62854953634852</v>
+        <v>5.783078462188334</v>
       </c>
       <c r="E7" t="n">
-        <v>15.07896519765383</v>
+        <v>5.274689096383836</v>
       </c>
       <c r="F7" t="n">
-        <v>15.07896519765383</v>
+        <v>5.274689096383836</v>
       </c>
       <c r="G7" t="n">
-        <v>15.55776378869788</v>
+        <v>5.718632065841412</v>
       </c>
       <c r="H7" t="n">
-        <v>17.15684526525831</v>
+        <v>7.31136877452386</v>
       </c>
       <c r="I7" t="n">
-        <v>15.0769712635127</v>
+        <v>5.274228029549539</v>
       </c>
       <c r="J7" t="n">
-        <v>17.51092921270434</v>
+        <v>7.665452721969945</v>
       </c>
       <c r="K7" t="n">
-        <v>15.42446893781261</v>
+        <v>5.578992447078198</v>
       </c>
       <c r="L7" t="n">
-        <v>14.9871245281485</v>
+        <v>5.141648037414088</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.73264219331228</v>
+        <v>4.772133968423932</v>
       </c>
       <c r="C8" t="n">
-        <v>23.53084172179414</v>
+        <v>5.94100315868056</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45352507146783</v>
+        <v>7.688274146045794</v>
       </c>
       <c r="E8" t="n">
-        <v>22.61592993743141</v>
+        <v>6.601194883396872</v>
       </c>
       <c r="F8" t="n">
-        <v>17.86181855267948</v>
+        <v>5.764471284214401</v>
       </c>
       <c r="G8" t="n">
-        <v>24.96443749451426</v>
+        <v>7.37420662909417</v>
       </c>
       <c r="H8" t="n">
-        <v>26.56351897110235</v>
+        <v>8.966943337781517</v>
       </c>
       <c r="I8" t="n">
-        <v>24.48364496932887</v>
+        <v>6.92980259280231</v>
       </c>
       <c r="J8" t="n">
-        <v>26.91894714180095</v>
+        <v>9.321263868518756</v>
       </c>
       <c r="K8" t="n">
-        <v>17.86420059670673</v>
+        <v>6.008385216716838</v>
       </c>
       <c r="L8" t="n">
-        <v>31.53863278911155</v>
+        <v>8.054713475558803</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.01887945034501</v>
+        <v>6.934511713944653</v>
       </c>
       <c r="C9" t="n">
-        <v>35.34903403166818</v>
+        <v>8.021004993924871</v>
       </c>
       <c r="D9" t="n">
-        <v>36.85648615478623</v>
+        <v>9.519195286788673</v>
       </c>
       <c r="E9" t="n">
-        <v>43.66153041004509</v>
+        <v>10.3052205465062</v>
       </c>
       <c r="F9" t="n">
-        <v>36.30502558654071</v>
+        <v>9.010475704585122</v>
       </c>
       <c r="G9" t="n">
-        <v>36.78568920457199</v>
+        <v>9.454746918790573</v>
       </c>
       <c r="H9" t="n">
-        <v>38.38477068113215</v>
+        <v>11.04748362747302</v>
       </c>
       <c r="I9" t="n">
-        <v>36.30489667938642</v>
+        <v>9.010342882498708</v>
       </c>
       <c r="J9" t="n">
-        <v>38.73885462857773</v>
+        <v>11.40156757491911</v>
       </c>
       <c r="K9" t="n">
-        <v>28.62525352340813</v>
+        <v>8.665026425521239</v>
       </c>
       <c r="L9" t="n">
-        <v>36.21504994402158</v>
+        <v>8.87776289036325</v>
       </c>
     </row>
   </sheetData>
@@ -1703,19 +1703,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.8247149543358</v>
+        <v>31.82471495433581</v>
       </c>
       <c r="C2" t="n">
         <v>31.25911544530609</v>
       </c>
       <c r="D2" t="n">
-        <v>34.41770038083048</v>
+        <v>34.41770038083049</v>
       </c>
       <c r="E2" t="n">
-        <v>31.59442393954864</v>
+        <v>31.59442393954866</v>
       </c>
       <c r="F2" t="n">
-        <v>31.59442393954864</v>
+        <v>31.59442393954866</v>
       </c>
       <c r="G2" t="n">
         <v>33.83149713253767</v>
@@ -1727,10 +1727,10 @@
         <v>32.59886053464709</v>
       </c>
       <c r="J2" t="n">
-        <v>38.18477220201763</v>
+        <v>38.18477220201761</v>
       </c>
       <c r="K2" t="n">
-        <v>33.49957843840522</v>
+        <v>33.49957843840523</v>
       </c>
       <c r="L2" t="n">
         <v>32.55724739298486</v>
@@ -1743,34 +1743,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.74192000914352</v>
+        <v>35.74192000914353</v>
       </c>
       <c r="C3" t="n">
-        <v>35.24171893031059</v>
+        <v>35.24171893031056</v>
       </c>
       <c r="D3" t="n">
-        <v>38.72439038492534</v>
+        <v>38.72439038492536</v>
       </c>
       <c r="E3" t="n">
-        <v>35.62806733891926</v>
+        <v>35.62806733891924</v>
       </c>
       <c r="F3" t="n">
-        <v>35.62806733891926</v>
+        <v>35.62806733891924</v>
       </c>
       <c r="G3" t="n">
-        <v>38.0501352177515</v>
+        <v>38.05013521775151</v>
       </c>
       <c r="H3" t="n">
-        <v>39.20859493312257</v>
+        <v>39.20859493312259</v>
       </c>
       <c r="I3" t="n">
-        <v>36.63284928958259</v>
+        <v>36.63284928958258</v>
       </c>
       <c r="J3" t="n">
-        <v>42.84751668390963</v>
+        <v>42.8475166839096</v>
       </c>
       <c r="K3" t="n">
-        <v>37.56268286984282</v>
+        <v>37.56268286984284</v>
       </c>
       <c r="L3" t="n">
         <v>36.5846012205489</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.961710288628689</v>
+        <v>2.126787786971154</v>
       </c>
       <c r="C4" t="n">
-        <v>5.897588752009648</v>
+        <v>2.331465242233454</v>
       </c>
       <c r="D4" t="n">
-        <v>7.503130250566882</v>
+        <v>3.668207748909376</v>
       </c>
       <c r="E4" t="n">
-        <v>6.269015018670317</v>
+        <v>2.56058472940912</v>
       </c>
       <c r="F4" t="n">
-        <v>6.26901501867032</v>
+        <v>2.560584729409121</v>
       </c>
       <c r="G4" t="n">
-        <v>7.146036837774838</v>
+        <v>3.318217563211358</v>
       </c>
       <c r="H4" t="n">
-        <v>7.752707943972903</v>
+        <v>3.917785442315345</v>
       </c>
       <c r="I4" t="n">
-        <v>6.364420605319374</v>
+        <v>2.577211360711122</v>
       </c>
       <c r="J4" t="n">
-        <v>8.912246265495325</v>
+        <v>5.077323763837841</v>
       </c>
       <c r="K4" t="n">
-        <v>6.539119536363011</v>
+        <v>2.704197034705385</v>
       </c>
       <c r="L4" t="n">
-        <v>6.397626623975056</v>
+        <v>2.562704122317582</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94.48042617329901</v>
+        <v>17.70608169825512</v>
       </c>
       <c r="C5" t="n">
-        <v>118.6427618093007</v>
+        <v>22.17461559279449</v>
       </c>
       <c r="D5" t="n">
-        <v>233.1199363803528</v>
+        <v>43.37676541258677</v>
       </c>
       <c r="E5" t="n">
-        <v>135.0801334994826</v>
+        <v>25.23134145918818</v>
       </c>
       <c r="F5" t="n">
-        <v>135.0801334994826</v>
+        <v>25.23134145918818</v>
       </c>
       <c r="G5" t="n">
-        <v>206.999394093627</v>
+        <v>38.49240824964624</v>
       </c>
       <c r="H5" t="n">
-        <v>289.4398750035871</v>
+        <v>53.49472657616963</v>
       </c>
       <c r="I5" t="n">
-        <v>135.0799335579085</v>
+        <v>25.23114151761408</v>
       </c>
       <c r="J5" t="n">
-        <v>381.5308709206206</v>
+        <v>70.65820134778306</v>
       </c>
       <c r="K5" t="n">
-        <v>145.1180964351719</v>
+        <v>27.09409683673652</v>
       </c>
       <c r="L5" t="n">
-        <v>151.3099914726399</v>
+        <v>28.06728019748337</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>762.6666095440937</v>
+        <v>135.3068493342829</v>
       </c>
       <c r="C6" t="n">
-        <v>637.6886304259726</v>
+        <v>113.5266879743281</v>
       </c>
       <c r="D6" t="n">
-        <v>639.2725876037</v>
+        <v>136.8849891250599</v>
       </c>
       <c r="E6" t="n">
-        <v>575.0593814803353</v>
+        <v>102.6676886842215</v>
       </c>
       <c r="F6" t="n">
-        <v>638.0153652420593</v>
+        <v>113.7479417662454</v>
       </c>
       <c r="G6" t="n">
-        <v>638.7944267037328</v>
+        <v>114.4883335772332</v>
       </c>
       <c r="H6" t="n">
-        <v>765.2457142909161</v>
+        <v>137.2365538369757</v>
       </c>
       <c r="I6" t="n">
-        <v>638.0128104712785</v>
+        <v>113.747327374733</v>
       </c>
       <c r="J6" t="n">
-        <v>672.8389422863752</v>
+        <v>121.9284216303429</v>
       </c>
       <c r="K6" t="n">
-        <v>638.1222824684744</v>
+        <v>113.8628331084324</v>
       </c>
       <c r="L6" t="n">
-        <v>638.0634766197833</v>
+        <v>113.7358931191763</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.39155103162397</v>
+        <v>3.082439752560037</v>
       </c>
       <c r="C7" t="n">
-        <v>11.64445672799396</v>
+        <v>3.342914000526053</v>
       </c>
       <c r="D7" t="n">
-        <v>12.93296744016889</v>
+        <v>4.623859089101039</v>
       </c>
       <c r="E7" t="n">
-        <v>11.78805051439607</v>
+        <v>3.531934971393492</v>
       </c>
       <c r="F7" t="n">
-        <v>11.78805051439607</v>
+        <v>3.531934971393492</v>
       </c>
       <c r="G7" t="n">
-        <v>12.57587758077011</v>
+        <v>4.273869528800243</v>
       </c>
       <c r="H7" t="n">
-        <v>13.18254868696825</v>
+        <v>4.873437407904236</v>
       </c>
       <c r="I7" t="n">
-        <v>11.79426134831472</v>
+        <v>3.532863326300005</v>
       </c>
       <c r="J7" t="n">
-        <v>14.34208700849065</v>
+        <v>6.032975729426713</v>
       </c>
       <c r="K7" t="n">
-        <v>11.96896027935836</v>
+        <v>3.659849000294265</v>
       </c>
       <c r="L7" t="n">
-        <v>11.82746736697038</v>
+        <v>3.518356087906473</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.34482272192151</v>
+        <v>3.426215568189624</v>
       </c>
       <c r="C8" t="n">
-        <v>19.2000013799201</v>
+        <v>4.672689852077348</v>
       </c>
       <c r="D8" t="n">
-        <v>21.65632612055768</v>
+        <v>6.159170208530193</v>
       </c>
       <c r="E8" t="n">
-        <v>17.81704069262976</v>
+        <v>4.593037237012924</v>
       </c>
       <c r="F8" t="n">
-        <v>13.92165544139857</v>
+        <v>3.907449436511164</v>
       </c>
       <c r="G8" t="n">
-        <v>20.13650994422018</v>
+        <v>5.604540817557094</v>
       </c>
       <c r="H8" t="n">
-        <v>20.74318105043854</v>
+        <v>6.204108696664555</v>
       </c>
       <c r="I8" t="n">
-        <v>19.35489371176493</v>
+        <v>4.863534615056856</v>
       </c>
       <c r="J8" t="n">
-        <v>21.90382137021963</v>
+        <v>7.363840969879587</v>
       </c>
       <c r="K8" t="n">
-        <v>13.81807236712204</v>
+        <v>3.98529272597722</v>
       </c>
       <c r="L8" t="n">
-        <v>25.24545682527519</v>
+        <v>5.879922219771705</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.71465714142873</v>
+        <v>4.899306418040772</v>
       </c>
       <c r="C9" t="n">
-        <v>26.7229025707802</v>
+        <v>5.9967204544765</v>
       </c>
       <c r="D9" t="n">
-        <v>28.01142098241904</v>
+        <v>7.277666898157099</v>
       </c>
       <c r="E9" t="n">
-        <v>32.36046831188043</v>
+        <v>7.152680484131343</v>
       </c>
       <c r="F9" t="n">
-        <v>26.87290409977427</v>
+        <v>6.186869188034013</v>
       </c>
       <c r="G9" t="n">
-        <v>27.65432342355632</v>
+        <v>6.927675982750686</v>
       </c>
       <c r="H9" t="n">
-        <v>28.26099452975441</v>
+        <v>7.527243861854683</v>
       </c>
       <c r="I9" t="n">
-        <v>26.87270719110099</v>
+        <v>6.186669780250453</v>
       </c>
       <c r="J9" t="n">
-        <v>29.42053285127697</v>
+        <v>8.686782183377154</v>
       </c>
       <c r="K9" t="n">
-        <v>24.29214534901586</v>
+        <v>5.828729560801685</v>
       </c>
       <c r="L9" t="n">
-        <v>26.90591320975668</v>
+        <v>6.172162541856903</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.85630884929037</v>
+        <v>30.85630884929035</v>
       </c>
       <c r="C2" t="n">
-        <v>30.40468648191138</v>
+        <v>30.40468648191137</v>
       </c>
       <c r="D2" t="n">
-        <v>33.43436455504654</v>
+        <v>33.43436455504662</v>
       </c>
       <c r="E2" t="n">
-        <v>29.91048779226294</v>
+        <v>29.91048779226292</v>
       </c>
       <c r="F2" t="n">
-        <v>29.91048779226294</v>
+        <v>29.91048779226292</v>
       </c>
       <c r="G2" t="n">
-        <v>32.56485951590104</v>
+        <v>32.56485951590103</v>
       </c>
       <c r="H2" t="n">
-        <v>32.94472455568746</v>
+        <v>32.94472455568748</v>
       </c>
       <c r="I2" t="n">
-        <v>30.98034139681821</v>
+        <v>30.98034139681819</v>
       </c>
       <c r="J2" t="n">
-        <v>36.36568617290237</v>
+        <v>36.36568617290227</v>
       </c>
       <c r="K2" t="n">
-        <v>31.89946551647061</v>
+        <v>31.89946551647058</v>
       </c>
       <c r="L2" t="n">
-        <v>31.25793754457699</v>
+        <v>31.25793754457698</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.61698139133672</v>
+        <v>34.61698139133671</v>
       </c>
       <c r="C3" t="n">
-        <v>34.2569151223958</v>
+        <v>34.25691512239581</v>
       </c>
       <c r="D3" t="n">
-        <v>37.5822794955869</v>
+        <v>37.58227949558692</v>
       </c>
       <c r="E3" t="n">
         <v>33.6899311937761</v>
       </c>
       <c r="F3" t="n">
-        <v>33.6899311937761</v>
+        <v>33.68993119377611</v>
       </c>
       <c r="G3" t="n">
-        <v>36.58216858314332</v>
+        <v>36.58216858314339</v>
       </c>
       <c r="H3" t="n">
-        <v>37.02000003049578</v>
+        <v>37.02000003049576</v>
       </c>
       <c r="I3" t="n">
-        <v>34.75960616662146</v>
+        <v>34.75960616662142</v>
       </c>
       <c r="J3" t="n">
-        <v>40.7648818395267</v>
+        <v>40.76488183952672</v>
       </c>
       <c r="K3" t="n">
-        <v>35.71485591254972</v>
+        <v>35.71485591254971</v>
       </c>
       <c r="L3" t="n">
-        <v>35.07904275529941</v>
+        <v>35.07904275529942</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.727943381014397</v>
+        <v>1.404396318169567</v>
       </c>
       <c r="C4" t="n">
-        <v>4.8524299777483</v>
+        <v>1.727283214050173</v>
       </c>
       <c r="D4" t="n">
-        <v>6.260488256599448</v>
+        <v>2.93694119375464</v>
       </c>
       <c r="E4" t="n">
-        <v>4.589765646269669</v>
+        <v>1.441289755780106</v>
       </c>
       <c r="F4" t="n">
-        <v>4.589765646269669</v>
+        <v>1.441289755780106</v>
       </c>
       <c r="G4" t="n">
-        <v>5.734321462496611</v>
+        <v>2.418423502985706</v>
       </c>
       <c r="H4" t="n">
-        <v>5.969400220709963</v>
+        <v>2.645853157865113</v>
       </c>
       <c r="I4" t="n">
-        <v>4.739704993479192</v>
+        <v>1.467475690016825</v>
       </c>
       <c r="J4" t="n">
-        <v>7.254953197915237</v>
+        <v>3.931406135070555</v>
       </c>
       <c r="K4" t="n">
-        <v>4.944493963097031</v>
+        <v>1.620946900252224</v>
       </c>
       <c r="L4" t="n">
-        <v>4.967100472206504</v>
+        <v>1.643553409361676</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.59732302560626</v>
+        <v>8.069407099502744</v>
       </c>
       <c r="C5" t="n">
-        <v>76.68164275768721</v>
+        <v>14.36922459481793</v>
       </c>
       <c r="D5" t="n">
-        <v>181.9780370096483</v>
+        <v>33.86322960671779</v>
       </c>
       <c r="E5" t="n">
-        <v>48.36057083352819</v>
+        <v>9.144951426994531</v>
       </c>
       <c r="F5" t="n">
-        <v>48.36057083352819</v>
+        <v>9.144951426994531</v>
       </c>
       <c r="G5" t="n">
-        <v>138.4010472363063</v>
+        <v>25.76776711265568</v>
       </c>
       <c r="H5" t="n">
-        <v>175.3261294412406</v>
+        <v>32.4526373391673</v>
       </c>
       <c r="I5" t="n">
-        <v>48.36032400011976</v>
+        <v>9.14470459358574</v>
       </c>
       <c r="J5" t="n">
-        <v>287.6030174328723</v>
+        <v>53.27266517306111</v>
       </c>
       <c r="K5" t="n">
-        <v>61.28393168400484</v>
+        <v>11.53668788540253</v>
       </c>
       <c r="L5" t="n">
-        <v>72.37183711275225</v>
+        <v>13.50678699381562</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>760.6175691928044</v>
+        <v>112.5132876934121</v>
       </c>
       <c r="C6" t="n">
-        <v>636.2755331762344</v>
+        <v>112.8577487748116</v>
       </c>
       <c r="D6" t="n">
-        <v>637.7133455264304</v>
+        <v>114.0726434710478</v>
       </c>
       <c r="E6" t="n">
-        <v>573.073869471812</v>
+        <v>101.494491486927</v>
       </c>
       <c r="F6" t="n">
-        <v>636.0254449475641</v>
+        <v>112.573968710624</v>
       </c>
       <c r="G6" t="n">
-        <v>637.0348440607796</v>
+        <v>135.4549969249884</v>
       </c>
       <c r="H6" t="n">
-        <v>762.5023140967292</v>
+        <v>135.7956452785585</v>
       </c>
       <c r="I6" t="n">
-        <v>636.0402275917622</v>
+        <v>134.5040491120193</v>
       </c>
       <c r="J6" t="n">
-        <v>670.7911019769965</v>
+        <v>137.0269085587982</v>
       </c>
       <c r="K6" t="n">
-        <v>636.1450928658246</v>
+        <v>112.7122517051724</v>
       </c>
       <c r="L6" t="n">
-        <v>636.2821115434265</v>
+        <v>112.7549947558275</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.689402863230375</v>
+        <v>2.277613182307953</v>
       </c>
       <c r="C7" t="n">
-        <v>10.04679735065778</v>
+        <v>2.641491866728521</v>
       </c>
       <c r="D7" t="n">
-        <v>11.22193937911819</v>
+        <v>3.810156586586461</v>
       </c>
       <c r="E7" t="n">
-        <v>9.682290376195507</v>
+        <v>2.337574103390443</v>
       </c>
       <c r="F7" t="n">
-        <v>9.682290376195507</v>
+        <v>2.337574103390443</v>
       </c>
       <c r="G7" t="n">
-        <v>10.69578094471259</v>
+        <v>3.291640367124096</v>
       </c>
       <c r="H7" t="n">
-        <v>10.93085970292595</v>
+        <v>3.519070022003509</v>
       </c>
       <c r="I7" t="n">
-        <v>9.701164475695183</v>
+        <v>2.340692554155215</v>
       </c>
       <c r="J7" t="n">
-        <v>12.21641268013121</v>
+        <v>4.804622999208974</v>
       </c>
       <c r="K7" t="n">
-        <v>9.905953445313033</v>
+        <v>2.494163764390629</v>
       </c>
       <c r="L7" t="n">
-        <v>9.928559954422555</v>
+        <v>2.516770273500075</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.26539511227138</v>
+        <v>2.554987816636201</v>
       </c>
       <c r="C8" t="n">
-        <v>16.52971693438587</v>
+        <v>3.782485707266658</v>
       </c>
       <c r="D8" t="n">
-        <v>18.74331365846385</v>
+        <v>5.133918452578255</v>
       </c>
       <c r="E8" t="n">
-        <v>14.83947392988533</v>
+        <v>3.245238403921559</v>
       </c>
       <c r="F8" t="n">
-        <v>11.42209437570982</v>
+        <v>2.643779605645735</v>
       </c>
       <c r="G8" t="n">
-        <v>17.19606324413678</v>
+        <v>4.435690045623563</v>
       </c>
       <c r="H8" t="n">
-        <v>17.43114200236019</v>
+        <v>4.663119700504792</v>
       </c>
       <c r="I8" t="n">
-        <v>16.20144677511939</v>
+        <v>3.484742232654742</v>
       </c>
       <c r="J8" t="n">
-        <v>18.71766273656378</v>
+        <v>5.948843002940939</v>
       </c>
       <c r="K8" t="n">
-        <v>11.39047447917691</v>
+        <v>2.755439464934914</v>
       </c>
       <c r="L8" t="n">
-        <v>21.57267496733768</v>
+        <v>4.566134504668473</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.60262248080621</v>
+        <v>3.670339827454609</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85592066294887</v>
+        <v>4.719897558429595</v>
       </c>
       <c r="D9" t="n">
-        <v>23.03107451825658</v>
+        <v>5.888564359812595</v>
       </c>
       <c r="E9" t="n">
-        <v>26.00632493397159</v>
+        <v>5.210604169991201</v>
       </c>
       <c r="F9" t="n">
-        <v>21.51053215831259</v>
+        <v>4.419344645762736</v>
       </c>
       <c r="G9" t="n">
-        <v>22.50490425700368</v>
+        <v>5.370046058825253</v>
       </c>
       <c r="H9" t="n">
-        <v>22.73998301521704</v>
+        <v>5.597475713704694</v>
       </c>
       <c r="I9" t="n">
-        <v>21.51028778798625</v>
+        <v>4.419098245856431</v>
       </c>
       <c r="J9" t="n">
-        <v>24.02553599242236</v>
+        <v>6.88302869091001</v>
       </c>
       <c r="K9" t="n">
-        <v>19.36619464373141</v>
+        <v>3.709176985047329</v>
       </c>
       <c r="L9" t="n">
-        <v>21.73768326671355</v>
+        <v>4.595175965201289</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.65675132235898</v>
+        <v>31.65675132235897</v>
       </c>
       <c r="C2" t="n">
-        <v>29.80707733842582</v>
+        <v>29.80707733842585</v>
       </c>
       <c r="D2" t="n">
-        <v>33.77849801175371</v>
+        <v>33.77849801175402</v>
       </c>
       <c r="E2" t="n">
-        <v>32.28305035572762</v>
+        <v>32.28305035572777</v>
       </c>
       <c r="F2" t="n">
-        <v>32.28305035572762</v>
+        <v>32.28305035572777</v>
       </c>
       <c r="G2" t="n">
-        <v>33.94606509585076</v>
+        <v>33.9460650958509</v>
       </c>
       <c r="H2" t="n">
-        <v>37.21919806430211</v>
+        <v>37.21919806430213</v>
       </c>
       <c r="I2" t="n">
-        <v>33.15142768440848</v>
+        <v>33.15142768440853</v>
       </c>
       <c r="J2" t="n">
-        <v>39.66801710678965</v>
+        <v>39.66801710678979</v>
       </c>
       <c r="K2" t="n">
         <v>34.68516948649444</v>
       </c>
       <c r="L2" t="n">
-        <v>33.33814052015317</v>
+        <v>33.3381405201532</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.55948783497582</v>
+        <v>35.55948783497583</v>
       </c>
       <c r="C3" t="n">
-        <v>33.57027490805152</v>
+        <v>33.57027490805155</v>
       </c>
       <c r="D3" t="n">
-        <v>37.99993604628236</v>
+        <v>37.99993604628261</v>
       </c>
       <c r="E3" t="n">
-        <v>36.41047061298595</v>
+        <v>36.4104706129861</v>
       </c>
       <c r="F3" t="n">
-        <v>36.41047061298595</v>
+        <v>36.4104706129861</v>
       </c>
       <c r="G3" t="n">
-        <v>38.19267290441088</v>
+        <v>38.19267290441097</v>
       </c>
       <c r="H3" t="n">
-        <v>41.95850741697623</v>
+        <v>41.95850741697619</v>
       </c>
       <c r="I3" t="n">
-        <v>37.27943544912261</v>
+        <v>37.27943544912267</v>
       </c>
       <c r="J3" t="n">
-        <v>44.53592542851607</v>
+        <v>44.53592542851612</v>
       </c>
       <c r="K3" t="n">
         <v>38.92019370601603</v>
       </c>
       <c r="L3" t="n">
-        <v>37.49351374162666</v>
+        <v>37.49351374162665</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.24546587450503</v>
+        <v>2.165909878374308</v>
       </c>
       <c r="C4" t="n">
-        <v>5.237099137843541</v>
+        <v>1.536407182503533</v>
       </c>
       <c r="D4" t="n">
-        <v>7.506754375316453</v>
+        <v>3.427198379185921</v>
       </c>
       <c r="E4" t="n">
-        <v>6.998265333380334</v>
+        <v>3.031107598009141</v>
       </c>
       <c r="F4" t="n">
-        <v>6.998265333380329</v>
+        <v>3.031107598009141</v>
       </c>
       <c r="G4" t="n">
-        <v>7.598873660663213</v>
+        <v>3.525491275020684</v>
       </c>
       <c r="H4" t="n">
-        <v>9.551431084578972</v>
+        <v>5.471875088448241</v>
       </c>
       <c r="I4" t="n">
-        <v>7.084050947353452</v>
+        <v>3.046089780765902</v>
       </c>
       <c r="J4" t="n">
-        <v>10.06521576724041</v>
+        <v>5.985659771109673</v>
       </c>
       <c r="K4" t="n">
-        <v>7.560522863143794</v>
+        <v>3.480966867013071</v>
       </c>
       <c r="L4" t="n">
-        <v>7.245298399910326</v>
+        <v>3.165742403779607</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.64874038789887</v>
+        <v>17.90088610747031</v>
       </c>
       <c r="C5" t="n">
-        <v>40.36306609061607</v>
+        <v>7.718577332692874</v>
       </c>
       <c r="D5" t="n">
-        <v>214.9072275928665</v>
+        <v>39.92968146768349</v>
       </c>
       <c r="E5" t="n">
-        <v>180.5566390928978</v>
+        <v>33.57738121416683</v>
       </c>
       <c r="F5" t="n">
-        <v>180.5566390928978</v>
+        <v>33.57738121416683</v>
       </c>
       <c r="G5" t="n">
-        <v>231.1724012867066</v>
+        <v>42.87443192398838</v>
       </c>
       <c r="H5" t="n">
-        <v>467.3774295183357</v>
+        <v>86.04925037617265</v>
       </c>
       <c r="I5" t="n">
-        <v>180.5564982127756</v>
+        <v>33.5772403340447</v>
       </c>
       <c r="J5" t="n">
-        <v>487.2095775118861</v>
+        <v>89.96306698312665</v>
       </c>
       <c r="K5" t="n">
-        <v>221.0231489412101</v>
+        <v>41.05038885317892</v>
       </c>
       <c r="L5" t="n">
-        <v>218.3308948732815</v>
+        <v>40.31680718178612</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>805.3521953274152</v>
+        <v>119.5458353698725</v>
       </c>
       <c r="C6" t="n">
-        <v>672.2307067550971</v>
+        <v>118.9272814870456</v>
       </c>
       <c r="D6" t="n">
-        <v>674.4703873820258</v>
+        <v>120.8127971523029</v>
       </c>
       <c r="E6" t="n">
-        <v>607.5816580360928</v>
+        <v>108.7337841409257</v>
       </c>
       <c r="F6" t="n">
-        <v>674.0358972169694</v>
+        <v>120.4297301733841</v>
       </c>
       <c r="G6" t="n">
-        <v>674.5302721125596</v>
+        <v>120.9054167665193</v>
       </c>
       <c r="H6" t="n">
-        <v>809.634210939281</v>
+        <v>146.286443579857</v>
       </c>
       <c r="I6" t="n">
-        <v>806.1907804002637</v>
+        <v>120.4260152722643</v>
       </c>
       <c r="J6" t="n">
-        <v>809.5926903847776</v>
+        <v>146.7024945413073</v>
       </c>
       <c r="K6" t="n">
-        <v>674.5325244350321</v>
+        <v>120.8680385075915</v>
       </c>
       <c r="L6" t="n">
-        <v>674.2108722819635</v>
+        <v>120.5516827709532</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.16926435950124</v>
+        <v>3.208498406084253</v>
       </c>
       <c r="C7" t="n">
-        <v>11.60870845999306</v>
+        <v>2.65781041712539</v>
       </c>
       <c r="D7" t="n">
-        <v>13.43055916878429</v>
+        <v>4.46978801718657</v>
       </c>
       <c r="E7" t="n">
-        <v>13.00212048973602</v>
+        <v>4.087786099802017</v>
       </c>
       <c r="F7" t="n">
-        <v>13.00212048973602</v>
+        <v>4.087786099802017</v>
       </c>
       <c r="G7" t="n">
-        <v>13.52267214565942</v>
+        <v>4.568079802730591</v>
       </c>
       <c r="H7" t="n">
-        <v>15.47522956957518</v>
+        <v>6.514463616158194</v>
       </c>
       <c r="I7" t="n">
-        <v>13.00784943234966</v>
+        <v>4.088678308475846</v>
       </c>
       <c r="J7" t="n">
-        <v>15.98901425223661</v>
+        <v>7.028248298819765</v>
       </c>
       <c r="K7" t="n">
-        <v>13.48432134814001</v>
+        <v>4.523555394723033</v>
       </c>
       <c r="L7" t="n">
-        <v>13.16909688490653</v>
+        <v>4.208330931489563</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.41305741120277</v>
+        <v>3.603405981043897</v>
       </c>
       <c r="C8" t="n">
-        <v>20.0958567723642</v>
+        <v>4.151548512008708</v>
       </c>
       <c r="D8" t="n">
-        <v>23.21768910819368</v>
+        <v>6.192322877188943</v>
       </c>
       <c r="E8" t="n">
-        <v>19.78695538053655</v>
+        <v>5.281917034112393</v>
       </c>
       <c r="F8" t="n">
-        <v>15.44632414146943</v>
+        <v>4.517965940176154</v>
       </c>
       <c r="G8" t="n">
-        <v>22.01428272843178</v>
+        <v>6.062603257200344</v>
       </c>
       <c r="H8" t="n">
-        <v>23.96684015237522</v>
+        <v>8.008987070632795</v>
       </c>
       <c r="I8" t="n">
-        <v>21.49946001512202</v>
+        <v>5.583201762945564</v>
       </c>
       <c r="J8" t="n">
-        <v>24.48185269945527</v>
+        <v>8.522987857430762</v>
       </c>
       <c r="K8" t="n">
-        <v>15.61205798250977</v>
+        <v>4.898037040342919</v>
       </c>
       <c r="L8" t="n">
-        <v>28.18707530294676</v>
+        <v>6.851495118742447</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.8596348365687</v>
+        <v>5.442003597945697</v>
       </c>
       <c r="C9" t="n">
-        <v>29.9075143492643</v>
+        <v>5.87840023618618</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72936216326224</v>
+        <v>7.690377326763875</v>
       </c>
       <c r="E9" t="n">
-        <v>37.77880953270325</v>
+        <v>8.448483347735589</v>
       </c>
       <c r="F9" t="n">
-        <v>31.30679195968209</v>
+        <v>7.309408261055864</v>
       </c>
       <c r="G9" t="n">
-        <v>31.82147803493064</v>
+        <v>7.788669621791184</v>
       </c>
       <c r="H9" t="n">
-        <v>33.77403545884641</v>
+        <v>9.73505343521893</v>
       </c>
       <c r="I9" t="n">
-        <v>31.30665532162091</v>
+        <v>7.309268127536542</v>
       </c>
       <c r="J9" t="n">
-        <v>34.28782014150785</v>
+        <v>10.24883811788029</v>
       </c>
       <c r="K9" t="n">
-        <v>24.72110506651445</v>
+        <v>6.50122931844067</v>
       </c>
       <c r="L9" t="n">
-        <v>31.46790277417777</v>
+        <v>7.428920750550144</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.50932538791187</v>
+        <v>30.50932538791188</v>
       </c>
       <c r="C2" t="n">
-        <v>29.26182928302203</v>
+        <v>29.26182928302202</v>
       </c>
       <c r="D2" t="n">
         <v>31.46565544735311</v>
       </c>
       <c r="E2" t="n">
-        <v>30.17069693281718</v>
+        <v>30.17069693281719</v>
       </c>
       <c r="F2" t="n">
-        <v>30.17069693281718</v>
+        <v>30.17069693281719</v>
       </c>
       <c r="G2" t="n">
         <v>31.33174695357747</v>
       </c>
       <c r="H2" t="n">
-        <v>32.80291156003011</v>
+        <v>32.80291156003012</v>
       </c>
       <c r="I2" t="n">
-        <v>31.03201880023347</v>
+        <v>31.03201880023349</v>
       </c>
       <c r="J2" t="n">
         <v>35.12372334568497</v>
       </c>
       <c r="K2" t="n">
-        <v>31.65420710094971</v>
+        <v>31.6542071009497</v>
       </c>
       <c r="L2" t="n">
         <v>30.56590026107073</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.23980452865459</v>
+        <v>34.23980452865461</v>
       </c>
       <c r="C3" t="n">
-        <v>32.93081587504643</v>
+        <v>32.93081587504641</v>
       </c>
       <c r="D3" t="n">
-        <v>35.33978220018707</v>
+        <v>35.33978220018706</v>
       </c>
       <c r="E3" t="n">
-        <v>33.97986781306462</v>
+        <v>33.97986781306461</v>
       </c>
       <c r="F3" t="n">
-        <v>33.97986781306462</v>
+        <v>33.97986781306461</v>
       </c>
       <c r="G3" t="n">
         <v>35.18575969328414</v>
       </c>
       <c r="H3" t="n">
-        <v>36.87883492843527</v>
+        <v>36.87883492843526</v>
       </c>
       <c r="I3" t="n">
-        <v>34.8419154989307</v>
+        <v>34.84191549893072</v>
       </c>
       <c r="J3" t="n">
-        <v>39.31365462873276</v>
+        <v>39.31365462873278</v>
       </c>
       <c r="K3" t="n">
-        <v>35.44315181452405</v>
+        <v>35.44315181452404</v>
       </c>
       <c r="L3" t="n">
-        <v>34.30493492904044</v>
+        <v>34.30493492904043</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.750784748043047</v>
+        <v>1.37225789712998</v>
       </c>
       <c r="C4" t="n">
-        <v>4.14387767914456</v>
+        <v>1.067611800155214</v>
       </c>
       <c r="D4" t="n">
-        <v>5.319282445238764</v>
+        <v>1.940755594325707</v>
       </c>
       <c r="E4" t="n">
-        <v>4.938749676499909</v>
+        <v>1.661957453036494</v>
       </c>
       <c r="F4" t="n">
-        <v>4.938749676499913</v>
+        <v>1.661957453036494</v>
       </c>
       <c r="G4" t="n">
-        <v>5.233363461625652</v>
+        <v>1.86004104271472</v>
       </c>
       <c r="H4" t="n">
-        <v>6.113953603309495</v>
+        <v>2.735426752396427</v>
       </c>
       <c r="I4" t="n">
-        <v>5.019032583187808</v>
+        <v>1.676028449008011</v>
       </c>
       <c r="J4" t="n">
-        <v>6.569105853904872</v>
+        <v>3.190579002991814</v>
       </c>
       <c r="K4" t="n">
-        <v>4.982167247453416</v>
+        <v>1.603640396540361</v>
       </c>
       <c r="L4" t="n">
-        <v>4.78466443933304</v>
+        <v>1.406137588419979</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.53400445878994</v>
+        <v>7.494104533049565</v>
       </c>
       <c r="C5" t="n">
-        <v>16.38873083150603</v>
+        <v>3.222705943293247</v>
       </c>
       <c r="D5" t="n">
-        <v>90.36795579864209</v>
+        <v>16.90932202341598</v>
       </c>
       <c r="E5" t="n">
-        <v>67.34564356264772</v>
+        <v>12.64557071748266</v>
       </c>
       <c r="F5" t="n">
-        <v>67.34564356264772</v>
+        <v>12.64557071748266</v>
       </c>
       <c r="G5" t="n">
-        <v>85.43940816738781</v>
+        <v>15.97630483443838</v>
       </c>
       <c r="H5" t="n">
-        <v>184.581693025109</v>
+        <v>34.14574872043306</v>
       </c>
       <c r="I5" t="n">
-        <v>67.34557220885051</v>
+        <v>12.6454993636854</v>
       </c>
       <c r="J5" t="n">
-        <v>215.8669205312975</v>
+        <v>40.02699418661098</v>
       </c>
       <c r="K5" t="n">
-        <v>59.62206739188703</v>
+        <v>11.22026276985202</v>
       </c>
       <c r="L5" t="n">
-        <v>47.10367161605885</v>
+        <v>8.854282811165177</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>636.0356006943616</v>
+        <v>112.4783849016418</v>
       </c>
       <c r="C6" t="n">
-        <v>635.6085661082537</v>
+        <v>112.2053963614665</v>
       </c>
       <c r="D6" t="n">
-        <v>761.276636069621</v>
+        <v>113.0525272294708</v>
       </c>
       <c r="E6" t="n">
-        <v>573.4305905057028</v>
+        <v>101.7165208968202</v>
       </c>
       <c r="F6" t="n">
-        <v>636.3085185440443</v>
+        <v>112.7830361716031</v>
       </c>
       <c r="G6" t="n">
-        <v>636.5181794079441</v>
+        <v>134.8749936262086</v>
       </c>
       <c r="H6" t="n">
-        <v>762.716417426476</v>
+        <v>135.8974596637213</v>
       </c>
       <c r="I6" t="n">
-        <v>636.3038485295068</v>
+        <v>134.6909810325018</v>
       </c>
       <c r="J6" t="n">
-        <v>670.0747097227263</v>
+        <v>119.967564651136</v>
       </c>
       <c r="K6" t="n">
-        <v>636.233594549446</v>
+        <v>112.7038909996828</v>
       </c>
       <c r="L6" t="n">
-        <v>636.0720525264678</v>
+        <v>112.5127172897129</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.56034754776427</v>
+        <v>2.218740945294159</v>
       </c>
       <c r="C7" t="n">
-        <v>9.312992126625629</v>
+        <v>1.977375937982238</v>
       </c>
       <c r="D7" t="n">
-        <v>10.12886379862855</v>
+        <v>2.787241907935541</v>
       </c>
       <c r="E7" t="n">
-        <v>9.819241579503842</v>
+        <v>2.520924023310786</v>
       </c>
       <c r="F7" t="n">
-        <v>9.819241579503842</v>
+        <v>2.520924023310786</v>
       </c>
       <c r="G7" t="n">
-        <v>10.04292626134688</v>
+        <v>2.706524090878898</v>
       </c>
       <c r="H7" t="n">
-        <v>10.92351640303072</v>
+        <v>3.581909800560615</v>
       </c>
       <c r="I7" t="n">
-        <v>9.828595382909036</v>
+        <v>2.52251149717219</v>
       </c>
       <c r="J7" t="n">
-        <v>11.37866865362611</v>
+        <v>4.037062051155993</v>
       </c>
       <c r="K7" t="n">
-        <v>9.791730047174648</v>
+        <v>2.450123444704539</v>
       </c>
       <c r="L7" t="n">
-        <v>9.59422723905427</v>
+        <v>2.252620636584151</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.07722201279713</v>
+        <v>2.485710849693338</v>
       </c>
       <c r="C8" t="n">
-        <v>15.669175969322</v>
+        <v>3.096064288235061</v>
       </c>
       <c r="D8" t="n">
-        <v>17.49833347547838</v>
+        <v>4.08426856403303</v>
       </c>
       <c r="E8" t="n">
-        <v>14.86004585365188</v>
+        <v>3.408105570753556</v>
       </c>
       <c r="F8" t="n">
-        <v>11.49356460815532</v>
+        <v>2.815604874756688</v>
       </c>
       <c r="G8" t="n">
-        <v>16.40726185020846</v>
+        <v>3.826647148449036</v>
       </c>
       <c r="H8" t="n">
-        <v>17.28785199192657</v>
+        <v>4.702032858136783</v>
       </c>
       <c r="I8" t="n">
-        <v>16.19293097177061</v>
+        <v>3.642634554742325</v>
       </c>
       <c r="J8" t="n">
-        <v>17.74395689787881</v>
+        <v>5.157352776074061</v>
       </c>
       <c r="K8" t="n">
-        <v>11.21856043400255</v>
+        <v>2.701245591425516</v>
       </c>
       <c r="L8" t="n">
-        <v>21.02214130090695</v>
+        <v>4.263933500571728</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.59367022300973</v>
+        <v>3.63260572847619</v>
       </c>
       <c r="C9" t="n">
-        <v>21.2583441437488</v>
+        <v>4.079757881603943</v>
       </c>
       <c r="D9" t="n">
-        <v>22.07419945186143</v>
+        <v>4.889620971512562</v>
       </c>
       <c r="E9" t="n">
-        <v>26.28841715509299</v>
+        <v>5.419498908908247</v>
       </c>
       <c r="F9" t="n">
-        <v>21.77401676154508</v>
+        <v>4.62496444394908</v>
       </c>
       <c r="G9" t="n">
-        <v>21.98827827847005</v>
+        <v>4.808906034500605</v>
       </c>
       <c r="H9" t="n">
-        <v>22.8688684201539</v>
+        <v>5.684291744182325</v>
       </c>
       <c r="I9" t="n">
-        <v>21.77394740003221</v>
+        <v>4.624893440793894</v>
       </c>
       <c r="J9" t="n">
-        <v>23.32402067074928</v>
+        <v>6.139443994777699</v>
       </c>
       <c r="K9" t="n">
-        <v>19.47043782090126</v>
+        <v>3.685539283566608</v>
       </c>
       <c r="L9" t="n">
-        <v>21.53957925617744</v>
+        <v>4.355002580205854</v>
       </c>
     </row>
   </sheetData>
@@ -3290,10 +3290,10 @@
         <v>30.15603074621771</v>
       </c>
       <c r="C2" t="n">
-        <v>29.12732090948504</v>
+        <v>29.12732090948506</v>
       </c>
       <c r="D2" t="n">
-        <v>31.23632292978256</v>
+        <v>31.23632292978258</v>
       </c>
       <c r="E2" t="n">
         <v>29.37987218964864</v>
@@ -3302,19 +3302,19 @@
         <v>29.37987218964864</v>
       </c>
       <c r="G2" t="n">
-        <v>30.58995841217894</v>
+        <v>30.58995841217893</v>
       </c>
       <c r="H2" t="n">
         <v>31.83027971123056</v>
       </c>
       <c r="I2" t="n">
-        <v>30.26319694093467</v>
+        <v>30.26319694093468</v>
       </c>
       <c r="J2" t="n">
-        <v>32.6134030096777</v>
+        <v>32.61340300967767</v>
       </c>
       <c r="K2" t="n">
-        <v>30.91686976096256</v>
+        <v>30.91686976096254</v>
       </c>
       <c r="L2" t="n">
         <v>30.00272444974552</v>
@@ -3330,10 +3330,10 @@
         <v>33.8169727360321</v>
       </c>
       <c r="C3" t="n">
-        <v>32.76350621182197</v>
+        <v>32.76350621182198</v>
       </c>
       <c r="D3" t="n">
-        <v>35.05953252898335</v>
+        <v>35.05953252898337</v>
       </c>
       <c r="E3" t="n">
         <v>33.05708254610344</v>
@@ -3345,19 +3345,19 @@
         <v>34.31607943973271</v>
       </c>
       <c r="H3" t="n">
-        <v>35.74349165772197</v>
+        <v>35.74349165772196</v>
       </c>
       <c r="I3" t="n">
-        <v>33.94095706849625</v>
+        <v>33.94095706849626</v>
       </c>
       <c r="J3" t="n">
-        <v>36.4300857643926</v>
+        <v>36.43008576439261</v>
       </c>
       <c r="K3" t="n">
-        <v>34.57048478932074</v>
+        <v>34.57048478932072</v>
       </c>
       <c r="L3" t="n">
-        <v>33.64067502327268</v>
+        <v>33.64067502327267</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.99157904247551</v>
+        <v>1.044026760363006</v>
       </c>
       <c r="C4" t="n">
-        <v>3.565121383320935</v>
+        <v>0.8907724971678049</v>
       </c>
       <c r="D4" t="n">
-        <v>4.633766969741941</v>
+        <v>1.686214687629441</v>
       </c>
       <c r="E4" t="n">
-        <v>3.896111769695057</v>
+        <v>1.080276484003171</v>
       </c>
       <c r="F4" t="n">
-        <v>3.896111769695058</v>
+        <v>1.080276484003172</v>
       </c>
       <c r="G4" t="n">
-        <v>4.243258709409841</v>
+        <v>1.300874508668806</v>
       </c>
       <c r="H4" t="n">
-        <v>4.986621342255347</v>
+        <v>2.039069060142846</v>
       </c>
       <c r="I4" t="n">
-        <v>4.01292397162945</v>
+        <v>1.100774013766638</v>
       </c>
       <c r="J4" t="n">
-        <v>4.607936425076797</v>
+        <v>1.660384142964302</v>
       </c>
       <c r="K4" t="n">
-        <v>3.962581966543246</v>
+        <v>1.015029684430757</v>
       </c>
       <c r="L4" t="n">
-        <v>3.900615584909447</v>
+        <v>0.9530633027969436</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.38026601557887</v>
+        <v>4.104435651046042</v>
       </c>
       <c r="C5" t="n">
-        <v>11.9947334537768</v>
+        <v>2.374384213529022</v>
       </c>
       <c r="D5" t="n">
-        <v>79.50230562273049</v>
+        <v>14.86307741915519</v>
       </c>
       <c r="E5" t="n">
-        <v>26.59905825170502</v>
+        <v>5.075995043185738</v>
       </c>
       <c r="F5" t="n">
-        <v>26.59905825170502</v>
+        <v>5.075995043185738</v>
       </c>
       <c r="G5" t="n">
-        <v>45.42713272478514</v>
+        <v>8.549236296098879</v>
       </c>
       <c r="H5" t="n">
-        <v>126.3479051004602</v>
+        <v>23.39865488584777</v>
       </c>
       <c r="I5" t="n">
-        <v>26.59898371570322</v>
+        <v>5.075920507183922</v>
       </c>
       <c r="J5" t="n">
-        <v>81.03590142111423</v>
+        <v>15.11170590937995</v>
       </c>
       <c r="K5" t="n">
-        <v>17.88482355890335</v>
+        <v>3.465344191408747</v>
       </c>
       <c r="L5" t="n">
-        <v>13.53700720754225</v>
+        <v>2.649068219190337</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>759.1714423668635</v>
+        <v>133.9556819852595</v>
       </c>
       <c r="C6" t="n">
-        <v>634.8400568164642</v>
+        <v>111.9951605313702</v>
       </c>
       <c r="D6" t="n">
-        <v>635.7851872482096</v>
+        <v>112.7688640547267</v>
       </c>
       <c r="E6" t="n">
-        <v>572.2182771523602</v>
+        <v>101.104977049358</v>
       </c>
       <c r="F6" t="n">
-        <v>635.0715972520717</v>
+        <v>112.1671613269655</v>
       </c>
       <c r="G6" t="n">
-        <v>759.4231220337977</v>
+        <v>134.212529733565</v>
       </c>
       <c r="H6" t="n">
-        <v>760.8931954429444</v>
+        <v>135.0786253809755</v>
       </c>
       <c r="I6" t="n">
-        <v>635.0771296913721</v>
+        <v>112.1680736186115</v>
       </c>
       <c r="J6" t="n">
-        <v>760.1190909504614</v>
+        <v>134.6303466189206</v>
       </c>
       <c r="K6" t="n">
-        <v>634.9750932146497</v>
+        <v>112.0732310623272</v>
       </c>
       <c r="L6" t="n">
-        <v>634.9639773344494</v>
+        <v>112.0202143688869</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.380680002469049</v>
+        <v>1.816508525136097</v>
       </c>
       <c r="C7" t="n">
-        <v>8.280125353670011</v>
+        <v>1.720613191452664</v>
       </c>
       <c r="D7" t="n">
-        <v>9.022891439424797</v>
+        <v>2.45870059010783</v>
       </c>
       <c r="E7" t="n">
-        <v>8.381199284175038</v>
+        <v>1.86965188227434</v>
       </c>
       <c r="F7" t="n">
-        <v>8.381199284175038</v>
+        <v>1.86965188227434</v>
       </c>
       <c r="G7" t="n">
-        <v>8.632359669403376</v>
+        <v>2.073356273441867</v>
       </c>
       <c r="H7" t="n">
-        <v>9.375722302248878</v>
+        <v>2.811550824915933</v>
       </c>
       <c r="I7" t="n">
-        <v>8.402024931622988</v>
+        <v>1.873255778539739</v>
       </c>
       <c r="J7" t="n">
-        <v>8.997037385070339</v>
+        <v>2.432865907737386</v>
       </c>
       <c r="K7" t="n">
-        <v>8.351682926536785</v>
+        <v>1.787511449203837</v>
       </c>
       <c r="L7" t="n">
-        <v>8.289716544902983</v>
+        <v>1.725545067570033</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.527128202419007</v>
+        <v>2.018283407233948</v>
       </c>
       <c r="C8" t="n">
-        <v>13.60002016976517</v>
+        <v>2.656914674011968</v>
       </c>
       <c r="D8" t="n">
-        <v>15.23141115272966</v>
+        <v>3.551400053728571</v>
       </c>
       <c r="E8" t="n">
-        <v>12.5774413205928</v>
+        <v>2.608190476682019</v>
       </c>
       <c r="F8" t="n">
-        <v>9.668968088096969</v>
+        <v>2.096299190536489</v>
       </c>
       <c r="G8" t="n">
-        <v>13.97151728301913</v>
+        <v>3.013048008346414</v>
       </c>
       <c r="H8" t="n">
-        <v>14.7148799158991</v>
+        <v>3.751242559826544</v>
       </c>
       <c r="I8" t="n">
-        <v>13.74118254523874</v>
+        <v>2.812947513444298</v>
       </c>
       <c r="J8" t="n">
-        <v>14.33701897839638</v>
+        <v>3.372702663070149</v>
       </c>
       <c r="K8" t="n">
-        <v>9.420249397302641</v>
+        <v>1.975579147039561</v>
       </c>
       <c r="L8" t="n">
-        <v>18.00850972239796</v>
+        <v>3.436052657540584</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.88074162859975</v>
+        <v>2.960519365136159</v>
       </c>
       <c r="C9" t="n">
-        <v>18.08564618639062</v>
+        <v>3.446384848660208</v>
       </c>
       <c r="D9" t="n">
-        <v>18.82839021379915</v>
+        <v>4.184468365046449</v>
       </c>
       <c r="E9" t="n">
-        <v>22.02204921608024</v>
+        <v>4.270441457280739</v>
       </c>
       <c r="F9" t="n">
-        <v>18.20761851346814</v>
+        <v>3.599101657258716</v>
       </c>
       <c r="G9" t="n">
-        <v>18.43788050212397</v>
+        <v>3.799127930649412</v>
       </c>
       <c r="H9" t="n">
-        <v>19.18124313496946</v>
+        <v>4.537322482123475</v>
       </c>
       <c r="I9" t="n">
-        <v>18.20754576434357</v>
+        <v>3.59902743574732</v>
       </c>
       <c r="J9" t="n">
-        <v>18.80255821779093</v>
+        <v>4.158637564944952</v>
       </c>
       <c r="K9" t="n">
-        <v>16.24200832384836</v>
+        <v>3.162533167256558</v>
       </c>
       <c r="L9" t="n">
-        <v>18.09523737762355</v>
+        <v>3.451316724777597</v>
       </c>
     </row>
   </sheetData>
@@ -3686,34 +3686,34 @@
         <v>31.18289252384946</v>
       </c>
       <c r="C2" t="n">
-        <v>29.3727576204524</v>
+        <v>29.37275762045238</v>
       </c>
       <c r="D2" t="n">
-        <v>32.08285811124601</v>
+        <v>32.08285811124599</v>
       </c>
       <c r="E2" t="n">
-        <v>31.70700754826711</v>
+        <v>31.70700754826708</v>
       </c>
       <c r="F2" t="n">
-        <v>31.70700754826711</v>
+        <v>31.70700754826708</v>
       </c>
       <c r="G2" t="n">
         <v>32.58829960990403</v>
       </c>
       <c r="H2" t="n">
-        <v>36.00549823038329</v>
+        <v>36.00549823038327</v>
       </c>
       <c r="I2" t="n">
-        <v>32.45229516581863</v>
+        <v>32.45229516581862</v>
       </c>
       <c r="J2" t="n">
         <v>36.88965946105112</v>
       </c>
       <c r="K2" t="n">
-        <v>33.28225570543446</v>
+        <v>33.28225570543442</v>
       </c>
       <c r="L2" t="n">
-        <v>32.39571535422356</v>
+        <v>32.39571535422358</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.02568656983578</v>
+        <v>35.02568656983576</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07664630306135</v>
+        <v>33.07664630306137</v>
       </c>
       <c r="D3" t="n">
-        <v>36.0608334226516</v>
+        <v>36.06083342265156</v>
       </c>
       <c r="E3" t="n">
-        <v>35.74066227720086</v>
+        <v>35.74066227720088</v>
       </c>
       <c r="F3" t="n">
         <v>35.74066227720087</v>
       </c>
       <c r="G3" t="n">
-        <v>36.64219584799933</v>
+        <v>36.64219584799932</v>
       </c>
       <c r="H3" t="n">
-        <v>40.5736709891782</v>
+        <v>40.57367098917818</v>
       </c>
       <c r="I3" t="n">
-        <v>36.48684887386491</v>
+        <v>36.48684887386489</v>
       </c>
       <c r="J3" t="n">
-        <v>41.33565515524636</v>
+        <v>41.33565515524641</v>
       </c>
       <c r="K3" t="n">
-        <v>37.31253631686803</v>
+        <v>37.31253631686799</v>
       </c>
       <c r="L3" t="n">
-        <v>36.42072945048427</v>
+        <v>36.42072945048425</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7943902155787</v>
+        <v>1.928891202962526</v>
       </c>
       <c r="C4" t="n">
-        <v>4.834951954082275</v>
+        <v>1.309864388199971</v>
       </c>
       <c r="D4" t="n">
-        <v>6.329381622509199</v>
+        <v>2.463882609892941</v>
       </c>
       <c r="E4" t="n">
-        <v>6.441974515434106</v>
+        <v>2.665272345805424</v>
       </c>
       <c r="F4" t="n">
-        <v>6.441974515434097</v>
+        <v>2.665272345805424</v>
       </c>
       <c r="G4" t="n">
-        <v>6.623885133713884</v>
+        <v>2.763297196019884</v>
       </c>
       <c r="H4" t="n">
-        <v>8.66051215157982</v>
+        <v>4.795013138963685</v>
       </c>
       <c r="I4" t="n">
-        <v>6.50898447849398</v>
+        <v>2.677024545666677</v>
       </c>
       <c r="J4" t="n">
-        <v>8.18161227210523</v>
+        <v>4.316113259489056</v>
       </c>
       <c r="K4" t="n">
-        <v>6.536384316004227</v>
+        <v>2.670885303388055</v>
       </c>
       <c r="L4" t="n">
-        <v>6.515534491672554</v>
+        <v>2.650035479056405</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.68100577565684</v>
+        <v>15.10893547011887</v>
       </c>
       <c r="C5" t="n">
-        <v>25.63105134612967</v>
+        <v>4.96997786136759</v>
       </c>
       <c r="D5" t="n">
-        <v>129.9138751257951</v>
+        <v>24.21475334861048</v>
       </c>
       <c r="E5" t="n">
-        <v>152.7407760900631</v>
+        <v>28.4138612834188</v>
       </c>
       <c r="F5" t="n">
-        <v>152.7407760900631</v>
+        <v>28.4138612834188</v>
       </c>
       <c r="G5" t="n">
-        <v>163.7001492866515</v>
+        <v>30.40871953713752</v>
       </c>
       <c r="H5" t="n">
-        <v>402.6074774310767</v>
+        <v>74.12967865245787</v>
       </c>
       <c r="I5" t="n">
-        <v>152.7407256609692</v>
+        <v>28.41381085432487</v>
       </c>
       <c r="J5" t="n">
-        <v>325.6469854431438</v>
+        <v>60.19001863483324</v>
       </c>
       <c r="K5" t="n">
-        <v>150.5961030709053</v>
+        <v>28.02539566686452</v>
       </c>
       <c r="L5" t="n">
-        <v>170.3209412722765</v>
+        <v>31.47978691622553</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>804.3635275985313</v>
+        <v>119.2699508759978</v>
       </c>
       <c r="C6" t="n">
-        <v>671.6451690076431</v>
+        <v>118.6684619537068</v>
       </c>
       <c r="D6" t="n">
-        <v>673.0065326755514</v>
+        <v>119.7990605594277</v>
       </c>
       <c r="E6" t="n">
-        <v>606.8534347502813</v>
+        <v>108.3376887745414</v>
       </c>
       <c r="F6" t="n">
-        <v>673.2409942710847</v>
+        <v>120.0218991868906</v>
       </c>
       <c r="G6" t="n">
-        <v>805.1930225166645</v>
+        <v>143.3114646138442</v>
       </c>
       <c r="H6" t="n">
-        <v>808.1920376025265</v>
+        <v>145.5125608558375</v>
       </c>
       <c r="I6" t="n">
-        <v>673.2195544151997</v>
+        <v>143.225191963491</v>
       </c>
       <c r="J6" t="n">
-        <v>807.1570985248123</v>
+        <v>144.935798078003</v>
       </c>
       <c r="K6" t="n">
-        <v>673.2496074946032</v>
+        <v>120.012411946994</v>
       </c>
       <c r="L6" t="n">
-        <v>673.2512441761526</v>
+        <v>119.995519747676</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.36147377010478</v>
+        <v>2.908697903249943</v>
       </c>
       <c r="C7" t="n">
-        <v>10.80554902795455</v>
+        <v>2.360689467507483</v>
       </c>
       <c r="D7" t="n">
-        <v>11.89647238840375</v>
+        <v>3.443690579381228</v>
       </c>
       <c r="E7" t="n">
-        <v>12.06955090685022</v>
+        <v>3.655725785327785</v>
       </c>
       <c r="F7" t="n">
-        <v>12.06955090685022</v>
+        <v>3.655725785327785</v>
       </c>
       <c r="G7" t="n">
-        <v>12.19096868824002</v>
+        <v>3.743103896307284</v>
       </c>
       <c r="H7" t="n">
-        <v>14.2275957061059</v>
+        <v>5.774819839251069</v>
       </c>
       <c r="I7" t="n">
-        <v>12.07606803301999</v>
+        <v>3.656831245954075</v>
       </c>
       <c r="J7" t="n">
-        <v>13.74869582663126</v>
+        <v>5.295919959776482</v>
       </c>
       <c r="K7" t="n">
-        <v>12.10346787053024</v>
+        <v>3.650692003675447</v>
       </c>
       <c r="L7" t="n">
-        <v>12.08261804619857</v>
+        <v>3.629842179343827</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.33400985841385</v>
+        <v>3.255864252911209</v>
       </c>
       <c r="C8" t="n">
-        <v>18.54826625714351</v>
+        <v>3.723407692460724</v>
       </c>
       <c r="D8" t="n">
-        <v>20.84197025673298</v>
+        <v>5.018098195676045</v>
       </c>
       <c r="E8" t="n">
-        <v>18.23993200540701</v>
+        <v>4.741712852789248</v>
       </c>
       <c r="F8" t="n">
-        <v>14.22780370859406</v>
+        <v>4.035578276376435</v>
       </c>
       <c r="G8" t="n">
-        <v>19.93890658119366</v>
+        <v>5.106740958078133</v>
       </c>
       <c r="H8" t="n">
-        <v>21.97553359908861</v>
+        <v>7.138456901027039</v>
       </c>
       <c r="I8" t="n">
-        <v>19.82400592597369</v>
+        <v>5.02046830772492</v>
       </c>
       <c r="J8" t="n">
-        <v>21.49776874099756</v>
+        <v>6.659756785314817</v>
       </c>
       <c r="K8" t="n">
-        <v>13.96872290614693</v>
+        <v>3.978976888165177</v>
       </c>
       <c r="L8" t="n">
-        <v>25.86344604558882</v>
+        <v>6.055267894094047</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.66613899391266</v>
+        <v>4.898318971859029</v>
       </c>
       <c r="C9" t="n">
-        <v>27.20482409173441</v>
+        <v>5.246961863093078</v>
       </c>
       <c r="D9" t="n">
-        <v>28.29574226899783</v>
+        <v>6.329962062726199</v>
       </c>
       <c r="E9" t="n">
-        <v>34.35446235158989</v>
+        <v>7.577870178349376</v>
       </c>
       <c r="F9" t="n">
-        <v>28.475389733983</v>
+        <v>6.543153403257256</v>
       </c>
       <c r="G9" t="n">
-        <v>28.59024375202019</v>
+        <v>6.62937629189287</v>
       </c>
       <c r="H9" t="n">
-        <v>30.62687076988568</v>
+        <v>8.661092234836678</v>
       </c>
       <c r="I9" t="n">
-        <v>28.47534309679958</v>
+        <v>6.543103641539667</v>
       </c>
       <c r="J9" t="n">
-        <v>30.14797089041139</v>
+        <v>8.182192355362055</v>
       </c>
       <c r="K9" t="n">
-        <v>25.43114703655929</v>
+        <v>6.017441249125485</v>
       </c>
       <c r="L9" t="n">
-        <v>28.48189310997904</v>
+        <v>6.516114574929398</v>
       </c>
     </row>
   </sheetData>
@@ -4079,34 +4079,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.04885386376684</v>
+        <v>30.04885386376685</v>
       </c>
       <c r="C2" t="n">
-        <v>28.98875872418033</v>
+        <v>28.98875872418031</v>
       </c>
       <c r="D2" t="n">
-        <v>31.14357311433589</v>
+        <v>31.14357311433591</v>
       </c>
       <c r="E2" t="n">
-        <v>29.81068504911826</v>
+        <v>29.81068504911824</v>
       </c>
       <c r="F2" t="n">
-        <v>29.81068504911826</v>
+        <v>29.81068504911824</v>
       </c>
       <c r="G2" t="n">
-        <v>30.61738874903803</v>
+        <v>30.61738874903805</v>
       </c>
       <c r="H2" t="n">
-        <v>31.87920586801505</v>
+        <v>31.87920586801507</v>
       </c>
       <c r="I2" t="n">
-        <v>30.46239953344502</v>
+        <v>30.46239953344504</v>
       </c>
       <c r="J2" t="n">
-        <v>33.18688663985306</v>
+        <v>33.18688663985305</v>
       </c>
       <c r="K2" t="n">
-        <v>30.98480607990571</v>
+        <v>30.98480607990572</v>
       </c>
       <c r="L2" t="n">
         <v>29.66798049673797</v>
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.71531367365315</v>
+        <v>33.71531367365317</v>
       </c>
       <c r="C3" t="n">
-        <v>32.59926317259208</v>
+        <v>32.59926317259207</v>
       </c>
       <c r="D3" t="n">
-        <v>34.97446758221714</v>
+        <v>34.97446758221717</v>
       </c>
       <c r="E3" t="n">
-        <v>33.53944196967722</v>
+        <v>33.53944196967719</v>
       </c>
       <c r="F3" t="n">
-        <v>33.53944196967722</v>
+        <v>33.5394419696772</v>
       </c>
       <c r="G3" t="n">
-        <v>34.36924656336171</v>
+        <v>34.36924656336172</v>
       </c>
       <c r="H3" t="n">
         <v>35.82145527873507</v>
       </c>
       <c r="I3" t="n">
-        <v>34.19182793860757</v>
+        <v>34.19182793860762</v>
       </c>
       <c r="J3" t="n">
-        <v>37.04361004024626</v>
+        <v>37.04361004024624</v>
       </c>
       <c r="K3" t="n">
-        <v>34.67597647526227</v>
+        <v>34.67597647526226</v>
       </c>
       <c r="L3" t="n">
-        <v>33.277295128071</v>
+        <v>33.27729512807103</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.491699872654851</v>
+        <v>1.285421191396926</v>
       </c>
       <c r="C4" t="n">
-        <v>3.944903649683434</v>
+        <v>1.009205167407759</v>
       </c>
       <c r="D4" t="n">
-        <v>5.142464079928596</v>
+        <v>1.936185398670678</v>
       </c>
       <c r="E4" t="n">
-        <v>4.614826993437479</v>
+        <v>1.51024558228549</v>
       </c>
       <c r="F4" t="n">
-        <v>4.614826993437479</v>
+        <v>1.51024558228549</v>
       </c>
       <c r="G4" t="n">
-        <v>4.824553683418195</v>
+        <v>1.622490658400061</v>
       </c>
       <c r="H4" t="n">
-        <v>5.57953989325175</v>
+        <v>2.373261211993845</v>
       </c>
       <c r="I4" t="n">
-        <v>4.702928548686965</v>
+        <v>1.525708734624341</v>
       </c>
       <c r="J4" t="n">
-        <v>5.244684287005363</v>
+        <v>2.038405605747433</v>
       </c>
       <c r="K4" t="n">
-        <v>4.589494125769582</v>
+        <v>1.383215444511719</v>
       </c>
       <c r="L4" t="n">
-        <v>4.265561206302682</v>
+        <v>1.059282525044756</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.58181311099393</v>
+        <v>6.933281090741087</v>
       </c>
       <c r="C5" t="n">
-        <v>15.48635782155497</v>
+        <v>3.040501090650363</v>
       </c>
       <c r="D5" t="n">
-        <v>95.03912104636538</v>
+        <v>17.75799693903145</v>
       </c>
       <c r="E5" t="n">
-        <v>58.41350089873421</v>
+        <v>10.97881213831127</v>
       </c>
       <c r="F5" t="n">
-        <v>58.41350089873421</v>
+        <v>10.97881213831127</v>
       </c>
       <c r="G5" t="n">
-        <v>68.18521603575164</v>
+        <v>12.77396717198529</v>
       </c>
       <c r="H5" t="n">
-        <v>152.675197527517</v>
+        <v>28.26209681534316</v>
       </c>
       <c r="I5" t="n">
-        <v>58.41344905249513</v>
+        <v>10.97876029207221</v>
       </c>
       <c r="J5" t="n">
-        <v>109.7677188764086</v>
+        <v>20.43445959380143</v>
       </c>
       <c r="K5" t="n">
-        <v>44.39432555921001</v>
+        <v>8.388865738836369</v>
       </c>
       <c r="L5" t="n">
-        <v>16.18686469444789</v>
+        <v>3.157431927589269</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>759.9731953482255</v>
+        <v>112.3699790221201</v>
       </c>
       <c r="C6" t="n">
-        <v>635.2803785338499</v>
+        <v>112.1242481449324</v>
       </c>
       <c r="D6" t="n">
-        <v>636.3713565449066</v>
+        <v>113.0324672427823</v>
       </c>
       <c r="E6" t="n">
-        <v>573.0166428985366</v>
+        <v>101.5489646395126</v>
       </c>
       <c r="F6" t="n">
-        <v>635.8681618963853</v>
+        <v>112.610831923194</v>
       </c>
       <c r="G6" t="n">
-        <v>635.9868175052735</v>
+        <v>112.7070484891232</v>
       </c>
       <c r="H6" t="n">
-        <v>761.8758732553321</v>
+        <v>135.4814151624595</v>
       </c>
       <c r="I6" t="n">
-        <v>635.8651923705421</v>
+        <v>134.4904512178412</v>
       </c>
       <c r="J6" t="n">
-        <v>668.5823669773866</v>
+        <v>135.0648762518975</v>
       </c>
       <c r="K6" t="n">
-        <v>635.7056292220364</v>
+        <v>112.4596546195754</v>
       </c>
       <c r="L6" t="n">
-        <v>635.4237142039616</v>
+        <v>112.1431168507134</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.04991864504532</v>
+        <v>2.087667690990592</v>
       </c>
       <c r="C7" t="n">
-        <v>8.82517666239991</v>
+        <v>1.868133212991669</v>
       </c>
       <c r="D7" t="n">
-        <v>9.700697123629025</v>
+        <v>2.738434410014894</v>
       </c>
       <c r="E7" t="n">
-        <v>9.247595133467675</v>
+        <v>2.325612770512655</v>
       </c>
       <c r="F7" t="n">
-        <v>9.247595133467675</v>
+        <v>2.325612770512655</v>
       </c>
       <c r="G7" t="n">
-        <v>9.382772455808531</v>
+        <v>2.424737157993727</v>
       </c>
       <c r="H7" t="n">
-        <v>10.13775866564227</v>
+        <v>3.175507711587509</v>
       </c>
       <c r="I7" t="n">
-        <v>9.261147321077409</v>
+        <v>2.327955234218007</v>
       </c>
       <c r="J7" t="n">
-        <v>9.802903059395849</v>
+        <v>2.840652105341098</v>
       </c>
       <c r="K7" t="n">
-        <v>9.147712898160128</v>
+        <v>2.185461944105382</v>
       </c>
       <c r="L7" t="n">
-        <v>8.823779978693164</v>
+        <v>1.861529024638422</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.34561031482352</v>
+        <v>2.315709423635899</v>
       </c>
       <c r="C8" t="n">
-        <v>14.58036361573052</v>
+        <v>2.881046111289276</v>
       </c>
       <c r="D8" t="n">
-        <v>16.39532044129513</v>
+        <v>3.916688107539603</v>
       </c>
       <c r="E8" t="n">
-        <v>13.79477310177688</v>
+        <v>3.125916088598542</v>
       </c>
       <c r="F8" t="n">
-        <v>10.69051310467087</v>
+        <v>2.579566332068337</v>
       </c>
       <c r="G8" t="n">
-        <v>15.15017223783093</v>
+        <v>3.439799514129433</v>
       </c>
       <c r="H8" t="n">
-        <v>15.90515844770374</v>
+        <v>4.190570067730093</v>
       </c>
       <c r="I8" t="n">
-        <v>15.02854710309976</v>
+        <v>3.343017590353713</v>
       </c>
       <c r="J8" t="n">
-        <v>15.57118165136261</v>
+        <v>3.855869132026184</v>
       </c>
       <c r="K8" t="n">
-        <v>10.36034029477455</v>
+        <v>2.39888436475307</v>
       </c>
       <c r="L8" t="n">
-        <v>19.26225279386749</v>
+        <v>3.698700230154202</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.76947684160634</v>
+        <v>3.446309926223391</v>
       </c>
       <c r="C9" t="n">
-        <v>20.267612674294</v>
+        <v>3.882001940172666</v>
       </c>
       <c r="D9" t="n">
-        <v>21.14312081109315</v>
+        <v>4.752300968096235</v>
       </c>
       <c r="E9" t="n">
-        <v>24.99975695052914</v>
+        <v>5.097993235293032</v>
       </c>
       <c r="F9" t="n">
-        <v>20.70363353940798</v>
+        <v>4.341875519032818</v>
       </c>
       <c r="G9" t="n">
-        <v>20.82520846770275</v>
+        <v>4.438605885174722</v>
       </c>
       <c r="H9" t="n">
-        <v>21.58019467753634</v>
+        <v>5.189376438768511</v>
       </c>
       <c r="I9" t="n">
-        <v>20.70358333297149</v>
+        <v>4.341823961399006</v>
       </c>
       <c r="J9" t="n">
-        <v>21.24533907128995</v>
+        <v>4.854520832522097</v>
       </c>
       <c r="K9" t="n">
-        <v>15.90238070462098</v>
+        <v>3.81969001269621</v>
       </c>
       <c r="L9" t="n">
-        <v>20.26621599058728</v>
+        <v>3.875397751819424</v>
       </c>
     </row>
   </sheetData>
@@ -4475,19 +4475,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.77580671263493</v>
+        <v>29.77580671263494</v>
       </c>
       <c r="C2" t="n">
-        <v>28.78418310720326</v>
+        <v>28.78418310720325</v>
       </c>
       <c r="D2" t="n">
-        <v>31.13800315400192</v>
+        <v>31.13800315400194</v>
       </c>
       <c r="E2" t="n">
-        <v>29.18235270007779</v>
+        <v>29.18235270007778</v>
       </c>
       <c r="F2" t="n">
-        <v>29.18235270007779</v>
+        <v>29.18235270007778</v>
       </c>
       <c r="G2" t="n">
         <v>30.23712590268937</v>
@@ -4496,16 +4496,16 @@
         <v>31.28659159216025</v>
       </c>
       <c r="I2" t="n">
-        <v>29.79953101467571</v>
+        <v>29.7995310146757</v>
       </c>
       <c r="J2" t="n">
         <v>32.24736111938981</v>
       </c>
       <c r="K2" t="n">
-        <v>30.70579733554405</v>
+        <v>30.70579733554401</v>
       </c>
       <c r="L2" t="n">
-        <v>29.61430253984185</v>
+        <v>29.61430253984184</v>
       </c>
     </row>
     <row r="3">
@@ -4515,34 +4515,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.28941053507874</v>
+        <v>33.28941053507876</v>
       </c>
       <c r="C3" t="n">
         <v>32.27282116516406</v>
       </c>
       <c r="D3" t="n">
-        <v>34.85621862079353</v>
+        <v>34.85621862079354</v>
       </c>
       <c r="E3" t="n">
-        <v>32.69968883983483</v>
+        <v>32.69968883983482</v>
       </c>
       <c r="F3" t="n">
-        <v>32.69968883983483</v>
+        <v>32.69968883983482</v>
       </c>
       <c r="G3" t="n">
-        <v>33.82002316562371</v>
+        <v>33.8200231656237</v>
       </c>
       <c r="H3" t="n">
         <v>35.02784574904527</v>
       </c>
       <c r="I3" t="n">
-        <v>33.31745341950774</v>
+        <v>33.31745341950773</v>
       </c>
       <c r="J3" t="n">
-        <v>35.87440669668356</v>
+        <v>35.87440669668361</v>
       </c>
       <c r="K3" t="n">
-        <v>34.2193039365858</v>
+        <v>34.21930393658577</v>
       </c>
       <c r="L3" t="n">
         <v>33.10368947161007</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.753948268449871</v>
+        <v>0.9914278991420314</v>
       </c>
       <c r="C4" t="n">
-        <v>3.367444065052658</v>
+        <v>0.8442664587094647</v>
       </c>
       <c r="D4" t="n">
-        <v>4.563716331682998</v>
+        <v>1.801195962375154</v>
       </c>
       <c r="E4" t="n">
-        <v>3.647383109503009</v>
+        <v>0.9848437061404636</v>
       </c>
       <c r="F4" t="n">
-        <v>3.647383109503012</v>
+        <v>0.9848437061404635</v>
       </c>
       <c r="G4" t="n">
-        <v>4.025626453309934</v>
+        <v>1.265212661325564</v>
       </c>
       <c r="H4" t="n">
-        <v>4.651859185339529</v>
+        <v>1.889338816031695</v>
       </c>
       <c r="I4" t="n">
-        <v>3.750397236991503</v>
+        <v>1.002900301512832</v>
       </c>
       <c r="J4" t="n">
-        <v>4.202903705015597</v>
+        <v>1.440383335707758</v>
       </c>
       <c r="K4" t="n">
-        <v>3.753563506445213</v>
+        <v>0.9910431371373756</v>
       </c>
       <c r="L4" t="n">
-        <v>3.658117214568892</v>
+        <v>0.8955968452610542</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.13521168325807</v>
+        <v>4.050530243572217</v>
       </c>
       <c r="C5" t="n">
-        <v>11.64973954828086</v>
+        <v>2.301950455859011</v>
       </c>
       <c r="D5" t="n">
-        <v>94.65330343578576</v>
+        <v>17.65696320678117</v>
       </c>
       <c r="E5" t="n">
-        <v>21.76798153604378</v>
+        <v>4.174069011930477</v>
       </c>
       <c r="F5" t="n">
-        <v>21.76798153604378</v>
+        <v>4.174069011930477</v>
       </c>
       <c r="G5" t="n">
-        <v>46.71980372533572</v>
+        <v>8.779387820485738</v>
       </c>
       <c r="H5" t="n">
-        <v>115.9737876222488</v>
+        <v>21.48199811476288</v>
       </c>
       <c r="I5" t="n">
-        <v>21.76789186253969</v>
+        <v>4.173979338426509</v>
       </c>
       <c r="J5" t="n">
-        <v>64.58509203559046</v>
+        <v>12.067648424304</v>
       </c>
       <c r="K5" t="n">
-        <v>20.27570490756685</v>
+        <v>3.898940007978044</v>
       </c>
       <c r="L5" t="n">
-        <v>12.75146702681397</v>
+        <v>2.496026403544096</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>758.7182113414494</v>
+        <v>112.0446526997711</v>
       </c>
       <c r="C6" t="n">
-        <v>634.527370397245</v>
+        <v>111.9284128912542</v>
       </c>
       <c r="D6" t="n">
-        <v>635.6562170256527</v>
+        <v>112.8734754826572</v>
       </c>
       <c r="E6" t="n">
-        <v>571.8849053707856</v>
+        <v>100.9946470822128</v>
       </c>
       <c r="F6" t="n">
-        <v>634.7277007708265</v>
+        <v>112.0549790126884</v>
       </c>
       <c r="G6" t="n">
-        <v>758.9898895263096</v>
+        <v>134.1389222421834</v>
       </c>
       <c r="H6" t="n">
-        <v>760.3095257424153</v>
+        <v>134.8850874094257</v>
       </c>
       <c r="I6" t="n">
-        <v>634.7346324778021</v>
+        <v>133.8766098823708</v>
       </c>
       <c r="J6" t="n">
-        <v>759.478476790434</v>
+        <v>118.1508921883324</v>
       </c>
       <c r="K6" t="n">
-        <v>634.6857364060496</v>
+        <v>112.0351049657641</v>
       </c>
       <c r="L6" t="n">
-        <v>634.6413712445855</v>
+        <v>111.9486489527914</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.948453119831481</v>
+        <v>1.729660748985002</v>
       </c>
       <c r="C7" t="n">
-        <v>7.847211480325855</v>
+        <v>1.632705519525313</v>
       </c>
       <c r="D7" t="n">
-        <v>8.758234026563455</v>
+        <v>2.539431072673908</v>
       </c>
       <c r="E7" t="n">
-        <v>7.928257412487715</v>
+        <v>1.738277579383209</v>
       </c>
       <c r="F7" t="n">
-        <v>7.928257412487715</v>
+        <v>1.738277579383209</v>
       </c>
       <c r="G7" t="n">
-        <v>8.220131304691552</v>
+        <v>2.003445511168536</v>
       </c>
       <c r="H7" t="n">
-        <v>8.846364036721143</v>
+        <v>2.627571665874664</v>
       </c>
       <c r="I7" t="n">
-        <v>7.944902088373119</v>
+        <v>1.741133151355805</v>
       </c>
       <c r="J7" t="n">
-        <v>8.397408556397208</v>
+        <v>2.178616185550729</v>
       </c>
       <c r="K7" t="n">
-        <v>7.948068357826828</v>
+        <v>1.729275986980349</v>
       </c>
       <c r="L7" t="n">
-        <v>7.852622065950504</v>
+        <v>1.633829695104026</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.891675589917241</v>
+        <v>1.895667902820569</v>
       </c>
       <c r="C8" t="n">
-        <v>12.63008852246617</v>
+        <v>2.474491874380702</v>
       </c>
       <c r="D8" t="n">
-        <v>14.3557824251135</v>
+        <v>3.524599585480487</v>
       </c>
       <c r="E8" t="n">
-        <v>11.67525712286778</v>
+        <v>2.397749524836686</v>
       </c>
       <c r="F8" t="n">
-        <v>9.000420729222048</v>
+        <v>1.926978322105956</v>
       </c>
       <c r="G8" t="n">
-        <v>13.01833672049479</v>
+        <v>2.847929659773981</v>
       </c>
       <c r="H8" t="n">
-        <v>13.64456945256179</v>
+        <v>3.472055814486694</v>
       </c>
       <c r="I8" t="n">
-        <v>12.74310750417636</v>
+        <v>2.585617299961251</v>
       </c>
       <c r="J8" t="n">
-        <v>13.19637158039096</v>
+        <v>3.023233673196981</v>
       </c>
       <c r="K8" t="n">
-        <v>8.819682541131954</v>
+        <v>1.882680082410813</v>
       </c>
       <c r="L8" t="n">
-        <v>16.67767951096541</v>
+        <v>3.187039797010418</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.40067202833068</v>
+        <v>2.86525127072754</v>
       </c>
       <c r="C9" t="n">
-        <v>17.50086485035212</v>
+        <v>3.331748503443483</v>
       </c>
       <c r="D9" t="n">
-        <v>18.41187606394811</v>
+        <v>4.238472062047173</v>
       </c>
       <c r="E9" t="n">
-        <v>21.29303197826169</v>
+        <v>4.090477890213778</v>
       </c>
       <c r="F9" t="n">
-        <v>17.59864352658262</v>
+        <v>3.440265526241507</v>
       </c>
       <c r="G9" t="n">
-        <v>17.87378467471776</v>
+        <v>3.70248849508671</v>
       </c>
       <c r="H9" t="n">
-        <v>18.50001740674738</v>
+        <v>4.326614649792837</v>
       </c>
       <c r="I9" t="n">
-        <v>17.59855545839933</v>
+        <v>3.440176135273973</v>
       </c>
       <c r="J9" t="n">
-        <v>18.05106192642344</v>
+        <v>3.877659169468902</v>
       </c>
       <c r="K9" t="n">
-        <v>15.67154203015673</v>
+        <v>3.088607345944725</v>
       </c>
       <c r="L9" t="n">
-        <v>17.50627543597673</v>
+        <v>3.332872679022199</v>
       </c>
     </row>
   </sheetData>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.95179979491953</v>
+        <v>33.95179979491958</v>
       </c>
       <c r="C2" t="n">
-        <v>38.89220694271875</v>
+        <v>38.89220694271877</v>
       </c>
       <c r="D2" t="n">
         <v>36.38642463103758</v>
@@ -4883,19 +4883,19 @@
         <v>40.74428993489916</v>
       </c>
       <c r="F2" t="n">
-        <v>36.57940190127768</v>
+        <v>36.57940190127766</v>
       </c>
       <c r="G2" t="n">
         <v>36.4850201700153</v>
       </c>
       <c r="H2" t="n">
-        <v>42.6192195312175</v>
+        <v>42.61921953121752</v>
       </c>
       <c r="I2" t="n">
-        <v>35.06695098716017</v>
+        <v>35.06695098716016</v>
       </c>
       <c r="J2" t="n">
-        <v>48.53578051193452</v>
+        <v>48.53578051193448</v>
       </c>
       <c r="K2" t="n">
         <v>37.40621666499798</v>
@@ -4914,34 +4914,34 @@
         <v>38.35689661219369</v>
       </c>
       <c r="C3" t="n">
-        <v>43.4640281101816</v>
+        <v>43.46402811018162</v>
       </c>
       <c r="D3" t="n">
-        <v>41.15721950474491</v>
+        <v>41.15721950474492</v>
       </c>
       <c r="E3" t="n">
-        <v>45.31705489476565</v>
+        <v>45.31705489476563</v>
       </c>
       <c r="F3" t="n">
-        <v>41.15216686114415</v>
+        <v>41.15216686114417</v>
       </c>
       <c r="G3" t="n">
-        <v>41.27062479857363</v>
+        <v>41.27062479857364</v>
       </c>
       <c r="H3" t="n">
-        <v>48.32719116237671</v>
+        <v>48.32719116237679</v>
       </c>
       <c r="I3" t="n">
-        <v>39.64028694994953</v>
+        <v>39.64028694994955</v>
       </c>
       <c r="J3" t="n">
-        <v>54.03190175535624</v>
+        <v>54.03190175535622</v>
       </c>
       <c r="K3" t="n">
-        <v>42.08944320934695</v>
+        <v>42.08944320934699</v>
       </c>
       <c r="L3" t="n">
-        <v>46.87293218258407</v>
+        <v>46.8729321825841</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.15901104108145</v>
+        <v>4.891162946555169</v>
       </c>
       <c r="C4" t="n">
-        <v>10.69449677592817</v>
+        <v>5.532182067930256</v>
       </c>
       <c r="D4" t="n">
-        <v>11.60629234234817</v>
+        <v>6.338444247821885</v>
       </c>
       <c r="E4" t="n">
-        <v>10.79796922123023</v>
+        <v>5.550393849309604</v>
       </c>
       <c r="F4" t="n">
-        <v>10.79796922123024</v>
+        <v>5.550393849309604</v>
       </c>
       <c r="G4" t="n">
-        <v>11.66646973021719</v>
+        <v>6.39733082502704</v>
       </c>
       <c r="H4" t="n">
-        <v>15.3101035650891</v>
+        <v>10.0422554705628</v>
       </c>
       <c r="I4" t="n">
-        <v>10.83251337065092</v>
+        <v>5.556285241547663</v>
       </c>
       <c r="J4" t="n">
-        <v>14.47683341779753</v>
+        <v>9.208985323271207</v>
       </c>
       <c r="K4" t="n">
-        <v>11.25973319762766</v>
+        <v>5.99188510310136</v>
       </c>
       <c r="L4" t="n">
-        <v>14.55963304908082</v>
+        <v>9.291784954554524</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>309.4519962410266</v>
+        <v>57.56672805631763</v>
       </c>
       <c r="C5" t="n">
-        <v>363.9208914760908</v>
+        <v>67.70002719829593</v>
       </c>
       <c r="D5" t="n">
-        <v>457.5403819484893</v>
+        <v>84.82284359322678</v>
       </c>
       <c r="E5" t="n">
-        <v>363.9208922419941</v>
+        <v>67.70002796419985</v>
       </c>
       <c r="F5" t="n">
-        <v>363.9208922419941</v>
+        <v>67.70002796419985</v>
       </c>
       <c r="G5" t="n">
-        <v>474.3184430040698</v>
+        <v>87.8240776800057</v>
       </c>
       <c r="H5" t="n">
-        <v>922.9643483145828</v>
+        <v>169.7894016808675</v>
       </c>
       <c r="I5" t="n">
-        <v>363.9206636278843</v>
+        <v>67.69979935008955</v>
       </c>
       <c r="J5" t="n">
-        <v>783.9875046735463</v>
+        <v>144.6428627304201</v>
       </c>
       <c r="K5" t="n">
-        <v>424.7324316959645</v>
+        <v>78.76307964449042</v>
       </c>
       <c r="L5" t="n">
-        <v>286.6623831370959</v>
+        <v>57.18186871054762</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>825.0446428182672</v>
+        <v>148.3110333622044</v>
       </c>
       <c r="C6" t="n">
-        <v>689.8740882211277</v>
+        <v>125.0677895145692</v>
       </c>
       <c r="D6" t="n">
-        <v>690.82728020097</v>
+        <v>125.8813374631837</v>
       </c>
       <c r="E6" t="n">
-        <v>622.3758264115722</v>
+        <v>113.1880961315638</v>
       </c>
       <c r="F6" t="n">
-        <v>690.0324739279682</v>
+        <v>125.0956660299271</v>
       </c>
       <c r="G6" t="n">
-        <v>690.8349177652568</v>
+        <v>149.8172012406762</v>
       </c>
       <c r="H6" t="n">
-        <v>694.6770898132559</v>
+        <v>153.5924013898978</v>
       </c>
       <c r="I6" t="n">
-        <v>825.7181451478369</v>
+        <v>148.9761556571968</v>
       </c>
       <c r="J6" t="n">
-        <v>829.7225673828914</v>
+        <v>152.6922337236489</v>
       </c>
       <c r="K6" t="n">
-        <v>690.4454306868192</v>
+        <v>125.5285672134771</v>
       </c>
       <c r="L6" t="n">
-        <v>693.9010244964538</v>
+        <v>128.8558692014216</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.09869756857035</v>
+        <v>6.112547768775027</v>
       </c>
       <c r="C7" t="n">
-        <v>17.77242774634609</v>
+        <v>6.77789791197377</v>
       </c>
       <c r="D7" t="n">
-        <v>18.54590102417102</v>
+        <v>7.559815369204586</v>
       </c>
       <c r="E7" t="n">
-        <v>17.77911713156394</v>
+        <v>6.779075874870599</v>
       </c>
       <c r="F7" t="n">
-        <v>17.77911713156395</v>
+        <v>6.779075874870599</v>
       </c>
       <c r="G7" t="n">
-        <v>18.60615625770608</v>
+        <v>7.618715647246884</v>
       </c>
       <c r="H7" t="n">
-        <v>22.24979009257799</v>
+        <v>11.26364029278267</v>
       </c>
       <c r="I7" t="n">
-        <v>17.77219989813981</v>
+        <v>6.777670063767501</v>
       </c>
       <c r="J7" t="n">
-        <v>21.41651994528643</v>
+        <v>10.43037014549106</v>
       </c>
       <c r="K7" t="n">
-        <v>18.19941972511655</v>
+        <v>7.213269925321214</v>
       </c>
       <c r="L7" t="n">
-        <v>21.49931957656971</v>
+        <v>10.51316977677437</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.9891815383283</v>
+        <v>6.621272944695851</v>
       </c>
       <c r="C8" t="n">
-        <v>28.10412868897675</v>
+        <v>8.596277268023698</v>
       </c>
       <c r="D8" t="n">
-        <v>30.41114901760906</v>
+        <v>9.648099004734098</v>
       </c>
       <c r="E8" t="n">
-        <v>26.07038919309814</v>
+        <v>8.238339749793449</v>
       </c>
       <c r="F8" t="n">
-        <v>20.90257427417341</v>
+        <v>7.328804328991103</v>
       </c>
       <c r="G8" t="n">
-        <v>28.92997584276723</v>
+        <v>9.435707884372086</v>
       </c>
       <c r="H8" t="n">
-        <v>32.57360967764585</v>
+        <v>13.08063252990906</v>
       </c>
       <c r="I8" t="n">
-        <v>28.09601948320099</v>
+        <v>8.594662300892717</v>
       </c>
       <c r="J8" t="n">
-        <v>31.74180038331439</v>
+        <v>12.24761949273704</v>
       </c>
       <c r="K8" t="n">
-        <v>20.95182567045475</v>
+        <v>7.697693369075829</v>
       </c>
       <c r="L8" t="n">
-        <v>39.58787976746002</v>
+        <v>13.69675635312048</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.19064177276427</v>
+        <v>9.472729930505634</v>
       </c>
       <c r="C9" t="n">
-        <v>44.58035141928881</v>
+        <v>11.49609245284566</v>
       </c>
       <c r="D9" t="n">
-        <v>45.35390492010723</v>
+        <v>12.27802402932325</v>
       </c>
       <c r="E9" t="n">
-        <v>53.48441775687853</v>
+        <v>13.06320875087474</v>
       </c>
       <c r="F9" t="n">
-        <v>44.58034156190288</v>
+        <v>11.4960913490506</v>
       </c>
       <c r="G9" t="n">
-        <v>45.41407993064886</v>
+        <v>12.33691018811878</v>
       </c>
       <c r="H9" t="n">
-        <v>49.05771376552075</v>
+        <v>15.98183483365455</v>
       </c>
       <c r="I9" t="n">
-        <v>44.58012357108264</v>
+        <v>11.49586460463941</v>
       </c>
       <c r="J9" t="n">
-        <v>48.22444361822916</v>
+        <v>15.14856468636296</v>
       </c>
       <c r="K9" t="n">
-        <v>40.53667559077143</v>
+        <v>11.144626936374</v>
       </c>
       <c r="L9" t="n">
-        <v>48.30724324951242</v>
+        <v>15.23136431764627</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.8372678468729</v>
+        <v>32.83726784687291</v>
       </c>
       <c r="C2" t="n">
         <v>38.45968267674767</v>
       </c>
       <c r="D2" t="n">
-        <v>35.86997010436566</v>
+        <v>35.86997010436563</v>
       </c>
       <c r="E2" t="n">
-        <v>40.2942041916896</v>
+        <v>40.29420419168962</v>
       </c>
       <c r="F2" t="n">
-        <v>36.18000736470008</v>
+        <v>36.1800073647001</v>
       </c>
       <c r="G2" t="n">
-        <v>35.89056532574733</v>
+        <v>35.89056532574728</v>
       </c>
       <c r="H2" t="n">
         <v>40.98407391766671</v>
       </c>
       <c r="I2" t="n">
-        <v>34.68296972470935</v>
+        <v>34.68296972470937</v>
       </c>
       <c r="J2" t="n">
         <v>46.56376478510526</v>
       </c>
       <c r="K2" t="n">
-        <v>36.22136701042211</v>
+        <v>36.22136701042212</v>
       </c>
       <c r="L2" t="n">
-        <v>40.40695978884693</v>
+        <v>40.40695978884695</v>
       </c>
     </row>
     <row r="3">
@@ -5307,34 +5307,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.06773277356688</v>
+        <v>37.06773277356689</v>
       </c>
       <c r="C3" t="n">
         <v>42.96661608928817</v>
       </c>
       <c r="D3" t="n">
-        <v>40.55596859206357</v>
+        <v>40.55596859206355</v>
       </c>
       <c r="E3" t="n">
-        <v>44.80207079507186</v>
+        <v>44.80207079507188</v>
       </c>
       <c r="F3" t="n">
-        <v>40.68787396808231</v>
+        <v>40.68787396808232</v>
       </c>
       <c r="G3" t="n">
-        <v>40.57965736293975</v>
+        <v>40.57965736293976</v>
       </c>
       <c r="H3" t="n">
         <v>46.43905709386354</v>
       </c>
       <c r="I3" t="n">
-        <v>39.19114022904458</v>
+        <v>39.19114022904457</v>
       </c>
       <c r="J3" t="n">
-        <v>51.77561824275514</v>
+        <v>51.77561824275513</v>
       </c>
       <c r="K3" t="n">
-        <v>40.73228286886221</v>
+        <v>40.73228286886224</v>
       </c>
       <c r="L3" t="n">
         <v>45.77431002615178</v>
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.914201782295608</v>
+        <v>4.132126760314248</v>
       </c>
       <c r="C4" t="n">
-        <v>9.827725413455681</v>
+        <v>5.197526829456841</v>
       </c>
       <c r="D4" t="n">
-        <v>10.71701476787949</v>
+        <v>5.93493974589812</v>
       </c>
       <c r="E4" t="n">
-        <v>9.919843145145011</v>
+        <v>5.213740488255373</v>
       </c>
       <c r="F4" t="n">
-        <v>9.919843145145018</v>
+        <v>5.213740488255373</v>
       </c>
       <c r="G4" t="n">
-        <v>10.73116547193284</v>
+        <v>5.947518490618</v>
       </c>
       <c r="H4" t="n">
-        <v>13.75604544152374</v>
+        <v>8.973970419542352</v>
       </c>
       <c r="I4" t="n">
-        <v>10.02414361498386</v>
+        <v>5.231933008968015</v>
       </c>
       <c r="J4" t="n">
-        <v>12.7981307371925</v>
+        <v>8.016055715210967</v>
       </c>
       <c r="K4" t="n">
-        <v>10.02411030463766</v>
+        <v>5.242035282656217</v>
       </c>
       <c r="L4" t="n">
-        <v>13.41334569815268</v>
+        <v>8.631270676171313</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237.9612084752056</v>
+        <v>44.44439971983015</v>
       </c>
       <c r="C5" t="n">
-        <v>318.8335658278513</v>
+        <v>59.58255444769961</v>
       </c>
       <c r="D5" t="n">
-        <v>396.2067246723203</v>
+        <v>73.78112832144771</v>
       </c>
       <c r="E5" t="n">
-        <v>318.8335669663331</v>
+        <v>59.5825555861815</v>
       </c>
       <c r="F5" t="n">
-        <v>318.8335669663331</v>
+        <v>59.5825555861815</v>
       </c>
       <c r="G5" t="n">
-        <v>408.1326595321995</v>
+        <v>75.89018106623328</v>
       </c>
       <c r="H5" t="n">
-        <v>766.9772589228124</v>
+        <v>141.5409032739215</v>
       </c>
       <c r="I5" t="n">
-        <v>318.8333674980329</v>
+        <v>59.58235611788129</v>
       </c>
       <c r="J5" t="n">
-        <v>629.7388577594468</v>
+        <v>116.5976230827672</v>
       </c>
       <c r="K5" t="n">
-        <v>320.0500645896232</v>
+        <v>59.80660294114984</v>
       </c>
       <c r="L5" t="n">
-        <v>762.6170162826628</v>
+        <v>59.85751201526703</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>641.603328837478</v>
+        <v>137.6820300050504</v>
       </c>
       <c r="C6" t="n">
-        <v>642.6113090494437</v>
+        <v>116.5674369459213</v>
       </c>
       <c r="D6" t="n">
-        <v>643.4686878315447</v>
+        <v>117.299233601664</v>
       </c>
       <c r="E6" t="n">
-        <v>579.7360063274481</v>
+        <v>105.5013846649216</v>
       </c>
       <c r="F6" t="n">
-        <v>642.7453713433673</v>
+        <v>116.591032847633</v>
       </c>
       <c r="G6" t="n">
-        <v>643.4202925271155</v>
+        <v>139.4974217353541</v>
       </c>
       <c r="H6" t="n">
-        <v>773.2390347963957</v>
+        <v>142.6429758217004</v>
       </c>
       <c r="I6" t="n">
-        <v>642.7132706701668</v>
+        <v>138.7818362537041</v>
       </c>
       <c r="J6" t="n">
-        <v>677.8700641175018</v>
+        <v>141.6269557113742</v>
       </c>
       <c r="K6" t="n">
-        <v>642.6839964279693</v>
+        <v>116.590174637011</v>
       </c>
       <c r="L6" t="n">
-        <v>646.262161625492</v>
+        <v>120.0126616758513</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.993535220453</v>
+        <v>5.202089439632263</v>
       </c>
       <c r="C7" t="n">
-        <v>16.10367538295956</v>
+        <v>6.302094018104311</v>
       </c>
       <c r="D7" t="n">
-        <v>16.79630349617236</v>
+        <v>7.004894556279988</v>
       </c>
       <c r="E7" t="n">
-        <v>16.08708130226126</v>
+        <v>6.2991743980263</v>
       </c>
       <c r="F7" t="n">
-        <v>16.08708130226126</v>
+        <v>6.2991743980263</v>
       </c>
       <c r="G7" t="n">
-        <v>16.8104989100903</v>
+        <v>7.017481169936012</v>
       </c>
       <c r="H7" t="n">
-        <v>19.83537887968122</v>
+        <v>10.04393309886035</v>
       </c>
       <c r="I7" t="n">
-        <v>16.10347705314127</v>
+        <v>6.301895688286015</v>
       </c>
       <c r="J7" t="n">
-        <v>18.87746417534978</v>
+        <v>9.086018394528958</v>
       </c>
       <c r="K7" t="n">
-        <v>16.10344374279507</v>
+        <v>6.311997961974215</v>
       </c>
       <c r="L7" t="n">
-        <v>19.49267913631017</v>
+        <v>9.701233355489316</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.38307377593548</v>
+        <v>5.622648223118326</v>
       </c>
       <c r="C8" t="n">
-        <v>24.84678407767279</v>
+        <v>7.840881140048971</v>
       </c>
       <c r="D8" t="n">
-        <v>26.87458137413196</v>
+        <v>8.778671453189459</v>
       </c>
       <c r="E8" t="n">
-        <v>23.10674715338127</v>
+        <v>7.534635581128934</v>
       </c>
       <c r="F8" t="n">
-        <v>18.68520418667578</v>
+        <v>6.756444023205487</v>
       </c>
       <c r="G8" t="n">
-        <v>25.56824314598816</v>
+        <v>8.558844147101988</v>
       </c>
       <c r="H8" t="n">
-        <v>28.59312311559225</v>
+        <v>11.58529607602867</v>
       </c>
       <c r="I8" t="n">
-        <v>24.86122128903913</v>
+        <v>7.843258665452003</v>
       </c>
       <c r="J8" t="n">
-        <v>27.63645993771579</v>
+        <v>10.62760164035214</v>
       </c>
       <c r="K8" t="n">
-        <v>18.37468960906956</v>
+        <v>6.711737232272514</v>
       </c>
       <c r="L8" t="n">
-        <v>34.90254669823906</v>
+        <v>12.4133700316928</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.22069120932552</v>
+        <v>7.882068879152063</v>
       </c>
       <c r="C9" t="n">
-        <v>37.65292143772979</v>
+        <v>10.09476130319291</v>
       </c>
       <c r="D9" t="n">
-        <v>38.34559664414108</v>
+        <v>10.79757012977148</v>
       </c>
       <c r="E9" t="n">
-        <v>44.94847163217663</v>
+        <v>11.37877906856703</v>
       </c>
       <c r="F9" t="n">
-        <v>37.65291378852984</v>
+        <v>10.09476089504278</v>
       </c>
       <c r="G9" t="n">
-        <v>38.35974496486053</v>
+        <v>10.81014845502461</v>
       </c>
       <c r="H9" t="n">
-        <v>41.38462493445144</v>
+        <v>13.83660038394894</v>
       </c>
       <c r="I9" t="n">
-        <v>37.65272310791156</v>
+        <v>10.09456297337461</v>
       </c>
       <c r="J9" t="n">
-        <v>40.42671023011999</v>
+        <v>12.87868567961755</v>
       </c>
       <c r="K9" t="n">
-        <v>29.69204929780561</v>
+        <v>8.703592526696978</v>
       </c>
       <c r="L9" t="n">
-        <v>41.04192519108037</v>
+        <v>13.49390064057792</v>
       </c>
     </row>
   </sheetData>
@@ -5666,34 +5666,34 @@
         <v>32.46354279866552</v>
       </c>
       <c r="C2" t="n">
-        <v>37.74139495606202</v>
+        <v>37.74139495606205</v>
       </c>
       <c r="D2" t="n">
-        <v>35.22540034732457</v>
+        <v>35.2254003473246</v>
       </c>
       <c r="E2" t="n">
-        <v>39.56569769713714</v>
+        <v>39.5656976971372</v>
       </c>
       <c r="F2" t="n">
-        <v>35.48112446993989</v>
+        <v>35.48112446993991</v>
       </c>
       <c r="G2" t="n">
-        <v>35.23106177535434</v>
+        <v>35.23106177535436</v>
       </c>
       <c r="H2" t="n">
-        <v>39.69260462908808</v>
+        <v>39.69260462908812</v>
       </c>
       <c r="I2" t="n">
-        <v>34.00360166649239</v>
+        <v>34.00360166649246</v>
       </c>
       <c r="J2" t="n">
-        <v>45.6061534469113</v>
+        <v>45.60615344691129</v>
       </c>
       <c r="K2" t="n">
-        <v>34.39992254954852</v>
+        <v>34.39992254954856</v>
       </c>
       <c r="L2" t="n">
-        <v>39.2554857786446</v>
+        <v>39.25548577864465</v>
       </c>
     </row>
     <row r="3">
@@ -5706,31 +5706,31 @@
         <v>36.63157316344306</v>
       </c>
       <c r="C3" t="n">
-        <v>42.13989639268767</v>
+        <v>42.13989639268769</v>
       </c>
       <c r="D3" t="n">
-        <v>39.80828146146857</v>
+        <v>39.80828146146861</v>
       </c>
       <c r="E3" t="n">
-        <v>43.96521424174927</v>
+        <v>43.96521424174932</v>
       </c>
       <c r="F3" t="n">
-        <v>39.880641014552</v>
+        <v>39.88064101455204</v>
       </c>
       <c r="G3" t="n">
-        <v>39.81479327646407</v>
+        <v>39.81479327646413</v>
       </c>
       <c r="H3" t="n">
-        <v>44.9471835811273</v>
+        <v>44.94718358112729</v>
       </c>
       <c r="I3" t="n">
-        <v>38.40274832357527</v>
+        <v>38.40274832357534</v>
       </c>
       <c r="J3" t="n">
-        <v>50.67988830970228</v>
+        <v>50.67988830970227</v>
       </c>
       <c r="K3" t="n">
-        <v>38.64610401661787</v>
+        <v>38.64610401661785</v>
       </c>
       <c r="L3" t="n">
         <v>44.44360037842068</v>
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.309318843952422</v>
+        <v>3.847579065560749</v>
       </c>
       <c r="C4" t="n">
-        <v>8.929224473139142</v>
+        <v>4.711569147764356</v>
       </c>
       <c r="D4" t="n">
-        <v>9.951126126798538</v>
+        <v>5.489386348406859</v>
       </c>
       <c r="E4" t="n">
-        <v>9.024036523235084</v>
+        <v>4.728257476038733</v>
       </c>
       <c r="F4" t="n">
-        <v>9.024036523235088</v>
+        <v>4.728257476038733</v>
       </c>
       <c r="G4" t="n">
-        <v>9.956323605623325</v>
+        <v>5.493074259430853</v>
       </c>
       <c r="H4" t="n">
-        <v>12.60574414396402</v>
+        <v>8.144004365572339</v>
       </c>
       <c r="I4" t="n">
-        <v>9.237067029891939</v>
+        <v>4.765584488568574</v>
       </c>
       <c r="J4" t="n">
-        <v>11.89372177251341</v>
+        <v>7.431981994121737</v>
       </c>
       <c r="K4" t="n">
-        <v>8.618608508008705</v>
+        <v>4.156868729617008</v>
       </c>
       <c r="L4" t="n">
-        <v>12.34620866368997</v>
+        <v>7.884468885298277</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.403532837699</v>
+        <v>40.12016053191326</v>
       </c>
       <c r="C5" t="n">
-        <v>284.9096383900959</v>
+        <v>53.28412173395333</v>
       </c>
       <c r="D5" t="n">
-        <v>353.0333668638202</v>
+        <v>65.87186039093382</v>
       </c>
       <c r="E5" t="n">
-        <v>284.909640098285</v>
+        <v>53.28412344214246</v>
       </c>
       <c r="F5" t="n">
-        <v>284.909640098285</v>
+        <v>53.28412344214246</v>
       </c>
       <c r="G5" t="n">
-        <v>366.4032226123062</v>
+        <v>68.22772814467245</v>
       </c>
       <c r="H5" t="n">
-        <v>662.3484639542855</v>
+        <v>122.4987224325463</v>
       </c>
       <c r="I5" t="n">
-        <v>284.9094382094036</v>
+        <v>53.2839215532608</v>
       </c>
       <c r="J5" t="n">
-        <v>583.919244384781</v>
+        <v>108.1084734283549</v>
       </c>
       <c r="K5" t="n">
-        <v>223.9811149111498</v>
+        <v>42.06066965118418</v>
       </c>
       <c r="L5" t="n">
-        <v>683.1908457237678</v>
+        <v>125.9531243681046</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>640.7879758305853</v>
+        <v>115.1638220920294</v>
       </c>
       <c r="C6" t="n">
-        <v>641.621364842975</v>
+        <v>116.0653852494731</v>
       </c>
       <c r="D6" t="n">
-        <v>768.4242666722774</v>
+        <v>138.9806583610747</v>
       </c>
       <c r="E6" t="n">
-        <v>578.7640162270714</v>
+        <v>105.0024933605676</v>
       </c>
       <c r="F6" t="n">
-        <v>641.7603251100746</v>
+        <v>116.0898436638981</v>
       </c>
       <c r="G6" t="n">
-        <v>642.4349805922561</v>
+        <v>116.8093172858995</v>
       </c>
       <c r="H6" t="n">
-        <v>771.6076586369588</v>
+        <v>141.7283405924986</v>
       </c>
       <c r="I6" t="n">
-        <v>767.5461772252845</v>
+        <v>138.2279871597777</v>
       </c>
       <c r="J6" t="n">
-        <v>770.5686105053042</v>
+        <v>124.4480651166115</v>
       </c>
       <c r="K6" t="n">
-        <v>640.9819795581534</v>
+        <v>115.4528214313738</v>
       </c>
       <c r="L6" t="n">
-        <v>644.9968364345876</v>
+        <v>119.2309787696336</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.12088703951783</v>
+        <v>4.870415062437909</v>
       </c>
       <c r="C7" t="n">
-        <v>15.04883540614969</v>
+        <v>5.788620666138113</v>
       </c>
       <c r="D7" t="n">
-        <v>15.76267696961428</v>
+        <v>6.512219291200103</v>
       </c>
       <c r="E7" t="n">
-        <v>15.00113618956692</v>
+        <v>5.780227011612931</v>
       </c>
       <c r="F7" t="n">
-        <v>15.00113618956692</v>
+        <v>5.780227011612931</v>
       </c>
       <c r="G7" t="n">
-        <v>15.7678918011887</v>
+        <v>6.515910256307992</v>
       </c>
       <c r="H7" t="n">
-        <v>18.41731233952939</v>
+        <v>9.166840362449499</v>
       </c>
       <c r="I7" t="n">
-        <v>15.04863522545732</v>
+        <v>5.788420485445743</v>
       </c>
       <c r="J7" t="n">
-        <v>17.7052899680788</v>
+        <v>8.454817990998897</v>
       </c>
       <c r="K7" t="n">
-        <v>14.43017670357406</v>
+        <v>5.179704726494172</v>
       </c>
       <c r="L7" t="n">
-        <v>18.15777685925534</v>
+        <v>8.907304882175451</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.29153962054119</v>
+        <v>5.252449914627926</v>
       </c>
       <c r="C8" t="n">
-        <v>23.15991530497481</v>
+        <v>7.216170720595986</v>
       </c>
       <c r="D8" t="n">
-        <v>25.15928014900445</v>
+        <v>8.166021441811463</v>
       </c>
       <c r="E8" t="n">
-        <v>21.52788273606657</v>
+        <v>6.928934397572489</v>
       </c>
       <c r="F8" t="n">
-        <v>17.38075688607574</v>
+        <v>6.199040251929116</v>
       </c>
       <c r="G8" t="n">
-        <v>23.92346529003387</v>
+        <v>7.951291182566984</v>
       </c>
       <c r="H8" t="n">
-        <v>26.57288582839062</v>
+        <v>10.60222128871131</v>
       </c>
       <c r="I8" t="n">
-        <v>23.20420871430247</v>
+        <v>7.223801411704732</v>
       </c>
       <c r="J8" t="n">
-        <v>25.86203965779358</v>
+        <v>9.890405928609811</v>
       </c>
       <c r="K8" t="n">
-        <v>16.48965630673915</v>
+        <v>5.54217313468715</v>
       </c>
       <c r="L8" t="n">
-        <v>32.56510068020896</v>
+        <v>11.44299386092338</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.2145515891435</v>
+        <v>7.174900010684939</v>
       </c>
       <c r="C9" t="n">
-        <v>33.76827014450178</v>
+        <v>9.083241162235819</v>
       </c>
       <c r="D9" t="n">
-        <v>34.48213139938282</v>
+        <v>9.8068432529871</v>
       </c>
       <c r="E9" t="n">
-        <v>40.26028341122538</v>
+        <v>10.22583689853582</v>
       </c>
       <c r="F9" t="n">
-        <v>33.76826379847861</v>
+        <v>9.083241452883671</v>
       </c>
       <c r="G9" t="n">
-        <v>34.48732653954077</v>
+        <v>9.810530752405715</v>
       </c>
       <c r="H9" t="n">
-        <v>37.13674707788148</v>
+        <v>12.46146085854721</v>
       </c>
       <c r="I9" t="n">
-        <v>33.76806996380941</v>
+        <v>9.083040981543455</v>
       </c>
       <c r="J9" t="n">
-        <v>36.42472470643087</v>
+        <v>11.74943848709661</v>
       </c>
       <c r="K9" t="n">
-        <v>29.89001908410804</v>
+        <v>7.9006369707245</v>
       </c>
       <c r="L9" t="n">
-        <v>36.87721159760741</v>
+        <v>12.20192537827316</v>
       </c>
     </row>
   </sheetData>
@@ -6062,31 +6062,31 @@
         <v>29.54058465892441</v>
       </c>
       <c r="C2" t="n">
-        <v>37.57115285071124</v>
+        <v>37.57115285071127</v>
       </c>
       <c r="D2" t="n">
-        <v>32.69346070789878</v>
+        <v>32.69346070789879</v>
       </c>
       <c r="E2" t="n">
-        <v>39.40282383613921</v>
+        <v>39.40282383613922</v>
       </c>
       <c r="F2" t="n">
         <v>35.30119740263979</v>
       </c>
       <c r="G2" t="n">
-        <v>33.35760182353248</v>
+        <v>33.35760182353246</v>
       </c>
       <c r="H2" t="n">
-        <v>34.83042571736745</v>
+        <v>34.83042571736746</v>
       </c>
       <c r="I2" t="n">
-        <v>33.79325790904857</v>
+        <v>33.79325790904856</v>
       </c>
       <c r="J2" t="n">
-        <v>48.9300389652074</v>
+        <v>48.93003896520737</v>
       </c>
       <c r="K2" t="n">
-        <v>34.82569084351495</v>
+        <v>34.82569084351496</v>
       </c>
       <c r="L2" t="n">
         <v>36.16381881485157</v>
@@ -6102,34 +6102,34 @@
         <v>33.26874637347011</v>
       </c>
       <c r="C3" t="n">
-        <v>41.93747440222631</v>
+        <v>41.93747440222632</v>
       </c>
       <c r="D3" t="n">
         <v>36.89520694609661</v>
       </c>
       <c r="E3" t="n">
-        <v>43.76997782285601</v>
+        <v>43.76997782285602</v>
       </c>
       <c r="F3" t="n">
-        <v>39.66835138935657</v>
+        <v>39.66835138935659</v>
       </c>
       <c r="G3" t="n">
-        <v>37.65910680549296</v>
+        <v>37.65910680549297</v>
       </c>
       <c r="H3" t="n">
-        <v>39.35391718175262</v>
+        <v>39.35391718175264</v>
       </c>
       <c r="I3" t="n">
-        <v>38.16137595215695</v>
+        <v>38.16137595215697</v>
       </c>
       <c r="J3" t="n">
-        <v>54.48980451949935</v>
+        <v>54.48980451949934</v>
       </c>
       <c r="K3" t="n">
-        <v>39.12613846474549</v>
+        <v>39.12613846474548</v>
       </c>
       <c r="L3" t="n">
-        <v>40.88675374217761</v>
+        <v>40.88675374217765</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.643877934888016</v>
+        <v>2.131680178643244</v>
       </c>
       <c r="C4" t="n">
-        <v>9.015059660371175</v>
+        <v>4.632793112584867</v>
       </c>
       <c r="D4" t="n">
-        <v>8.518129147312226</v>
+        <v>4.005931391067458</v>
       </c>
       <c r="E4" t="n">
-        <v>9.113265130107294</v>
+        <v>4.650078328129808</v>
       </c>
       <c r="F4" t="n">
-        <v>9.113265130107292</v>
+        <v>4.650078328129807</v>
       </c>
       <c r="G4" t="n">
-        <v>8.918408105757372</v>
+        <v>4.401698778735673</v>
       </c>
       <c r="H4" t="n">
-        <v>9.78820470463865</v>
+        <v>5.276006948393878</v>
       </c>
       <c r="I4" t="n">
-        <v>9.207841345650447</v>
+        <v>4.666745330017955</v>
       </c>
       <c r="J4" t="n">
-        <v>13.89260661134921</v>
+        <v>9.380408855104417</v>
       </c>
       <c r="K4" t="n">
-        <v>8.908748303087107</v>
+        <v>4.396550546842329</v>
       </c>
       <c r="L4" t="n">
-        <v>10.58068481152536</v>
+        <v>6.068487055280592</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.22559891106224</v>
+        <v>14.02606300599896</v>
       </c>
       <c r="C5" t="n">
-        <v>304.4644854058227</v>
+        <v>56.63189176202182</v>
       </c>
       <c r="D5" t="n">
-        <v>234.5985479747275</v>
+        <v>43.79608488908544</v>
       </c>
       <c r="E5" t="n">
-        <v>304.4644866836931</v>
+        <v>56.63189303989196</v>
       </c>
       <c r="F5" t="n">
-        <v>304.4644866836931</v>
+        <v>56.63189303989196</v>
       </c>
       <c r="G5" t="n">
-        <v>285.4247691513026</v>
+        <v>53.06681805905458</v>
       </c>
       <c r="H5" t="n">
-        <v>387.8889410233052</v>
+        <v>71.82173617989423</v>
       </c>
       <c r="I5" t="n">
-        <v>304.4645128827739</v>
+        <v>56.63191923897296</v>
       </c>
       <c r="J5" t="n">
-        <v>829.0571310176751</v>
+        <v>152.849364373216</v>
       </c>
       <c r="K5" t="n">
-        <v>277.4699879302892</v>
+        <v>51.66332846510996</v>
       </c>
       <c r="L5" t="n">
-        <v>136.9748644281779</v>
+        <v>94.98660219687577</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>685.3523623141007</v>
+        <v>121.5843727821177</v>
       </c>
       <c r="C6" t="n">
-        <v>687.9376213078224</v>
+        <v>124.1231633150653</v>
       </c>
       <c r="D6" t="n">
-        <v>687.145932339649</v>
+        <v>147.1479256271489</v>
       </c>
       <c r="E6" t="n">
-        <v>620.4695330516065</v>
+        <v>112.2487808992789</v>
       </c>
       <c r="F6" t="n">
-        <v>687.9583268522263</v>
+        <v>124.1268085438257</v>
       </c>
       <c r="G6" t="n">
-        <v>822.0458891578503</v>
+        <v>123.8543913822102</v>
       </c>
       <c r="H6" t="n">
-        <v>823.6291842821405</v>
+        <v>148.512018577895</v>
       </c>
       <c r="I6" t="n">
-        <v>822.3353223977435</v>
+        <v>124.1194379334924</v>
       </c>
       <c r="J6" t="n">
-        <v>827.4287116088199</v>
+        <v>152.5627625588106</v>
       </c>
       <c r="K6" t="n">
-        <v>687.6429313184719</v>
+        <v>123.8537661102588</v>
       </c>
       <c r="L6" t="n">
-        <v>689.3887963450768</v>
+        <v>125.5387140378238</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.49633035336002</v>
+        <v>3.161711798712982</v>
       </c>
       <c r="C7" t="n">
-        <v>15.06026628717131</v>
+        <v>5.696749473136535</v>
       </c>
       <c r="D7" t="n">
-        <v>14.37055195887996</v>
+        <v>5.03595780032207</v>
       </c>
       <c r="E7" t="n">
-        <v>15.03208068052144</v>
+        <v>5.691789859358078</v>
       </c>
       <c r="F7" t="n">
-        <v>15.03208068052144</v>
+        <v>5.691789859358078</v>
       </c>
       <c r="G7" t="n">
-        <v>14.7708605242294</v>
+        <v>5.431730398805418</v>
       </c>
       <c r="H7" t="n">
-        <v>15.64065712311066</v>
+        <v>6.306038568463628</v>
       </c>
       <c r="I7" t="n">
-        <v>15.06029376412247</v>
+        <v>5.696776950087696</v>
       </c>
       <c r="J7" t="n">
-        <v>19.74505902982121</v>
+        <v>10.41044047517416</v>
       </c>
       <c r="K7" t="n">
-        <v>14.76120072155911</v>
+        <v>5.42658216691207</v>
       </c>
       <c r="L7" t="n">
-        <v>16.43313722999738</v>
+        <v>7.09851867535034</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.46066947292218</v>
+        <v>3.507435481882581</v>
       </c>
       <c r="C8" t="n">
-        <v>22.90330951772272</v>
+        <v>7.077125074219849</v>
       </c>
       <c r="D8" t="n">
-        <v>23.4638021869238</v>
+        <v>6.636369831785792</v>
       </c>
       <c r="E8" t="n">
-        <v>21.29127671883658</v>
+        <v>6.793408356132312</v>
       </c>
       <c r="F8" t="n">
-        <v>17.19497422035</v>
+        <v>6.072459120305215</v>
       </c>
       <c r="G8" t="n">
-        <v>22.63973688467874</v>
+        <v>6.816652630740162</v>
       </c>
       <c r="H8" t="n">
-        <v>23.50953348356868</v>
+        <v>7.690960800399891</v>
       </c>
       <c r="I8" t="n">
-        <v>22.92917012457183</v>
+        <v>7.08169918202244</v>
       </c>
       <c r="J8" t="n">
-        <v>27.61509579210745</v>
+        <v>11.79556693783109</v>
       </c>
       <c r="K8" t="n">
-        <v>16.61586003122802</v>
+        <v>5.753002203645052</v>
       </c>
       <c r="L8" t="n">
-        <v>30.46979645966116</v>
+        <v>9.568970686384764</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.01484265411599</v>
+        <v>5.892969948846421</v>
       </c>
       <c r="C9" t="n">
-        <v>36.8972211856163</v>
+        <v>9.540053514437506</v>
       </c>
       <c r="D9" t="n">
-        <v>36.20754010785497</v>
+        <v>8.879267693716292</v>
       </c>
       <c r="E9" t="n">
-        <v>44.18856928987461</v>
+        <v>10.82333182679844</v>
       </c>
       <c r="F9" t="n">
-        <v>36.89721826150114</v>
+        <v>9.540054052758283</v>
       </c>
       <c r="G9" t="n">
-        <v>36.60781542267438</v>
+        <v>9.275034440106388</v>
       </c>
       <c r="H9" t="n">
-        <v>37.47761202155569</v>
+        <v>10.1493426097646</v>
       </c>
       <c r="I9" t="n">
-        <v>36.89724866256746</v>
+        <v>9.54008099138867</v>
       </c>
       <c r="J9" t="n">
-        <v>41.58201392826621</v>
+        <v>14.25374451647513</v>
       </c>
       <c r="K9" t="n">
-        <v>28.64210760714964</v>
+        <v>8.625562721248443</v>
       </c>
       <c r="L9" t="n">
-        <v>38.27009212844239</v>
+        <v>10.94182271665131</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.51829481884599</v>
+        <v>28.51829481884602</v>
       </c>
       <c r="C2" t="n">
-        <v>35.92052552701694</v>
+        <v>35.92052552701695</v>
       </c>
       <c r="D2" t="n">
-        <v>31.81906002776926</v>
+        <v>31.8190600277693</v>
       </c>
       <c r="E2" t="n">
-        <v>37.72574807202433</v>
+        <v>37.7257480720243</v>
       </c>
       <c r="F2" t="n">
-        <v>33.69989367647683</v>
+        <v>33.69989367647685</v>
       </c>
       <c r="G2" t="n">
         <v>31.79948644350006</v>
       </c>
       <c r="H2" t="n">
-        <v>30.6081975330815</v>
+        <v>30.60819753308153</v>
       </c>
       <c r="I2" t="n">
         <v>32.22879131535669</v>
       </c>
       <c r="J2" t="n">
-        <v>43.58698441192467</v>
+        <v>43.58698441192463</v>
       </c>
       <c r="K2" t="n">
-        <v>31.805835908391</v>
+        <v>31.80583590839098</v>
       </c>
       <c r="L2" t="n">
-        <v>33.23908979921782</v>
+        <v>33.23908979921783</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.0808170457449</v>
+        <v>32.08081704574492</v>
       </c>
       <c r="C3" t="n">
-        <v>40.03984136948435</v>
+        <v>40.03984136948434</v>
       </c>
       <c r="D3" t="n">
-        <v>35.87738078745977</v>
+        <v>35.87738078745978</v>
       </c>
       <c r="E3" t="n">
-        <v>41.84581333794385</v>
+        <v>41.84581333794386</v>
       </c>
       <c r="F3" t="n">
-        <v>37.81995894239636</v>
+        <v>37.81995894239638</v>
       </c>
       <c r="G3" t="n">
-        <v>35.8548671108944</v>
+        <v>35.85486711089442</v>
       </c>
       <c r="H3" t="n">
-        <v>34.48537776903654</v>
+        <v>34.48537776903652</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3497186274782</v>
+        <v>36.34971862747817</v>
       </c>
       <c r="J3" t="n">
-        <v>48.36275292593611</v>
+        <v>48.3627529259361</v>
       </c>
       <c r="K3" t="n">
-        <v>35.66291988865004</v>
+        <v>35.66291988865002</v>
       </c>
       <c r="L3" t="n">
-        <v>37.51068290003705</v>
+        <v>37.51068290003707</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.197579272150045</v>
+        <v>1.387092018350127</v>
       </c>
       <c r="C4" t="n">
-        <v>7.262554566261846</v>
+        <v>3.568702594083758</v>
       </c>
       <c r="D4" t="n">
-        <v>7.159744323568503</v>
+        <v>3.349257069768675</v>
       </c>
       <c r="E4" t="n">
-        <v>7.337097043740322</v>
+        <v>3.581823095155434</v>
       </c>
       <c r="F4" t="n">
-        <v>7.337097043740322</v>
+        <v>3.581823095155433</v>
       </c>
       <c r="G4" t="n">
-        <v>7.153612110235744</v>
+        <v>3.338590011066209</v>
       </c>
       <c r="H4" t="n">
-        <v>6.440285133656433</v>
+        <v>2.629797879856606</v>
       </c>
       <c r="I4" t="n">
-        <v>7.439202338782875</v>
+        <v>3.59981562440325</v>
       </c>
       <c r="J4" t="n">
-        <v>9.999105105499064</v>
+        <v>6.188617851699131</v>
       </c>
       <c r="K4" t="n">
-        <v>6.36333257656884</v>
+        <v>2.552845322768976</v>
       </c>
       <c r="L4" t="n">
-        <v>8.003713526159153</v>
+        <v>4.19322627235931</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.92944806120814</v>
+        <v>4.683900907360263</v>
       </c>
       <c r="C5" t="n">
-        <v>206.4877807396006</v>
+        <v>38.6323422105954</v>
       </c>
       <c r="D5" t="n">
-        <v>177.6966722577507</v>
+        <v>33.36375622354797</v>
       </c>
       <c r="E5" t="n">
-        <v>206.487781983662</v>
+        <v>38.63234345465676</v>
       </c>
       <c r="F5" t="n">
-        <v>206.487781983662</v>
+        <v>38.63234345465676</v>
       </c>
       <c r="G5" t="n">
-        <v>187.8057055648401</v>
+        <v>35.13335828679327</v>
       </c>
       <c r="H5" t="n">
-        <v>131.4125451843436</v>
+        <v>24.62491552959474</v>
       </c>
       <c r="I5" t="n">
-        <v>206.4878086795574</v>
+        <v>38.63237015055201</v>
       </c>
       <c r="J5" t="n">
-        <v>457.2803090786994</v>
+        <v>84.9101093244218</v>
       </c>
       <c r="K5" t="n">
-        <v>120.4324707739786</v>
+        <v>22.62901353672826</v>
       </c>
       <c r="L5" t="n">
-        <v>46.41684961760188</v>
+        <v>10.95393818781958</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>637.0792727834735</v>
+        <v>134.5465979929792</v>
       </c>
       <c r="C6" t="n">
-        <v>639.3644717976246</v>
+        <v>114.8186394239844</v>
       </c>
       <c r="D6" t="n">
-        <v>639.069295213368</v>
+        <v>114.5653374525017</v>
       </c>
       <c r="E6" t="n">
-        <v>576.5420207103155</v>
+        <v>103.7618891176365</v>
       </c>
       <c r="F6" t="n">
-        <v>639.3701521260676</v>
+        <v>114.8196401868913</v>
       </c>
       <c r="G6" t="n">
-        <v>639.0353056215589</v>
+        <v>114.5497674664497</v>
       </c>
       <c r="H6" t="n">
-        <v>763.5452012462567</v>
+        <v>113.8450702443715</v>
       </c>
       <c r="I6" t="n">
-        <v>639.3208958501064</v>
+        <v>114.8109930797868</v>
       </c>
       <c r="J6" t="n">
-        <v>674.2073099383682</v>
+        <v>139.4113650823238</v>
       </c>
       <c r="K6" t="n">
-        <v>638.1333952637755</v>
+        <v>113.7443757532144</v>
       </c>
       <c r="L6" t="n">
-        <v>639.9675388613572</v>
+        <v>115.4188589286664</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.06871742276928</v>
+        <v>2.244412328213633</v>
       </c>
       <c r="C7" t="n">
-        <v>12.31031254944544</v>
+        <v>4.457107994310153</v>
       </c>
       <c r="D7" t="n">
-        <v>12.03086447015413</v>
+        <v>4.206574210922287</v>
       </c>
       <c r="E7" t="n">
-        <v>12.27987918870506</v>
+        <v>4.451752747955419</v>
       </c>
       <c r="F7" t="n">
-        <v>12.27987918870506</v>
+        <v>4.451752747955419</v>
       </c>
       <c r="G7" t="n">
-        <v>12.02475026085491</v>
+        <v>4.195910320929702</v>
       </c>
       <c r="H7" t="n">
-        <v>11.31142328427563</v>
+        <v>3.48711818972009</v>
       </c>
       <c r="I7" t="n">
-        <v>12.31034048940201</v>
+        <v>4.457135934266734</v>
       </c>
       <c r="J7" t="n">
-        <v>14.87024325611809</v>
+        <v>7.04593816156261</v>
       </c>
       <c r="K7" t="n">
-        <v>11.23447072718801</v>
+        <v>3.410165632632466</v>
       </c>
       <c r="L7" t="n">
-        <v>12.87485167677835</v>
+        <v>5.050546582222797</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.35325406778228</v>
+        <v>2.470490776510886</v>
       </c>
       <c r="C8" t="n">
-        <v>18.17707397933726</v>
+        <v>5.489658000376134</v>
       </c>
       <c r="D8" t="n">
-        <v>18.88190582304918</v>
+        <v>5.412357482498122</v>
       </c>
       <c r="E8" t="n">
-        <v>16.91921354894076</v>
+        <v>5.268275590932486</v>
       </c>
       <c r="F8" t="n">
-        <v>13.72285039359973</v>
+        <v>4.705715678640757</v>
       </c>
       <c r="G8" t="n">
-        <v>17.91976163969895</v>
+        <v>5.233432317984335</v>
       </c>
       <c r="H8" t="n">
-        <v>17.20643466311774</v>
+        <v>4.524640186774392</v>
       </c>
       <c r="I8" t="n">
-        <v>18.2053518682461</v>
+        <v>5.494657931321374</v>
       </c>
       <c r="J8" t="n">
-        <v>20.76616071891192</v>
+        <v>8.083619629391542</v>
       </c>
       <c r="K8" t="n">
-        <v>12.43336543755167</v>
+        <v>3.621171100513123</v>
       </c>
       <c r="L8" t="n">
-        <v>23.5858894307564</v>
+        <v>6.935689216708096</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.25011295870048</v>
+        <v>4.212337931874135</v>
       </c>
       <c r="C9" t="n">
-        <v>28.23545580892904</v>
+        <v>7.259933192791864</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95603010798954</v>
+        <v>7.00940334799386</v>
       </c>
       <c r="E9" t="n">
-        <v>33.70964390215667</v>
+        <v>8.223391317085886</v>
       </c>
       <c r="F9" t="n">
-        <v>28.23545593746659</v>
+        <v>7.259934240521023</v>
       </c>
       <c r="G9" t="n">
-        <v>27.94989352033839</v>
+        <v>6.998735519411412</v>
       </c>
       <c r="H9" t="n">
-        <v>27.23656654375931</v>
+        <v>6.289943388201817</v>
       </c>
       <c r="I9" t="n">
-        <v>28.23548374888563</v>
+        <v>7.259961132748447</v>
       </c>
       <c r="J9" t="n">
-        <v>30.79538651560176</v>
+        <v>9.848763360044332</v>
       </c>
       <c r="K9" t="n">
-        <v>24.29955767686913</v>
+        <v>5.709620923316513</v>
       </c>
       <c r="L9" t="n">
-        <v>28.79999493626196</v>
+        <v>7.853371780704498</v>
       </c>
     </row>
   </sheetData>
@@ -6851,34 +6851,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.39282444902243</v>
+        <v>28.39282444902242</v>
       </c>
       <c r="C2" t="n">
-        <v>34.47783197842646</v>
+        <v>34.47783197842652</v>
       </c>
       <c r="D2" t="n">
-        <v>30.20528424451249</v>
+        <v>30.20528424451252</v>
       </c>
       <c r="E2" t="n">
-        <v>36.27004697793389</v>
+        <v>36.27004697793387</v>
       </c>
       <c r="F2" t="n">
-        <v>32.28093735074919</v>
+        <v>32.28093735074921</v>
       </c>
       <c r="G2" t="n">
-        <v>30.63564093492585</v>
+        <v>30.63564093492584</v>
       </c>
       <c r="H2" t="n">
-        <v>30.40507579072533</v>
+        <v>30.40507579072534</v>
       </c>
       <c r="I2" t="n">
-        <v>30.83893794103079</v>
+        <v>30.83893794103081</v>
       </c>
       <c r="J2" t="n">
         <v>39.97624993857863</v>
       </c>
       <c r="K2" t="n">
-        <v>30.43052473921642</v>
+        <v>30.43052473921643</v>
       </c>
       <c r="L2" t="n">
         <v>32.37593232449274</v>
@@ -6894,7 +6894,7 @@
         <v>31.92937237356822</v>
       </c>
       <c r="C3" t="n">
-        <v>38.38123459092235</v>
+        <v>38.38123459092239</v>
       </c>
       <c r="D3" t="n">
         <v>34.01407658829736</v>
@@ -6903,25 +6903,25 @@
         <v>40.17420630571817</v>
       </c>
       <c r="F3" t="n">
-        <v>36.18509667853346</v>
+        <v>36.18509667853348</v>
       </c>
       <c r="G3" t="n">
-        <v>34.50907593039253</v>
+        <v>34.50907593039255</v>
       </c>
       <c r="H3" t="n">
-        <v>34.24453807152172</v>
+        <v>34.2445380715217</v>
       </c>
       <c r="I3" t="n">
         <v>34.74381117860194</v>
       </c>
       <c r="J3" t="n">
-        <v>44.21892215925125</v>
+        <v>44.21892215925127</v>
       </c>
       <c r="K3" t="n">
-        <v>34.08343099353647</v>
+        <v>34.08343099353648</v>
       </c>
       <c r="L3" t="n">
-        <v>36.51071887742106</v>
+        <v>36.51071887742104</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.659465196087717</v>
+        <v>1.23686324912456</v>
       </c>
       <c r="C4" t="n">
-        <v>5.958225086735769</v>
+        <v>2.664243267941177</v>
       </c>
       <c r="D4" t="n">
-        <v>5.736895744070201</v>
+        <v>2.314293797107068</v>
       </c>
       <c r="E4" t="n">
-        <v>6.026068808966611</v>
+        <v>2.676184797679032</v>
       </c>
       <c r="F4" t="n">
-        <v>6.026068808966611</v>
+        <v>2.676184797679031</v>
       </c>
       <c r="G4" t="n">
-        <v>5.997771606772199</v>
+        <v>2.571010893891058</v>
       </c>
       <c r="H4" t="n">
-        <v>5.855783023233414</v>
+        <v>2.433181076270237</v>
       </c>
       <c r="I4" t="n">
-        <v>6.146393405801344</v>
+        <v>2.697359298994125</v>
       </c>
       <c r="J4" t="n">
-        <v>7.454012424810259</v>
+        <v>4.031410477847094</v>
       </c>
       <c r="K4" t="n">
-        <v>5.119963227090273</v>
+        <v>1.697361280127093</v>
       </c>
       <c r="L4" t="n">
-        <v>7.026957791562979</v>
+        <v>3.60435584459981</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.20212903907619</v>
+        <v>4.324372068760548</v>
       </c>
       <c r="C5" t="n">
-        <v>146.1413749946402</v>
+        <v>27.33647751804322</v>
       </c>
       <c r="D5" t="n">
-        <v>111.8384118874374</v>
+        <v>20.98816053715338</v>
       </c>
       <c r="E5" t="n">
-        <v>146.1413762503318</v>
+        <v>27.33647877373492</v>
       </c>
       <c r="F5" t="n">
-        <v>146.1413762503318</v>
+        <v>27.33647877373492</v>
       </c>
       <c r="G5" t="n">
-        <v>138.208867866216</v>
+        <v>25.84016370946692</v>
       </c>
       <c r="H5" t="n">
-        <v>136.6225979063979</v>
+        <v>25.44814037099825</v>
       </c>
       <c r="I5" t="n">
-        <v>146.1413730614811</v>
+        <v>27.33647558488413</v>
       </c>
       <c r="J5" t="n">
-        <v>280.262651681378</v>
+        <v>52.04573072683235</v>
       </c>
       <c r="K5" t="n">
-        <v>59.0855346696162</v>
+        <v>11.1953018025461</v>
       </c>
       <c r="L5" t="n">
-        <v>71.34494940902673</v>
+        <v>49.1441538524498</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>636.1765084640363</v>
+        <v>112.3838622620219</v>
       </c>
       <c r="C6" t="n">
-        <v>637.6806853418738</v>
+        <v>113.847395670388</v>
       </c>
       <c r="D6" t="n">
-        <v>761.7819156210237</v>
+        <v>113.4584232177803</v>
       </c>
       <c r="E6" t="n">
-        <v>574.8856938346613</v>
+        <v>102.7954782596944</v>
       </c>
       <c r="F6" t="n">
-        <v>637.7020675331022</v>
+        <v>113.8511599707136</v>
       </c>
       <c r="G6" t="n">
-        <v>637.514814874721</v>
+        <v>135.6148208450698</v>
       </c>
       <c r="H6" t="n">
-        <v>762.24139734686</v>
+        <v>135.5570484758828</v>
       </c>
       <c r="I6" t="n">
-        <v>637.6634366737509</v>
+        <v>113.8443583118916</v>
       </c>
       <c r="J6" t="n">
-        <v>671.2270987250155</v>
+        <v>137.1316151695724</v>
       </c>
       <c r="K6" t="n">
-        <v>636.5090748930428</v>
+        <v>112.8218443311952</v>
       </c>
       <c r="L6" t="n">
-        <v>638.6285079003383</v>
+        <v>114.766228061402</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.199634692168384</v>
+        <v>2.035933076104914</v>
       </c>
       <c r="C7" t="n">
-        <v>10.68656483504115</v>
+        <v>3.496431059133631</v>
       </c>
       <c r="D7" t="n">
-        <v>10.27705638759607</v>
+        <v>3.113362066037795</v>
       </c>
       <c r="E7" t="n">
-        <v>10.65377581330031</v>
+        <v>3.490661226028443</v>
       </c>
       <c r="F7" t="n">
-        <v>10.65377581330031</v>
+        <v>3.490661226028443</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5379411028529</v>
+        <v>3.370080720871413</v>
       </c>
       <c r="H7" t="n">
-        <v>10.39595251931408</v>
+        <v>3.232250903250593</v>
       </c>
       <c r="I7" t="n">
-        <v>10.686562901882</v>
+        <v>3.496429125974478</v>
       </c>
       <c r="J7" t="n">
-        <v>11.99418192089093</v>
+        <v>4.830480304827453</v>
       </c>
       <c r="K7" t="n">
-        <v>9.660132723170827</v>
+        <v>2.496431107107448</v>
       </c>
       <c r="L7" t="n">
-        <v>11.56712728764365</v>
+        <v>4.403425671580164</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.19185430547431</v>
+        <v>2.210563727100497</v>
       </c>
       <c r="C8" t="n">
-        <v>15.77391567295233</v>
+        <v>4.39180480176054</v>
       </c>
       <c r="D8" t="n">
-        <v>16.25052485312514</v>
+        <v>4.164692510274147</v>
       </c>
       <c r="E8" t="n">
-        <v>14.64887856214128</v>
+        <v>4.193799306014427</v>
       </c>
       <c r="F8" t="n">
-        <v>11.79000960814193</v>
+        <v>3.690638372836968</v>
       </c>
       <c r="G8" t="n">
-        <v>15.65590149007256</v>
+        <v>4.270841744141222</v>
       </c>
       <c r="H8" t="n">
-        <v>15.51391290652654</v>
+        <v>4.133011926519126</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80452328910177</v>
+        <v>4.397190149244294</v>
       </c>
       <c r="J8" t="n">
-        <v>17.11295312888754</v>
+        <v>5.731384032553218</v>
       </c>
       <c r="K8" t="n">
-        <v>10.5757145839114</v>
+        <v>2.657573513724616</v>
       </c>
       <c r="L8" t="n">
-        <v>20.99476889695551</v>
+        <v>6.062690585828175</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.15262994579336</v>
+        <v>3.611660232204687</v>
       </c>
       <c r="C9" t="n">
-        <v>23.63689354399954</v>
+        <v>5.775688899559915</v>
       </c>
       <c r="D9" t="n">
-        <v>23.22739675944712</v>
+        <v>5.392621959133166</v>
       </c>
       <c r="E9" t="n">
-        <v>28.24973348659634</v>
+        <v>6.587549759747738</v>
       </c>
       <c r="F9" t="n">
-        <v>23.63689327659116</v>
+        <v>5.775689887185975</v>
       </c>
       <c r="G9" t="n">
-        <v>23.48826981181119</v>
+        <v>5.649338561297693</v>
       </c>
       <c r="H9" t="n">
-        <v>23.34628122827236</v>
+        <v>5.511508743676877</v>
       </c>
       <c r="I9" t="n">
-        <v>23.63689161084032</v>
+        <v>5.775686966400762</v>
       </c>
       <c r="J9" t="n">
-        <v>24.9445106298492</v>
+        <v>7.109738145253734</v>
       </c>
       <c r="K9" t="n">
-        <v>20.29439191138637</v>
+        <v>4.351522701682145</v>
       </c>
       <c r="L9" t="n">
-        <v>24.51745599660191</v>
+        <v>6.68268351200645</v>
       </c>
     </row>
   </sheetData>
@@ -7253,31 +7253,31 @@
         <v>38.60661786482554</v>
       </c>
       <c r="D2" t="n">
-        <v>36.09302280516371</v>
+        <v>36.09302280516369</v>
       </c>
       <c r="E2" t="n">
         <v>40.44962506237417</v>
       </c>
       <c r="F2" t="n">
-        <v>36.31246232970728</v>
+        <v>36.31246232970727</v>
       </c>
       <c r="G2" t="n">
-        <v>35.66220004468604</v>
+        <v>35.66220004468602</v>
       </c>
       <c r="H2" t="n">
         <v>42.21852475897634</v>
       </c>
       <c r="I2" t="n">
-        <v>34.80331369253114</v>
+        <v>34.80331369253113</v>
       </c>
       <c r="J2" t="n">
-        <v>48.49588905135725</v>
+        <v>48.49588905135727</v>
       </c>
       <c r="K2" t="n">
-        <v>36.59848283905086</v>
+        <v>36.59848283905085</v>
       </c>
       <c r="L2" t="n">
-        <v>40.08823464963668</v>
+        <v>40.0882346496367</v>
       </c>
     </row>
     <row r="3">
@@ -7287,19 +7287,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.30129224383079</v>
+        <v>36.30129224383077</v>
       </c>
       <c r="C3" t="n">
-        <v>43.13138027976597</v>
+        <v>43.13138027976595</v>
       </c>
       <c r="D3" t="n">
-        <v>40.81224124674617</v>
+        <v>40.81224124674616</v>
       </c>
       <c r="E3" t="n">
-        <v>44.97529726811699</v>
+        <v>44.975297268117</v>
       </c>
       <c r="F3" t="n">
-        <v>40.8381345354501</v>
+        <v>40.83813453545013</v>
       </c>
       <c r="G3" t="n">
         <v>40.3167058275309</v>
@@ -7308,16 +7308,16 @@
         <v>47.85862171225588</v>
       </c>
       <c r="I3" t="n">
-        <v>39.32970539561387</v>
+        <v>39.32970539561389</v>
       </c>
       <c r="J3" t="n">
-        <v>53.98734590936375</v>
+        <v>53.9873459093638</v>
       </c>
       <c r="K3" t="n">
-        <v>41.16018079327048</v>
+        <v>41.16018079327044</v>
       </c>
       <c r="L3" t="n">
-        <v>45.40741630337497</v>
+        <v>45.40741630337494</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.831108299416186</v>
+        <v>3.791501674366601</v>
       </c>
       <c r="C4" t="n">
-        <v>10.24838236801058</v>
+        <v>5.330832834053785</v>
       </c>
       <c r="D4" t="n">
-        <v>11.16248664162567</v>
+        <v>6.122880016576084</v>
       </c>
       <c r="E4" t="n">
-        <v>10.35157818052355</v>
+        <v>5.348996098173219</v>
       </c>
       <c r="F4" t="n">
-        <v>10.35157818052355</v>
+        <v>5.348996098173219</v>
       </c>
       <c r="G4" t="n">
-        <v>10.90906429991305</v>
+        <v>5.867246442941797</v>
       </c>
       <c r="H4" t="n">
-        <v>14.80241499393069</v>
+        <v>9.762808368881103</v>
       </c>
       <c r="I4" t="n">
-        <v>10.41363516079065</v>
+        <v>5.359792983243758</v>
       </c>
       <c r="J4" t="n">
-        <v>14.21868614979728</v>
+        <v>9.179079524747694</v>
       </c>
       <c r="K4" t="n">
-        <v>10.53908585533138</v>
+        <v>5.499479230281783</v>
       </c>
       <c r="L4" t="n">
-        <v>13.53676844938059</v>
+        <v>8.497161824330997</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>211.9705259224344</v>
+        <v>39.54403898228896</v>
       </c>
       <c r="C5" t="n">
-        <v>351.3871732025586</v>
+        <v>65.37125969559892</v>
       </c>
       <c r="D5" t="n">
-        <v>424.7512061581236</v>
+        <v>78.91449425705076</v>
       </c>
       <c r="E5" t="n">
-        <v>351.3871741749077</v>
+        <v>65.37126066794788</v>
       </c>
       <c r="F5" t="n">
-        <v>351.3871741749076</v>
+        <v>65.37126066794788</v>
       </c>
       <c r="G5" t="n">
-        <v>417.0641780815269</v>
+        <v>77.35054608116643</v>
       </c>
       <c r="H5" t="n">
-        <v>827.5012173111922</v>
+        <v>152.7977968016693</v>
       </c>
       <c r="I5" t="n">
-        <v>351.3870223018527</v>
+        <v>65.37110879489308</v>
       </c>
       <c r="J5" t="n">
-        <v>788.7127992216907</v>
+        <v>145.4900426867859</v>
       </c>
       <c r="K5" t="n">
-        <v>374.9593775528888</v>
+        <v>69.63745022151367</v>
       </c>
       <c r="L5" t="n">
-        <v>789.5674915607265</v>
+        <v>145.0785683518475</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>687.8959954849149</v>
+        <v>123.3069211714074</v>
       </c>
       <c r="C6" t="n">
-        <v>689.4022447624495</v>
+        <v>124.8619119677833</v>
       </c>
       <c r="D6" t="n">
-        <v>690.3252236373023</v>
+        <v>125.6555210801152</v>
       </c>
       <c r="E6" t="n">
-        <v>621.9128381918911</v>
+        <v>112.9837772769437</v>
       </c>
       <c r="F6" t="n">
-        <v>689.5196378781268</v>
+        <v>124.8825739572461</v>
       </c>
       <c r="G6" t="n">
-        <v>825.318009498126</v>
+        <v>149.2032200211463</v>
       </c>
       <c r="H6" t="n">
-        <v>829.9733913267012</v>
+        <v>153.2328994260409</v>
       </c>
       <c r="I6" t="n">
-        <v>689.4785223462893</v>
+        <v>148.6957665614482</v>
       </c>
       <c r="J6" t="n">
-        <v>829.015564289907</v>
+        <v>152.5833293003562</v>
       </c>
       <c r="K6" t="n">
-        <v>689.6160890815383</v>
+        <v>125.0170311504759</v>
       </c>
       <c r="L6" t="n">
-        <v>692.7628943383837</v>
+        <v>128.0409593330351</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.36776201971493</v>
+        <v>4.941952722905344</v>
       </c>
       <c r="C7" t="n">
-        <v>16.95043978179519</v>
+        <v>6.510394932488298</v>
       </c>
       <c r="D7" t="n">
-        <v>17.6990801731834</v>
+        <v>7.273320471896454</v>
       </c>
       <c r="E7" t="n">
-        <v>16.94404762208792</v>
+        <v>6.509270713601484</v>
       </c>
       <c r="F7" t="n">
-        <v>16.94404762208792</v>
+        <v>6.509270713601484</v>
       </c>
       <c r="G7" t="n">
-        <v>17.44571802021179</v>
+        <v>7.017697491480535</v>
       </c>
       <c r="H7" t="n">
-        <v>21.33906871422945</v>
+        <v>10.91325941741984</v>
       </c>
       <c r="I7" t="n">
-        <v>16.95028888108939</v>
+        <v>6.510244031782502</v>
       </c>
       <c r="J7" t="n">
-        <v>20.75533987009604</v>
+        <v>10.32953057328644</v>
       </c>
       <c r="K7" t="n">
-        <v>17.07573957563012</v>
+        <v>6.649930278820529</v>
       </c>
       <c r="L7" t="n">
-        <v>20.07342216967932</v>
+        <v>9.647612872869733</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.92766655526891</v>
+        <v>5.392495918721529</v>
       </c>
       <c r="C8" t="n">
-        <v>26.38670611586738</v>
+        <v>8.171177798305253</v>
       </c>
       <c r="D8" t="n">
-        <v>28.56701226589697</v>
+        <v>9.18607650984959</v>
       </c>
       <c r="E8" t="n">
-        <v>24.50533958073189</v>
+        <v>7.840058091111817</v>
       </c>
       <c r="F8" t="n">
-        <v>19.72468832709278</v>
+        <v>6.998663475030511</v>
       </c>
       <c r="G8" t="n">
-        <v>26.88674446975634</v>
+        <v>8.679318137596718</v>
       </c>
       <c r="H8" t="n">
-        <v>30.78009516377943</v>
+        <v>12.57488006353698</v>
       </c>
       <c r="I8" t="n">
-        <v>26.39131533063394</v>
+        <v>8.171864677898684</v>
       </c>
       <c r="J8" t="n">
-        <v>30.1977186471734</v>
+        <v>11.99138922904711</v>
       </c>
       <c r="K8" t="n">
-        <v>19.50782373973271</v>
+        <v>7.07797708938317</v>
       </c>
       <c r="L8" t="n">
-        <v>36.70235583904257</v>
+        <v>12.57430518281908</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.59476243460822</v>
+        <v>8.149904778543945</v>
       </c>
       <c r="C9" t="n">
-        <v>42.50528655465272</v>
+        <v>11.00804794014022</v>
       </c>
       <c r="D9" t="n">
-        <v>43.25398846984299</v>
+        <v>11.7709843077375</v>
       </c>
       <c r="E9" t="n">
-        <v>50.96145537184707</v>
+        <v>12.49633444511758</v>
       </c>
       <c r="F9" t="n">
-        <v>42.50527738006414</v>
+        <v>11.00804712662822</v>
       </c>
       <c r="G9" t="n">
-        <v>43.0005647930693</v>
+        <v>11.51535049913247</v>
       </c>
       <c r="H9" t="n">
-        <v>46.89391548708696</v>
+        <v>15.41091242507177</v>
       </c>
       <c r="I9" t="n">
-        <v>42.50513565394692</v>
+        <v>11.00789703943443</v>
       </c>
       <c r="J9" t="n">
-        <v>46.31018664295352</v>
+        <v>14.82718358093837</v>
       </c>
       <c r="K9" t="n">
-        <v>38.21254714229593</v>
+        <v>10.40032558865728</v>
       </c>
       <c r="L9" t="n">
-        <v>45.62826894253682</v>
+        <v>14.14526588052167</v>
       </c>
     </row>
   </sheetData>
@@ -7643,13 +7643,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.7383366156159</v>
+        <v>28.73833661561588</v>
       </c>
       <c r="C2" t="n">
         <v>36.12449183511968</v>
       </c>
       <c r="D2" t="n">
-        <v>34.94649984645142</v>
+        <v>34.94649984645145</v>
       </c>
       <c r="E2" t="n">
         <v>37.94529603681052</v>
@@ -7661,19 +7661,19 @@
         <v>33.28438422434526</v>
       </c>
       <c r="H2" t="n">
-        <v>32.94084398235314</v>
+        <v>32.94084398235312</v>
       </c>
       <c r="I2" t="n">
-        <v>32.41286535517312</v>
+        <v>32.41286535517309</v>
       </c>
       <c r="J2" t="n">
         <v>45.00849884798653</v>
       </c>
       <c r="K2" t="n">
-        <v>32.53972283161384</v>
+        <v>32.53972283161383</v>
       </c>
       <c r="L2" t="n">
-        <v>37.35694864484917</v>
+        <v>37.35694864484914</v>
       </c>
     </row>
     <row r="3">
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.34367272587611</v>
+        <v>32.3436727258761</v>
       </c>
       <c r="C3" t="n">
-        <v>40.28109400539848</v>
+        <v>40.28109400539847</v>
       </c>
       <c r="D3" t="n">
         <v>39.48434645847603</v>
@@ -7695,25 +7695,25 @@
         <v>42.10274027772071</v>
       </c>
       <c r="F3" t="n">
-        <v>38.03104670030893</v>
+        <v>38.03104670030892</v>
       </c>
       <c r="G3" t="n">
         <v>37.57256918684009</v>
       </c>
       <c r="H3" t="n">
-        <v>37.17821804963538</v>
+        <v>37.17821804963535</v>
       </c>
       <c r="I3" t="n">
         <v>36.57078173322112</v>
       </c>
       <c r="J3" t="n">
-        <v>49.99398883913815</v>
+        <v>49.99398883913818</v>
       </c>
       <c r="K3" t="n">
-        <v>36.510646761779</v>
+        <v>36.51064676177901</v>
       </c>
       <c r="L3" t="n">
-        <v>42.25671833800411</v>
+        <v>42.2567183380041</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.660370941777799</v>
+        <v>1.564543215159968</v>
       </c>
       <c r="C4" t="n">
-        <v>7.664136696436129</v>
+        <v>3.717657462514985</v>
       </c>
       <c r="D4" t="n">
-        <v>9.350860920318359</v>
+        <v>5.25503319370068</v>
       </c>
       <c r="E4" t="n">
-        <v>7.747005588675695</v>
+        <v>3.73224335194748</v>
       </c>
       <c r="F4" t="n">
-        <v>7.747005588675698</v>
+        <v>3.73224335194748</v>
       </c>
       <c r="G4" t="n">
-        <v>8.365652593818927</v>
+        <v>4.267477306830319</v>
       </c>
       <c r="H4" t="n">
-        <v>8.1587414156715</v>
+        <v>4.06291368905392</v>
       </c>
       <c r="I4" t="n">
-        <v>7.863447575836155</v>
+        <v>3.752612291270802</v>
       </c>
       <c r="J4" t="n">
-        <v>11.122447837037</v>
+        <v>7.026620110419309</v>
       </c>
       <c r="K4" t="n">
-        <v>7.107215972565928</v>
+        <v>3.01138824594834</v>
       </c>
       <c r="L4" t="n">
-        <v>10.78304904325215</v>
+        <v>6.687221316634377</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.39260466182144</v>
+        <v>5.917416326301144</v>
       </c>
       <c r="C5" t="n">
-        <v>213.2906634797311</v>
+        <v>39.90792598027413</v>
       </c>
       <c r="D5" t="n">
-        <v>333.3138015406766</v>
+        <v>62.27251043392861</v>
       </c>
       <c r="E5" t="n">
-        <v>213.290664650213</v>
+        <v>39.90792715075635</v>
       </c>
       <c r="F5" t="n">
-        <v>213.290664650213</v>
+        <v>39.90792715075635</v>
       </c>
       <c r="G5" t="n">
-        <v>264.96281767289</v>
+        <v>49.42857811603669</v>
       </c>
       <c r="H5" t="n">
-        <v>261.4841174768795</v>
+        <v>48.64817963423644</v>
       </c>
       <c r="I5" t="n">
-        <v>213.290513132852</v>
+        <v>39.90777563339505</v>
       </c>
       <c r="J5" t="n">
-        <v>558.2268952352265</v>
+        <v>103.3170023307412</v>
       </c>
       <c r="K5" t="n">
-        <v>150.5218769804259</v>
+        <v>28.25236844656074</v>
       </c>
       <c r="L5" t="n">
-        <v>563.5001858099163</v>
+        <v>21.50122428985073</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>637.7964833904012</v>
+        <v>134.8625193353273</v>
       </c>
       <c r="C6" t="n">
-        <v>639.925907674096</v>
+        <v>114.9957285516112</v>
       </c>
       <c r="D6" t="n">
-        <v>641.7195281325693</v>
+        <v>116.5519180199829</v>
       </c>
       <c r="E6" t="n">
-        <v>577.0832584104828</v>
+        <v>103.9354233056241</v>
       </c>
       <c r="F6" t="n">
-        <v>640.02415904355</v>
+        <v>115.0130217570188</v>
       </c>
       <c r="G6" t="n">
-        <v>765.7405210168653</v>
+        <v>115.523432494936</v>
       </c>
       <c r="H6" t="n">
-        <v>766.1411740651531</v>
+        <v>137.4678211124944</v>
       </c>
       <c r="I6" t="n">
-        <v>765.238315998883</v>
+        <v>137.050588411438</v>
       </c>
       <c r="J6" t="n">
-        <v>768.8746820705124</v>
+        <v>123.9762995848798</v>
       </c>
       <c r="K6" t="n">
-        <v>639.0949029828266</v>
+        <v>114.2412205570437</v>
       </c>
       <c r="L6" t="n">
-        <v>643.0564867954009</v>
+        <v>117.9673457580297</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.94580640975814</v>
+        <v>2.494779852483945</v>
       </c>
       <c r="C7" t="n">
-        <v>13.1490333906957</v>
+        <v>4.682999275473863</v>
       </c>
       <c r="D7" t="n">
-        <v>14.63626926897905</v>
+        <v>6.185265058024386</v>
       </c>
       <c r="E7" t="n">
-        <v>13.12696043467324</v>
+        <v>4.679115399712324</v>
       </c>
       <c r="F7" t="n">
-        <v>13.12696043467325</v>
+        <v>4.679115399712324</v>
       </c>
       <c r="G7" t="n">
-        <v>13.65108806179945</v>
+        <v>5.197713944154299</v>
       </c>
       <c r="H7" t="n">
-        <v>13.44417688365214</v>
+        <v>4.9931503263779</v>
       </c>
       <c r="I7" t="n">
-        <v>13.14888304381662</v>
+        <v>4.68284892859478</v>
       </c>
       <c r="J7" t="n">
-        <v>16.40788330501741</v>
+        <v>7.956856747743282</v>
       </c>
       <c r="K7" t="n">
-        <v>12.39265144054661</v>
+        <v>3.941624883272318</v>
       </c>
       <c r="L7" t="n">
-        <v>16.06848451123259</v>
+        <v>7.61745795395835</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.68547090912487</v>
+        <v>2.800960802713445</v>
       </c>
       <c r="C8" t="n">
-        <v>20.14963335458378</v>
+        <v>5.915104862452597</v>
       </c>
       <c r="D8" t="n">
-        <v>22.75206587976797</v>
+        <v>7.613645253783451</v>
       </c>
       <c r="E8" t="n">
-        <v>18.70751014036655</v>
+        <v>5.661292142592324</v>
       </c>
       <c r="F8" t="n">
-        <v>15.04294795095387</v>
+        <v>5.016329200750484</v>
       </c>
       <c r="G8" t="n">
-        <v>20.67179831414487</v>
+        <v>6.433358941871625</v>
       </c>
       <c r="H8" t="n">
-        <v>20.46488713600569</v>
+        <v>6.228795324096671</v>
       </c>
       <c r="I8" t="n">
-        <v>20.16959329616207</v>
+        <v>5.918493926312111</v>
       </c>
       <c r="J8" t="n">
-        <v>23.4296314266847</v>
+        <v>9.192684410460272</v>
       </c>
       <c r="K8" t="n">
-        <v>14.03421780441713</v>
+        <v>4.230540561748034</v>
       </c>
       <c r="L8" t="n">
-        <v>28.60568863945137</v>
+        <v>9.824005868568436</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.49589266638598</v>
+        <v>4.703595021681755</v>
       </c>
       <c r="C9" t="n">
-        <v>30.98738555133429</v>
+        <v>7.822549238734269</v>
       </c>
       <c r="D9" t="n">
-        <v>32.47465361276898</v>
+        <v>9.324820685519409</v>
       </c>
       <c r="E9" t="n">
-        <v>37.08993428102784</v>
+        <v>8.896598773817857</v>
       </c>
       <c r="F9" t="n">
-        <v>30.98738372800525</v>
+        <v>7.822549882305731</v>
       </c>
       <c r="G9" t="n">
-        <v>31.4894402224382</v>
+        <v>8.337263907414712</v>
       </c>
       <c r="H9" t="n">
-        <v>31.28252904429057</v>
+        <v>8.132700289638315</v>
       </c>
       <c r="I9" t="n">
-        <v>30.98723520445521</v>
+        <v>7.822398891855192</v>
       </c>
       <c r="J9" t="n">
-        <v>34.24623546565609</v>
+        <v>11.09640671100371</v>
       </c>
       <c r="K9" t="n">
-        <v>27.16696369760628</v>
+        <v>5.909213374246003</v>
       </c>
       <c r="L9" t="n">
-        <v>33.90683667187115</v>
+        <v>10.75700791721877</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Ammonia/ammonia resource use fossils results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.38637711722358</v>
+        <v>39.89396451210332</v>
       </c>
       <c r="C2" t="n">
-        <v>39.56457782970475</v>
+        <v>43.11531204630147</v>
       </c>
       <c r="D2" t="n">
-        <v>36.92083881005443</v>
+        <v>39.9747201833106</v>
       </c>
       <c r="E2" t="n">
-        <v>41.42462648574184</v>
+        <v>44.67052959608354</v>
       </c>
       <c r="F2" t="n">
-        <v>37.234552605682</v>
+        <v>41.18284127568891</v>
       </c>
       <c r="G2" t="n">
-        <v>37.09737803300438</v>
+        <v>39.98401109197933</v>
       </c>
       <c r="H2" t="n">
-        <v>44.05961174057669</v>
+        <v>40.35116886127719</v>
       </c>
       <c r="I2" t="n">
-        <v>35.70534228953645</v>
+        <v>39.91080865471692</v>
       </c>
       <c r="J2" t="n">
-        <v>48.73437416941216</v>
+        <v>46.35415247698372</v>
       </c>
       <c r="K2" t="n">
-        <v>38.54934569135133</v>
+        <v>41.35672400476088</v>
       </c>
       <c r="L2" t="n">
-        <v>41.82462817766544</v>
+        <v>40.23443536241391</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.0108801300609</v>
+        <v>41.52538470085293</v>
       </c>
       <c r="C3" t="n">
-        <v>44.23618762552474</v>
+        <v>46.94111368462546</v>
       </c>
       <c r="D3" t="n">
-        <v>41.77582893959842</v>
+        <v>42.10392277483401</v>
       </c>
       <c r="E3" t="n">
-        <v>46.09720485732934</v>
+        <v>49.5030606578084</v>
       </c>
       <c r="F3" t="n">
-        <v>41.90713097726951</v>
+        <v>43.74599177162282</v>
       </c>
       <c r="G3" t="n">
-        <v>41.97888561598073</v>
+        <v>42.17374782710719</v>
       </c>
       <c r="H3" t="n">
-        <v>49.98802245249211</v>
+        <v>44.81468083487223</v>
       </c>
       <c r="I3" t="n">
-        <v>40.37848981689168</v>
+        <v>41.64631868249835</v>
       </c>
       <c r="J3" t="n">
-        <v>54.25469321077517</v>
+        <v>53.92227067878848</v>
       </c>
       <c r="K3" t="n">
-        <v>43.39923394076216</v>
+        <v>44.37538452665594</v>
       </c>
       <c r="L3" t="n">
-        <v>47.41606001949941</v>
+        <v>43.98261510676959</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.824555706130798</v>
+        <v>5.824555706130826</v>
       </c>
       <c r="C4" t="n">
-        <v>5.986415281912107</v>
+        <v>5.986415281912098</v>
       </c>
       <c r="D4" t="n">
-        <v>6.736728161861281</v>
+        <v>6.736728161861283</v>
       </c>
       <c r="E4" t="n">
-        <v>6.007545955334663</v>
+        <v>6.007545955334662</v>
       </c>
       <c r="F4" t="n">
-        <v>6.007545955334668</v>
+        <v>6.007545955334665</v>
       </c>
       <c r="G4" t="n">
-        <v>6.84194293524467</v>
+        <v>6.841942935244687</v>
       </c>
       <c r="H4" t="n">
-        <v>10.9789182573762</v>
+        <v>10.97891825737618</v>
       </c>
       <c r="I4" t="n">
-        <v>6.016353056575388</v>
+        <v>6.01635305657539</v>
       </c>
       <c r="J4" t="n">
-        <v>9.369824171885758</v>
+        <v>9.369824171885766</v>
       </c>
       <c r="K4" t="n">
-        <v>6.716537035361984</v>
+        <v>6.71653703536199</v>
       </c>
       <c r="L4" t="n">
-        <v>9.65111225515199</v>
+        <v>9.651112255151977</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.84226036526377</v>
+        <v>76.84226036526408</v>
       </c>
       <c r="C5" t="n">
-        <v>81.10134376455304</v>
+        <v>81.10134376455318</v>
       </c>
       <c r="D5" t="n">
-        <v>96.50762295332392</v>
+        <v>96.50762295332407</v>
       </c>
       <c r="E5" t="n">
-        <v>81.10134464462072</v>
+        <v>81.10134464462077</v>
       </c>
       <c r="F5" t="n">
-        <v>81.10134464462072</v>
+        <v>81.10134464462077</v>
       </c>
       <c r="G5" t="n">
-        <v>100.7106224461238</v>
+        <v>100.7106224461239</v>
       </c>
       <c r="H5" t="n">
-        <v>199.4353284154292</v>
+        <v>199.435328415429</v>
       </c>
       <c r="I5" t="n">
         <v>81.10111890448201</v>
       </c>
       <c r="J5" t="n">
-        <v>154.8784268808505</v>
+        <v>154.8784268808508</v>
       </c>
       <c r="K5" t="n">
-        <v>96.11204853501839</v>
+        <v>96.1120485350185</v>
       </c>
       <c r="L5" t="n">
-        <v>60.25458774974938</v>
+        <v>176.3165863365548</v>
       </c>
     </row>
     <row r="6">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133.5928877198341</v>
+        <v>133.5928877198342</v>
       </c>
       <c r="C6" t="n">
-        <v>133.761697702263</v>
+        <v>133.7616977022629</v>
       </c>
       <c r="D6" t="n">
-        <v>134.5195363662912</v>
+        <v>134.5195350239059</v>
       </c>
       <c r="E6" t="n">
         <v>121.0641146946522</v>
@@ -693,16 +693,16 @@
         <v>160.1892650335897</v>
       </c>
       <c r="H6" t="n">
-        <v>164.471265226727</v>
+        <v>164.4712652267268</v>
       </c>
       <c r="I6" t="n">
-        <v>133.7846850702788</v>
+        <v>159.3636751549204</v>
       </c>
       <c r="J6" t="n">
-        <v>143.683739884066</v>
+        <v>162.7873071981606</v>
       </c>
       <c r="K6" t="n">
-        <v>134.4984787744294</v>
+        <v>134.4984787744292</v>
       </c>
       <c r="L6" t="n">
         <v>137.4527097376681</v>
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.189842887971294</v>
+        <v>7.189842887971276</v>
       </c>
       <c r="C7" t="n">
         <v>7.381865098486912</v>
       </c>
       <c r="D7" t="n">
-        <v>8.102000284789735</v>
+        <v>8.102000284789732</v>
       </c>
       <c r="E7" t="n">
-        <v>7.382319333803898</v>
+        <v>7.382319333803894</v>
       </c>
       <c r="F7" t="n">
-        <v>7.382319333803898</v>
+        <v>7.382319333803897</v>
       </c>
       <c r="G7" t="n">
-        <v>8.207230117085134</v>
+        <v>8.207230117085132</v>
       </c>
       <c r="H7" t="n">
-        <v>12.34420543921666</v>
+        <v>12.34420543921664</v>
       </c>
       <c r="I7" t="n">
-        <v>7.381640238415844</v>
+        <v>7.381640238415845</v>
       </c>
       <c r="J7" t="n">
         <v>10.73511135372622</v>
       </c>
       <c r="K7" t="n">
-        <v>8.081824217202438</v>
+        <v>8.081824217202445</v>
       </c>
       <c r="L7" t="n">
-        <v>11.01639943699245</v>
+        <v>11.01639943699244</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.783123164024673</v>
+        <v>7.783123164024652</v>
       </c>
       <c r="C8" t="n">
-        <v>9.459807822466415</v>
+        <v>9.459807822491761</v>
       </c>
       <c r="D8" t="n">
-        <v>10.48693057024744</v>
+        <v>10.48693057024743</v>
       </c>
       <c r="E8" t="n">
-        <v>9.053897641691485</v>
+        <v>9.053897641691478</v>
       </c>
       <c r="F8" t="n">
         <v>8.022464040266849</v>
       </c>
       <c r="G8" t="n">
-        <v>10.28444237949462</v>
+        <v>10.2844423794946</v>
       </c>
       <c r="H8" t="n">
-        <v>14.42141770162665</v>
+        <v>14.42141770162662</v>
       </c>
       <c r="I8" t="n">
-        <v>9.458852500825317</v>
+        <v>9.458852500825326</v>
       </c>
       <c r="J8" t="n">
         <v>12.81261524917617</v>
       </c>
       <c r="K8" t="n">
-        <v>8.647539694942612</v>
+        <v>8.647539694942608</v>
       </c>
       <c r="L8" t="n">
-        <v>14.64370274154936</v>
+        <v>14.64370274154933</v>
       </c>
     </row>
     <row r="9">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.49242049144986</v>
+        <v>11.49242049144982</v>
       </c>
       <c r="C9" t="n">
-        <v>13.35615399483912</v>
+        <v>13.35615399483911</v>
       </c>
       <c r="D9" t="n">
-        <v>14.07630462975436</v>
+        <v>14.07630462975435</v>
       </c>
       <c r="E9" t="n">
-        <v>15.28527186001479</v>
+        <v>15.28527186001478</v>
       </c>
       <c r="F9" t="n">
         <v>13.35615267239145</v>
@@ -813,19 +813,19 @@
         <v>14.18151901343733</v>
       </c>
       <c r="H9" t="n">
-        <v>18.31849433556886</v>
+        <v>18.31849433556883</v>
       </c>
       <c r="I9" t="n">
         <v>13.35592913476805</v>
       </c>
       <c r="J9" t="n">
-        <v>16.70940025007843</v>
+        <v>16.70940025007842</v>
       </c>
       <c r="K9" t="n">
-        <v>13.08751718905331</v>
+        <v>11.95113009541437</v>
       </c>
       <c r="L9" t="n">
-        <v>16.99068833334466</v>
+        <v>16.99068833334463</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.38681955985925</v>
+        <v>38.82516479012548</v>
       </c>
       <c r="C2" t="n">
-        <v>34.11806238391606</v>
+        <v>41.96801060703181</v>
       </c>
       <c r="D2" t="n">
-        <v>31.92924727835528</v>
+        <v>39.01159572512179</v>
       </c>
       <c r="E2" t="n">
-        <v>35.92643291417328</v>
+        <v>43.47634830483077</v>
       </c>
       <c r="F2" t="n">
-        <v>31.89115563641193</v>
+        <v>40.11750409995546</v>
       </c>
       <c r="G2" t="n">
-        <v>31.54955609821791</v>
+        <v>38.99161333243863</v>
       </c>
       <c r="H2" t="n">
-        <v>31.00498812744911</v>
+        <v>38.96100627776218</v>
       </c>
       <c r="I2" t="n">
-        <v>30.46930664205257</v>
+        <v>38.93481661974662</v>
       </c>
       <c r="J2" t="n">
-        <v>42.41996105870039</v>
+        <v>45.00100235709159</v>
       </c>
       <c r="K2" t="n">
-        <v>31.22668510206057</v>
+        <v>39.98779555746675</v>
       </c>
       <c r="L2" t="n">
-        <v>31.12986278111052</v>
+        <v>38.96839604882285</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.93596837271097</v>
+        <v>38.52323501677817</v>
       </c>
       <c r="C3" t="n">
-        <v>37.97929012273315</v>
+        <v>44.3106695144361</v>
       </c>
       <c r="D3" t="n">
-        <v>36.01049406067265</v>
+        <v>39.84510954020712</v>
       </c>
       <c r="E3" t="n">
-        <v>39.7885422123154</v>
+        <v>46.79784209851467</v>
       </c>
       <c r="F3" t="n">
-        <v>35.75326493455403</v>
+        <v>41.25345651803036</v>
       </c>
       <c r="G3" t="n">
-        <v>35.57377055072362</v>
+        <v>39.70614651539605</v>
       </c>
       <c r="H3" t="n">
-        <v>34.94810158805911</v>
+        <v>39.50578285744215</v>
       </c>
       <c r="I3" t="n">
-        <v>34.33141619621505</v>
+        <v>39.3012458487898</v>
       </c>
       <c r="J3" t="n">
-        <v>47.0295620053402</v>
+        <v>50.75595538428271</v>
       </c>
       <c r="K3" t="n">
-        <v>35.00722704579658</v>
+        <v>40.88253054142606</v>
       </c>
       <c r="L3" t="n">
-        <v>35.09110183392133</v>
+        <v>39.55759550052311</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.244126713048688</v>
+        <v>1.244126713048698</v>
       </c>
       <c r="C4" t="n">
-        <v>2.438497048399755</v>
+        <v>2.438497048399757</v>
       </c>
       <c r="D4" t="n">
-        <v>3.349949886299086</v>
+        <v>3.349949886299079</v>
       </c>
       <c r="E4" t="n">
+        <v>2.452393127290688</v>
+      </c>
+      <c r="F4" t="n">
         <v>2.452393127290685</v>
       </c>
-      <c r="F4" t="n">
-        <v>2.452393127290689</v>
-      </c>
       <c r="G4" t="n">
-        <v>3.124672464251723</v>
+        <v>3.124672464251734</v>
       </c>
       <c r="H4" t="n">
-        <v>2.800711727963269</v>
+        <v>2.800711727963275</v>
       </c>
       <c r="I4" t="n">
         <v>2.485271998463304</v>
       </c>
       <c r="J4" t="n">
-        <v>5.440956630848363</v>
+        <v>5.440956630848355</v>
       </c>
       <c r="K4" t="n">
-        <v>2.159884797291026</v>
+        <v>2.159884797291032</v>
       </c>
       <c r="L4" t="n">
-        <v>2.874990299128426</v>
+        <v>2.87499029912843</v>
       </c>
     </row>
     <row r="5">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.744709436545521</v>
+        <v>3.744709436545508</v>
       </c>
       <c r="C5" t="n">
-        <v>23.28024493923708</v>
+        <v>23.28024493923709</v>
       </c>
       <c r="D5" t="n">
-        <v>36.48507500107404</v>
+        <v>36.485075001074</v>
       </c>
       <c r="E5" t="n">
         <v>23.28024640982802</v>
@@ -1046,22 +1046,22 @@
         <v>23.28024640982802</v>
       </c>
       <c r="G5" t="n">
-        <v>34.38616457735224</v>
+        <v>34.38616457735175</v>
       </c>
       <c r="H5" t="n">
-        <v>31.78464601607826</v>
+        <v>31.78464601607829</v>
       </c>
       <c r="I5" t="n">
         <v>23.28006772866162</v>
       </c>
       <c r="J5" t="n">
-        <v>77.92563444184381</v>
+        <v>77.92563444184395</v>
       </c>
       <c r="K5" t="n">
-        <v>17.53879721760877</v>
+        <v>17.53879721760876</v>
       </c>
       <c r="L5" t="n">
-        <v>35.20540133908856</v>
+        <v>35.20540133908863</v>
       </c>
     </row>
     <row r="6">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.3499926087727</v>
+        <v>112.4176223750569</v>
       </c>
       <c r="C6" t="n">
         <v>113.6396951956017</v>
       </c>
       <c r="D6" t="n">
-        <v>136.4869008777443</v>
+        <v>136.4869008777441</v>
       </c>
       <c r="E6" t="n">
-        <v>102.585239816188</v>
+        <v>102.5852398161879</v>
       </c>
       <c r="F6" t="n">
-        <v>113.6609196365085</v>
+        <v>113.6609196365086</v>
       </c>
       <c r="G6" t="n">
-        <v>114.29816812626</v>
+        <v>136.2305383599758</v>
       </c>
       <c r="H6" t="n">
         <v>136.0102972780772</v>
@@ -1095,10 +1095,10 @@
         <v>113.6587676604715</v>
       </c>
       <c r="J6" t="n">
-        <v>138.6122881372218</v>
+        <v>122.2998015728126</v>
       </c>
       <c r="K6" t="n">
-        <v>113.3144733210018</v>
+        <v>113.314473321002</v>
       </c>
       <c r="L6" t="n">
         <v>114.0574638905829</v>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.092544722623881</v>
+        <v>2.092544722623883</v>
       </c>
       <c r="C7" t="n">
         <v>3.333867218613948</v>
       </c>
       <c r="D7" t="n">
-        <v>4.198367112450859</v>
+        <v>4.198367112450857</v>
       </c>
       <c r="E7" t="n">
-        <v>3.326895985600877</v>
+        <v>3.326895985600878</v>
       </c>
       <c r="F7" t="n">
-        <v>3.326895985600877</v>
+        <v>3.326895985600878</v>
       </c>
       <c r="G7" t="n">
-        <v>3.973090473826915</v>
+        <v>3.973090473826928</v>
       </c>
       <c r="H7" t="n">
-        <v>3.649129737538465</v>
+        <v>3.649129737538474</v>
       </c>
       <c r="I7" t="n">
-        <v>3.333690008038496</v>
+        <v>3.333690008038501</v>
       </c>
       <c r="J7" t="n">
-        <v>6.289374640423553</v>
+        <v>6.289374640423555</v>
       </c>
       <c r="K7" t="n">
-        <v>3.008302806866219</v>
+        <v>3.008302806866213</v>
       </c>
       <c r="L7" t="n">
-        <v>3.723408308703622</v>
+        <v>3.72340830870362</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.325342867341408</v>
+        <v>2.325342867341404</v>
       </c>
       <c r="C8" t="n">
-        <v>4.370542635845529</v>
+        <v>4.370542635852704</v>
       </c>
       <c r="D8" t="n">
-        <v>5.409605312396469</v>
+        <v>5.409605312396461</v>
       </c>
       <c r="E8" t="n">
-        <v>4.149611396101175</v>
+        <v>4.149611396101174</v>
       </c>
       <c r="F8" t="n">
         <v>3.588196110208</v>
       </c>
       <c r="G8" t="n">
-        <v>5.016286591493663</v>
+        <v>5.016286591493665</v>
       </c>
       <c r="H8" t="n">
-        <v>4.692325855206846</v>
+        <v>4.692325855206859</v>
       </c>
       <c r="I8" t="n">
-        <v>4.376886125705242</v>
+        <v>4.376886125705241</v>
       </c>
       <c r="J8" t="n">
-        <v>7.332730023367908</v>
+        <v>7.33273002336789</v>
       </c>
       <c r="K8" t="n">
-        <v>3.226047393276881</v>
+        <v>3.226047393276886</v>
       </c>
       <c r="L8" t="n">
-        <v>5.613132872427248</v>
+        <v>5.613132872427233</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.777408708016183</v>
+        <v>3.77740870801619</v>
       </c>
       <c r="C9" t="n">
-        <v>5.77303522242436</v>
+        <v>5.773035222424358</v>
       </c>
       <c r="D9" t="n">
-        <v>6.637536661660226</v>
+        <v>6.637536661660221</v>
       </c>
       <c r="E9" t="n">
-        <v>6.64348778523858</v>
+        <v>6.643487785238574</v>
       </c>
       <c r="F9" t="n">
-        <v>5.773036341005484</v>
+        <v>5.773036341005483</v>
       </c>
       <c r="G9" t="n">
-        <v>6.412258477637334</v>
+        <v>6.412258477637332</v>
       </c>
       <c r="H9" t="n">
-        <v>6.088297741348883</v>
+        <v>6.08829774134888</v>
       </c>
       <c r="I9" t="n">
-        <v>5.77285801184891</v>
+        <v>5.772858011848908</v>
       </c>
       <c r="J9" t="n">
-        <v>8.728542644233967</v>
+        <v>8.728542644233952</v>
       </c>
       <c r="K9" t="n">
-        <v>5.01042442050864</v>
+        <v>5.010424420508627</v>
       </c>
       <c r="L9" t="n">
-        <v>6.162576312514037</v>
+        <v>6.162576312514026</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.33786235871408</v>
+        <v>41.64419315755702</v>
       </c>
       <c r="C2" t="n">
-        <v>32.29031044479255</v>
+        <v>40.81143021191213</v>
       </c>
       <c r="D2" t="n">
-        <v>35.79842461537221</v>
+        <v>41.77368766205468</v>
       </c>
       <c r="E2" t="n">
-        <v>34.02041293627796</v>
+        <v>40.94910171922232</v>
       </c>
       <c r="F2" t="n">
-        <v>34.02041293627796</v>
+        <v>40.9491017409734</v>
       </c>
       <c r="G2" t="n">
-        <v>35.69229028829412</v>
+        <v>41.76810202322032</v>
       </c>
       <c r="H2" t="n">
-        <v>38.37021054213558</v>
+        <v>41.90823715439376</v>
       </c>
       <c r="I2" t="n">
-        <v>34.95683857904696</v>
+        <v>41.72945834880769</v>
       </c>
       <c r="J2" t="n">
-        <v>40.45413657621465</v>
+        <v>43.17987863514766</v>
       </c>
       <c r="K2" t="n">
-        <v>36.24888377846293</v>
+        <v>42.41633430544261</v>
       </c>
       <c r="L2" t="n">
-        <v>34.71861746945855</v>
+        <v>41.71491044936107</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.48732923935518</v>
+        <v>42.58581490763001</v>
       </c>
       <c r="C3" t="n">
-        <v>36.43043268145245</v>
+        <v>41.19870948100025</v>
       </c>
       <c r="D3" t="n">
-        <v>40.31748553844798</v>
+        <v>43.50626147366209</v>
       </c>
       <c r="E3" t="n">
-        <v>38.41323768631706</v>
+        <v>41.90395766845104</v>
       </c>
       <c r="F3" t="n">
-        <v>38.41323768631706</v>
+        <v>41.90395769020211</v>
       </c>
       <c r="G3" t="n">
-        <v>40.19540907664857</v>
+        <v>43.46944097604786</v>
       </c>
       <c r="H3" t="n">
-        <v>43.27668260828552</v>
+        <v>44.48878905033553</v>
       </c>
       <c r="I3" t="n">
-        <v>39.35049627142519</v>
+        <v>43.19212544582736</v>
       </c>
       <c r="J3" t="n">
-        <v>45.44883425669848</v>
+        <v>46.7476436341604</v>
       </c>
       <c r="K3" t="n">
-        <v>40.71637609349013</v>
+        <v>44.46860465879421</v>
       </c>
       <c r="L3" t="n">
-        <v>39.07560081205218</v>
+        <v>43.11235351739845</v>
       </c>
     </row>
     <row r="4">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.193974122904979</v>
+        <v>3.193974122904982</v>
       </c>
       <c r="C4" t="n">
-        <v>3.089111490883501</v>
+        <v>3.089111490883496</v>
       </c>
       <c r="D4" t="n">
         <v>4.656674121621076</v>
@@ -1402,10 +1402,10 @@
         <v>4.138750767931356</v>
       </c>
       <c r="G4" t="n">
-        <v>4.592226568336041</v>
+        <v>4.592226568336049</v>
       </c>
       <c r="H4" t="n">
-        <v>6.184963277018488</v>
+        <v>6.184963277018491</v>
       </c>
       <c r="I4" t="n">
         <v>4.147822532044172</v>
@@ -1414,10 +1414,10 @@
         <v>6.539047224464577</v>
       </c>
       <c r="K4" t="n">
-        <v>4.45258694957283</v>
+        <v>4.452586949572826</v>
       </c>
       <c r="L4" t="n">
-        <v>4.015242539908722</v>
+        <v>4.015242539908719</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.77286854937943</v>
+        <v>33.77286854937946</v>
       </c>
       <c r="C5" t="n">
-        <v>32.99736338349761</v>
+        <v>32.99736338349763</v>
       </c>
       <c r="D5" t="n">
-        <v>58.9459433637077</v>
+        <v>58.94594336370767</v>
       </c>
       <c r="E5" t="n">
-        <v>50.47334724204194</v>
+        <v>50.47334724204188</v>
       </c>
       <c r="F5" t="n">
-        <v>50.47334724204194</v>
+        <v>50.47334724204188</v>
       </c>
       <c r="G5" t="n">
-        <v>59.43569780760392</v>
+        <v>59.43569780760382</v>
       </c>
       <c r="H5" t="n">
-        <v>97.04319100712836</v>
+        <v>97.04319100712834</v>
       </c>
       <c r="I5" t="n">
-        <v>50.47321358375645</v>
+        <v>50.47321358375636</v>
       </c>
       <c r="J5" t="n">
-        <v>97.22458350337433</v>
+        <v>97.22458350337422</v>
       </c>
       <c r="K5" t="n">
-        <v>55.51041190293629</v>
+        <v>55.51041190293618</v>
       </c>
       <c r="L5" t="n">
-        <v>54.32035584851553</v>
+        <v>54.32035584851548</v>
       </c>
     </row>
     <row r="6">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120.6419424506911</v>
+        <v>143.9938059248152</v>
       </c>
       <c r="C6" t="n">
-        <v>120.555389313356</v>
+        <v>120.5553893133561</v>
       </c>
       <c r="D6" t="n">
-        <v>122.1159597119773</v>
+        <v>122.1159608933655</v>
       </c>
       <c r="E6" t="n">
         <v>109.9022324936318</v>
@@ -1482,19 +1482,19 @@
         <v>121.6002885126127</v>
       </c>
       <c r="G6" t="n">
-        <v>145.3920583702463</v>
+        <v>122.0401948961221</v>
       </c>
       <c r="H6" t="n">
-        <v>147.1582402182158</v>
+        <v>147.1582402182156</v>
       </c>
       <c r="I6" t="n">
-        <v>144.9476543339545</v>
+        <v>121.5957908598303</v>
       </c>
       <c r="J6" t="n">
         <v>147.4155634226884</v>
       </c>
       <c r="K6" t="n">
-        <v>121.9041447365704</v>
+        <v>121.9041447365706</v>
       </c>
       <c r="L6" t="n">
         <v>121.4682543273678</v>
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.320379620410344</v>
+        <v>4.320379620410352</v>
       </c>
       <c r="C7" t="n">
-        <v>4.284890140975702</v>
+        <v>4.284890140975693</v>
       </c>
       <c r="D7" t="n">
-        <v>5.783078462188334</v>
+        <v>5.783078462188338</v>
       </c>
       <c r="E7" t="n">
-        <v>5.274689096383836</v>
+        <v>5.274689096383833</v>
       </c>
       <c r="F7" t="n">
-        <v>5.274689096383836</v>
+        <v>5.274689096383833</v>
       </c>
       <c r="G7" t="n">
-        <v>5.718632065841412</v>
+        <v>5.7186320658414</v>
       </c>
       <c r="H7" t="n">
-        <v>7.31136877452386</v>
+        <v>7.311368774523861</v>
       </c>
       <c r="I7" t="n">
-        <v>5.274228029549539</v>
+        <v>5.27422802954954</v>
       </c>
       <c r="J7" t="n">
-        <v>7.665452721969945</v>
+        <v>7.665452721969943</v>
       </c>
       <c r="K7" t="n">
-        <v>5.578992447078198</v>
+        <v>5.578992447078197</v>
       </c>
       <c r="L7" t="n">
-        <v>5.141648037414088</v>
+        <v>5.141648037414084</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.772133968423932</v>
+        <v>4.772133968423943</v>
       </c>
       <c r="C8" t="n">
-        <v>5.94100315868056</v>
+        <v>5.941003158680562</v>
       </c>
       <c r="D8" t="n">
-        <v>7.688274146045794</v>
+        <v>7.6882741460458</v>
       </c>
       <c r="E8" t="n">
         <v>6.601194883396872</v>
       </c>
       <c r="F8" t="n">
-        <v>5.764471284214401</v>
+        <v>5.764471284214405</v>
       </c>
       <c r="G8" t="n">
-        <v>7.37420662909417</v>
+        <v>7.37420662909419</v>
       </c>
       <c r="H8" t="n">
-        <v>8.966943337781517</v>
+        <v>8.966943337781515</v>
       </c>
       <c r="I8" t="n">
-        <v>6.92980259280231</v>
+        <v>6.929802592802313</v>
       </c>
       <c r="J8" t="n">
-        <v>9.321263868518756</v>
+        <v>9.321263868518752</v>
       </c>
       <c r="K8" t="n">
-        <v>6.008385216716838</v>
+        <v>6.008385216716846</v>
       </c>
       <c r="L8" t="n">
-        <v>8.054713475558803</v>
+        <v>8.054713475558817</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.934511713944653</v>
+        <v>6.934511713944657</v>
       </c>
       <c r="C9" t="n">
-        <v>8.021004993924871</v>
+        <v>8.021004993924862</v>
       </c>
       <c r="D9" t="n">
-        <v>9.519195286788673</v>
+        <v>9.519195286788678</v>
       </c>
       <c r="E9" t="n">
-        <v>10.3052205465062</v>
+        <v>10.30522054650621</v>
       </c>
       <c r="F9" t="n">
         <v>9.010475704585122</v>
       </c>
       <c r="G9" t="n">
-        <v>9.454746918790573</v>
+        <v>9.454746918790576</v>
       </c>
       <c r="H9" t="n">
         <v>11.04748362747302</v>
       </c>
       <c r="I9" t="n">
-        <v>9.010342882498708</v>
+        <v>9.01034288249871</v>
       </c>
       <c r="J9" t="n">
         <v>11.40156757491911</v>
       </c>
       <c r="K9" t="n">
-        <v>8.665026425521239</v>
+        <v>8.665026425521237</v>
       </c>
       <c r="L9" t="n">
-        <v>8.87776289036325</v>
+        <v>8.877762890363259</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.82471495433581</v>
+        <v>41.37888975282154</v>
       </c>
       <c r="C2" t="n">
-        <v>31.25911544530609</v>
+        <v>40.56076130789975</v>
       </c>
       <c r="D2" t="n">
-        <v>34.41770038083049</v>
+        <v>41.5153534257341</v>
       </c>
       <c r="E2" t="n">
-        <v>31.59442393954866</v>
+        <v>40.58282179528175</v>
       </c>
       <c r="F2" t="n">
-        <v>31.59442393954866</v>
+        <v>40.58282054736654</v>
       </c>
       <c r="G2" t="n">
-        <v>33.83149713253767</v>
+        <v>41.48450271306984</v>
       </c>
       <c r="H2" t="n">
-        <v>34.83780031121859</v>
+        <v>41.53623126787917</v>
       </c>
       <c r="I2" t="n">
-        <v>32.59886053464709</v>
+        <v>41.41968620515169</v>
       </c>
       <c r="J2" t="n">
-        <v>38.18477220201761</v>
+        <v>42.80263194231093</v>
       </c>
       <c r="K2" t="n">
-        <v>33.49957843840523</v>
+        <v>42.01561564008128</v>
       </c>
       <c r="L2" t="n">
-        <v>32.55724739298486</v>
+        <v>41.41562786092037</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.74192000914353</v>
+        <v>41.9165715392181</v>
       </c>
       <c r="C3" t="n">
-        <v>35.24171893031056</v>
+        <v>40.69616933004057</v>
       </c>
       <c r="D3" t="n">
-        <v>38.72439038492536</v>
+        <v>42.88744779644043</v>
       </c>
       <c r="E3" t="n">
-        <v>35.62806733891924</v>
+        <v>40.82511241515169</v>
       </c>
       <c r="F3" t="n">
-        <v>35.62806733891924</v>
+        <v>40.82511116723645</v>
       </c>
       <c r="G3" t="n">
-        <v>38.05013521775151</v>
+        <v>42.66973561940192</v>
       </c>
       <c r="H3" t="n">
-        <v>39.20859493312259</v>
+        <v>43.05493256316469</v>
       </c>
       <c r="I3" t="n">
-        <v>36.63284928958258</v>
+        <v>42.20655146173947</v>
       </c>
       <c r="J3" t="n">
-        <v>42.8475166839096</v>
+        <v>45.70131636440535</v>
       </c>
       <c r="K3" t="n">
-        <v>37.56268286984284</v>
+        <v>43.2464692718999</v>
       </c>
       <c r="L3" t="n">
-        <v>36.5846012205489</v>
+        <v>42.19526784877328</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.126787786971154</v>
+        <v>2.126787786971164</v>
       </c>
       <c r="C4" t="n">
-        <v>2.331465242233454</v>
+        <v>2.331465242233455</v>
       </c>
       <c r="D4" t="n">
-        <v>3.668207748909376</v>
+        <v>3.668207748909381</v>
       </c>
       <c r="E4" t="n">
+        <v>2.560584729409121</v>
+      </c>
+      <c r="F4" t="n">
         <v>2.56058472940912</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.560584729409121</v>
       </c>
       <c r="G4" t="n">
         <v>3.318217563211358</v>
       </c>
       <c r="H4" t="n">
-        <v>3.917785442315345</v>
+        <v>3.917785442315348</v>
       </c>
       <c r="I4" t="n">
-        <v>2.577211360711122</v>
+        <v>2.577211360711126</v>
       </c>
       <c r="J4" t="n">
-        <v>5.077323763837841</v>
+        <v>5.077323763837854</v>
       </c>
       <c r="K4" t="n">
-        <v>2.704197034705385</v>
+        <v>2.70419703470539</v>
       </c>
       <c r="L4" t="n">
-        <v>2.562704122317582</v>
+        <v>2.562704122317586</v>
       </c>
     </row>
     <row r="5">
@@ -1823,34 +1823,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.70608169825512</v>
+        <v>17.70608169825508</v>
       </c>
       <c r="C5" t="n">
-        <v>22.17461559279449</v>
+        <v>22.17461559279452</v>
       </c>
       <c r="D5" t="n">
-        <v>43.37676541258677</v>
+        <v>43.37676541258674</v>
       </c>
       <c r="E5" t="n">
-        <v>25.23134145918818</v>
+        <v>25.23134145918819</v>
       </c>
       <c r="F5" t="n">
-        <v>25.23134145918818</v>
+        <v>25.23134145918819</v>
       </c>
       <c r="G5" t="n">
-        <v>38.49240824964624</v>
+        <v>38.4924082496464</v>
       </c>
       <c r="H5" t="n">
-        <v>53.49472657616963</v>
+        <v>53.4947265761697</v>
       </c>
       <c r="I5" t="n">
-        <v>25.23114151761408</v>
+        <v>25.23114151761409</v>
       </c>
       <c r="J5" t="n">
-        <v>70.65820134778306</v>
+        <v>70.65820134778301</v>
       </c>
       <c r="K5" t="n">
-        <v>27.09409683673652</v>
+        <v>27.09409683673648</v>
       </c>
       <c r="L5" t="n">
         <v>28.06728019748337</v>
@@ -1866,31 +1866,31 @@
         <v>135.3068493342829</v>
       </c>
       <c r="C6" t="n">
-        <v>113.5266879743281</v>
+        <v>113.526687974328</v>
       </c>
       <c r="D6" t="n">
         <v>136.8849891250599</v>
       </c>
       <c r="E6" t="n">
-        <v>102.6676886842215</v>
+        <v>102.6676886842213</v>
       </c>
       <c r="F6" t="n">
-        <v>113.7479417662454</v>
+        <v>113.7479417662453</v>
       </c>
       <c r="G6" t="n">
-        <v>114.4883335772332</v>
+        <v>136.4982791105231</v>
       </c>
       <c r="H6" t="n">
         <v>137.2365538369757</v>
       </c>
       <c r="I6" t="n">
-        <v>113.747327374733</v>
+        <v>113.7473273747328</v>
       </c>
       <c r="J6" t="n">
-        <v>121.9284216303429</v>
+        <v>121.9284216303427</v>
       </c>
       <c r="K6" t="n">
-        <v>113.8628331084324</v>
+        <v>113.8628331084323</v>
       </c>
       <c r="L6" t="n">
         <v>113.7358931191763</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.082439752560037</v>
+        <v>3.082439752560047</v>
       </c>
       <c r="C7" t="n">
-        <v>3.342914000526053</v>
+        <v>3.342914000526056</v>
       </c>
       <c r="D7" t="n">
-        <v>4.623859089101039</v>
+        <v>4.62385908910105</v>
       </c>
       <c r="E7" t="n">
         <v>3.531934971393492</v>
@@ -1918,22 +1918,22 @@
         <v>3.531934971393492</v>
       </c>
       <c r="G7" t="n">
-        <v>4.273869528800243</v>
+        <v>4.273869528800248</v>
       </c>
       <c r="H7" t="n">
-        <v>4.873437407904236</v>
+        <v>4.873437407904235</v>
       </c>
       <c r="I7" t="n">
-        <v>3.532863326300005</v>
+        <v>3.532863326300007</v>
       </c>
       <c r="J7" t="n">
-        <v>6.032975729426713</v>
+        <v>6.032975729426734</v>
       </c>
       <c r="K7" t="n">
-        <v>3.659849000294265</v>
+        <v>3.65984900029427</v>
       </c>
       <c r="L7" t="n">
-        <v>3.518356087906473</v>
+        <v>3.518356087906469</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.426215568189624</v>
+        <v>3.426215568189613</v>
       </c>
       <c r="C8" t="n">
-        <v>4.672689852077348</v>
+        <v>4.672689852059539</v>
       </c>
       <c r="D8" t="n">
-        <v>6.159170208530193</v>
+        <v>6.159170208530192</v>
       </c>
       <c r="E8" t="n">
-        <v>4.593037237012924</v>
+        <v>4.5930372370129</v>
       </c>
       <c r="F8" t="n">
-        <v>3.907449436511164</v>
+        <v>3.907449436511162</v>
       </c>
       <c r="G8" t="n">
-        <v>5.604540817557094</v>
+        <v>5.604540817557107</v>
       </c>
       <c r="H8" t="n">
-        <v>6.204108696664555</v>
+        <v>6.204108696664598</v>
       </c>
       <c r="I8" t="n">
-        <v>4.863534615056856</v>
+        <v>4.863534615056866</v>
       </c>
       <c r="J8" t="n">
-        <v>7.363840969879587</v>
+        <v>7.363840969879581</v>
       </c>
       <c r="K8" t="n">
-        <v>3.98529272597722</v>
+        <v>3.985292725977244</v>
       </c>
       <c r="L8" t="n">
-        <v>5.879922219771705</v>
+        <v>5.879922219771718</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.899306418040772</v>
+        <v>4.899306418040782</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9967204544765</v>
+        <v>5.996720454476503</v>
       </c>
       <c r="D9" t="n">
-        <v>7.277666898157099</v>
+        <v>7.277666898157119</v>
       </c>
       <c r="E9" t="n">
-        <v>7.152680484131343</v>
+        <v>7.152680484131347</v>
       </c>
       <c r="F9" t="n">
-        <v>6.186869188034013</v>
+        <v>6.186869188034015</v>
       </c>
       <c r="G9" t="n">
-        <v>6.927675982750686</v>
+        <v>6.927675982750695</v>
       </c>
       <c r="H9" t="n">
-        <v>7.527243861854683</v>
+        <v>7.527243861854688</v>
       </c>
       <c r="I9" t="n">
-        <v>6.186669780250453</v>
+        <v>6.186669780250456</v>
       </c>
       <c r="J9" t="n">
-        <v>8.686782183377154</v>
+        <v>8.686782183377192</v>
       </c>
       <c r="K9" t="n">
-        <v>5.828729560801685</v>
+        <v>5.82872956080169</v>
       </c>
       <c r="L9" t="n">
-        <v>6.172162541856903</v>
+        <v>6.17216254185693</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.85630884929035</v>
+        <v>41.2460699385739</v>
       </c>
       <c r="C2" t="n">
-        <v>30.40468648191137</v>
+        <v>40.38836854980381</v>
       </c>
       <c r="D2" t="n">
-        <v>33.43436455504662</v>
+        <v>41.3817478899368</v>
       </c>
       <c r="E2" t="n">
-        <v>29.91048779226292</v>
+        <v>40.36141218606083</v>
       </c>
       <c r="F2" t="n">
-        <v>29.91048779226292</v>
+        <v>40.3614097330695</v>
       </c>
       <c r="G2" t="n">
-        <v>32.56485951590103</v>
+        <v>41.33598756670268</v>
       </c>
       <c r="H2" t="n">
-        <v>32.94472455568748</v>
+        <v>41.35477654470904</v>
       </c>
       <c r="I2" t="n">
-        <v>30.98034139681819</v>
+        <v>41.25264667647166</v>
       </c>
       <c r="J2" t="n">
-        <v>36.36568617290227</v>
+        <v>42.51726525827617</v>
       </c>
       <c r="K2" t="n">
-        <v>31.89946551647058</v>
+        <v>41.83031544108881</v>
       </c>
       <c r="L2" t="n">
-        <v>31.25793754457698</v>
+        <v>41.26562953415561</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.61698139133671</v>
+        <v>41.52820581922867</v>
       </c>
       <c r="C3" t="n">
-        <v>34.25691512239581</v>
+        <v>40.29191057797387</v>
       </c>
       <c r="D3" t="n">
-        <v>37.58227949558692</v>
+        <v>42.49401485975861</v>
       </c>
       <c r="E3" t="n">
-        <v>33.6899311937761</v>
+        <v>40.10352317913296</v>
       </c>
       <c r="F3" t="n">
-        <v>33.68993119377611</v>
+        <v>40.10352072614158</v>
       </c>
       <c r="G3" t="n">
-        <v>36.58216858314339</v>
+        <v>42.16944366435347</v>
       </c>
       <c r="H3" t="n">
-        <v>37.02000003049576</v>
+        <v>42.31610221270574</v>
       </c>
       <c r="I3" t="n">
-        <v>34.75960616662142</v>
+        <v>41.57470554332495</v>
       </c>
       <c r="J3" t="n">
-        <v>40.76488183952672</v>
+        <v>44.85493333314216</v>
       </c>
       <c r="K3" t="n">
-        <v>35.71485591254971</v>
+        <v>42.59709166806486</v>
       </c>
       <c r="L3" t="n">
-        <v>35.07904275529942</v>
+        <v>41.68003431162788</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.404396318169567</v>
+        <v>1.404396318169562</v>
       </c>
       <c r="C4" t="n">
-        <v>1.727283214050173</v>
+        <v>1.727283214050158</v>
       </c>
       <c r="D4" t="n">
-        <v>2.93694119375464</v>
+        <v>2.936941193754655</v>
       </c>
       <c r="E4" t="n">
-        <v>1.441289755780106</v>
+        <v>1.441289755780093</v>
       </c>
       <c r="F4" t="n">
-        <v>1.441289755780106</v>
+        <v>1.441289755780094</v>
       </c>
       <c r="G4" t="n">
-        <v>2.418423502985706</v>
+        <v>2.418423502985684</v>
       </c>
       <c r="H4" t="n">
-        <v>2.645853157865113</v>
+        <v>2.645853157865109</v>
       </c>
       <c r="I4" t="n">
-        <v>1.467475690016825</v>
+        <v>1.467475690016822</v>
       </c>
       <c r="J4" t="n">
-        <v>3.931406135070555</v>
+        <v>3.931406135070428</v>
       </c>
       <c r="K4" t="n">
-        <v>1.620946900252224</v>
+        <v>1.620946900252223</v>
       </c>
       <c r="L4" t="n">
-        <v>1.643553409361676</v>
+        <v>1.643553409361677</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.069407099502744</v>
+        <v>8.069407099502662</v>
       </c>
       <c r="C5" t="n">
-        <v>14.36922459481793</v>
+        <v>14.36922459481774</v>
       </c>
       <c r="D5" t="n">
-        <v>33.86322960671779</v>
+        <v>33.86322960671388</v>
       </c>
       <c r="E5" t="n">
-        <v>9.144951426994531</v>
+        <v>9.144951426994464</v>
       </c>
       <c r="F5" t="n">
-        <v>9.144951426994531</v>
+        <v>9.144951426994464</v>
       </c>
       <c r="G5" t="n">
-        <v>25.76776711265568</v>
+        <v>25.76776711265529</v>
       </c>
       <c r="H5" t="n">
-        <v>32.4526373391673</v>
+        <v>32.45263733916728</v>
       </c>
       <c r="I5" t="n">
-        <v>9.14470459358574</v>
+        <v>9.144704593585594</v>
       </c>
       <c r="J5" t="n">
-        <v>53.27266517306111</v>
+        <v>53.27266517306207</v>
       </c>
       <c r="K5" t="n">
-        <v>11.53668788540253</v>
+        <v>11.53668788540248</v>
       </c>
       <c r="L5" t="n">
-        <v>13.50678699381562</v>
+        <v>13.50678699381556</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.5132876934121</v>
+        <v>112.5132876934122</v>
       </c>
       <c r="C6" t="n">
         <v>112.8577487748116</v>
       </c>
       <c r="D6" t="n">
-        <v>114.0726434710478</v>
+        <v>114.0726415891649</v>
       </c>
       <c r="E6" t="n">
-        <v>101.494491486927</v>
+        <v>101.4944914869267</v>
       </c>
       <c r="F6" t="n">
-        <v>112.573968710624</v>
+        <v>112.5739687106238</v>
       </c>
       <c r="G6" t="n">
-        <v>135.4549969249884</v>
+        <v>135.4549969249881</v>
       </c>
       <c r="H6" t="n">
         <v>135.7956452785585</v>
       </c>
       <c r="I6" t="n">
-        <v>134.5040491120193</v>
+        <v>134.5040491120194</v>
       </c>
       <c r="J6" t="n">
-        <v>137.0269085587982</v>
+        <v>137.0269085587977</v>
       </c>
       <c r="K6" t="n">
-        <v>112.7122517051724</v>
+        <v>112.7122517051722</v>
       </c>
       <c r="L6" t="n">
-        <v>112.7549947558275</v>
+        <v>112.7549947558273</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.277613182307953</v>
+        <v>2.277613182307954</v>
       </c>
       <c r="C7" t="n">
-        <v>2.641491866728521</v>
+        <v>2.641491866728491</v>
       </c>
       <c r="D7" t="n">
-        <v>3.810156586586461</v>
+        <v>3.810156586586329</v>
       </c>
       <c r="E7" t="n">
-        <v>2.337574103390443</v>
+        <v>2.337574103390425</v>
       </c>
       <c r="F7" t="n">
-        <v>2.337574103390443</v>
+        <v>2.337574103390425</v>
       </c>
       <c r="G7" t="n">
-        <v>3.291640367124096</v>
+        <v>3.291640367124078</v>
       </c>
       <c r="H7" t="n">
-        <v>3.519070022003509</v>
+        <v>3.519070022003506</v>
       </c>
       <c r="I7" t="n">
-        <v>2.340692554155215</v>
+        <v>2.340692554155217</v>
       </c>
       <c r="J7" t="n">
-        <v>4.804622999208974</v>
+        <v>4.804622999208824</v>
       </c>
       <c r="K7" t="n">
-        <v>2.494163764390629</v>
+        <v>2.494163764390617</v>
       </c>
       <c r="L7" t="n">
-        <v>2.516770273500075</v>
+        <v>2.516770273500069</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.554987816636201</v>
+        <v>2.554987816636188</v>
       </c>
       <c r="C8" t="n">
-        <v>3.782485707266658</v>
+        <v>3.782485707282038</v>
       </c>
       <c r="D8" t="n">
-        <v>5.133918452578255</v>
+        <v>5.133918452578223</v>
       </c>
       <c r="E8" t="n">
-        <v>3.245238403921559</v>
+        <v>3.245238403921556</v>
       </c>
       <c r="F8" t="n">
-        <v>2.643779605645735</v>
+        <v>2.643779605645741</v>
       </c>
       <c r="G8" t="n">
-        <v>4.435690045623563</v>
+        <v>4.435690045623581</v>
       </c>
       <c r="H8" t="n">
-        <v>4.663119700504792</v>
+        <v>4.663119700504786</v>
       </c>
       <c r="I8" t="n">
-        <v>3.484742232654742</v>
+        <v>3.484742232654729</v>
       </c>
       <c r="J8" t="n">
-        <v>5.948843002940939</v>
+        <v>5.948843002940871</v>
       </c>
       <c r="K8" t="n">
-        <v>2.755439464934914</v>
+        <v>2.755439464934907</v>
       </c>
       <c r="L8" t="n">
-        <v>4.566134504668473</v>
+        <v>4.566134504668451</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.670339827454609</v>
+        <v>3.670339827454671</v>
       </c>
       <c r="C9" t="n">
-        <v>4.719897558429595</v>
+        <v>4.719897558429659</v>
       </c>
       <c r="D9" t="n">
-        <v>5.888564359812595</v>
+        <v>5.88856435981262</v>
       </c>
       <c r="E9" t="n">
-        <v>5.210604169991201</v>
+        <v>5.2106041699912</v>
       </c>
       <c r="F9" t="n">
         <v>4.419344645762736</v>
       </c>
       <c r="G9" t="n">
-        <v>5.370046058825253</v>
+        <v>5.37004605882525</v>
       </c>
       <c r="H9" t="n">
-        <v>5.597475713704694</v>
+        <v>5.597475713704679</v>
       </c>
       <c r="I9" t="n">
-        <v>4.419098245856431</v>
+        <v>4.419098245856385</v>
       </c>
       <c r="J9" t="n">
-        <v>6.88302869091001</v>
+        <v>6.883028690909995</v>
       </c>
       <c r="K9" t="n">
-        <v>3.709176985047329</v>
+        <v>4.159166206290248</v>
       </c>
       <c r="L9" t="n">
-        <v>4.595175965201289</v>
+        <v>4.59517596520124</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.65675132235897</v>
+        <v>41.23730920896681</v>
       </c>
       <c r="C2" t="n">
-        <v>29.80707733842585</v>
+        <v>40.41349646573113</v>
       </c>
       <c r="D2" t="n">
-        <v>33.77849801175402</v>
+        <v>41.3489725231013</v>
       </c>
       <c r="E2" t="n">
-        <v>32.28305035572777</v>
+        <v>40.59233136895633</v>
       </c>
       <c r="F2" t="n">
-        <v>32.28305035572777</v>
+        <v>40.59233082113058</v>
       </c>
       <c r="G2" t="n">
-        <v>33.9460650958509</v>
+        <v>41.35779124592228</v>
       </c>
       <c r="H2" t="n">
-        <v>37.21919806430213</v>
+        <v>41.53004316305198</v>
       </c>
       <c r="I2" t="n">
-        <v>33.15142768440853</v>
+        <v>41.31603155521825</v>
       </c>
       <c r="J2" t="n">
-        <v>39.66801710678979</v>
+        <v>42.89533167303797</v>
       </c>
       <c r="K2" t="n">
-        <v>34.68516948649444</v>
+        <v>42.03313083330244</v>
       </c>
       <c r="L2" t="n">
-        <v>33.3381405201532</v>
+        <v>41.32441588522249</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.55948783497583</v>
+        <v>41.74236337287607</v>
       </c>
       <c r="C3" t="n">
-        <v>33.57027490805155</v>
+        <v>40.11973815815449</v>
       </c>
       <c r="D3" t="n">
-        <v>37.99993604628261</v>
+        <v>42.53665444395484</v>
       </c>
       <c r="E3" t="n">
-        <v>36.4104706129861</v>
+        <v>41.10797653738754</v>
       </c>
       <c r="F3" t="n">
-        <v>36.4104706129861</v>
+        <v>41.10797598956178</v>
       </c>
       <c r="G3" t="n">
-        <v>38.19267290441097</v>
+        <v>42.60158921893041</v>
       </c>
       <c r="H3" t="n">
-        <v>41.95850741697619</v>
+        <v>43.84335823003386</v>
       </c>
       <c r="I3" t="n">
-        <v>37.27943544912267</v>
+        <v>42.30262006083346</v>
       </c>
       <c r="J3" t="n">
-        <v>44.53592542851612</v>
+        <v>46.33627464307374</v>
       </c>
       <c r="K3" t="n">
-        <v>38.92019370601603</v>
+        <v>43.69231786279175</v>
       </c>
       <c r="L3" t="n">
-        <v>37.49351374162665</v>
+        <v>42.37964775759337</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.165909878374308</v>
+        <v>2.16590987837429</v>
       </c>
       <c r="C4" t="n">
-        <v>1.536407182503533</v>
+        <v>1.536407182503502</v>
       </c>
       <c r="D4" t="n">
-        <v>3.427198379185921</v>
+        <v>3.42719837918571</v>
       </c>
       <c r="E4" t="n">
-        <v>3.031107598009141</v>
+        <v>3.031107598009075</v>
       </c>
       <c r="F4" t="n">
-        <v>3.031107598009141</v>
+        <v>3.031107598009075</v>
       </c>
       <c r="G4" t="n">
-        <v>3.525491275020684</v>
+        <v>3.525491275020541</v>
       </c>
       <c r="H4" t="n">
-        <v>5.471875088448241</v>
+        <v>5.471875088448229</v>
       </c>
       <c r="I4" t="n">
-        <v>3.046089780765902</v>
+        <v>3.046089780765816</v>
       </c>
       <c r="J4" t="n">
-        <v>5.985659771109673</v>
+        <v>5.985659771109654</v>
       </c>
       <c r="K4" t="n">
-        <v>3.480966867013071</v>
+        <v>3.480966867013052</v>
       </c>
       <c r="L4" t="n">
-        <v>3.165742403779607</v>
+        <v>3.165742403779588</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.90088610747031</v>
+        <v>17.90088610746994</v>
       </c>
       <c r="C5" t="n">
-        <v>7.718577332692874</v>
+        <v>7.718577332692728</v>
       </c>
       <c r="D5" t="n">
-        <v>39.92968146768349</v>
+        <v>39.92968146768204</v>
       </c>
       <c r="E5" t="n">
-        <v>33.57738121416683</v>
+        <v>33.57738121416598</v>
       </c>
       <c r="F5" t="n">
-        <v>33.57738121416683</v>
+        <v>33.57738121416598</v>
       </c>
       <c r="G5" t="n">
-        <v>42.87443192398838</v>
+        <v>42.87443192398785</v>
       </c>
       <c r="H5" t="n">
-        <v>86.04925037617265</v>
+        <v>86.04925037617257</v>
       </c>
       <c r="I5" t="n">
-        <v>33.5772403340447</v>
+        <v>33.57724033404389</v>
       </c>
       <c r="J5" t="n">
-        <v>89.96306698312665</v>
+        <v>89.96306698312682</v>
       </c>
       <c r="K5" t="n">
-        <v>41.05038885317892</v>
+        <v>41.05038885317887</v>
       </c>
       <c r="L5" t="n">
-        <v>40.31680718178612</v>
+        <v>40.316807181786</v>
       </c>
     </row>
     <row r="6">
@@ -2658,34 +2658,34 @@
         <v>119.5458353698725</v>
       </c>
       <c r="C6" t="n">
-        <v>118.9272814870456</v>
+        <v>118.9272814870454</v>
       </c>
       <c r="D6" t="n">
-        <v>120.8127971523029</v>
+        <v>120.8127953798546</v>
       </c>
       <c r="E6" t="n">
-        <v>108.7337841409257</v>
+        <v>108.7337841409256</v>
       </c>
       <c r="F6" t="n">
-        <v>120.4297301733841</v>
+        <v>120.4297301733839</v>
       </c>
       <c r="G6" t="n">
-        <v>120.9054167665193</v>
+        <v>120.9054167665188</v>
       </c>
       <c r="H6" t="n">
-        <v>146.286443579857</v>
+        <v>146.2864435798573</v>
       </c>
       <c r="I6" t="n">
-        <v>120.4260152722643</v>
+        <v>143.6888734023904</v>
       </c>
       <c r="J6" t="n">
-        <v>146.7024945413073</v>
+        <v>129.3704527068454</v>
       </c>
       <c r="K6" t="n">
         <v>120.8680385075915</v>
       </c>
       <c r="L6" t="n">
-        <v>120.5516827709532</v>
+        <v>120.551682770953</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.208498406084253</v>
+        <v>3.208498406084247</v>
       </c>
       <c r="C7" t="n">
-        <v>2.65781041712539</v>
+        <v>2.657810417125378</v>
       </c>
       <c r="D7" t="n">
-        <v>4.46978801718657</v>
+        <v>4.469788017186667</v>
       </c>
       <c r="E7" t="n">
-        <v>4.087786099802017</v>
+        <v>4.087786099801953</v>
       </c>
       <c r="F7" t="n">
-        <v>4.087786099802017</v>
+        <v>4.087786099801953</v>
       </c>
       <c r="G7" t="n">
-        <v>4.568079802730591</v>
+        <v>4.568079802730502</v>
       </c>
       <c r="H7" t="n">
-        <v>6.514463616158194</v>
+        <v>6.514463616158185</v>
       </c>
       <c r="I7" t="n">
-        <v>4.088678308475846</v>
+        <v>4.088678308475774</v>
       </c>
       <c r="J7" t="n">
-        <v>7.028248298819765</v>
+        <v>7.028248298819612</v>
       </c>
       <c r="K7" t="n">
-        <v>4.523555394723033</v>
+        <v>4.523555394723011</v>
       </c>
       <c r="L7" t="n">
-        <v>4.208330931489563</v>
+        <v>4.208330931489545</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.603405981043897</v>
+        <v>3.60340598104387</v>
       </c>
       <c r="C8" t="n">
-        <v>4.151548512008708</v>
+        <v>4.151548512030828</v>
       </c>
       <c r="D8" t="n">
-        <v>6.192322877188943</v>
+        <v>6.192322877188987</v>
       </c>
       <c r="E8" t="n">
-        <v>5.281917034112393</v>
+        <v>5.281917034112332</v>
       </c>
       <c r="F8" t="n">
-        <v>4.517965940176154</v>
+        <v>4.51796594017606</v>
       </c>
       <c r="G8" t="n">
-        <v>6.062603257200344</v>
+        <v>6.062603257200205</v>
       </c>
       <c r="H8" t="n">
-        <v>8.008987070632795</v>
+        <v>8.00898707063277</v>
       </c>
       <c r="I8" t="n">
-        <v>5.583201762945564</v>
+        <v>5.583201762945481</v>
       </c>
       <c r="J8" t="n">
-        <v>8.522987857430762</v>
+        <v>8.522987857430701</v>
       </c>
       <c r="K8" t="n">
-        <v>4.898037040342919</v>
+        <v>4.898037040342923</v>
       </c>
       <c r="L8" t="n">
-        <v>6.851495118742447</v>
+        <v>6.851495118742366</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.442003597945697</v>
+        <v>5.442003597945633</v>
       </c>
       <c r="C9" t="n">
-        <v>5.87840023618618</v>
+        <v>5.878400236186013</v>
       </c>
       <c r="D9" t="n">
-        <v>7.690377326763875</v>
+        <v>7.690377326763683</v>
       </c>
       <c r="E9" t="n">
-        <v>8.448483347735589</v>
+        <v>8.448483347735294</v>
       </c>
       <c r="F9" t="n">
-        <v>7.309408261055864</v>
+        <v>7.309408261055763</v>
       </c>
       <c r="G9" t="n">
-        <v>7.788669621791184</v>
+        <v>7.788669621791136</v>
       </c>
       <c r="H9" t="n">
-        <v>9.73505343521893</v>
+        <v>9.735053435218827</v>
       </c>
       <c r="I9" t="n">
-        <v>7.309268127536542</v>
+        <v>7.309268127536411</v>
       </c>
       <c r="J9" t="n">
-        <v>10.24883811788029</v>
+        <v>10.24883811788025</v>
       </c>
       <c r="K9" t="n">
-        <v>6.50122931844067</v>
+        <v>7.172224756901184</v>
       </c>
       <c r="L9" t="n">
-        <v>7.428920750550144</v>
+        <v>7.428920750550183</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.50932538791188</v>
+        <v>40.86202786548662</v>
       </c>
       <c r="C2" t="n">
-        <v>29.26182928302202</v>
+        <v>40.13634422690648</v>
       </c>
       <c r="D2" t="n">
-        <v>31.46565544735311</v>
+        <v>40.91235761709054</v>
       </c>
       <c r="E2" t="n">
-        <v>30.17069693281719</v>
+        <v>40.17172710214477</v>
       </c>
       <c r="F2" t="n">
-        <v>30.17069693281719</v>
+        <v>40.17172518188841</v>
       </c>
       <c r="G2" t="n">
-        <v>31.33174695357747</v>
+        <v>40.90531027902679</v>
       </c>
       <c r="H2" t="n">
-        <v>32.80291156003012</v>
+        <v>40.98240275124753</v>
       </c>
       <c r="I2" t="n">
-        <v>31.03201880023349</v>
+        <v>40.88959905615865</v>
       </c>
       <c r="J2" t="n">
-        <v>35.12372334568497</v>
+        <v>42.3178464003548</v>
       </c>
       <c r="K2" t="n">
-        <v>31.6542071009497</v>
+        <v>41.51149137960066</v>
       </c>
       <c r="L2" t="n">
-        <v>30.56590026107073</v>
+        <v>40.86398065162833</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.23980452865461</v>
+        <v>41.11355974841658</v>
       </c>
       <c r="C3" t="n">
-        <v>32.93081587504641</v>
+        <v>39.80113308070288</v>
       </c>
       <c r="D3" t="n">
-        <v>35.33978220018706</v>
+        <v>41.4715314763522</v>
       </c>
       <c r="E3" t="n">
-        <v>33.97986781306461</v>
+        <v>40.12464463984642</v>
       </c>
       <c r="F3" t="n">
-        <v>33.97986781306461</v>
+        <v>40.12464271959004</v>
       </c>
       <c r="G3" t="n">
-        <v>35.18575969328414</v>
+        <v>41.42215280059364</v>
       </c>
       <c r="H3" t="n">
-        <v>36.87883492843526</v>
+        <v>41.97947633125951</v>
       </c>
       <c r="I3" t="n">
-        <v>34.84191549893072</v>
+        <v>41.30966308939077</v>
       </c>
       <c r="J3" t="n">
-        <v>39.31365462873278</v>
+        <v>44.40055890646345</v>
       </c>
       <c r="K3" t="n">
-        <v>35.44315181452404</v>
+        <v>42.29729728328305</v>
       </c>
       <c r="L3" t="n">
-        <v>34.30493492904043</v>
+        <v>41.13538844787261</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.37225789712998</v>
+        <v>1.37225789712999</v>
       </c>
       <c r="C4" t="n">
-        <v>1.067611800155214</v>
+        <v>1.067611800155217</v>
       </c>
       <c r="D4" t="n">
-        <v>1.940755594325707</v>
+        <v>1.940755594325708</v>
       </c>
       <c r="E4" t="n">
         <v>1.661957453036494</v>
@@ -2986,22 +2986,22 @@
         <v>1.661957453036494</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86004104271472</v>
+        <v>1.860041042714721</v>
       </c>
       <c r="H4" t="n">
-        <v>2.735426752396427</v>
+        <v>2.735426752396442</v>
       </c>
       <c r="I4" t="n">
-        <v>1.676028449008011</v>
+        <v>1.67602844900801</v>
       </c>
       <c r="J4" t="n">
-        <v>3.190579002991814</v>
+        <v>3.190579002991822</v>
       </c>
       <c r="K4" t="n">
         <v>1.603640396540361</v>
       </c>
       <c r="L4" t="n">
-        <v>1.406137588419979</v>
+        <v>1.406137588419983</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.494104533049565</v>
+        <v>7.494104533049576</v>
       </c>
       <c r="C5" t="n">
-        <v>3.222705943293247</v>
+        <v>3.222705943293238</v>
       </c>
       <c r="D5" t="n">
-        <v>16.90932202341598</v>
+        <v>16.90932202341599</v>
       </c>
       <c r="E5" t="n">
-        <v>12.64557071748266</v>
+        <v>12.64557071748264</v>
       </c>
       <c r="F5" t="n">
-        <v>12.64557071748266</v>
+        <v>12.64557071748264</v>
       </c>
       <c r="G5" t="n">
-        <v>15.97630483443838</v>
+        <v>15.97630483443813</v>
       </c>
       <c r="H5" t="n">
-        <v>34.14574872043306</v>
+        <v>34.14574872043301</v>
       </c>
       <c r="I5" t="n">
-        <v>12.6454993636854</v>
+        <v>12.64549936368542</v>
       </c>
       <c r="J5" t="n">
-        <v>40.02699418661098</v>
+        <v>40.02699418661097</v>
       </c>
       <c r="K5" t="n">
-        <v>11.22026276985202</v>
+        <v>11.22026276985199</v>
       </c>
       <c r="L5" t="n">
-        <v>8.854282811165177</v>
+        <v>8.854282811165179</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.4783849016418</v>
+        <v>112.4783849016422</v>
       </c>
       <c r="C6" t="n">
-        <v>112.2053963614665</v>
+        <v>112.2053963614667</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0525272294708</v>
+        <v>134.9892491112798</v>
       </c>
       <c r="E6" t="n">
-        <v>101.7165208968202</v>
+        <v>101.7165208968201</v>
       </c>
       <c r="F6" t="n">
-        <v>112.7830361716031</v>
+        <v>112.7830361716032</v>
       </c>
       <c r="G6" t="n">
-        <v>134.8749936262086</v>
+        <v>112.9661680472268</v>
       </c>
       <c r="H6" t="n">
         <v>135.8974596637213</v>
       </c>
       <c r="I6" t="n">
-        <v>134.6909810325018</v>
+        <v>134.690981032502</v>
       </c>
       <c r="J6" t="n">
-        <v>119.967564651136</v>
+        <v>136.2699076002103</v>
       </c>
       <c r="K6" t="n">
-        <v>112.7038909996828</v>
+        <v>112.7038909996829</v>
       </c>
       <c r="L6" t="n">
         <v>112.5127172897129</v>
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.218740945294159</v>
+        <v>2.218740945294163</v>
       </c>
       <c r="C7" t="n">
-        <v>1.977375937982238</v>
+        <v>1.977375937982242</v>
       </c>
       <c r="D7" t="n">
-        <v>2.787241907935541</v>
+        <v>2.787241907935533</v>
       </c>
       <c r="E7" t="n">
-        <v>2.520924023310786</v>
+        <v>2.520924023310785</v>
       </c>
       <c r="F7" t="n">
-        <v>2.520924023310786</v>
+        <v>2.520924023310785</v>
       </c>
       <c r="G7" t="n">
-        <v>2.706524090878898</v>
+        <v>2.706524090878905</v>
       </c>
       <c r="H7" t="n">
-        <v>3.581909800560615</v>
+        <v>3.581909800560613</v>
       </c>
       <c r="I7" t="n">
-        <v>2.52251149717219</v>
+        <v>2.522511497172189</v>
       </c>
       <c r="J7" t="n">
-        <v>4.037062051155993</v>
+        <v>4.037062051155994</v>
       </c>
       <c r="K7" t="n">
-        <v>2.450123444704539</v>
+        <v>2.450123444704535</v>
       </c>
       <c r="L7" t="n">
-        <v>2.252620636584151</v>
+        <v>2.25262063658416</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.485710849693338</v>
+        <v>2.485710849693348</v>
       </c>
       <c r="C8" t="n">
-        <v>3.096064288235061</v>
+        <v>3.096064288218387</v>
       </c>
       <c r="D8" t="n">
-        <v>4.08426856403303</v>
+        <v>4.084268564033028</v>
       </c>
       <c r="E8" t="n">
-        <v>3.408105570753556</v>
+        <v>3.408105570753552</v>
       </c>
       <c r="F8" t="n">
-        <v>2.815604874756688</v>
+        <v>2.815604874756687</v>
       </c>
       <c r="G8" t="n">
-        <v>3.826647148449036</v>
+        <v>3.826647148449035</v>
       </c>
       <c r="H8" t="n">
-        <v>4.702032858136783</v>
+        <v>4.702032858136784</v>
       </c>
       <c r="I8" t="n">
-        <v>3.642634554742325</v>
+        <v>3.642634554742326</v>
       </c>
       <c r="J8" t="n">
-        <v>5.157352776074061</v>
+        <v>5.157352776074067</v>
       </c>
       <c r="K8" t="n">
-        <v>2.701245591425516</v>
+        <v>2.701245591425517</v>
       </c>
       <c r="L8" t="n">
-        <v>4.263933500571728</v>
+        <v>4.263933500571723</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.63260572847619</v>
+        <v>3.632605728476192</v>
       </c>
       <c r="C9" t="n">
-        <v>4.079757881603943</v>
+        <v>4.07975788160393</v>
       </c>
       <c r="D9" t="n">
-        <v>4.889620971512562</v>
+        <v>4.889620971512564</v>
       </c>
       <c r="E9" t="n">
-        <v>5.419498908908247</v>
+        <v>5.419498908908245</v>
       </c>
       <c r="F9" t="n">
-        <v>4.62496444394908</v>
+        <v>4.624964443949082</v>
       </c>
       <c r="G9" t="n">
-        <v>4.808906034500605</v>
+        <v>4.808906034500608</v>
       </c>
       <c r="H9" t="n">
-        <v>5.684291744182325</v>
+        <v>5.684291744182318</v>
       </c>
       <c r="I9" t="n">
-        <v>4.624893440793894</v>
+        <v>4.624893440793897</v>
       </c>
       <c r="J9" t="n">
-        <v>6.139443994777699</v>
+        <v>6.139443994777697</v>
       </c>
       <c r="K9" t="n">
-        <v>3.685539283566608</v>
+        <v>4.153576003650089</v>
       </c>
       <c r="L9" t="n">
-        <v>4.355002580205854</v>
+        <v>4.355002580205863</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.15603074621771</v>
+        <v>40.77280998630033</v>
       </c>
       <c r="C2" t="n">
-        <v>29.12732090948506</v>
+        <v>40.03936330144668</v>
       </c>
       <c r="D2" t="n">
-        <v>31.23632292978258</v>
+        <v>40.82966361828824</v>
       </c>
       <c r="E2" t="n">
-        <v>29.37987218964864</v>
+        <v>40.04236045150699</v>
       </c>
       <c r="F2" t="n">
-        <v>29.37987218964864</v>
+        <v>40.04235749866795</v>
       </c>
       <c r="G2" t="n">
-        <v>30.58995841217893</v>
+        <v>40.7956467375101</v>
       </c>
       <c r="H2" t="n">
-        <v>31.83027971123056</v>
+        <v>40.86071675155624</v>
       </c>
       <c r="I2" t="n">
-        <v>30.26319694093468</v>
+        <v>40.77850992687081</v>
       </c>
       <c r="J2" t="n">
-        <v>32.61340300967767</v>
+        <v>42.00978458888304</v>
       </c>
       <c r="K2" t="n">
-        <v>30.91686976096254</v>
+        <v>41.44414419994202</v>
       </c>
       <c r="L2" t="n">
-        <v>30.00272444974552</v>
+        <v>40.76400605172694</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.8169727360321</v>
+        <v>40.96312274504498</v>
       </c>
       <c r="C3" t="n">
-        <v>32.76350621182198</v>
+        <v>39.7078146057607</v>
       </c>
       <c r="D3" t="n">
-        <v>35.05953252898337</v>
+        <v>41.36773309463089</v>
       </c>
       <c r="E3" t="n">
-        <v>33.05708254610344</v>
+        <v>39.78831221085949</v>
       </c>
       <c r="F3" t="n">
-        <v>33.05708254610344</v>
+        <v>39.78830925802047</v>
       </c>
       <c r="G3" t="n">
-        <v>34.31607943973271</v>
+        <v>41.12588517280857</v>
       </c>
       <c r="H3" t="n">
-        <v>35.74349165772196</v>
+        <v>41.59492721040269</v>
       </c>
       <c r="I3" t="n">
-        <v>33.94095706849626</v>
+        <v>41.00349551793991</v>
       </c>
       <c r="J3" t="n">
-        <v>36.43008576439261</v>
+        <v>43.30455388401612</v>
       </c>
       <c r="K3" t="n">
-        <v>34.57048478932072</v>
+        <v>42.05695488832086</v>
       </c>
       <c r="L3" t="n">
-        <v>33.64067502327267</v>
+        <v>40.90519268899493</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.044026760363006</v>
+        <v>1.044026760363056</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8907724971678049</v>
+        <v>0.8907724971678058</v>
       </c>
       <c r="D4" t="n">
-        <v>1.686214687629441</v>
+        <v>1.686214687629467</v>
       </c>
       <c r="E4" t="n">
         <v>1.080276484003171</v>
       </c>
       <c r="F4" t="n">
-        <v>1.080276484003172</v>
+        <v>1.080276484003171</v>
       </c>
       <c r="G4" t="n">
-        <v>1.300874508668806</v>
+        <v>1.30087450866896</v>
       </c>
       <c r="H4" t="n">
-        <v>2.039069060142846</v>
+        <v>2.039069060142809</v>
       </c>
       <c r="I4" t="n">
-        <v>1.100774013766638</v>
+        <v>1.100774013766608</v>
       </c>
       <c r="J4" t="n">
-        <v>1.660384142964302</v>
+        <v>1.660384142964324</v>
       </c>
       <c r="K4" t="n">
-        <v>1.015029684430757</v>
+        <v>1.015029684430749</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9530633027969436</v>
+        <v>0.9530633027969133</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.104435651046042</v>
+        <v>4.104435651046057</v>
       </c>
       <c r="C5" t="n">
-        <v>2.374384213529022</v>
+        <v>2.374384213529016</v>
       </c>
       <c r="D5" t="n">
-        <v>14.86307741915519</v>
+        <v>14.8630774191552</v>
       </c>
       <c r="E5" t="n">
-        <v>5.075995043185738</v>
+        <v>5.075995043185731</v>
       </c>
       <c r="F5" t="n">
-        <v>5.075995043185738</v>
+        <v>5.075995043185731</v>
       </c>
       <c r="G5" t="n">
-        <v>8.549236296098879</v>
+        <v>8.54923629609879</v>
       </c>
       <c r="H5" t="n">
-        <v>23.39865488584777</v>
+        <v>23.39865488584779</v>
       </c>
       <c r="I5" t="n">
-        <v>5.075920507183922</v>
+        <v>5.0759205071839</v>
       </c>
       <c r="J5" t="n">
-        <v>15.11170590937995</v>
+        <v>15.11170590937949</v>
       </c>
       <c r="K5" t="n">
-        <v>3.465344191408747</v>
+        <v>3.465344191408824</v>
       </c>
       <c r="L5" t="n">
-        <v>2.649068219190337</v>
+        <v>2.64906821919035</v>
       </c>
     </row>
     <row r="6">
@@ -3450,34 +3450,34 @@
         <v>133.9556819852595</v>
       </c>
       <c r="C6" t="n">
-        <v>111.9951605313702</v>
+        <v>111.9951605313703</v>
       </c>
       <c r="D6" t="n">
         <v>112.7688640547267</v>
       </c>
       <c r="E6" t="n">
-        <v>101.104977049358</v>
+        <v>101.1049770493579</v>
       </c>
       <c r="F6" t="n">
         <v>112.1671613269655</v>
       </c>
       <c r="G6" t="n">
-        <v>134.212529733565</v>
+        <v>134.2125297335654</v>
       </c>
       <c r="H6" t="n">
-        <v>135.0786253809755</v>
+        <v>113.1131714127543</v>
       </c>
       <c r="I6" t="n">
-        <v>112.1680736186115</v>
+        <v>134.0124292386633</v>
       </c>
       <c r="J6" t="n">
-        <v>134.6303466189206</v>
+        <v>118.3882989049781</v>
       </c>
       <c r="K6" t="n">
-        <v>112.0732310623272</v>
+        <v>112.073231062317</v>
       </c>
       <c r="L6" t="n">
-        <v>112.0202143688869</v>
+        <v>112.020214368887</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.816508525136097</v>
+        <v>1.816508525136093</v>
       </c>
       <c r="C7" t="n">
         <v>1.720613191452664</v>
       </c>
       <c r="D7" t="n">
-        <v>2.45870059010783</v>
+        <v>2.458700590107799</v>
       </c>
       <c r="E7" t="n">
-        <v>1.86965188227434</v>
+        <v>1.869651882274335</v>
       </c>
       <c r="F7" t="n">
-        <v>1.86965188227434</v>
+        <v>1.869651882274335</v>
       </c>
       <c r="G7" t="n">
-        <v>2.073356273441867</v>
+        <v>2.07335627344187</v>
       </c>
       <c r="H7" t="n">
-        <v>2.811550824915933</v>
+        <v>2.811550824915906</v>
       </c>
       <c r="I7" t="n">
-        <v>1.873255778539739</v>
+        <v>1.873255778539736</v>
       </c>
       <c r="J7" t="n">
-        <v>2.432865907737386</v>
+        <v>2.432865907737384</v>
       </c>
       <c r="K7" t="n">
-        <v>1.787511449203837</v>
+        <v>1.787511449203785</v>
       </c>
       <c r="L7" t="n">
-        <v>1.725545067570033</v>
+        <v>1.725545067570003</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.018283407233948</v>
+        <v>2.01828340723393</v>
       </c>
       <c r="C8" t="n">
-        <v>2.656914674011968</v>
+        <v>2.656914674022894</v>
       </c>
       <c r="D8" t="n">
-        <v>3.551400053728571</v>
+        <v>3.551400053728559</v>
       </c>
       <c r="E8" t="n">
-        <v>2.608190476682019</v>
+        <v>2.608190476682011</v>
       </c>
       <c r="F8" t="n">
-        <v>2.096299190536489</v>
+        <v>2.096299190536484</v>
       </c>
       <c r="G8" t="n">
-        <v>3.013048008346414</v>
+        <v>3.013048008346401</v>
       </c>
       <c r="H8" t="n">
-        <v>3.751242559826544</v>
+        <v>3.751242559826545</v>
       </c>
       <c r="I8" t="n">
-        <v>2.812947513444298</v>
+        <v>2.812947513444291</v>
       </c>
       <c r="J8" t="n">
-        <v>3.372702663070149</v>
+        <v>3.372702663070113</v>
       </c>
       <c r="K8" t="n">
-        <v>1.975579147039561</v>
+        <v>1.975579147039521</v>
       </c>
       <c r="L8" t="n">
-        <v>3.436052657540584</v>
+        <v>3.436052657540561</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.960519365136159</v>
+        <v>2.960519365136161</v>
       </c>
       <c r="C9" t="n">
-        <v>3.446384848660208</v>
+        <v>3.446384848660216</v>
       </c>
       <c r="D9" t="n">
-        <v>4.184468365046449</v>
+        <v>4.184468365046401</v>
       </c>
       <c r="E9" t="n">
-        <v>4.270441457280739</v>
+        <v>4.270441457280725</v>
       </c>
       <c r="F9" t="n">
-        <v>3.599101657258716</v>
+        <v>3.599101657258718</v>
       </c>
       <c r="G9" t="n">
-        <v>3.799127930649412</v>
+        <v>3.799127930649395</v>
       </c>
       <c r="H9" t="n">
-        <v>4.537322482123475</v>
+        <v>4.537322482123487</v>
       </c>
       <c r="I9" t="n">
-        <v>3.59902743574732</v>
+        <v>3.599027435747292</v>
       </c>
       <c r="J9" t="n">
-        <v>4.158637564944952</v>
+        <v>4.158637564944925</v>
       </c>
       <c r="K9" t="n">
-        <v>3.162533167256558</v>
+        <v>3.176208711605879</v>
       </c>
       <c r="L9" t="n">
-        <v>3.451316724777597</v>
+        <v>3.451316724777572</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.18289252384946</v>
+        <v>40.95300181189385</v>
       </c>
       <c r="C2" t="n">
-        <v>29.37275762045238</v>
+        <v>40.15984031007255</v>
       </c>
       <c r="D2" t="n">
-        <v>32.08285811124599</v>
+        <v>41.00036521328288</v>
       </c>
       <c r="E2" t="n">
-        <v>31.70700754826708</v>
+        <v>40.39854636384089</v>
       </c>
       <c r="F2" t="n">
-        <v>31.70700754826708</v>
+        <v>40.39854512202128</v>
       </c>
       <c r="G2" t="n">
-        <v>32.58829960990403</v>
+        <v>41.02696559546965</v>
       </c>
       <c r="H2" t="n">
-        <v>36.00549823038327</v>
+        <v>41.20722559716969</v>
       </c>
       <c r="I2" t="n">
-        <v>32.45229516581862</v>
+        <v>41.01987358667562</v>
       </c>
       <c r="J2" t="n">
-        <v>36.88965946105112</v>
+        <v>42.57185580066095</v>
       </c>
       <c r="K2" t="n">
-        <v>33.28225570543442</v>
+        <v>41.72718472091655</v>
       </c>
       <c r="L2" t="n">
-        <v>32.39571535422358</v>
+        <v>41.01597968414225</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.02568656983576</v>
+        <v>41.35901033519236</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07664630306137</v>
+        <v>39.78737270151247</v>
       </c>
       <c r="D3" t="n">
-        <v>36.06083342265156</v>
+        <v>41.69548394760621</v>
       </c>
       <c r="E3" t="n">
-        <v>35.74066227720088</v>
+        <v>40.80924902203168</v>
       </c>
       <c r="F3" t="n">
-        <v>35.74066227720087</v>
+        <v>40.809247780212</v>
       </c>
       <c r="G3" t="n">
-        <v>36.64219584799932</v>
+        <v>41.88643105250867</v>
       </c>
       <c r="H3" t="n">
-        <v>40.57367098917818</v>
+        <v>43.1808032084664</v>
       </c>
       <c r="I3" t="n">
-        <v>36.48684887386489</v>
+        <v>41.83490598682354</v>
       </c>
       <c r="J3" t="n">
-        <v>41.33565515524641</v>
+        <v>45.19189847423817</v>
       </c>
       <c r="K3" t="n">
-        <v>37.31253631686799</v>
+        <v>42.99569785866356</v>
       </c>
       <c r="L3" t="n">
-        <v>36.42072945048425</v>
+        <v>41.81918325648097</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.928891202962526</v>
+        <v>1.928891202962567</v>
       </c>
       <c r="C4" t="n">
-        <v>1.309864388199971</v>
+        <v>1.309864388199968</v>
       </c>
       <c r="D4" t="n">
-        <v>2.463882609892941</v>
+        <v>2.463882609892888</v>
       </c>
       <c r="E4" t="n">
-        <v>2.665272345805424</v>
+        <v>2.665272345805399</v>
       </c>
       <c r="F4" t="n">
-        <v>2.665272345805424</v>
+        <v>2.665272345805417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.763297196019884</v>
+        <v>2.763297196019937</v>
       </c>
       <c r="H4" t="n">
-        <v>4.795013138963685</v>
+        <v>4.795013138963717</v>
       </c>
       <c r="I4" t="n">
-        <v>2.677024545666677</v>
+        <v>2.677024545666665</v>
       </c>
       <c r="J4" t="n">
-        <v>4.316113259489056</v>
+        <v>4.316113259489087</v>
       </c>
       <c r="K4" t="n">
-        <v>2.670885303388055</v>
+        <v>2.670885303388073</v>
       </c>
       <c r="L4" t="n">
-        <v>2.650035479056405</v>
+        <v>2.650035479056408</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.10893547011887</v>
+        <v>15.10893547011892</v>
       </c>
       <c r="C5" t="n">
-        <v>4.96997786136759</v>
+        <v>4.969977861367576</v>
       </c>
       <c r="D5" t="n">
-        <v>24.21475334861048</v>
+        <v>24.21475334861046</v>
       </c>
       <c r="E5" t="n">
-        <v>28.4138612834188</v>
+        <v>28.4138612834184</v>
       </c>
       <c r="F5" t="n">
-        <v>28.4138612834188</v>
+        <v>28.4138612834184</v>
       </c>
       <c r="G5" t="n">
-        <v>30.40871953713752</v>
+        <v>30.40871953713803</v>
       </c>
       <c r="H5" t="n">
         <v>74.12967865245787</v>
       </c>
       <c r="I5" t="n">
-        <v>28.41381085432487</v>
+        <v>28.41381085432477</v>
       </c>
       <c r="J5" t="n">
-        <v>60.19001863483324</v>
+        <v>60.19001863483538</v>
       </c>
       <c r="K5" t="n">
-        <v>28.02539566686452</v>
+        <v>28.02539566686542</v>
       </c>
       <c r="L5" t="n">
-        <v>31.47978691622553</v>
+        <v>31.47978691622559</v>
       </c>
     </row>
     <row r="6">
@@ -3843,34 +3843,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119.2699508759978</v>
+        <v>119.2699508759977</v>
       </c>
       <c r="C6" t="n">
-        <v>118.6684619537068</v>
+        <v>118.6684619537065</v>
       </c>
       <c r="D6" t="n">
         <v>119.7990605594277</v>
       </c>
       <c r="E6" t="n">
-        <v>108.3376887745414</v>
+        <v>108.3376887745413</v>
       </c>
       <c r="F6" t="n">
         <v>120.0218991868906</v>
       </c>
       <c r="G6" t="n">
-        <v>143.3114646138442</v>
+        <v>120.1043568690551</v>
       </c>
       <c r="H6" t="n">
         <v>145.5125608558375</v>
       </c>
       <c r="I6" t="n">
-        <v>143.225191963491</v>
+        <v>120.018084218702</v>
       </c>
       <c r="J6" t="n">
-        <v>144.935798078003</v>
+        <v>127.6508346782989</v>
       </c>
       <c r="K6" t="n">
-        <v>120.012411946994</v>
+        <v>120.0124119469881</v>
       </c>
       <c r="L6" t="n">
         <v>119.995519747676</v>
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.908697903249943</v>
+        <v>2.908697903249965</v>
       </c>
       <c r="C7" t="n">
-        <v>2.360689467507483</v>
+        <v>2.360689467507488</v>
       </c>
       <c r="D7" t="n">
-        <v>3.443690579381228</v>
+        <v>3.443690579381181</v>
       </c>
       <c r="E7" t="n">
-        <v>3.655725785327785</v>
+        <v>3.655725785327781</v>
       </c>
       <c r="F7" t="n">
-        <v>3.655725785327785</v>
+        <v>3.655725785327782</v>
       </c>
       <c r="G7" t="n">
-        <v>3.743103896307284</v>
+        <v>3.743103896307219</v>
       </c>
       <c r="H7" t="n">
-        <v>5.774819839251069</v>
+        <v>5.7748198392511</v>
       </c>
       <c r="I7" t="n">
-        <v>3.656831245954075</v>
+        <v>3.656831245954074</v>
       </c>
       <c r="J7" t="n">
-        <v>5.295919959776482</v>
+        <v>5.295919959776249</v>
       </c>
       <c r="K7" t="n">
-        <v>3.650692003675447</v>
+        <v>3.650692003675338</v>
       </c>
       <c r="L7" t="n">
-        <v>3.629842179343827</v>
+        <v>3.629842179343814</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.255864252911209</v>
+        <v>3.255864252911189</v>
       </c>
       <c r="C8" t="n">
-        <v>3.723407692460724</v>
+        <v>3.723407692439046</v>
       </c>
       <c r="D8" t="n">
-        <v>5.018098195676045</v>
+        <v>5.01809819567606</v>
       </c>
       <c r="E8" t="n">
-        <v>4.741712852789248</v>
+        <v>4.741712852789242</v>
       </c>
       <c r="F8" t="n">
-        <v>4.035578276376435</v>
+        <v>4.035578276376407</v>
       </c>
       <c r="G8" t="n">
-        <v>5.106740958078133</v>
+        <v>5.106740958078072</v>
       </c>
       <c r="H8" t="n">
-        <v>7.138456901027039</v>
+        <v>7.138456901027014</v>
       </c>
       <c r="I8" t="n">
-        <v>5.02046830772492</v>
+        <v>5.020468307724878</v>
       </c>
       <c r="J8" t="n">
-        <v>6.659756785314817</v>
+        <v>6.659756785314768</v>
       </c>
       <c r="K8" t="n">
-        <v>3.978976888165177</v>
+        <v>3.978976888165057</v>
       </c>
       <c r="L8" t="n">
-        <v>6.055267894094047</v>
+        <v>6.055267894094052</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.898318971859029</v>
+        <v>4.898318971859066</v>
       </c>
       <c r="C9" t="n">
-        <v>5.246961863093078</v>
+        <v>5.246961863093026</v>
       </c>
       <c r="D9" t="n">
-        <v>6.329962062726199</v>
+        <v>6.329962062726083</v>
       </c>
       <c r="E9" t="n">
         <v>7.577870178349376</v>
       </c>
       <c r="F9" t="n">
-        <v>6.543153403257256</v>
+        <v>6.54315340325728</v>
       </c>
       <c r="G9" t="n">
-        <v>6.62937629189287</v>
+        <v>6.629376291892831</v>
       </c>
       <c r="H9" t="n">
-        <v>8.661092234836678</v>
+        <v>8.661092234836623</v>
       </c>
       <c r="I9" t="n">
-        <v>6.543103641539667</v>
+        <v>6.543103641539637</v>
       </c>
       <c r="J9" t="n">
-        <v>8.182192355362055</v>
+        <v>8.182192355361913</v>
       </c>
       <c r="K9" t="n">
-        <v>6.017441249125485</v>
+        <v>6.017441249125526</v>
       </c>
       <c r="L9" t="n">
-        <v>6.516114574929398</v>
+        <v>6.516114574929404</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.04885386376685</v>
+        <v>40.29329471757915</v>
       </c>
       <c r="C2" t="n">
-        <v>28.98875872418031</v>
+        <v>39.695493205646</v>
       </c>
       <c r="D2" t="n">
-        <v>31.14357311433591</v>
+        <v>40.35090761744907</v>
       </c>
       <c r="E2" t="n">
-        <v>29.81068504911824</v>
+        <v>39.77171666359668</v>
       </c>
       <c r="F2" t="n">
-        <v>29.81068504911824</v>
+        <v>39.77171434026809</v>
       </c>
       <c r="G2" t="n">
-        <v>30.61738874903805</v>
+        <v>40.32321557938975</v>
       </c>
       <c r="H2" t="n">
-        <v>31.87920586801507</v>
+        <v>40.38930112626841</v>
       </c>
       <c r="I2" t="n">
-        <v>30.46239953344504</v>
+        <v>40.31512172925132</v>
       </c>
       <c r="J2" t="n">
-        <v>33.18688663985305</v>
+        <v>41.9176186531845</v>
       </c>
       <c r="K2" t="n">
-        <v>30.98480607990572</v>
+        <v>40.94407746439011</v>
       </c>
       <c r="L2" t="n">
-        <v>29.66798049673797</v>
+        <v>40.2721538564108</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.71531367365317</v>
+        <v>40.5382147776027</v>
       </c>
       <c r="C3" t="n">
-        <v>32.59926317259207</v>
+        <v>39.44710209735113</v>
       </c>
       <c r="D3" t="n">
-        <v>34.97446758221717</v>
+        <v>40.94807885824033</v>
       </c>
       <c r="E3" t="n">
-        <v>33.53944196967719</v>
+        <v>39.79637240752051</v>
       </c>
       <c r="F3" t="n">
-        <v>33.5394419696772</v>
+        <v>39.79637008419191</v>
       </c>
       <c r="G3" t="n">
-        <v>34.36924656336172</v>
+        <v>40.75149908566149</v>
       </c>
       <c r="H3" t="n">
-        <v>35.82145527873507</v>
+        <v>41.22929671574026</v>
       </c>
       <c r="I3" t="n">
-        <v>34.19182793860762</v>
+        <v>40.69339929514658</v>
       </c>
       <c r="J3" t="n">
-        <v>37.04361004024624</v>
+        <v>43.58554803094378</v>
       </c>
       <c r="K3" t="n">
-        <v>34.67597647526226</v>
+        <v>41.659422050425</v>
       </c>
       <c r="L3" t="n">
-        <v>33.27729512807103</v>
+        <v>40.39464007857248</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.285421191396926</v>
+        <v>1.285421191396932</v>
       </c>
       <c r="C4" t="n">
         <v>1.009205167407759</v>
       </c>
       <c r="D4" t="n">
-        <v>1.936185398670678</v>
+        <v>1.93618539867069</v>
       </c>
       <c r="E4" t="n">
-        <v>1.51024558228549</v>
+        <v>1.5102455822855</v>
       </c>
       <c r="F4" t="n">
-        <v>1.51024558228549</v>
+        <v>1.5102455822855</v>
       </c>
       <c r="G4" t="n">
-        <v>1.622490658400061</v>
+        <v>1.622490658400055</v>
       </c>
       <c r="H4" t="n">
-        <v>2.373261211993845</v>
+        <v>2.373261211993842</v>
       </c>
       <c r="I4" t="n">
-        <v>1.525708734624341</v>
+        <v>1.525708734624349</v>
       </c>
       <c r="J4" t="n">
-        <v>2.038405605747433</v>
+        <v>2.038405605747447</v>
       </c>
       <c r="K4" t="n">
-        <v>1.383215444511719</v>
+        <v>1.383215444511715</v>
       </c>
       <c r="L4" t="n">
-        <v>1.059282525044756</v>
+        <v>1.059282525044758</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.933281090741087</v>
+        <v>6.93328109074109</v>
       </c>
       <c r="C5" t="n">
-        <v>3.040501090650363</v>
+        <v>3.040501090650367</v>
       </c>
       <c r="D5" t="n">
-        <v>17.75799693903145</v>
+        <v>17.75799693903181</v>
       </c>
       <c r="E5" t="n">
-        <v>10.97881213831127</v>
+        <v>10.97881213831142</v>
       </c>
       <c r="F5" t="n">
-        <v>10.97881213831127</v>
+        <v>10.97881213831142</v>
       </c>
       <c r="G5" t="n">
-        <v>12.77396717198529</v>
+        <v>12.77396717198526</v>
       </c>
       <c r="H5" t="n">
-        <v>28.26209681534316</v>
+        <v>28.26209681534317</v>
       </c>
       <c r="I5" t="n">
-        <v>10.97876029207221</v>
+        <v>10.97876029207244</v>
       </c>
       <c r="J5" t="n">
-        <v>20.43445959380143</v>
+        <v>20.43445959380189</v>
       </c>
       <c r="K5" t="n">
-        <v>8.388865738836369</v>
+        <v>8.388865738836374</v>
       </c>
       <c r="L5" t="n">
-        <v>3.157431927589269</v>
+        <v>3.157431927589277</v>
       </c>
     </row>
     <row r="6">
@@ -4239,19 +4239,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.3699790221201</v>
+        <v>134.250163674614</v>
       </c>
       <c r="C6" t="n">
-        <v>112.1242481449324</v>
+        <v>112.1242481449326</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0324672427823</v>
+        <v>113.0324698705199</v>
       </c>
       <c r="E6" t="n">
         <v>101.5489646395126</v>
       </c>
       <c r="F6" t="n">
-        <v>112.610831923194</v>
+        <v>112.6108319231941</v>
       </c>
       <c r="G6" t="n">
         <v>112.7070484891232</v>
@@ -4260,16 +4260,16 @@
         <v>135.4814151624595</v>
       </c>
       <c r="I6" t="n">
-        <v>134.4904512178412</v>
+        <v>134.4904512178414</v>
       </c>
       <c r="J6" t="n">
-        <v>135.0648762518975</v>
+        <v>118.7858371266464</v>
       </c>
       <c r="K6" t="n">
-        <v>112.4596546195754</v>
+        <v>112.4596546195753</v>
       </c>
       <c r="L6" t="n">
-        <v>112.1431168507134</v>
+        <v>112.1431168507133</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.087667690990592</v>
+        <v>2.087667690990591</v>
       </c>
       <c r="C7" t="n">
-        <v>1.868133212991669</v>
+        <v>1.868133212991671</v>
       </c>
       <c r="D7" t="n">
-        <v>2.738434410014894</v>
+        <v>2.738434410014903</v>
       </c>
       <c r="E7" t="n">
-        <v>2.325612770512655</v>
+        <v>2.325612770512663</v>
       </c>
       <c r="F7" t="n">
-        <v>2.325612770512655</v>
+        <v>2.32561277051266</v>
       </c>
       <c r="G7" t="n">
-        <v>2.424737157993727</v>
+        <v>2.424737157993722</v>
       </c>
       <c r="H7" t="n">
-        <v>3.175507711587509</v>
+        <v>3.175507711587506</v>
       </c>
       <c r="I7" t="n">
-        <v>2.327955234218007</v>
+        <v>2.327955234218013</v>
       </c>
       <c r="J7" t="n">
-        <v>2.840652105341098</v>
+        <v>2.840652105341104</v>
       </c>
       <c r="K7" t="n">
-        <v>2.185461944105382</v>
+        <v>2.185461944105376</v>
       </c>
       <c r="L7" t="n">
-        <v>1.861529024638422</v>
+        <v>1.861529024638415</v>
       </c>
     </row>
     <row r="8">
@@ -4322,34 +4322,34 @@
         <v>2.315709423635899</v>
       </c>
       <c r="C8" t="n">
-        <v>2.881046111289276</v>
+        <v>2.881046111289272</v>
       </c>
       <c r="D8" t="n">
-        <v>3.916688107539603</v>
+        <v>3.91668810753961</v>
       </c>
       <c r="E8" t="n">
-        <v>3.125916088598542</v>
+        <v>3.125916088598561</v>
       </c>
       <c r="F8" t="n">
-        <v>2.579566332068337</v>
+        <v>2.579566332068351</v>
       </c>
       <c r="G8" t="n">
         <v>3.439799514129433</v>
       </c>
       <c r="H8" t="n">
-        <v>4.190570067730093</v>
+        <v>4.190570067730073</v>
       </c>
       <c r="I8" t="n">
-        <v>3.343017590353713</v>
+        <v>3.343017590353718</v>
       </c>
       <c r="J8" t="n">
-        <v>3.855869132026184</v>
+        <v>3.855869132026172</v>
       </c>
       <c r="K8" t="n">
-        <v>2.39888436475307</v>
+        <v>2.398884364753077</v>
       </c>
       <c r="L8" t="n">
-        <v>3.698700230154202</v>
+        <v>3.698700230154199</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.446309926223391</v>
+        <v>3.446309926223404</v>
       </c>
       <c r="C9" t="n">
-        <v>3.882001940172666</v>
+        <v>3.882001940172677</v>
       </c>
       <c r="D9" t="n">
-        <v>4.752300968096235</v>
+        <v>4.752300968096273</v>
       </c>
       <c r="E9" t="n">
-        <v>5.097993235293032</v>
+        <v>5.097993235293036</v>
       </c>
       <c r="F9" t="n">
-        <v>4.341875519032818</v>
+        <v>4.341875519032823</v>
       </c>
       <c r="G9" t="n">
-        <v>4.438605885174722</v>
+        <v>4.438605885174717</v>
       </c>
       <c r="H9" t="n">
-        <v>5.189376438768511</v>
+        <v>5.189376438768518</v>
       </c>
       <c r="I9" t="n">
-        <v>4.341823961399006</v>
+        <v>4.341823961399009</v>
       </c>
       <c r="J9" t="n">
-        <v>4.854520832522097</v>
+        <v>4.854520832522152</v>
       </c>
       <c r="K9" t="n">
-        <v>3.81969001269621</v>
+        <v>3.374283471600739</v>
       </c>
       <c r="L9" t="n">
-        <v>3.875397751819424</v>
+        <v>3.875397751819414</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.77580671263494</v>
+        <v>39.83272885727792</v>
       </c>
       <c r="C2" t="n">
-        <v>28.78418310720325</v>
+        <v>39.13179863280165</v>
       </c>
       <c r="D2" t="n">
-        <v>31.13800315400194</v>
+        <v>39.90441855044703</v>
       </c>
       <c r="E2" t="n">
-        <v>29.18235270007778</v>
+        <v>39.31943158422834</v>
       </c>
       <c r="F2" t="n">
-        <v>29.18235270007778</v>
+        <v>39.31942810564638</v>
       </c>
       <c r="G2" t="n">
-        <v>30.23712590268937</v>
+        <v>39.85700716999681</v>
       </c>
       <c r="H2" t="n">
-        <v>31.28659159216025</v>
+        <v>39.9119735557859</v>
       </c>
       <c r="I2" t="n">
-        <v>29.7995310146757</v>
+        <v>39.83403654767768</v>
       </c>
       <c r="J2" t="n">
-        <v>32.24736111938981</v>
+        <v>41.3010869509368</v>
       </c>
       <c r="K2" t="n">
-        <v>30.70579733554401</v>
+        <v>40.60732934797539</v>
       </c>
       <c r="L2" t="n">
-        <v>29.61430253984184</v>
+        <v>39.82346873047887</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.28941053507876</v>
+        <v>40.44631293335848</v>
       </c>
       <c r="C3" t="n">
-        <v>32.27282116516406</v>
+        <v>39.24401587116821</v>
       </c>
       <c r="D3" t="n">
-        <v>34.85621862079354</v>
+        <v>40.95658487983876</v>
       </c>
       <c r="E3" t="n">
-        <v>32.69968883983482</v>
+        <v>39.60590382332205</v>
       </c>
       <c r="F3" t="n">
-        <v>32.69968883983482</v>
+        <v>39.60590034474008</v>
       </c>
       <c r="G3" t="n">
-        <v>33.8200231656237</v>
+        <v>40.61935499938603</v>
       </c>
       <c r="H3" t="n">
-        <v>35.02784574904527</v>
+        <v>41.01640244555711</v>
       </c>
       <c r="I3" t="n">
-        <v>33.31745341950773</v>
+        <v>40.45538644262034</v>
       </c>
       <c r="J3" t="n">
-        <v>35.87440669668361</v>
+        <v>43.08831868094906</v>
       </c>
       <c r="K3" t="n">
-        <v>34.21930393658577</v>
+        <v>41.72446657825051</v>
       </c>
       <c r="L3" t="n">
-        <v>33.10368947161007</v>
+        <v>40.38525685007791</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9914278991420314</v>
+        <v>0.9914278991420322</v>
       </c>
       <c r="C4" t="n">
         <v>0.8442664587094647</v>
       </c>
       <c r="D4" t="n">
-        <v>1.801195962375154</v>
+        <v>1.801195962375155</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9848437061404636</v>
+        <v>0.9848437061404625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9848437061404635</v>
+        <v>0.9848437061404625</v>
       </c>
       <c r="G4" t="n">
-        <v>1.265212661325564</v>
+        <v>1.265212661325565</v>
       </c>
       <c r="H4" t="n">
-        <v>1.889338816031695</v>
+        <v>1.889338816031694</v>
       </c>
       <c r="I4" t="n">
-        <v>1.002900301512832</v>
+        <v>1.002900301512833</v>
       </c>
       <c r="J4" t="n">
-        <v>1.440383335707758</v>
+        <v>1.440383335707759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9910431371373756</v>
+        <v>0.9910431371373779</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8955968452610542</v>
+        <v>0.8955968452610568</v>
       </c>
     </row>
     <row r="5">
@@ -4595,34 +4595,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.050530243572217</v>
+        <v>4.050530243572216</v>
       </c>
       <c r="C5" t="n">
-        <v>2.301950455859011</v>
+        <v>2.301950455859012</v>
       </c>
       <c r="D5" t="n">
-        <v>17.65696320678117</v>
+        <v>17.65696320678111</v>
       </c>
       <c r="E5" t="n">
-        <v>4.174069011930477</v>
+        <v>4.174069011930479</v>
       </c>
       <c r="F5" t="n">
-        <v>4.174069011930477</v>
+        <v>4.174069011930479</v>
       </c>
       <c r="G5" t="n">
-        <v>8.779387820485738</v>
+        <v>8.779387820485724</v>
       </c>
       <c r="H5" t="n">
-        <v>21.48199811476288</v>
+        <v>21.48199811476283</v>
       </c>
       <c r="I5" t="n">
-        <v>4.173979338426509</v>
+        <v>4.173979338426504</v>
       </c>
       <c r="J5" t="n">
         <v>12.067648424304</v>
       </c>
       <c r="K5" t="n">
-        <v>3.898940007978044</v>
+        <v>3.898940007978041</v>
       </c>
       <c r="L5" t="n">
         <v>2.496026403544096</v>
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.0446526997711</v>
+        <v>133.86513748</v>
       </c>
       <c r="C6" t="n">
-        <v>111.9284128912542</v>
+        <v>111.9284128912543</v>
       </c>
       <c r="D6" t="n">
-        <v>112.8734754826572</v>
+        <v>112.8734729657156</v>
       </c>
       <c r="E6" t="n">
-        <v>100.9946470822128</v>
+        <v>100.9946470822127</v>
       </c>
       <c r="F6" t="n">
-        <v>112.0549790126884</v>
+        <v>112.0549790126883</v>
       </c>
       <c r="G6" t="n">
-        <v>134.1389222421834</v>
+        <v>112.3184374619546</v>
       </c>
       <c r="H6" t="n">
         <v>134.8850874094257</v>
       </c>
       <c r="I6" t="n">
-        <v>133.8766098823708</v>
+        <v>112.0561251021419</v>
       </c>
       <c r="J6" t="n">
-        <v>118.1508921883324</v>
+        <v>134.3688834784544</v>
       </c>
       <c r="K6" t="n">
-        <v>112.0351049657641</v>
+        <v>112.035104965764</v>
       </c>
       <c r="L6" t="n">
-        <v>111.9486489527914</v>
+        <v>111.9486489527913</v>
       </c>
     </row>
     <row r="7">
@@ -4675,13 +4675,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.729660748985002</v>
+        <v>1.729660748985007</v>
       </c>
       <c r="C7" t="n">
-        <v>1.632705519525313</v>
+        <v>1.632705519525312</v>
       </c>
       <c r="D7" t="n">
-        <v>2.539431072673908</v>
+        <v>2.539431072673912</v>
       </c>
       <c r="E7" t="n">
         <v>1.738277579383209</v>
@@ -4690,22 +4690,22 @@
         <v>1.738277579383209</v>
       </c>
       <c r="G7" t="n">
-        <v>2.003445511168536</v>
+        <v>2.003445511168538</v>
       </c>
       <c r="H7" t="n">
-        <v>2.627571665874664</v>
+        <v>2.627571665874668</v>
       </c>
       <c r="I7" t="n">
         <v>1.741133151355805</v>
       </c>
       <c r="J7" t="n">
-        <v>2.178616185550729</v>
+        <v>2.178616185550732</v>
       </c>
       <c r="K7" t="n">
-        <v>1.729275986980349</v>
+        <v>1.72927598698035</v>
       </c>
       <c r="L7" t="n">
-        <v>1.633829695104026</v>
+        <v>1.633829695104029</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.895667902820569</v>
+        <v>1.895667902820573</v>
       </c>
       <c r="C8" t="n">
-        <v>2.474491874380702</v>
+        <v>2.474491874371281</v>
       </c>
       <c r="D8" t="n">
-        <v>3.524599585480487</v>
+        <v>3.524599585480484</v>
       </c>
       <c r="E8" t="n">
-        <v>2.397749524836686</v>
+        <v>2.397749524836684</v>
       </c>
       <c r="F8" t="n">
-        <v>1.926978322105956</v>
+        <v>1.92697832210596</v>
       </c>
       <c r="G8" t="n">
-        <v>2.847929659773981</v>
+        <v>2.847929659773983</v>
       </c>
       <c r="H8" t="n">
-        <v>3.472055814486694</v>
+        <v>3.472055814486698</v>
       </c>
       <c r="I8" t="n">
-        <v>2.585617299961251</v>
+        <v>2.58561729996125</v>
       </c>
       <c r="J8" t="n">
-        <v>3.023233673196981</v>
+        <v>3.023233673196987</v>
       </c>
       <c r="K8" t="n">
-        <v>1.882680082410813</v>
+        <v>1.882680082410818</v>
       </c>
       <c r="L8" t="n">
-        <v>3.187039797010418</v>
+        <v>3.187039797010422</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.86525127072754</v>
+        <v>2.865251270727545</v>
       </c>
       <c r="C9" t="n">
-        <v>3.331748503443483</v>
+        <v>3.331748503443484</v>
       </c>
       <c r="D9" t="n">
-        <v>4.238472062047173</v>
+        <v>4.238472062047169</v>
       </c>
       <c r="E9" t="n">
-        <v>4.090477890213778</v>
+        <v>4.090477890213781</v>
       </c>
       <c r="F9" t="n">
-        <v>3.440265526241507</v>
+        <v>3.440265526241503</v>
       </c>
       <c r="G9" t="n">
-        <v>3.70248849508671</v>
+        <v>3.702488495086709</v>
       </c>
       <c r="H9" t="n">
         <v>4.326614649792837</v>
       </c>
       <c r="I9" t="n">
-        <v>3.440176135273973</v>
+        <v>3.440176135273974</v>
       </c>
       <c r="J9" t="n">
-        <v>3.877659169468902</v>
+        <v>3.877659169468899</v>
       </c>
       <c r="K9" t="n">
-        <v>3.088607345944725</v>
+        <v>3.088607345944734</v>
       </c>
       <c r="L9" t="n">
-        <v>3.332872679022199</v>
+        <v>3.332872679022197</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.95179979491958</v>
+        <v>39.72580994011476</v>
       </c>
       <c r="C2" t="n">
-        <v>38.89220694271877</v>
+        <v>42.96124916834455</v>
       </c>
       <c r="D2" t="n">
-        <v>36.38642463103758</v>
+        <v>39.85393940968527</v>
       </c>
       <c r="E2" t="n">
-        <v>40.74428993489916</v>
+        <v>44.50936084117232</v>
       </c>
       <c r="F2" t="n">
-        <v>36.57940190127766</v>
+        <v>41.04263587065569</v>
       </c>
       <c r="G2" t="n">
-        <v>36.4850201700153</v>
+        <v>39.85912829707512</v>
       </c>
       <c r="H2" t="n">
-        <v>42.61921953121752</v>
+        <v>40.18242547721953</v>
       </c>
       <c r="I2" t="n">
-        <v>35.06695098716016</v>
+        <v>39.78455575458194</v>
       </c>
       <c r="J2" t="n">
-        <v>48.53578051193448</v>
+        <v>46.20144520049066</v>
       </c>
       <c r="K2" t="n">
-        <v>37.40621666499798</v>
+        <v>41.15735977728419</v>
       </c>
       <c r="L2" t="n">
-        <v>41.35584782991738</v>
+        <v>40.11733093295646</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.35689661219369</v>
+        <v>40.93719722333537</v>
       </c>
       <c r="C3" t="n">
-        <v>43.46402811018162</v>
+        <v>46.60071116893666</v>
       </c>
       <c r="D3" t="n">
-        <v>41.15721950474492</v>
+        <v>41.85146775157067</v>
       </c>
       <c r="E3" t="n">
-        <v>45.31705489476563</v>
+        <v>49.1512350085736</v>
       </c>
       <c r="F3" t="n">
-        <v>41.15216686114417</v>
+        <v>43.42877034640717</v>
       </c>
       <c r="G3" t="n">
-        <v>41.27062479857364</v>
+        <v>41.89190439359093</v>
       </c>
       <c r="H3" t="n">
-        <v>48.32719116237679</v>
+        <v>44.21916330590751</v>
       </c>
       <c r="I3" t="n">
-        <v>39.64028694994955</v>
+        <v>41.3521266253388</v>
       </c>
       <c r="J3" t="n">
-        <v>54.03190175535622</v>
+        <v>53.73341970640298</v>
       </c>
       <c r="K3" t="n">
-        <v>42.08944320934699</v>
+        <v>43.83555928904402</v>
       </c>
       <c r="L3" t="n">
-        <v>46.8729321825841</v>
+        <v>43.75534548155709</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.891162946555169</v>
+        <v>4.891162946555209</v>
       </c>
       <c r="C4" t="n">
-        <v>5.532182067930256</v>
+        <v>5.53218206793025</v>
       </c>
       <c r="D4" t="n">
-        <v>6.338444247821885</v>
+        <v>6.338444247821908</v>
       </c>
       <c r="E4" t="n">
-        <v>5.550393849309604</v>
+        <v>5.550393849309598</v>
       </c>
       <c r="F4" t="n">
-        <v>5.550393849309604</v>
+        <v>5.550393849309598</v>
       </c>
       <c r="G4" t="n">
-        <v>6.39733082502704</v>
+        <v>6.39733082502706</v>
       </c>
       <c r="H4" t="n">
-        <v>10.0422554705628</v>
+        <v>10.04225547056283</v>
       </c>
       <c r="I4" t="n">
-        <v>5.556285241547663</v>
+        <v>5.556285241547661</v>
       </c>
       <c r="J4" t="n">
-        <v>9.208985323271207</v>
+        <v>9.208985323271245</v>
       </c>
       <c r="K4" t="n">
-        <v>5.99188510310136</v>
+        <v>5.991885103101383</v>
       </c>
       <c r="L4" t="n">
-        <v>9.291784954554524</v>
+        <v>9.291784954554544</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.56672805631763</v>
+        <v>57.56672805631811</v>
       </c>
       <c r="C5" t="n">
-        <v>67.70002719829593</v>
+        <v>67.70002719829577</v>
       </c>
       <c r="D5" t="n">
-        <v>84.82284359322678</v>
+        <v>84.82284359322675</v>
       </c>
       <c r="E5" t="n">
-        <v>67.70002796419985</v>
+        <v>67.70002796419968</v>
       </c>
       <c r="F5" t="n">
-        <v>67.70002796419985</v>
+        <v>67.70002796419968</v>
       </c>
       <c r="G5" t="n">
-        <v>87.8240776800057</v>
+        <v>87.82407768000581</v>
       </c>
       <c r="H5" t="n">
-        <v>169.7894016808675</v>
+        <v>169.7894016808673</v>
       </c>
       <c r="I5" t="n">
-        <v>67.69979935008955</v>
+        <v>67.69979935008948</v>
       </c>
       <c r="J5" t="n">
         <v>144.6428627304201</v>
       </c>
       <c r="K5" t="n">
-        <v>78.76307964449042</v>
+        <v>78.76307964449067</v>
       </c>
       <c r="L5" t="n">
-        <v>57.18186871054762</v>
+        <v>57.18186871054759</v>
       </c>
     </row>
     <row r="6">
@@ -5031,22 +5031,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>148.3110333622044</v>
+        <v>124.4248091530167</v>
       </c>
       <c r="C6" t="n">
         <v>125.0677895145692</v>
       </c>
       <c r="D6" t="n">
-        <v>125.8813374631837</v>
+        <v>125.8813359884838</v>
       </c>
       <c r="E6" t="n">
-        <v>113.1880961315638</v>
+        <v>113.1880961315637</v>
       </c>
       <c r="F6" t="n">
-        <v>125.0956660299271</v>
+        <v>125.095666029927</v>
       </c>
       <c r="G6" t="n">
-        <v>149.8172012406762</v>
+        <v>125.9309770314885</v>
       </c>
       <c r="H6" t="n">
         <v>153.5924013898978</v>
@@ -5055,13 +5055,13 @@
         <v>148.9761556571968</v>
       </c>
       <c r="J6" t="n">
-        <v>152.6922337236489</v>
+        <v>134.8656897275702</v>
       </c>
       <c r="K6" t="n">
-        <v>125.5285672134771</v>
+        <v>125.528567213477</v>
       </c>
       <c r="L6" t="n">
-        <v>128.8558692014216</v>
+        <v>128.8558692014217</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.112547768775027</v>
+        <v>6.11254776877503</v>
       </c>
       <c r="C7" t="n">
-        <v>6.77789791197377</v>
+        <v>6.777897911973765</v>
       </c>
       <c r="D7" t="n">
-        <v>7.559815369204586</v>
+        <v>7.559815369204602</v>
       </c>
       <c r="E7" t="n">
-        <v>6.779075874870599</v>
+        <v>6.779075874870587</v>
       </c>
       <c r="F7" t="n">
-        <v>6.779075874870599</v>
+        <v>6.779075874870587</v>
       </c>
       <c r="G7" t="n">
-        <v>7.618715647246884</v>
+        <v>7.618715647246897</v>
       </c>
       <c r="H7" t="n">
-        <v>11.26364029278267</v>
+        <v>11.26364029278266</v>
       </c>
       <c r="I7" t="n">
-        <v>6.777670063767501</v>
+        <v>6.777670063767503</v>
       </c>
       <c r="J7" t="n">
-        <v>10.43037014549106</v>
+        <v>10.43037014549109</v>
       </c>
       <c r="K7" t="n">
-        <v>7.213269925321214</v>
+        <v>7.213269925321231</v>
       </c>
       <c r="L7" t="n">
-        <v>10.51316977677437</v>
+        <v>10.51316977677436</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.621272944695851</v>
+        <v>6.621272944695887</v>
       </c>
       <c r="C8" t="n">
-        <v>8.596277268023698</v>
+        <v>8.596277268045673</v>
       </c>
       <c r="D8" t="n">
-        <v>9.648099004734098</v>
+        <v>9.648099004734103</v>
       </c>
       <c r="E8" t="n">
-        <v>8.238339749793449</v>
+        <v>8.23833974979344</v>
       </c>
       <c r="F8" t="n">
-        <v>7.328804328991103</v>
+        <v>7.328804328991092</v>
       </c>
       <c r="G8" t="n">
-        <v>9.435707884372086</v>
+        <v>9.435707884372105</v>
       </c>
       <c r="H8" t="n">
-        <v>13.08063252990906</v>
+        <v>13.08063252990908</v>
       </c>
       <c r="I8" t="n">
-        <v>8.594662300892717</v>
+        <v>8.594662300892709</v>
       </c>
       <c r="J8" t="n">
-        <v>12.24761949273704</v>
+        <v>12.24761949273707</v>
       </c>
       <c r="K8" t="n">
-        <v>7.697693369075829</v>
+        <v>7.697693369075867</v>
       </c>
       <c r="L8" t="n">
-        <v>13.69675635312048</v>
+        <v>13.69675635312046</v>
       </c>
     </row>
     <row r="9">
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.472729930505634</v>
+        <v>9.472729930505682</v>
       </c>
       <c r="C9" t="n">
-        <v>11.49609245284566</v>
+        <v>11.49609245284565</v>
       </c>
       <c r="D9" t="n">
         <v>12.27802402932325</v>
@@ -5163,25 +5163,25 @@
         <v>13.06320875087474</v>
       </c>
       <c r="F9" t="n">
-        <v>11.4960913490506</v>
+        <v>11.49609134905059</v>
       </c>
       <c r="G9" t="n">
-        <v>12.33691018811878</v>
+        <v>12.33691018811879</v>
       </c>
       <c r="H9" t="n">
-        <v>15.98183483365455</v>
+        <v>15.98183483365457</v>
       </c>
       <c r="I9" t="n">
-        <v>11.49586460463941</v>
+        <v>11.4958646046394</v>
       </c>
       <c r="J9" t="n">
-        <v>15.14856468636296</v>
+        <v>15.14856468636299</v>
       </c>
       <c r="K9" t="n">
-        <v>11.144626936374</v>
+        <v>11.14462693637402</v>
       </c>
       <c r="L9" t="n">
-        <v>15.23136431764627</v>
+        <v>15.23136431764626</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.83726784687291</v>
+        <v>39.56059172854726</v>
       </c>
       <c r="C2" t="n">
-        <v>38.45968267674767</v>
+        <v>42.79459298774843</v>
       </c>
       <c r="D2" t="n">
-        <v>35.86997010436563</v>
+        <v>39.72019682492726</v>
       </c>
       <c r="E2" t="n">
-        <v>40.29420419168962</v>
+        <v>44.32755933398813</v>
       </c>
       <c r="F2" t="n">
-        <v>36.1800073647001</v>
+        <v>40.90302744512852</v>
       </c>
       <c r="G2" t="n">
-        <v>35.89056532574728</v>
+        <v>39.72128071052319</v>
       </c>
       <c r="H2" t="n">
-        <v>40.98407391766671</v>
+        <v>39.98941944988391</v>
       </c>
       <c r="I2" t="n">
-        <v>34.68296972470937</v>
+        <v>39.65778483380656</v>
       </c>
       <c r="J2" t="n">
-        <v>46.56376478510526</v>
+        <v>45.89161538539245</v>
       </c>
       <c r="K2" t="n">
-        <v>36.22136701042212</v>
+        <v>40.92156163048812</v>
       </c>
       <c r="L2" t="n">
-        <v>40.40695978884695</v>
+        <v>39.96068530185054</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.06773277356689</v>
+        <v>40.46416016637052</v>
       </c>
       <c r="C3" t="n">
-        <v>42.96661608928817</v>
+        <v>46.33192915151722</v>
       </c>
       <c r="D3" t="n">
-        <v>40.55596859206355</v>
+        <v>41.59835099161167</v>
       </c>
       <c r="E3" t="n">
-        <v>44.80207079507188</v>
+        <v>48.85784752860403</v>
       </c>
       <c r="F3" t="n">
-        <v>40.68787396808232</v>
+        <v>43.20503074781421</v>
       </c>
       <c r="G3" t="n">
-        <v>40.57965736293976</v>
+        <v>41.60973800974752</v>
       </c>
       <c r="H3" t="n">
-        <v>46.43905709386354</v>
+        <v>43.54577354642247</v>
       </c>
       <c r="I3" t="n">
-        <v>39.19114022904457</v>
+        <v>41.14957104621198</v>
       </c>
       <c r="J3" t="n">
-        <v>51.77561824275513</v>
+        <v>52.80782941283297</v>
       </c>
       <c r="K3" t="n">
-        <v>40.73228286886224</v>
+        <v>43.2415521094538</v>
       </c>
       <c r="L3" t="n">
-        <v>45.77431002615178</v>
+        <v>43.3405141259453</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.132126760314248</v>
+        <v>4.132126760314254</v>
       </c>
       <c r="C4" t="n">
         <v>5.197526829456841</v>
       </c>
       <c r="D4" t="n">
-        <v>5.93493974589812</v>
+        <v>5.93493974589813</v>
       </c>
       <c r="E4" t="n">
-        <v>5.213740488255373</v>
+        <v>5.213740488255376</v>
       </c>
       <c r="F4" t="n">
-        <v>5.213740488255373</v>
+        <v>5.213740488255375</v>
       </c>
       <c r="G4" t="n">
-        <v>5.947518490618</v>
+        <v>5.947518490618015</v>
       </c>
       <c r="H4" t="n">
-        <v>8.973970419542352</v>
+        <v>8.973970419542347</v>
       </c>
       <c r="I4" t="n">
-        <v>5.231933008968015</v>
+        <v>5.231933008968017</v>
       </c>
       <c r="J4" t="n">
-        <v>8.016055715210967</v>
+        <v>8.016055715210959</v>
       </c>
       <c r="K4" t="n">
-        <v>5.242035282656217</v>
+        <v>5.242035282656218</v>
       </c>
       <c r="L4" t="n">
-        <v>8.631270676171313</v>
+        <v>8.631270676171312</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.44439971983015</v>
+        <v>44.44439971983017</v>
       </c>
       <c r="C5" t="n">
-        <v>59.58255444769961</v>
+        <v>59.58255444769952</v>
       </c>
       <c r="D5" t="n">
-        <v>73.78112832144771</v>
+        <v>73.78112832144797</v>
       </c>
       <c r="E5" t="n">
-        <v>59.5825555861815</v>
+        <v>59.5825555861814</v>
       </c>
       <c r="F5" t="n">
-        <v>59.5825555861815</v>
+        <v>59.58255558618141</v>
       </c>
       <c r="G5" t="n">
-        <v>75.89018106623328</v>
+        <v>75.89018106623347</v>
       </c>
       <c r="H5" t="n">
-        <v>141.5409032739215</v>
+        <v>141.5409032739211</v>
       </c>
       <c r="I5" t="n">
-        <v>59.58235611788129</v>
+        <v>59.5823561178812</v>
       </c>
       <c r="J5" t="n">
         <v>116.5976230827672</v>
       </c>
       <c r="K5" t="n">
-        <v>59.80660294114984</v>
+        <v>59.80660294114999</v>
       </c>
       <c r="L5" t="n">
-        <v>59.85751201526703</v>
+        <v>59.85751201526708</v>
       </c>
     </row>
     <row r="6">
@@ -5427,13 +5427,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137.6820300050504</v>
+        <v>115.485412518647</v>
       </c>
       <c r="C6" t="n">
         <v>116.5674369459213</v>
       </c>
       <c r="D6" t="n">
-        <v>117.299233601664</v>
+        <v>117.2992336016642</v>
       </c>
       <c r="E6" t="n">
         <v>105.5013846649216</v>
@@ -5442,7 +5442,7 @@
         <v>116.591032847633</v>
       </c>
       <c r="G6" t="n">
-        <v>139.4974217353541</v>
+        <v>117.3008042489507</v>
       </c>
       <c r="H6" t="n">
         <v>142.6429758217004</v>
@@ -5451,7 +5451,7 @@
         <v>138.7818362537041</v>
       </c>
       <c r="J6" t="n">
-        <v>141.6269557113742</v>
+        <v>125.0687153558832</v>
       </c>
       <c r="K6" t="n">
         <v>116.590174637011</v>
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.202089439632263</v>
+        <v>5.202089439632257</v>
       </c>
       <c r="C7" t="n">
-        <v>6.302094018104311</v>
+        <v>6.302094018104313</v>
       </c>
       <c r="D7" t="n">
-        <v>7.004894556279988</v>
+        <v>7.004894556280005</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2991743980263</v>
+        <v>6.299174398026299</v>
       </c>
       <c r="F7" t="n">
-        <v>6.2991743980263</v>
+        <v>6.299174398026299</v>
       </c>
       <c r="G7" t="n">
-        <v>7.017481169936012</v>
+        <v>7.01748116993601</v>
       </c>
       <c r="H7" t="n">
-        <v>10.04393309886035</v>
+        <v>10.04393309886034</v>
       </c>
       <c r="I7" t="n">
         <v>6.301895688286015</v>
       </c>
       <c r="J7" t="n">
-        <v>9.086018394528958</v>
+        <v>9.086018394528963</v>
       </c>
       <c r="K7" t="n">
-        <v>6.311997961974215</v>
+        <v>6.311997961974223</v>
       </c>
       <c r="L7" t="n">
-        <v>9.701233355489316</v>
+        <v>9.701233355489318</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.622648223118326</v>
+        <v>5.622648223118323</v>
       </c>
       <c r="C8" t="n">
-        <v>7.840881140048971</v>
+        <v>7.84088114004898</v>
       </c>
       <c r="D8" t="n">
-        <v>8.778671453189459</v>
+        <v>8.778671453189482</v>
       </c>
       <c r="E8" t="n">
-        <v>7.534635581128934</v>
+        <v>7.53463558112894</v>
       </c>
       <c r="F8" t="n">
-        <v>6.756444023205487</v>
+        <v>6.756444023205489</v>
       </c>
       <c r="G8" t="n">
-        <v>8.558844147101988</v>
+        <v>8.558844147102002</v>
       </c>
       <c r="H8" t="n">
         <v>11.58529607602867</v>
       </c>
       <c r="I8" t="n">
-        <v>7.843258665452003</v>
+        <v>7.843258665452005</v>
       </c>
       <c r="J8" t="n">
         <v>10.62760164035214</v>
       </c>
       <c r="K8" t="n">
-        <v>6.711737232272514</v>
+        <v>6.711737232272517</v>
       </c>
       <c r="L8" t="n">
-        <v>12.4133700316928</v>
+        <v>12.41337003169282</v>
       </c>
     </row>
     <row r="9">
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.882068879152063</v>
+        <v>7.882068879152076</v>
       </c>
       <c r="C9" t="n">
-        <v>10.09476130319291</v>
+        <v>10.09476130319292</v>
       </c>
       <c r="D9" t="n">
-        <v>10.79757012977148</v>
+        <v>10.79757012977147</v>
       </c>
       <c r="E9" t="n">
-        <v>11.37877906856703</v>
+        <v>11.37877906856704</v>
       </c>
       <c r="F9" t="n">
-        <v>10.09476089504278</v>
+        <v>10.09476089504279</v>
       </c>
       <c r="G9" t="n">
         <v>10.81014845502461</v>
@@ -5571,13 +5571,13 @@
         <v>10.09456297337461</v>
       </c>
       <c r="J9" t="n">
-        <v>12.87868567961755</v>
+        <v>12.87868567961756</v>
       </c>
       <c r="K9" t="n">
-        <v>8.703592526696978</v>
+        <v>9.459969715904023</v>
       </c>
       <c r="L9" t="n">
-        <v>13.49390064057792</v>
+        <v>13.49390064057791</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.46354279866552</v>
+        <v>39.43729550887269</v>
       </c>
       <c r="C2" t="n">
-        <v>37.74139495606205</v>
+        <v>42.62335404244798</v>
       </c>
       <c r="D2" t="n">
-        <v>35.2254003473246</v>
+        <v>39.58264658616771</v>
       </c>
       <c r="E2" t="n">
-        <v>39.5656976971372</v>
+        <v>44.14729926229981</v>
       </c>
       <c r="F2" t="n">
-        <v>35.48112446993991</v>
+        <v>40.74742462307069</v>
       </c>
       <c r="G2" t="n">
-        <v>35.23106177535436</v>
+        <v>39.58294453588041</v>
       </c>
       <c r="H2" t="n">
-        <v>39.69260462908812</v>
+        <v>39.81767239025582</v>
       </c>
       <c r="I2" t="n">
-        <v>34.00360166649246</v>
+        <v>39.51840122139517</v>
       </c>
       <c r="J2" t="n">
-        <v>45.60615344691129</v>
+        <v>45.67519399306963</v>
       </c>
       <c r="K2" t="n">
-        <v>34.39992254954856</v>
+        <v>40.64338812755108</v>
       </c>
       <c r="L2" t="n">
-        <v>39.25548577864465</v>
+        <v>39.79622319890691</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.63157316344306</v>
+        <v>40.27070041246533</v>
       </c>
       <c r="C3" t="n">
-        <v>42.13989639268769</v>
+        <v>45.97315084536039</v>
       </c>
       <c r="D3" t="n">
-        <v>39.80828146146861</v>
+        <v>41.3017367019465</v>
       </c>
       <c r="E3" t="n">
-        <v>43.96521424174932</v>
+        <v>48.48449407366004</v>
       </c>
       <c r="F3" t="n">
-        <v>39.88064101455204</v>
+        <v>42.87237894257137</v>
       </c>
       <c r="G3" t="n">
-        <v>39.81479327646413</v>
+        <v>41.308293735683</v>
       </c>
       <c r="H3" t="n">
-        <v>44.94718358112729</v>
+        <v>42.99774028034812</v>
       </c>
       <c r="I3" t="n">
-        <v>38.40274832357534</v>
+        <v>40.84368718966</v>
       </c>
       <c r="J3" t="n">
-        <v>50.67988830970227</v>
+        <v>52.31735116476256</v>
       </c>
       <c r="K3" t="n">
-        <v>38.64610401661785</v>
+        <v>42.40499219046941</v>
       </c>
       <c r="L3" t="n">
-        <v>44.44360037842068</v>
+        <v>42.85080386502624</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.847579065560749</v>
+        <v>3.847579065560785</v>
       </c>
       <c r="C4" t="n">
-        <v>4.711569147764356</v>
+        <v>4.711569147764361</v>
       </c>
       <c r="D4" t="n">
-        <v>5.489386348406859</v>
+        <v>5.489386348406907</v>
       </c>
       <c r="E4" t="n">
-        <v>4.728257476038733</v>
+        <v>4.728257476038746</v>
       </c>
       <c r="F4" t="n">
-        <v>4.728257476038733</v>
+        <v>4.728257476038744</v>
       </c>
       <c r="G4" t="n">
-        <v>5.493074259430853</v>
+        <v>5.493074259430854</v>
       </c>
       <c r="H4" t="n">
-        <v>8.144004365572339</v>
+        <v>8.144004365572389</v>
       </c>
       <c r="I4" t="n">
-        <v>4.765584488568574</v>
+        <v>4.765584488568575</v>
       </c>
       <c r="J4" t="n">
-        <v>7.431981994121737</v>
+        <v>7.431981994121788</v>
       </c>
       <c r="K4" t="n">
-        <v>4.156868729617008</v>
+        <v>4.156868729617053</v>
       </c>
       <c r="L4" t="n">
-        <v>7.884468885298277</v>
+        <v>7.884468885298336</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.12016053191326</v>
+        <v>40.12016053191343</v>
       </c>
       <c r="C5" t="n">
-        <v>53.28412173395333</v>
+        <v>53.28412173395334</v>
       </c>
       <c r="D5" t="n">
-        <v>65.87186039093382</v>
+        <v>65.87186039093389</v>
       </c>
       <c r="E5" t="n">
-        <v>53.28412344214246</v>
+        <v>53.28412344214254</v>
       </c>
       <c r="F5" t="n">
-        <v>53.28412344214246</v>
+        <v>53.28412344214254</v>
       </c>
       <c r="G5" t="n">
-        <v>68.22772814467245</v>
+        <v>68.22772814467244</v>
       </c>
       <c r="H5" t="n">
         <v>122.4987224325463</v>
       </c>
       <c r="I5" t="n">
-        <v>53.2839215532608</v>
+        <v>53.28392155326095</v>
       </c>
       <c r="J5" t="n">
-        <v>108.1084734283549</v>
+        <v>108.1084734283548</v>
       </c>
       <c r="K5" t="n">
-        <v>42.06066965118418</v>
+        <v>42.06066965118417</v>
       </c>
       <c r="L5" t="n">
-        <v>125.9531243681046</v>
+        <v>45.73637319761381</v>
       </c>
     </row>
     <row r="6">
@@ -5829,7 +5829,7 @@
         <v>116.0653852494731</v>
       </c>
       <c r="D6" t="n">
-        <v>138.9806583610747</v>
+        <v>116.8220727077537</v>
       </c>
       <c r="E6" t="n">
         <v>105.0024933605676</v>
@@ -5838,19 +5838,19 @@
         <v>116.0898436638981</v>
       </c>
       <c r="G6" t="n">
-        <v>116.8093172858995</v>
+        <v>138.95547693064</v>
       </c>
       <c r="H6" t="n">
         <v>141.7283405924986</v>
       </c>
       <c r="I6" t="n">
-        <v>138.2279871597777</v>
+        <v>116.0818275150373</v>
       </c>
       <c r="J6" t="n">
-        <v>124.4480651166115</v>
+        <v>140.958761687564</v>
       </c>
       <c r="K6" t="n">
-        <v>115.4528214313738</v>
+        <v>115.4528214313737</v>
       </c>
       <c r="L6" t="n">
         <v>119.2309787696336</v>
@@ -5863,34 +5863,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.870415062437909</v>
+        <v>4.870415062437925</v>
       </c>
       <c r="C7" t="n">
-        <v>5.788620666138113</v>
+        <v>5.7886206661381</v>
       </c>
       <c r="D7" t="n">
-        <v>6.512219291200103</v>
+        <v>6.512219291200057</v>
       </c>
       <c r="E7" t="n">
-        <v>5.780227011612931</v>
+        <v>5.780227011612938</v>
       </c>
       <c r="F7" t="n">
-        <v>5.780227011612931</v>
+        <v>5.780227011612937</v>
       </c>
       <c r="G7" t="n">
-        <v>6.515910256307992</v>
+        <v>6.515910256308005</v>
       </c>
       <c r="H7" t="n">
-        <v>9.166840362449499</v>
+        <v>9.166840362449516</v>
       </c>
       <c r="I7" t="n">
-        <v>5.788420485445743</v>
+        <v>5.788420485445739</v>
       </c>
       <c r="J7" t="n">
-        <v>8.454817990998897</v>
+        <v>8.454817990998913</v>
       </c>
       <c r="K7" t="n">
-        <v>5.179704726494172</v>
+        <v>5.179704726494178</v>
       </c>
       <c r="L7" t="n">
         <v>8.907304882175451</v>
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.252449914627926</v>
+        <v>5.252449914627996</v>
       </c>
       <c r="C8" t="n">
-        <v>7.216170720595986</v>
+        <v>7.216170720595987</v>
       </c>
       <c r="D8" t="n">
-        <v>8.166021441811463</v>
+        <v>8.166021441811475</v>
       </c>
       <c r="E8" t="n">
-        <v>6.928934397572489</v>
+        <v>6.928934397572486</v>
       </c>
       <c r="F8" t="n">
-        <v>6.199040251929116</v>
+        <v>6.199040251929111</v>
       </c>
       <c r="G8" t="n">
-        <v>7.951291182566984</v>
+        <v>7.951291182567023</v>
       </c>
       <c r="H8" t="n">
-        <v>10.60222128871131</v>
+        <v>10.60222128871134</v>
       </c>
       <c r="I8" t="n">
-        <v>7.223801411704732</v>
+        <v>7.223801411704725</v>
       </c>
       <c r="J8" t="n">
-        <v>9.890405928609811</v>
+        <v>9.890405928609859</v>
       </c>
       <c r="K8" t="n">
-        <v>5.54217313468715</v>
+        <v>5.542173134687163</v>
       </c>
       <c r="L8" t="n">
-        <v>11.44299386092338</v>
+        <v>11.44299386092344</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.174900010684939</v>
+        <v>7.174900010684919</v>
       </c>
       <c r="C9" t="n">
-        <v>9.083241162235819</v>
+        <v>9.083241162235822</v>
       </c>
       <c r="D9" t="n">
-        <v>9.8068432529871</v>
+        <v>9.806843252987145</v>
       </c>
       <c r="E9" t="n">
-        <v>10.22583689853582</v>
+        <v>10.22583689853581</v>
       </c>
       <c r="F9" t="n">
         <v>9.083241452883671</v>
       </c>
       <c r="G9" t="n">
-        <v>9.810530752405715</v>
+        <v>9.810530752405722</v>
       </c>
       <c r="H9" t="n">
-        <v>12.46146085854721</v>
+        <v>12.4614608585473</v>
       </c>
       <c r="I9" t="n">
-        <v>9.083040981543455</v>
+        <v>9.08304098154346</v>
       </c>
       <c r="J9" t="n">
-        <v>11.74943848709661</v>
+        <v>11.74943848709669</v>
       </c>
       <c r="K9" t="n">
-        <v>7.9006369707245</v>
+        <v>7.900636970724527</v>
       </c>
       <c r="L9" t="n">
-        <v>12.20192537827316</v>
+        <v>12.20192537827324</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.54058465892441</v>
+        <v>39.15454063994349</v>
       </c>
       <c r="C2" t="n">
-        <v>37.57115285071127</v>
+        <v>42.51748204483947</v>
       </c>
       <c r="D2" t="n">
-        <v>32.69346070789879</v>
+        <v>39.32047024428478</v>
       </c>
       <c r="E2" t="n">
-        <v>39.40282383613922</v>
+        <v>44.04655005423509</v>
       </c>
       <c r="F2" t="n">
-        <v>35.30119740263979</v>
+        <v>40.63247995975872</v>
       </c>
       <c r="G2" t="n">
-        <v>33.35760182353246</v>
+        <v>39.3554226721101</v>
       </c>
       <c r="H2" t="n">
-        <v>34.83042571736746</v>
+        <v>39.43162647903551</v>
       </c>
       <c r="I2" t="n">
-        <v>33.79325790904856</v>
+        <v>39.37842408545998</v>
       </c>
       <c r="J2" t="n">
-        <v>48.93003896520737</v>
+        <v>45.78567807371423</v>
       </c>
       <c r="K2" t="n">
-        <v>34.82569084351496</v>
+        <v>40.58290402803306</v>
       </c>
       <c r="L2" t="n">
-        <v>36.16381881485157</v>
+        <v>39.50402534619136</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.26874637347011</v>
+        <v>39.10365311102804</v>
       </c>
       <c r="C3" t="n">
-        <v>41.93747440222632</v>
+        <v>45.87675208383347</v>
       </c>
       <c r="D3" t="n">
-        <v>36.89520694609661</v>
+        <v>40.27770926165003</v>
       </c>
       <c r="E3" t="n">
-        <v>43.76997782285602</v>
+        <v>48.39769921582934</v>
       </c>
       <c r="F3" t="n">
-        <v>39.66835138935659</v>
+        <v>42.76215246419557</v>
       </c>
       <c r="G3" t="n">
-        <v>37.65910680549297</v>
+        <v>40.53041174013801</v>
       </c>
       <c r="H3" t="n">
-        <v>39.35391718175264</v>
+        <v>41.08613539042383</v>
       </c>
       <c r="I3" t="n">
-        <v>38.16137595215697</v>
+        <v>40.69214185982189</v>
       </c>
       <c r="J3" t="n">
-        <v>54.48980451949934</v>
+        <v>53.57354443914116</v>
       </c>
       <c r="K3" t="n">
-        <v>39.12613846474548</v>
+        <v>42.55218234369272</v>
       </c>
       <c r="L3" t="n">
-        <v>40.88675374217765</v>
+        <v>41.60381409650373</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.131680178643244</v>
+        <v>2.131680178643245</v>
       </c>
       <c r="C4" t="n">
         <v>4.632793112584867</v>
       </c>
       <c r="D4" t="n">
-        <v>4.005931391067458</v>
+        <v>4.005931391067454</v>
       </c>
       <c r="E4" t="n">
+        <v>4.650078328129811</v>
+      </c>
+      <c r="F4" t="n">
         <v>4.650078328129808</v>
       </c>
-      <c r="F4" t="n">
-        <v>4.650078328129807</v>
-      </c>
       <c r="G4" t="n">
-        <v>4.401698778735673</v>
+        <v>4.401698778735674</v>
       </c>
       <c r="H4" t="n">
-        <v>5.276006948393878</v>
+        <v>5.276006948393881</v>
       </c>
       <c r="I4" t="n">
-        <v>4.666745330017955</v>
+        <v>4.666745330017952</v>
       </c>
       <c r="J4" t="n">
-        <v>9.380408855104417</v>
+        <v>9.38040885510442</v>
       </c>
       <c r="K4" t="n">
-        <v>4.396550546842329</v>
+        <v>4.396550546842331</v>
       </c>
       <c r="L4" t="n">
-        <v>6.068487055280592</v>
+        <v>6.068487055280591</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.02606300599896</v>
+        <v>14.02606300599906</v>
       </c>
       <c r="C5" t="n">
-        <v>56.63189176202182</v>
+        <v>56.63189176202176</v>
       </c>
       <c r="D5" t="n">
-        <v>43.79608488908544</v>
+        <v>43.79608488908548</v>
       </c>
       <c r="E5" t="n">
-        <v>56.63189303989196</v>
+        <v>56.63189303989199</v>
       </c>
       <c r="F5" t="n">
-        <v>56.63189303989196</v>
+        <v>56.63189303989201</v>
       </c>
       <c r="G5" t="n">
-        <v>53.06681805905458</v>
+        <v>53.06681805905457</v>
       </c>
       <c r="H5" t="n">
-        <v>71.82173617989423</v>
+        <v>71.82173617989419</v>
       </c>
       <c r="I5" t="n">
-        <v>56.63191923897296</v>
+        <v>56.63191923897291</v>
       </c>
       <c r="J5" t="n">
         <v>152.849364373216</v>
       </c>
       <c r="K5" t="n">
-        <v>51.66332846510996</v>
+        <v>51.66332846511003</v>
       </c>
       <c r="L5" t="n">
-        <v>94.98660219687577</v>
+        <v>94.98660219687575</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>121.5843727821177</v>
+        <v>145.2421160683528</v>
       </c>
       <c r="C6" t="n">
-        <v>124.1231633150653</v>
+        <v>124.1231633150651</v>
       </c>
       <c r="D6" t="n">
-        <v>147.1479256271489</v>
+        <v>147.1479256271488</v>
       </c>
       <c r="E6" t="n">
-        <v>112.2487808992789</v>
+        <v>112.2487808992788</v>
       </c>
       <c r="F6" t="n">
-        <v>124.1268085438257</v>
+        <v>124.1268085438256</v>
       </c>
       <c r="G6" t="n">
-        <v>123.8543913822102</v>
+        <v>147.5121346684452</v>
       </c>
       <c r="H6" t="n">
-        <v>148.512018577895</v>
+        <v>124.7410378836388</v>
       </c>
       <c r="I6" t="n">
-        <v>124.1194379334924</v>
+        <v>147.7771812197274</v>
       </c>
       <c r="J6" t="n">
         <v>152.5627625588106</v>
       </c>
       <c r="K6" t="n">
-        <v>123.8537661102588</v>
+        <v>123.8537661102587</v>
       </c>
       <c r="L6" t="n">
-        <v>125.5387140378238</v>
+        <v>125.5387140378237</v>
       </c>
     </row>
     <row r="7">
@@ -6262,31 +6262,31 @@
         <v>3.161711798712982</v>
       </c>
       <c r="C7" t="n">
-        <v>5.696749473136535</v>
+        <v>5.696749473136529</v>
       </c>
       <c r="D7" t="n">
-        <v>5.03595780032207</v>
+        <v>5.035957800322066</v>
       </c>
       <c r="E7" t="n">
-        <v>5.691789859358078</v>
+        <v>5.691789859358074</v>
       </c>
       <c r="F7" t="n">
-        <v>5.691789859358078</v>
+        <v>5.691789859358076</v>
       </c>
       <c r="G7" t="n">
-        <v>5.431730398805418</v>
+        <v>5.431730398805415</v>
       </c>
       <c r="H7" t="n">
-        <v>6.306038568463628</v>
+        <v>6.306038568463624</v>
       </c>
       <c r="I7" t="n">
-        <v>5.696776950087696</v>
+        <v>5.696776950087694</v>
       </c>
       <c r="J7" t="n">
         <v>10.41044047517416</v>
       </c>
       <c r="K7" t="n">
-        <v>5.42658216691207</v>
+        <v>5.426582166912064</v>
       </c>
       <c r="L7" t="n">
         <v>7.09851867535034</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.507435481882581</v>
+        <v>3.507435481882583</v>
       </c>
       <c r="C8" t="n">
-        <v>7.077125074219849</v>
+        <v>7.077125074219843</v>
       </c>
       <c r="D8" t="n">
-        <v>6.636369831785792</v>
+        <v>6.636369831785793</v>
       </c>
       <c r="E8" t="n">
-        <v>6.793408356132312</v>
+        <v>6.793408356132309</v>
       </c>
       <c r="F8" t="n">
-        <v>6.072459120305215</v>
+        <v>6.072459120305208</v>
       </c>
       <c r="G8" t="n">
-        <v>6.816652630740162</v>
+        <v>6.816652630740161</v>
       </c>
       <c r="H8" t="n">
-        <v>7.690960800399891</v>
+        <v>7.690960800399887</v>
       </c>
       <c r="I8" t="n">
-        <v>7.08169918202244</v>
+        <v>7.081699182022437</v>
       </c>
       <c r="J8" t="n">
-        <v>11.79556693783109</v>
+        <v>11.79556693783108</v>
       </c>
       <c r="K8" t="n">
-        <v>5.753002203645052</v>
+        <v>5.753002203645058</v>
       </c>
       <c r="L8" t="n">
-        <v>9.568970686384764</v>
+        <v>9.568970686384759</v>
       </c>
     </row>
     <row r="9">
@@ -6339,22 +6339,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.892969948846421</v>
+        <v>5.892969948846417</v>
       </c>
       <c r="C9" t="n">
         <v>9.540053514437506</v>
       </c>
       <c r="D9" t="n">
-        <v>8.879267693716292</v>
+        <v>8.879267693716294</v>
       </c>
       <c r="E9" t="n">
         <v>10.82333182679844</v>
       </c>
       <c r="F9" t="n">
-        <v>9.540054052758283</v>
+        <v>9.540054052758279</v>
       </c>
       <c r="G9" t="n">
-        <v>9.275034440106388</v>
+        <v>9.275034440106385</v>
       </c>
       <c r="H9" t="n">
         <v>10.1493426097646</v>
@@ -6363,10 +6363,10 @@
         <v>9.54008099138867</v>
       </c>
       <c r="J9" t="n">
-        <v>14.25374451647513</v>
+        <v>14.25374451647514</v>
       </c>
       <c r="K9" t="n">
-        <v>8.625562721248443</v>
+        <v>8.625562721248437</v>
       </c>
       <c r="L9" t="n">
         <v>10.94182271665131</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.51829481884602</v>
+        <v>38.88242261075715</v>
       </c>
       <c r="C2" t="n">
-        <v>35.92052552701695</v>
+        <v>42.14628692162066</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8190600277693</v>
+        <v>39.056135327855</v>
       </c>
       <c r="E2" t="n">
-        <v>37.7257480720243</v>
+        <v>43.65221337099769</v>
       </c>
       <c r="F2" t="n">
-        <v>33.69989367647685</v>
+        <v>40.30121220790645</v>
       </c>
       <c r="G2" t="n">
-        <v>31.79948644350006</v>
+        <v>39.05510520899119</v>
       </c>
       <c r="H2" t="n">
-        <v>30.60819753308153</v>
+        <v>38.99002661962634</v>
       </c>
       <c r="I2" t="n">
-        <v>32.22879131535669</v>
+        <v>39.07776872374773</v>
       </c>
       <c r="J2" t="n">
-        <v>43.58698441192463</v>
+        <v>45.12704792442422</v>
       </c>
       <c r="K2" t="n">
-        <v>31.80583590839098</v>
+        <v>40.08976972781336</v>
       </c>
       <c r="L2" t="n">
-        <v>33.23908979921783</v>
+        <v>39.13107138397531</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.08081704574492</v>
+        <v>38.6024532478198</v>
       </c>
       <c r="C3" t="n">
-        <v>40.03984136948434</v>
+        <v>45.05427019096024</v>
       </c>
       <c r="D3" t="n">
-        <v>35.87738078745978</v>
+        <v>39.83062474417351</v>
       </c>
       <c r="E3" t="n">
-        <v>41.84581333794386</v>
+        <v>47.53776171275797</v>
       </c>
       <c r="F3" t="n">
-        <v>37.81995894239638</v>
+        <v>42.00632268926584</v>
       </c>
       <c r="G3" t="n">
-        <v>35.85486711089442</v>
+        <v>39.82708272174188</v>
       </c>
       <c r="H3" t="n">
-        <v>34.48537776903652</v>
+        <v>39.38131104656533</v>
       </c>
       <c r="I3" t="n">
-        <v>36.34971862747817</v>
+        <v>39.98683825681401</v>
       </c>
       <c r="J3" t="n">
-        <v>48.3627529259361</v>
+        <v>51.23345737272905</v>
       </c>
       <c r="K3" t="n">
-        <v>35.66291988865002</v>
+        <v>41.15646547751039</v>
       </c>
       <c r="L3" t="n">
-        <v>37.51068290003707</v>
+        <v>40.37786846780985</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.387092018350127</v>
+        <v>1.387092018350145</v>
       </c>
       <c r="C4" t="n">
-        <v>3.568702594083758</v>
+        <v>3.568702594083762</v>
       </c>
       <c r="D4" t="n">
-        <v>3.349257069768675</v>
+        <v>3.349257069768677</v>
       </c>
       <c r="E4" t="n">
-        <v>3.581823095155434</v>
+        <v>3.581823095155437</v>
       </c>
       <c r="F4" t="n">
-        <v>3.581823095155433</v>
+        <v>3.581823095155437</v>
       </c>
       <c r="G4" t="n">
-        <v>3.338590011066209</v>
+        <v>3.338590011066218</v>
       </c>
       <c r="H4" t="n">
-        <v>2.629797879856606</v>
+        <v>2.629797879856611</v>
       </c>
       <c r="I4" t="n">
-        <v>3.59981562440325</v>
+        <v>3.599815624403249</v>
       </c>
       <c r="J4" t="n">
         <v>6.188617851699131</v>
       </c>
       <c r="K4" t="n">
-        <v>2.552845322768976</v>
+        <v>2.552845322768979</v>
       </c>
       <c r="L4" t="n">
-        <v>4.19322627235931</v>
+        <v>4.193226272359313</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.683900907360263</v>
+        <v>4.683900907360269</v>
       </c>
       <c r="C5" t="n">
-        <v>38.6323422105954</v>
+        <v>38.63234221059546</v>
       </c>
       <c r="D5" t="n">
         <v>33.36375622354797</v>
       </c>
       <c r="E5" t="n">
-        <v>38.63234345465676</v>
+        <v>38.63234345465679</v>
       </c>
       <c r="F5" t="n">
-        <v>38.63234345465676</v>
+        <v>38.63234345465679</v>
       </c>
       <c r="G5" t="n">
-        <v>35.13335828679327</v>
+        <v>35.13335828679337</v>
       </c>
       <c r="H5" t="n">
-        <v>24.62491552959474</v>
+        <v>24.62491552959475</v>
       </c>
       <c r="I5" t="n">
-        <v>38.63237015055201</v>
+        <v>38.63237015055202</v>
       </c>
       <c r="J5" t="n">
-        <v>84.9101093244218</v>
+        <v>84.91010932442173</v>
       </c>
       <c r="K5" t="n">
-        <v>22.62901353672826</v>
+        <v>22.62901353672825</v>
       </c>
       <c r="L5" t="n">
-        <v>10.95393818781958</v>
+        <v>10.95393818781959</v>
       </c>
     </row>
     <row r="6">
@@ -6615,31 +6615,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.5465979929792</v>
+        <v>134.5465979929793</v>
       </c>
       <c r="C6" t="n">
-        <v>114.8186394239844</v>
+        <v>114.8186394239843</v>
       </c>
       <c r="D6" t="n">
-        <v>114.5653374525017</v>
+        <v>114.5653374237374</v>
       </c>
       <c r="E6" t="n">
-        <v>103.7618891176365</v>
+        <v>103.7618891176364</v>
       </c>
       <c r="F6" t="n">
         <v>114.8196401868913</v>
       </c>
       <c r="G6" t="n">
-        <v>114.5497674664497</v>
+        <v>136.4980959856953</v>
       </c>
       <c r="H6" t="n">
-        <v>113.8450702443715</v>
+        <v>135.8802623936428</v>
       </c>
       <c r="I6" t="n">
-        <v>114.8109930797868</v>
+        <v>136.7593215990322</v>
       </c>
       <c r="J6" t="n">
-        <v>139.4113650823238</v>
+        <v>123.0892612688459</v>
       </c>
       <c r="K6" t="n">
         <v>113.7443757532144</v>
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.244412328213633</v>
+        <v>2.244412328213632</v>
       </c>
       <c r="C7" t="n">
-        <v>4.457107994310153</v>
+        <v>4.457107994310157</v>
       </c>
       <c r="D7" t="n">
-        <v>4.206574210922287</v>
+        <v>4.206574210922282</v>
       </c>
       <c r="E7" t="n">
-        <v>4.451752747955419</v>
+        <v>4.451752747955426</v>
       </c>
       <c r="F7" t="n">
-        <v>4.451752747955419</v>
+        <v>4.451752747955425</v>
       </c>
       <c r="G7" t="n">
-        <v>4.195910320929702</v>
+        <v>4.195910320929708</v>
       </c>
       <c r="H7" t="n">
-        <v>3.48711818972009</v>
+        <v>3.487118189720097</v>
       </c>
       <c r="I7" t="n">
-        <v>4.457135934266734</v>
+        <v>4.457135934266735</v>
       </c>
       <c r="J7" t="n">
-        <v>7.04593816156261</v>
+        <v>7.04593816156262</v>
       </c>
       <c r="K7" t="n">
         <v>3.410165632632466</v>
       </c>
       <c r="L7" t="n">
-        <v>5.050546582222797</v>
+        <v>5.0505465822228</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.470490776510886</v>
+        <v>2.470490776510912</v>
       </c>
       <c r="C8" t="n">
-        <v>5.489658000376134</v>
+        <v>5.489658000376139</v>
       </c>
       <c r="D8" t="n">
-        <v>5.412357482498122</v>
+        <v>5.41235748249814</v>
       </c>
       <c r="E8" t="n">
-        <v>5.268275590932486</v>
+        <v>5.268275590932495</v>
       </c>
       <c r="F8" t="n">
-        <v>4.705715678640757</v>
+        <v>4.705715678640759</v>
       </c>
       <c r="G8" t="n">
-        <v>5.233432317984335</v>
+        <v>5.233432317984344</v>
       </c>
       <c r="H8" t="n">
-        <v>4.524640186774392</v>
+        <v>4.524640186774389</v>
       </c>
       <c r="I8" t="n">
-        <v>5.494657931321374</v>
+        <v>5.494657931321376</v>
       </c>
       <c r="J8" t="n">
         <v>8.083619629391542</v>
       </c>
       <c r="K8" t="n">
-        <v>3.621171100513123</v>
+        <v>3.621171100513124</v>
       </c>
       <c r="L8" t="n">
-        <v>6.935689216708096</v>
+        <v>6.935689216708099</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.212337931874135</v>
+        <v>4.212337931874144</v>
       </c>
       <c r="C9" t="n">
-        <v>7.259933192791864</v>
+        <v>7.259933192791879</v>
       </c>
       <c r="D9" t="n">
-        <v>7.00940334799386</v>
+        <v>7.009403347993877</v>
       </c>
       <c r="E9" t="n">
-        <v>8.223391317085886</v>
+        <v>8.223391317085897</v>
       </c>
       <c r="F9" t="n">
-        <v>7.259934240521023</v>
+        <v>7.25993424052103</v>
       </c>
       <c r="G9" t="n">
-        <v>6.998735519411412</v>
+        <v>6.998735519411424</v>
       </c>
       <c r="H9" t="n">
         <v>6.289943388201817</v>
       </c>
       <c r="I9" t="n">
-        <v>7.259961132748447</v>
+        <v>7.259961132748459</v>
       </c>
       <c r="J9" t="n">
-        <v>9.848763360044332</v>
+        <v>9.848763360044344</v>
       </c>
       <c r="K9" t="n">
-        <v>5.709620923316513</v>
+        <v>5.729247050779565</v>
       </c>
       <c r="L9" t="n">
-        <v>7.853371780704498</v>
+        <v>7.85337178070452</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.39282444902242</v>
+        <v>38.73537705002167</v>
       </c>
       <c r="C2" t="n">
-        <v>34.47783197842652</v>
+        <v>41.88960113106351</v>
       </c>
       <c r="D2" t="n">
-        <v>30.20528424451252</v>
+        <v>38.8307632092232</v>
       </c>
       <c r="E2" t="n">
-        <v>36.27004697793387</v>
+        <v>43.38387655253985</v>
       </c>
       <c r="F2" t="n">
-        <v>32.28093735074921</v>
+        <v>40.06345987444439</v>
       </c>
       <c r="G2" t="n">
-        <v>30.63564093492584</v>
+        <v>38.85341202708239</v>
       </c>
       <c r="H2" t="n">
-        <v>30.40507579072534</v>
+        <v>38.83979491240937</v>
       </c>
       <c r="I2" t="n">
-        <v>30.83893794103081</v>
+        <v>38.86417689808324</v>
       </c>
       <c r="J2" t="n">
-        <v>39.97624993857863</v>
+        <v>44.71149968772895</v>
       </c>
       <c r="K2" t="n">
-        <v>30.43052473921643</v>
+        <v>39.82746796772503</v>
       </c>
       <c r="L2" t="n">
-        <v>32.37593232449274</v>
+        <v>38.94563449483029</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.92937237356822</v>
+        <v>38.47589530418091</v>
       </c>
       <c r="C3" t="n">
-        <v>38.38123459092239</v>
+        <v>44.38571219559084</v>
       </c>
       <c r="D3" t="n">
-        <v>34.01407658829736</v>
+        <v>39.15205464619196</v>
       </c>
       <c r="E3" t="n">
-        <v>40.17420630571817</v>
+        <v>46.85044685894856</v>
       </c>
       <c r="F3" t="n">
-        <v>36.18509667853348</v>
+        <v>41.36949360754261</v>
       </c>
       <c r="G3" t="n">
-        <v>34.50907593039255</v>
+        <v>39.31433015402379</v>
       </c>
       <c r="H3" t="n">
-        <v>34.2445380715217</v>
+        <v>39.23022891739446</v>
       </c>
       <c r="I3" t="n">
-        <v>34.74381117860194</v>
+        <v>39.38988785651635</v>
       </c>
       <c r="J3" t="n">
-        <v>44.21892215925127</v>
+        <v>49.69464166539549</v>
       </c>
       <c r="K3" t="n">
-        <v>34.08343099353648</v>
+        <v>40.49980389767989</v>
       </c>
       <c r="L3" t="n">
-        <v>36.51071887742104</v>
+        <v>39.97814520938575</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.23686324912456</v>
+        <v>1.236863249124559</v>
       </c>
       <c r="C4" t="n">
-        <v>2.664243267941177</v>
+        <v>2.664243267941179</v>
       </c>
       <c r="D4" t="n">
-        <v>2.314293797107068</v>
+        <v>2.314293797107067</v>
       </c>
       <c r="E4" t="n">
-        <v>2.676184797679032</v>
+        <v>2.676184797679037</v>
       </c>
       <c r="F4" t="n">
-        <v>2.676184797679031</v>
+        <v>2.676184797679037</v>
       </c>
       <c r="G4" t="n">
-        <v>2.571010893891058</v>
+        <v>2.571010893891048</v>
       </c>
       <c r="H4" t="n">
-        <v>2.433181076270237</v>
+        <v>2.433181076270236</v>
       </c>
       <c r="I4" t="n">
-        <v>2.697359298994125</v>
+        <v>2.697359298994122</v>
       </c>
       <c r="J4" t="n">
-        <v>4.031410477847094</v>
+        <v>4.031410477847092</v>
       </c>
       <c r="K4" t="n">
         <v>1.697361280127093</v>
       </c>
       <c r="L4" t="n">
-        <v>3.60435584459981</v>
+        <v>3.604355844599808</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.324372068760548</v>
+        <v>4.324372068760545</v>
       </c>
       <c r="C5" t="n">
-        <v>27.33647751804322</v>
+        <v>27.33647751804329</v>
       </c>
       <c r="D5" t="n">
-        <v>20.98816053715338</v>
+        <v>20.98816053715341</v>
       </c>
       <c r="E5" t="n">
-        <v>27.33647877373492</v>
+        <v>27.33647877373495</v>
       </c>
       <c r="F5" t="n">
-        <v>27.33647877373492</v>
+        <v>27.33647877373495</v>
       </c>
       <c r="G5" t="n">
-        <v>25.84016370946692</v>
+        <v>25.84016370946691</v>
       </c>
       <c r="H5" t="n">
         <v>25.44814037099825</v>
       </c>
       <c r="I5" t="n">
-        <v>27.33647558488413</v>
+        <v>27.33647558488415</v>
       </c>
       <c r="J5" t="n">
-        <v>52.04573072683235</v>
+        <v>52.04573072683232</v>
       </c>
       <c r="K5" t="n">
-        <v>11.1953018025461</v>
+        <v>11.19530180254607</v>
       </c>
       <c r="L5" t="n">
-        <v>49.1441538524498</v>
+        <v>14.924322307935</v>
       </c>
     </row>
     <row r="6">
@@ -7020,28 +7020,28 @@
         <v>113.4584232177803</v>
       </c>
       <c r="E6" t="n">
-        <v>102.7954782596944</v>
+        <v>102.7954782596945</v>
       </c>
       <c r="F6" t="n">
-        <v>113.8511599707136</v>
+        <v>113.8511599707137</v>
       </c>
       <c r="G6" t="n">
-        <v>135.6148208450698</v>
+        <v>113.7180099067884</v>
       </c>
       <c r="H6" t="n">
-        <v>135.5570484758828</v>
+        <v>135.557048475883</v>
       </c>
       <c r="I6" t="n">
-        <v>113.8443583118916</v>
+        <v>113.8443583118914</v>
       </c>
       <c r="J6" t="n">
-        <v>137.1316151695724</v>
+        <v>120.8554730336598</v>
       </c>
       <c r="K6" t="n">
-        <v>112.8218443311952</v>
+        <v>112.8218443311953</v>
       </c>
       <c r="L6" t="n">
-        <v>114.766228061402</v>
+        <v>114.7662280614021</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.035933076104914</v>
+        <v>2.035933076104913</v>
       </c>
       <c r="C7" t="n">
-        <v>3.496431059133631</v>
+        <v>3.496431059133626</v>
       </c>
       <c r="D7" t="n">
-        <v>3.113362066037795</v>
+        <v>3.11336206603779</v>
       </c>
       <c r="E7" t="n">
-        <v>3.490661226028443</v>
+        <v>3.490661226028442</v>
       </c>
       <c r="F7" t="n">
-        <v>3.490661226028443</v>
+        <v>3.490661226028442</v>
       </c>
       <c r="G7" t="n">
-        <v>3.370080720871413</v>
+        <v>3.370080720871414</v>
       </c>
       <c r="H7" t="n">
-        <v>3.232250903250593</v>
+        <v>3.232250903250592</v>
       </c>
       <c r="I7" t="n">
-        <v>3.496429125974478</v>
+        <v>3.49642912597448</v>
       </c>
       <c r="J7" t="n">
-        <v>4.830480304827453</v>
+        <v>4.830480304827447</v>
       </c>
       <c r="K7" t="n">
-        <v>2.496431107107448</v>
+        <v>2.496431107107445</v>
       </c>
       <c r="L7" t="n">
-        <v>4.403425671580164</v>
+        <v>4.403425671580163</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.210563727100497</v>
+        <v>2.210563727100496</v>
       </c>
       <c r="C8" t="n">
         <v>4.39180480176054</v>
       </c>
       <c r="D8" t="n">
-        <v>4.164692510274147</v>
+        <v>4.164692510274152</v>
       </c>
       <c r="E8" t="n">
         <v>4.193799306014427</v>
       </c>
       <c r="F8" t="n">
-        <v>3.690638372836968</v>
+        <v>3.690638372836973</v>
       </c>
       <c r="G8" t="n">
-        <v>4.270841744141222</v>
+        <v>4.270841744141195</v>
       </c>
       <c r="H8" t="n">
-        <v>4.133011926519126</v>
+        <v>4.133011926519124</v>
       </c>
       <c r="I8" t="n">
         <v>4.397190149244294</v>
       </c>
       <c r="J8" t="n">
-        <v>5.731384032553218</v>
+        <v>5.73138403255321</v>
       </c>
       <c r="K8" t="n">
-        <v>2.657573513724616</v>
+        <v>2.657573513724615</v>
       </c>
       <c r="L8" t="n">
-        <v>6.062690585828175</v>
+        <v>6.062690585828164</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.611660232204687</v>
+        <v>3.611660232204686</v>
       </c>
       <c r="C9" t="n">
-        <v>5.775688899559915</v>
+        <v>5.775688899559899</v>
       </c>
       <c r="D9" t="n">
-        <v>5.392621959133166</v>
+        <v>5.392621959133157</v>
       </c>
       <c r="E9" t="n">
-        <v>6.587549759747738</v>
+        <v>6.587549759747735</v>
       </c>
       <c r="F9" t="n">
-        <v>5.775689887185975</v>
+        <v>5.775689887185959</v>
       </c>
       <c r="G9" t="n">
-        <v>5.649338561297693</v>
+        <v>5.649338561297689</v>
       </c>
       <c r="H9" t="n">
-        <v>5.511508743676877</v>
+        <v>5.511508743676876</v>
       </c>
       <c r="I9" t="n">
-        <v>5.775686966400762</v>
+        <v>5.775686966400761</v>
       </c>
       <c r="J9" t="n">
-        <v>7.109738145253734</v>
+        <v>7.109738145253722</v>
       </c>
       <c r="K9" t="n">
-        <v>4.351522701682145</v>
+        <v>4.35152270168213</v>
       </c>
       <c r="L9" t="n">
-        <v>6.68268351200645</v>
+        <v>6.682683512006439</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.17116489864409</v>
+        <v>39.53065265210493</v>
       </c>
       <c r="C2" t="n">
-        <v>38.60661786482554</v>
+        <v>42.82822308126441</v>
       </c>
       <c r="D2" t="n">
-        <v>36.09302280516369</v>
+        <v>39.73705224428787</v>
       </c>
       <c r="E2" t="n">
-        <v>40.44962506237417</v>
+        <v>44.36814283513358</v>
       </c>
       <c r="F2" t="n">
-        <v>36.31246232970727</v>
+        <v>40.92449498684181</v>
       </c>
       <c r="G2" t="n">
-        <v>35.66220004468602</v>
+        <v>39.71437889808684</v>
       </c>
       <c r="H2" t="n">
-        <v>42.21852475897634</v>
+        <v>40.06040995392646</v>
       </c>
       <c r="I2" t="n">
-        <v>34.80331369253113</v>
+        <v>39.66923953350296</v>
       </c>
       <c r="J2" t="n">
-        <v>48.49588905135727</v>
+        <v>46.05204684694939</v>
       </c>
       <c r="K2" t="n">
-        <v>36.59848283905085</v>
+        <v>40.97548752789438</v>
       </c>
       <c r="L2" t="n">
-        <v>40.0882346496367</v>
+        <v>39.94899396491952</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.30129224383077</v>
+        <v>40.21739230859985</v>
       </c>
       <c r="C3" t="n">
-        <v>43.13138027976595</v>
+        <v>46.41848917186226</v>
       </c>
       <c r="D3" t="n">
-        <v>40.81224124674616</v>
+        <v>41.68200574264366</v>
       </c>
       <c r="E3" t="n">
-        <v>44.975297268117</v>
+        <v>48.95606285676036</v>
       </c>
       <c r="F3" t="n">
-        <v>40.83813453545013</v>
+        <v>43.27169158167909</v>
       </c>
       <c r="G3" t="n">
-        <v>40.3167058275309</v>
+        <v>41.52607901887318</v>
       </c>
       <c r="H3" t="n">
-        <v>47.85862171225588</v>
+        <v>43.99210751074573</v>
       </c>
       <c r="I3" t="n">
-        <v>39.32970539561389</v>
+        <v>41.19970733647136</v>
       </c>
       <c r="J3" t="n">
-        <v>53.9873459093638</v>
+        <v>53.60630393486804</v>
       </c>
       <c r="K3" t="n">
-        <v>41.16018079327044</v>
+        <v>43.42798864181739</v>
       </c>
       <c r="L3" t="n">
-        <v>45.40741630337494</v>
+        <v>43.22218976774576</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.791501674366601</v>
+        <v>3.791501674366591</v>
       </c>
       <c r="C4" t="n">
-        <v>5.330832834053785</v>
+        <v>5.330832834053775</v>
       </c>
       <c r="D4" t="n">
-        <v>6.122880016576084</v>
+        <v>6.122880016576075</v>
       </c>
       <c r="E4" t="n">
-        <v>5.348996098173219</v>
+        <v>5.348996098173211</v>
       </c>
       <c r="F4" t="n">
-        <v>5.348996098173219</v>
+        <v>5.348996098173211</v>
       </c>
       <c r="G4" t="n">
-        <v>5.867246442941797</v>
+        <v>5.867246442941773</v>
       </c>
       <c r="H4" t="n">
-        <v>9.762808368881103</v>
+        <v>9.762808368881077</v>
       </c>
       <c r="I4" t="n">
-        <v>5.359792983243758</v>
+        <v>5.359792983243748</v>
       </c>
       <c r="J4" t="n">
-        <v>9.179079524747694</v>
+        <v>9.179079524747685</v>
       </c>
       <c r="K4" t="n">
-        <v>5.499479230281783</v>
+        <v>5.499479230281777</v>
       </c>
       <c r="L4" t="n">
-        <v>8.497161824330997</v>
+        <v>8.497161824330979</v>
       </c>
     </row>
     <row r="5">
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.54403898228896</v>
+        <v>39.54403898228888</v>
       </c>
       <c r="C5" t="n">
-        <v>65.37125969559892</v>
+        <v>65.37125969559884</v>
       </c>
       <c r="D5" t="n">
-        <v>78.91449425705076</v>
+        <v>78.91449425705075</v>
       </c>
       <c r="E5" t="n">
         <v>65.37126066794788</v>
@@ -7382,22 +7382,22 @@
         <v>65.37126066794788</v>
       </c>
       <c r="G5" t="n">
-        <v>77.35054608116643</v>
+        <v>77.35054608116599</v>
       </c>
       <c r="H5" t="n">
-        <v>152.7977968016693</v>
+        <v>152.7977968016694</v>
       </c>
       <c r="I5" t="n">
-        <v>65.37110879489308</v>
+        <v>65.37110879489309</v>
       </c>
       <c r="J5" t="n">
-        <v>145.4900426867859</v>
+        <v>145.4900426867858</v>
       </c>
       <c r="K5" t="n">
-        <v>69.63745022151367</v>
+        <v>69.63745022151355</v>
       </c>
       <c r="L5" t="n">
-        <v>145.0785683518475</v>
+        <v>46.06276198936966</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.3069211714074</v>
+        <v>123.3069211714075</v>
       </c>
       <c r="C6" t="n">
-        <v>124.8619119677833</v>
+        <v>124.8619119677834</v>
       </c>
       <c r="D6" t="n">
-        <v>125.6555210801152</v>
+        <v>125.6555210801151</v>
       </c>
       <c r="E6" t="n">
-        <v>112.9837772769437</v>
+        <v>112.9837772769435</v>
       </c>
       <c r="F6" t="n">
-        <v>124.8825739572461</v>
+        <v>124.8825739572462</v>
       </c>
       <c r="G6" t="n">
         <v>149.2032200211463</v>
       </c>
       <c r="H6" t="n">
-        <v>153.2328994260409</v>
+        <v>153.232899426041</v>
       </c>
       <c r="I6" t="n">
         <v>148.6957665614482</v>
       </c>
       <c r="J6" t="n">
-        <v>152.5833293003562</v>
+        <v>152.5833293003563</v>
       </c>
       <c r="K6" t="n">
-        <v>125.0170311504759</v>
+        <v>125.0170311504757</v>
       </c>
       <c r="L6" t="n">
-        <v>128.0409593330351</v>
+        <v>128.040959333035</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.941952722905344</v>
+        <v>4.941952722905322</v>
       </c>
       <c r="C7" t="n">
-        <v>6.510394932488298</v>
+        <v>6.510394932488287</v>
       </c>
       <c r="D7" t="n">
-        <v>7.273320471896454</v>
+        <v>7.273320471896435</v>
       </c>
       <c r="E7" t="n">
-        <v>6.509270713601484</v>
+        <v>6.509270713601472</v>
       </c>
       <c r="F7" t="n">
-        <v>6.509270713601484</v>
+        <v>6.509270713601472</v>
       </c>
       <c r="G7" t="n">
-        <v>7.017697491480535</v>
+        <v>7.017697491480523</v>
       </c>
       <c r="H7" t="n">
-        <v>10.91325941741984</v>
+        <v>10.91325941741982</v>
       </c>
       <c r="I7" t="n">
-        <v>6.510244031782502</v>
+        <v>6.510244031782495</v>
       </c>
       <c r="J7" t="n">
-        <v>10.32953057328644</v>
+        <v>10.32953057328641</v>
       </c>
       <c r="K7" t="n">
-        <v>6.649930278820529</v>
+        <v>6.649930278820509</v>
       </c>
       <c r="L7" t="n">
-        <v>9.647612872869733</v>
+        <v>9.647612872869697</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.392495918721529</v>
+        <v>5.392495918721503</v>
       </c>
       <c r="C8" t="n">
-        <v>8.171177798305253</v>
+        <v>8.171177798285864</v>
       </c>
       <c r="D8" t="n">
-        <v>9.18607650984959</v>
+        <v>9.186076509849569</v>
       </c>
       <c r="E8" t="n">
-        <v>7.840058091111817</v>
+        <v>7.840058091111795</v>
       </c>
       <c r="F8" t="n">
-        <v>6.998663475030511</v>
+        <v>6.998663475030498</v>
       </c>
       <c r="G8" t="n">
-        <v>8.679318137596718</v>
+        <v>8.679318137596688</v>
       </c>
       <c r="H8" t="n">
-        <v>12.57488006353698</v>
+        <v>12.57488006353693</v>
       </c>
       <c r="I8" t="n">
-        <v>8.171864677898684</v>
+        <v>8.171864677898666</v>
       </c>
       <c r="J8" t="n">
-        <v>11.99138922904711</v>
+        <v>11.99138922904706</v>
       </c>
       <c r="K8" t="n">
-        <v>7.07797708938317</v>
+        <v>7.077977089383133</v>
       </c>
       <c r="L8" t="n">
-        <v>12.57430518281908</v>
+        <v>12.57430518281901</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.149904778543945</v>
+        <v>8.149904778543906</v>
       </c>
       <c r="C9" t="n">
-        <v>11.00804794014022</v>
+        <v>11.0080479401402</v>
       </c>
       <c r="D9" t="n">
-        <v>11.7709843077375</v>
+        <v>11.77098430773746</v>
       </c>
       <c r="E9" t="n">
-        <v>12.49633444511758</v>
+        <v>12.49633444511754</v>
       </c>
       <c r="F9" t="n">
-        <v>11.00804712662822</v>
+        <v>11.0080471266282</v>
       </c>
       <c r="G9" t="n">
-        <v>11.51535049913247</v>
+        <v>11.51535049913243</v>
       </c>
       <c r="H9" t="n">
-        <v>15.41091242507177</v>
+        <v>15.41091242507174</v>
       </c>
       <c r="I9" t="n">
-        <v>11.00789703943443</v>
+        <v>11.00789703943441</v>
       </c>
       <c r="J9" t="n">
-        <v>14.82718358093837</v>
+        <v>14.82718358093832</v>
       </c>
       <c r="K9" t="n">
-        <v>10.40032558865728</v>
+        <v>10.40032558865725</v>
       </c>
       <c r="L9" t="n">
-        <v>14.14526588052167</v>
+        <v>14.14526588052163</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.73833661561588</v>
+        <v>39.04493957255399</v>
       </c>
       <c r="C2" t="n">
-        <v>36.12449183511968</v>
+        <v>42.32270411766963</v>
       </c>
       <c r="D2" t="n">
-        <v>34.94649984645145</v>
+        <v>39.37166287298752</v>
       </c>
       <c r="E2" t="n">
-        <v>37.94529603681052</v>
+        <v>43.84253650176903</v>
       </c>
       <c r="F2" t="n">
-        <v>33.87360245939875</v>
+        <v>40.45338141098799</v>
       </c>
       <c r="G2" t="n">
-        <v>33.28438422434526</v>
+        <v>39.28418902902357</v>
       </c>
       <c r="H2" t="n">
-        <v>32.94084398235312</v>
+        <v>39.26378152757619</v>
       </c>
       <c r="I2" t="n">
-        <v>32.41286535517309</v>
+        <v>39.23838145905376</v>
       </c>
       <c r="J2" t="n">
-        <v>45.00849884798653</v>
+        <v>45.42319877244569</v>
       </c>
       <c r="K2" t="n">
-        <v>32.53972283161383</v>
+        <v>40.31129174019638</v>
       </c>
       <c r="L2" t="n">
-        <v>37.35694864484914</v>
+        <v>39.50038795146245</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.3436727258761</v>
+        <v>38.76962952449717</v>
       </c>
       <c r="C3" t="n">
-        <v>40.28109400539847</v>
+        <v>45.23574282110591</v>
       </c>
       <c r="D3" t="n">
-        <v>39.48434645847603</v>
+        <v>41.08426258504394</v>
       </c>
       <c r="E3" t="n">
-        <v>42.10274027772071</v>
+        <v>47.74120825172405</v>
       </c>
       <c r="F3" t="n">
-        <v>38.03104670030892</v>
+        <v>42.14678839976361</v>
       </c>
       <c r="G3" t="n">
-        <v>37.57256918684009</v>
+        <v>40.46889365936865</v>
       </c>
       <c r="H3" t="n">
-        <v>37.17821804963535</v>
+        <v>40.34307463746584</v>
       </c>
       <c r="I3" t="n">
-        <v>36.57078173322112</v>
+        <v>40.14124496868283</v>
       </c>
       <c r="J3" t="n">
-        <v>49.99398883913818</v>
+        <v>51.95265467220104</v>
       </c>
       <c r="K3" t="n">
-        <v>36.51064676177901</v>
+        <v>41.5564481244603</v>
       </c>
       <c r="L3" t="n">
-        <v>42.2567183380041</v>
+        <v>42.02269796755363</v>
       </c>
     </row>
     <row r="4">
@@ -7726,34 +7726,34 @@
         <v>1.564543215159968</v>
       </c>
       <c r="C4" t="n">
-        <v>3.717657462514985</v>
+        <v>3.717657462514984</v>
       </c>
       <c r="D4" t="n">
-        <v>5.25503319370068</v>
+        <v>5.255033193700681</v>
       </c>
       <c r="E4" t="n">
-        <v>3.73224335194748</v>
+        <v>3.732243351947479</v>
       </c>
       <c r="F4" t="n">
         <v>3.73224335194748</v>
       </c>
       <c r="G4" t="n">
-        <v>4.267477306830319</v>
+        <v>4.267477306830321</v>
       </c>
       <c r="H4" t="n">
-        <v>4.06291368905392</v>
+        <v>4.062913689053914</v>
       </c>
       <c r="I4" t="n">
         <v>3.752612291270802</v>
       </c>
       <c r="J4" t="n">
-        <v>7.026620110419309</v>
+        <v>7.0266201104193</v>
       </c>
       <c r="K4" t="n">
-        <v>3.01138824594834</v>
+        <v>3.011388245948335</v>
       </c>
       <c r="L4" t="n">
-        <v>6.687221316634377</v>
+        <v>6.687221316634373</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.917416326301144</v>
+        <v>5.917416326301149</v>
       </c>
       <c r="C5" t="n">
-        <v>39.90792598027413</v>
+        <v>39.90792598027414</v>
       </c>
       <c r="D5" t="n">
-        <v>62.27251043392861</v>
+        <v>62.27251043392864</v>
       </c>
       <c r="E5" t="n">
-        <v>39.90792715075635</v>
+        <v>39.90792715075636</v>
       </c>
       <c r="F5" t="n">
-        <v>39.90792715075635</v>
+        <v>39.90792715075636</v>
       </c>
       <c r="G5" t="n">
-        <v>49.42857811603669</v>
+        <v>49.42857811603667</v>
       </c>
       <c r="H5" t="n">
-        <v>48.64817963423644</v>
+        <v>48.64817963423658</v>
       </c>
       <c r="I5" t="n">
-        <v>39.90777563339505</v>
+        <v>39.90777563339501</v>
       </c>
       <c r="J5" t="n">
         <v>103.3170023307412</v>
       </c>
       <c r="K5" t="n">
-        <v>28.25236844656074</v>
+        <v>28.25236844656077</v>
       </c>
       <c r="L5" t="n">
-        <v>21.50122428985073</v>
+        <v>103.9654368604552</v>
       </c>
     </row>
     <row r="6">
@@ -7803,13 +7803,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.8625193353273</v>
+        <v>134.8625193353272</v>
       </c>
       <c r="C6" t="n">
         <v>114.9957285516112</v>
       </c>
       <c r="D6" t="n">
-        <v>116.5519180199829</v>
+        <v>116.5519179537493</v>
       </c>
       <c r="E6" t="n">
         <v>103.9354233056241</v>
@@ -7818,7 +7818,7 @@
         <v>115.0130217570188</v>
       </c>
       <c r="G6" t="n">
-        <v>115.523432494936</v>
+        <v>137.5654534269977</v>
       </c>
       <c r="H6" t="n">
         <v>137.4678211124944</v>
@@ -7827,7 +7827,7 @@
         <v>137.050588411438</v>
       </c>
       <c r="J6" t="n">
-        <v>123.9762995848798</v>
+        <v>123.9762995848797</v>
       </c>
       <c r="K6" t="n">
         <v>114.2412205570437</v>
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.494779852483945</v>
+        <v>2.494779852483951</v>
       </c>
       <c r="C7" t="n">
-        <v>4.682999275473863</v>
+        <v>4.682999275473865</v>
       </c>
       <c r="D7" t="n">
-        <v>6.185265058024386</v>
+        <v>6.185265058024383</v>
       </c>
       <c r="E7" t="n">
-        <v>4.679115399712324</v>
+        <v>4.679115399712323</v>
       </c>
       <c r="F7" t="n">
-        <v>4.679115399712324</v>
+        <v>4.679115399712323</v>
       </c>
       <c r="G7" t="n">
-        <v>5.197713944154299</v>
+        <v>5.1977139441543</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9931503263779</v>
+        <v>4.993150326377897</v>
       </c>
       <c r="I7" t="n">
         <v>4.68284892859478</v>
       </c>
       <c r="J7" t="n">
-        <v>7.956856747743282</v>
+        <v>7.956856747743284</v>
       </c>
       <c r="K7" t="n">
-        <v>3.941624883272318</v>
+        <v>3.941624883272322</v>
       </c>
       <c r="L7" t="n">
-        <v>7.61745795395835</v>
+        <v>7.617457953958359</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.800960802713445</v>
+        <v>2.800960802713448</v>
       </c>
       <c r="C8" t="n">
-        <v>5.915104862452597</v>
+        <v>5.915104862452596</v>
       </c>
       <c r="D8" t="n">
-        <v>7.613645253783451</v>
+        <v>7.613645253783449</v>
       </c>
       <c r="E8" t="n">
-        <v>5.661292142592324</v>
+        <v>5.661292142592321</v>
       </c>
       <c r="F8" t="n">
         <v>5.016329200750484</v>
       </c>
       <c r="G8" t="n">
-        <v>6.433358941871625</v>
+        <v>6.433358941871626</v>
       </c>
       <c r="H8" t="n">
-        <v>6.228795324096671</v>
+        <v>6.228795324096664</v>
       </c>
       <c r="I8" t="n">
-        <v>5.918493926312111</v>
+        <v>5.918493926312106</v>
       </c>
       <c r="J8" t="n">
-        <v>9.192684410460272</v>
+        <v>9.192684410460265</v>
       </c>
       <c r="K8" t="n">
-        <v>4.230540561748034</v>
+        <v>4.230540561748031</v>
       </c>
       <c r="L8" t="n">
-        <v>9.824005868568436</v>
+        <v>9.824005868568433</v>
       </c>
     </row>
     <row r="9">
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.703595021681755</v>
+        <v>4.703595021681753</v>
       </c>
       <c r="C9" t="n">
-        <v>7.822549238734269</v>
+        <v>7.822549238734277</v>
       </c>
       <c r="D9" t="n">
         <v>9.324820685519409</v>
       </c>
       <c r="E9" t="n">
-        <v>8.896598773817857</v>
+        <v>8.896598773817859</v>
       </c>
       <c r="F9" t="n">
-        <v>7.822549882305731</v>
+        <v>7.822549882305733</v>
       </c>
       <c r="G9" t="n">
-        <v>8.337263907414712</v>
+        <v>8.337263907414718</v>
       </c>
       <c r="H9" t="n">
         <v>8.132700289638315</v>
       </c>
       <c r="I9" t="n">
-        <v>7.822398891855192</v>
+        <v>7.822398891855189</v>
       </c>
       <c r="J9" t="n">
-        <v>11.09640671100371</v>
+        <v>11.0964067110037</v>
       </c>
       <c r="K9" t="n">
-        <v>5.909213374246003</v>
+        <v>6.541903826424965</v>
       </c>
       <c r="L9" t="n">
         <v>10.75700791721877</v>

--- a/Results/Ammonia/ammonia resource use fossils results.xlsx
+++ b/Results/Ammonia/ammonia resource use fossils results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.89396451210332</v>
+        <v>39.89396451210336</v>
       </c>
       <c r="C2" t="n">
-        <v>43.11531204630147</v>
+        <v>43.1153120463015</v>
       </c>
       <c r="D2" t="n">
-        <v>39.9747201833106</v>
+        <v>39.97472018331065</v>
       </c>
       <c r="E2" t="n">
-        <v>44.67052959608354</v>
+        <v>44.67052959608356</v>
       </c>
       <c r="F2" t="n">
-        <v>41.18284127568891</v>
+        <v>41.18284127568892</v>
       </c>
       <c r="G2" t="n">
-        <v>39.98401109197933</v>
+        <v>39.98401109197936</v>
       </c>
       <c r="H2" t="n">
-        <v>40.35116886127719</v>
+        <v>40.35116886127724</v>
       </c>
       <c r="I2" t="n">
-        <v>39.91080865471692</v>
+        <v>39.91080865471694</v>
       </c>
       <c r="J2" t="n">
-        <v>46.35415247698372</v>
+        <v>46.35415247698376</v>
       </c>
       <c r="K2" t="n">
-        <v>41.35672400476088</v>
+        <v>41.35672400476093</v>
       </c>
       <c r="L2" t="n">
-        <v>40.23443536241391</v>
+        <v>40.23443536241395</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.52538470085293</v>
+        <v>41.52538470085297</v>
       </c>
       <c r="C3" t="n">
-        <v>46.94111368462546</v>
+        <v>46.94111368462549</v>
       </c>
       <c r="D3" t="n">
-        <v>42.10392277483401</v>
+        <v>42.10392277483405</v>
       </c>
       <c r="E3" t="n">
-        <v>49.5030606578084</v>
+        <v>49.50306065780839</v>
       </c>
       <c r="F3" t="n">
-        <v>43.74599177162282</v>
+        <v>43.74599177162283</v>
       </c>
       <c r="G3" t="n">
-        <v>42.17374782710719</v>
+        <v>42.17374782710723</v>
       </c>
       <c r="H3" t="n">
-        <v>44.81468083487223</v>
+        <v>44.81468083487229</v>
       </c>
       <c r="I3" t="n">
-        <v>41.64631868249835</v>
+        <v>41.6463186824984</v>
       </c>
       <c r="J3" t="n">
         <v>53.92227067878848</v>
       </c>
       <c r="K3" t="n">
-        <v>44.37538452665594</v>
+        <v>44.37538452665595</v>
       </c>
       <c r="L3" t="n">
-        <v>43.98261510676959</v>
+        <v>43.98261510676967</v>
       </c>
     </row>
     <row r="4">
@@ -595,22 +595,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.824555706130826</v>
+        <v>5.824555706130832</v>
       </c>
       <c r="C4" t="n">
-        <v>5.986415281912098</v>
+        <v>5.986415281912102</v>
       </c>
       <c r="D4" t="n">
-        <v>6.736728161861283</v>
+        <v>6.736728161861285</v>
       </c>
       <c r="E4" t="n">
-        <v>6.007545955334662</v>
+        <v>6.007545955334669</v>
       </c>
       <c r="F4" t="n">
-        <v>6.007545955334665</v>
+        <v>6.007545955334669</v>
       </c>
       <c r="G4" t="n">
-        <v>6.841942935244687</v>
+        <v>6.841942935244682</v>
       </c>
       <c r="H4" t="n">
         <v>10.97891825737618</v>
@@ -619,13 +619,13 @@
         <v>6.01635305657539</v>
       </c>
       <c r="J4" t="n">
-        <v>9.369824171885766</v>
+        <v>9.369824171885762</v>
       </c>
       <c r="K4" t="n">
         <v>6.71653703536199</v>
       </c>
       <c r="L4" t="n">
-        <v>9.651112255151977</v>
+        <v>9.651112255151979</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.84226036526408</v>
+        <v>76.84226036526418</v>
       </c>
       <c r="C5" t="n">
-        <v>81.10134376455318</v>
+        <v>81.10134376455345</v>
       </c>
       <c r="D5" t="n">
         <v>96.50762295332407</v>
       </c>
       <c r="E5" t="n">
-        <v>81.10134464462077</v>
+        <v>81.10134464462092</v>
       </c>
       <c r="F5" t="n">
-        <v>81.10134464462077</v>
+        <v>81.10134464462092</v>
       </c>
       <c r="G5" t="n">
-        <v>100.7106224461239</v>
+        <v>100.7106224461235</v>
       </c>
       <c r="H5" t="n">
-        <v>199.435328415429</v>
+        <v>199.4353284154291</v>
       </c>
       <c r="I5" t="n">
-        <v>81.10111890448201</v>
+        <v>81.10111890448226</v>
       </c>
       <c r="J5" t="n">
         <v>154.8784268808508</v>
       </c>
       <c r="K5" t="n">
-        <v>96.1120485350185</v>
+        <v>96.1120485350186</v>
       </c>
       <c r="L5" t="n">
-        <v>176.3165863365548</v>
+        <v>176.3165863365552</v>
       </c>
     </row>
     <row r="6">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133.5928877198342</v>
+        <v>133.5928877198341</v>
       </c>
       <c r="C6" t="n">
-        <v>133.7616977022629</v>
+        <v>133.761697702263</v>
       </c>
       <c r="D6" t="n">
-        <v>134.5195350239059</v>
+        <v>134.5195350239061</v>
       </c>
       <c r="E6" t="n">
         <v>121.0641146946522</v>
       </c>
       <c r="F6" t="n">
-        <v>133.7923509218805</v>
+        <v>133.7923509218806</v>
       </c>
       <c r="G6" t="n">
         <v>160.1892650335897</v>
@@ -702,10 +702,10 @@
         <v>162.7873071981606</v>
       </c>
       <c r="K6" t="n">
-        <v>134.4984787744292</v>
+        <v>134.4984787744294</v>
       </c>
       <c r="L6" t="n">
-        <v>137.4527097376681</v>
+        <v>137.452709737668</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.189842887971276</v>
+        <v>7.18984288797129</v>
       </c>
       <c r="C7" t="n">
-        <v>7.381865098486912</v>
+        <v>7.381865098486916</v>
       </c>
       <c r="D7" t="n">
-        <v>8.102000284789732</v>
+        <v>8.10200028478973</v>
       </c>
       <c r="E7" t="n">
-        <v>7.382319333803894</v>
+        <v>7.382319333803901</v>
       </c>
       <c r="F7" t="n">
-        <v>7.382319333803897</v>
+        <v>7.382319333803901</v>
       </c>
       <c r="G7" t="n">
-        <v>8.207230117085132</v>
+        <v>8.207230117085137</v>
       </c>
       <c r="H7" t="n">
         <v>12.34420543921664</v>
       </c>
       <c r="I7" t="n">
-        <v>7.381640238415845</v>
+        <v>7.381640238415848</v>
       </c>
       <c r="J7" t="n">
         <v>10.73511135372622</v>
       </c>
       <c r="K7" t="n">
-        <v>8.081824217202445</v>
+        <v>8.081824217202442</v>
       </c>
       <c r="L7" t="n">
-        <v>11.01639943699244</v>
+        <v>11.01639943699243</v>
       </c>
     </row>
     <row r="8">
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.783123164024652</v>
+        <v>7.783123164024661</v>
       </c>
       <c r="C8" t="n">
-        <v>9.459807822491761</v>
+        <v>9.45980782249177</v>
       </c>
       <c r="D8" t="n">
-        <v>10.48693057024743</v>
+        <v>10.48693057024744</v>
       </c>
       <c r="E8" t="n">
-        <v>9.053897641691478</v>
+        <v>9.053897641691485</v>
       </c>
       <c r="F8" t="n">
-        <v>8.022464040266849</v>
+        <v>8.022464040266854</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2844423794946</v>
+        <v>10.28444237949462</v>
       </c>
       <c r="H8" t="n">
-        <v>14.42141770162662</v>
+        <v>14.42141770162664</v>
       </c>
       <c r="I8" t="n">
         <v>9.458852500825326</v>
@@ -785,7 +785,7 @@
         <v>8.647539694942608</v>
       </c>
       <c r="L8" t="n">
-        <v>14.64370274154933</v>
+        <v>14.64370274154934</v>
       </c>
     </row>
     <row r="9">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.49242049144982</v>
+        <v>11.49242049144983</v>
       </c>
       <c r="C9" t="n">
-        <v>13.35615399483911</v>
+        <v>13.35615399483912</v>
       </c>
       <c r="D9" t="n">
         <v>14.07630462975435</v>
@@ -807,19 +807,19 @@
         <v>15.28527186001478</v>
       </c>
       <c r="F9" t="n">
-        <v>13.35615267239145</v>
+        <v>13.35615267239146</v>
       </c>
       <c r="G9" t="n">
-        <v>14.18151901343733</v>
+        <v>14.18151901343734</v>
       </c>
       <c r="H9" t="n">
-        <v>18.31849433556883</v>
+        <v>18.31849433556884</v>
       </c>
       <c r="I9" t="n">
         <v>13.35592913476805</v>
       </c>
       <c r="J9" t="n">
-        <v>16.70940025007842</v>
+        <v>16.70940025007841</v>
       </c>
       <c r="K9" t="n">
         <v>11.95113009541437</v>
@@ -911,34 +911,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.82516479012548</v>
+        <v>38.82516479012549</v>
       </c>
       <c r="C2" t="n">
-        <v>41.96801060703181</v>
+        <v>41.96801060703185</v>
       </c>
       <c r="D2" t="n">
-        <v>39.01159572512179</v>
+        <v>39.01159572512181</v>
       </c>
       <c r="E2" t="n">
-        <v>43.47634830483077</v>
+        <v>43.47634830483079</v>
       </c>
       <c r="F2" t="n">
-        <v>40.11750409995546</v>
+        <v>40.11750409995552</v>
       </c>
       <c r="G2" t="n">
-        <v>38.99161333243863</v>
+        <v>38.99161333243859</v>
       </c>
       <c r="H2" t="n">
-        <v>38.96100627776218</v>
+        <v>38.96100627776216</v>
       </c>
       <c r="I2" t="n">
-        <v>38.93481661974662</v>
+        <v>38.93481661974663</v>
       </c>
       <c r="J2" t="n">
         <v>45.00100235709159</v>
       </c>
       <c r="K2" t="n">
-        <v>39.98779555746675</v>
+        <v>39.98779555746677</v>
       </c>
       <c r="L2" t="n">
         <v>38.96839604882285</v>
@@ -954,31 +954,31 @@
         <v>38.52323501677817</v>
       </c>
       <c r="C3" t="n">
-        <v>44.3106695144361</v>
+        <v>44.31066951443614</v>
       </c>
       <c r="D3" t="n">
-        <v>39.84510954020712</v>
+        <v>39.8451095402071</v>
       </c>
       <c r="E3" t="n">
-        <v>46.79784209851467</v>
+        <v>46.79784209851466</v>
       </c>
       <c r="F3" t="n">
-        <v>41.25345651803036</v>
+        <v>41.25345651803035</v>
       </c>
       <c r="G3" t="n">
-        <v>39.70614651539605</v>
+        <v>39.70614651539603</v>
       </c>
       <c r="H3" t="n">
-        <v>39.50578285744215</v>
+        <v>39.50578285744219</v>
       </c>
       <c r="I3" t="n">
-        <v>39.3012458487898</v>
+        <v>39.30124584878984</v>
       </c>
       <c r="J3" t="n">
-        <v>50.75595538428271</v>
+        <v>50.7559553842827</v>
       </c>
       <c r="K3" t="n">
-        <v>40.88253054142606</v>
+        <v>40.88253054142613</v>
       </c>
       <c r="L3" t="n">
         <v>39.55759550052311</v>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.244126713048698</v>
+        <v>1.244126713048685</v>
       </c>
       <c r="C4" t="n">
         <v>2.438497048399757</v>
       </c>
       <c r="D4" t="n">
-        <v>3.349949886299079</v>
+        <v>3.349949886299083</v>
       </c>
       <c r="E4" t="n">
         <v>2.452393127290688</v>
       </c>
       <c r="F4" t="n">
-        <v>2.452393127290685</v>
+        <v>2.452393127290688</v>
       </c>
       <c r="G4" t="n">
-        <v>3.124672464251734</v>
+        <v>3.12467246425172</v>
       </c>
       <c r="H4" t="n">
-        <v>2.800711727963275</v>
+        <v>2.800711727963269</v>
       </c>
       <c r="I4" t="n">
-        <v>2.485271998463304</v>
+        <v>2.485271998463306</v>
       </c>
       <c r="J4" t="n">
-        <v>5.440956630848355</v>
+        <v>5.440956630848343</v>
       </c>
       <c r="K4" t="n">
-        <v>2.159884797291032</v>
+        <v>2.159884797291016</v>
       </c>
       <c r="L4" t="n">
-        <v>2.87499029912843</v>
+        <v>2.874990299128425</v>
       </c>
     </row>
     <row r="5">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.744709436545508</v>
+        <v>3.744709436545509</v>
       </c>
       <c r="C5" t="n">
-        <v>23.28024493923709</v>
+        <v>23.2802449392371</v>
       </c>
       <c r="D5" t="n">
-        <v>36.485075001074</v>
+        <v>36.48507500107402</v>
       </c>
       <c r="E5" t="n">
         <v>23.28024640982802</v>
@@ -1046,22 +1046,22 @@
         <v>23.28024640982802</v>
       </c>
       <c r="G5" t="n">
-        <v>34.38616457735175</v>
+        <v>34.38616457735181</v>
       </c>
       <c r="H5" t="n">
         <v>31.78464601607829</v>
       </c>
       <c r="I5" t="n">
-        <v>23.28006772866162</v>
+        <v>23.28006772866168</v>
       </c>
       <c r="J5" t="n">
-        <v>77.92563444184395</v>
+        <v>77.92563444184358</v>
       </c>
       <c r="K5" t="n">
         <v>17.53879721760876</v>
       </c>
       <c r="L5" t="n">
-        <v>35.20540133908863</v>
+        <v>35.20540133908855</v>
       </c>
     </row>
     <row r="6">
@@ -1071,13 +1071,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.4176223750569</v>
+        <v>112.417622375057</v>
       </c>
       <c r="C6" t="n">
         <v>113.6396951956017</v>
       </c>
       <c r="D6" t="n">
-        <v>136.4869008777441</v>
+        <v>136.4869008777442</v>
       </c>
       <c r="E6" t="n">
         <v>102.5852398161879</v>
@@ -1092,7 +1092,7 @@
         <v>136.0102972780772</v>
       </c>
       <c r="I6" t="n">
-        <v>113.6587676604715</v>
+        <v>113.6587676604716</v>
       </c>
       <c r="J6" t="n">
         <v>122.2998015728126</v>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.092544722623883</v>
+        <v>2.092544722623875</v>
       </c>
       <c r="C7" t="n">
         <v>3.333867218613948</v>
       </c>
       <c r="D7" t="n">
-        <v>4.198367112450857</v>
+        <v>4.198367112450852</v>
       </c>
       <c r="E7" t="n">
-        <v>3.326895985600878</v>
+        <v>3.32689598560088</v>
       </c>
       <c r="F7" t="n">
-        <v>3.326895985600878</v>
+        <v>3.32689598560088</v>
       </c>
       <c r="G7" t="n">
-        <v>3.973090473826928</v>
+        <v>3.97309047382692</v>
       </c>
       <c r="H7" t="n">
-        <v>3.649129737538474</v>
+        <v>3.649129737538456</v>
       </c>
       <c r="I7" t="n">
         <v>3.333690008038501</v>
       </c>
       <c r="J7" t="n">
-        <v>6.289374640423555</v>
+        <v>6.289374640423538</v>
       </c>
       <c r="K7" t="n">
-        <v>3.008302806866213</v>
+        <v>3.008302806866211</v>
       </c>
       <c r="L7" t="n">
-        <v>3.72340830870362</v>
+        <v>3.723408308703613</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.325342867341404</v>
+        <v>2.325342867341407</v>
       </c>
       <c r="C8" t="n">
-        <v>4.370542635852704</v>
+        <v>4.37054263585271</v>
       </c>
       <c r="D8" t="n">
-        <v>5.409605312396461</v>
+        <v>5.40960531239647</v>
       </c>
       <c r="E8" t="n">
-        <v>4.149611396101174</v>
+        <v>4.14961139610118</v>
       </c>
       <c r="F8" t="n">
-        <v>3.588196110208</v>
+        <v>3.588196110208004</v>
       </c>
       <c r="G8" t="n">
-        <v>5.016286591493665</v>
+        <v>5.016286591493664</v>
       </c>
       <c r="H8" t="n">
-        <v>4.692325855206859</v>
+        <v>4.692325855206851</v>
       </c>
       <c r="I8" t="n">
-        <v>4.376886125705241</v>
+        <v>4.376886125705249</v>
       </c>
       <c r="J8" t="n">
-        <v>7.33273002336789</v>
+        <v>7.332730023367882</v>
       </c>
       <c r="K8" t="n">
-        <v>3.226047393276886</v>
+        <v>3.226047393276879</v>
       </c>
       <c r="L8" t="n">
-        <v>5.613132872427233</v>
+        <v>5.613132872427246</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.77740870801619</v>
+        <v>3.777408708016182</v>
       </c>
       <c r="C9" t="n">
-        <v>5.773035222424358</v>
+        <v>5.773035222424362</v>
       </c>
       <c r="D9" t="n">
-        <v>6.637536661660221</v>
+        <v>6.637536661660228</v>
       </c>
       <c r="E9" t="n">
-        <v>6.643487785238574</v>
+        <v>6.64348778523858</v>
       </c>
       <c r="F9" t="n">
-        <v>5.773036341005483</v>
+        <v>5.77303634100549</v>
       </c>
       <c r="G9" t="n">
-        <v>6.412258477637332</v>
+        <v>6.412258477637331</v>
       </c>
       <c r="H9" t="n">
-        <v>6.08829774134888</v>
+        <v>6.088297741348869</v>
       </c>
       <c r="I9" t="n">
-        <v>5.772858011848908</v>
+        <v>5.772858011848915</v>
       </c>
       <c r="J9" t="n">
-        <v>8.728542644233952</v>
+        <v>8.72854264423397</v>
       </c>
       <c r="K9" t="n">
         <v>5.010424420508627</v>
       </c>
       <c r="L9" t="n">
-        <v>6.162576312514026</v>
+        <v>6.162576312514025</v>
       </c>
     </row>
   </sheetData>
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.64419315755702</v>
+        <v>41.64419315755704</v>
       </c>
       <c r="C2" t="n">
         <v>40.81143021191213</v>
       </c>
       <c r="D2" t="n">
-        <v>41.77368766205468</v>
+        <v>41.77368766205469</v>
       </c>
       <c r="E2" t="n">
-        <v>40.94910171922232</v>
+        <v>40.94910171922233</v>
       </c>
       <c r="F2" t="n">
         <v>40.9491017409734</v>
@@ -1325,19 +1325,19 @@
         <v>41.76810202322032</v>
       </c>
       <c r="H2" t="n">
-        <v>41.90823715439376</v>
+        <v>41.90823715439377</v>
       </c>
       <c r="I2" t="n">
-        <v>41.72945834880769</v>
+        <v>41.7294583488077</v>
       </c>
       <c r="J2" t="n">
-        <v>43.17987863514766</v>
+        <v>43.17987863514769</v>
       </c>
       <c r="K2" t="n">
-        <v>42.41633430544261</v>
+        <v>42.41633430544262</v>
       </c>
       <c r="L2" t="n">
-        <v>41.71491044936107</v>
+        <v>41.71491044936108</v>
       </c>
     </row>
     <row r="3">
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.58581490763001</v>
+        <v>42.58581490763002</v>
       </c>
       <c r="C3" t="n">
-        <v>41.19870948100025</v>
+        <v>41.19870948100027</v>
       </c>
       <c r="D3" t="n">
-        <v>43.50626147366209</v>
+        <v>43.50626147366211</v>
       </c>
       <c r="E3" t="n">
-        <v>41.90395766845104</v>
+        <v>41.90395766845108</v>
       </c>
       <c r="F3" t="n">
-        <v>41.90395769020211</v>
+        <v>41.90395769020214</v>
       </c>
       <c r="G3" t="n">
-        <v>43.46944097604786</v>
+        <v>43.46944097604787</v>
       </c>
       <c r="H3" t="n">
-        <v>44.48878905033553</v>
+        <v>44.48878905033555</v>
       </c>
       <c r="I3" t="n">
         <v>43.19212544582736</v>
       </c>
       <c r="J3" t="n">
-        <v>46.7476436341604</v>
+        <v>46.74764363416043</v>
       </c>
       <c r="K3" t="n">
-        <v>44.46860465879421</v>
+        <v>44.46860465879422</v>
       </c>
       <c r="L3" t="n">
         <v>43.11235351739845</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.193974122904982</v>
+        <v>3.193974122904986</v>
       </c>
       <c r="C4" t="n">
-        <v>3.089111490883496</v>
+        <v>3.089111490883507</v>
       </c>
       <c r="D4" t="n">
-        <v>4.656674121621076</v>
+        <v>4.656674121621075</v>
       </c>
       <c r="E4" t="n">
-        <v>4.138750767931356</v>
+        <v>4.138750767931355</v>
       </c>
       <c r="F4" t="n">
-        <v>4.138750767931356</v>
+        <v>4.138750767931354</v>
       </c>
       <c r="G4" t="n">
         <v>4.592226568336049</v>
       </c>
       <c r="H4" t="n">
-        <v>6.184963277018491</v>
+        <v>6.184963277018484</v>
       </c>
       <c r="I4" t="n">
-        <v>4.147822532044172</v>
+        <v>4.147822532044168</v>
       </c>
       <c r="J4" t="n">
-        <v>6.539047224464577</v>
+        <v>6.539047224464586</v>
       </c>
       <c r="K4" t="n">
-        <v>4.452586949572826</v>
+        <v>4.452586949572833</v>
       </c>
       <c r="L4" t="n">
-        <v>4.015242539908719</v>
+        <v>4.015242539908721</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.77286854937946</v>
+        <v>33.77286854937948</v>
       </c>
       <c r="C5" t="n">
-        <v>32.99736338349763</v>
+        <v>32.99736338349768</v>
       </c>
       <c r="D5" t="n">
-        <v>58.94594336370767</v>
+        <v>58.94594336370766</v>
       </c>
       <c r="E5" t="n">
-        <v>50.47334724204188</v>
+        <v>50.47334724204187</v>
       </c>
       <c r="F5" t="n">
         <v>50.47334724204188</v>
       </c>
       <c r="G5" t="n">
-        <v>59.43569780760382</v>
+        <v>59.43569780760387</v>
       </c>
       <c r="H5" t="n">
-        <v>97.04319100712834</v>
+        <v>97.04319100712848</v>
       </c>
       <c r="I5" t="n">
-        <v>50.47321358375636</v>
+        <v>50.47321358375638</v>
       </c>
       <c r="J5" t="n">
-        <v>97.22458350337422</v>
+        <v>97.22458350337413</v>
       </c>
       <c r="K5" t="n">
-        <v>55.51041190293618</v>
+        <v>55.51041190293628</v>
       </c>
       <c r="L5" t="n">
-        <v>54.32035584851548</v>
+        <v>54.32035584851549</v>
       </c>
     </row>
     <row r="6">
@@ -1467,19 +1467,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>143.9938059248152</v>
+        <v>143.9938059248151</v>
       </c>
       <c r="C6" t="n">
-        <v>120.5553893133561</v>
+        <v>120.5553893133562</v>
       </c>
       <c r="D6" t="n">
-        <v>122.1159608933655</v>
+        <v>122.1159608933656</v>
       </c>
       <c r="E6" t="n">
         <v>109.9022324936318</v>
       </c>
       <c r="F6" t="n">
-        <v>121.6002885126127</v>
+        <v>121.6002885126129</v>
       </c>
       <c r="G6" t="n">
         <v>122.0401948961221</v>
@@ -1488,7 +1488,7 @@
         <v>147.1582402182156</v>
       </c>
       <c r="I6" t="n">
-        <v>121.5957908598303</v>
+        <v>121.5957908598304</v>
       </c>
       <c r="J6" t="n">
         <v>147.4155634226884</v>
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.320379620410352</v>
+        <v>4.320379620410346</v>
       </c>
       <c r="C7" t="n">
-        <v>4.284890140975693</v>
+        <v>4.284890140975705</v>
       </c>
       <c r="D7" t="n">
-        <v>5.783078462188338</v>
+        <v>5.783078462188328</v>
       </c>
       <c r="E7" t="n">
-        <v>5.274689096383833</v>
+        <v>5.274689096383838</v>
       </c>
       <c r="F7" t="n">
-        <v>5.274689096383833</v>
+        <v>5.274689096383839</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7186320658414</v>
+        <v>5.718632065841423</v>
       </c>
       <c r="H7" t="n">
-        <v>7.311368774523861</v>
+        <v>7.311368774523863</v>
       </c>
       <c r="I7" t="n">
-        <v>5.27422802954954</v>
+        <v>5.274228029549541</v>
       </c>
       <c r="J7" t="n">
-        <v>7.665452721969943</v>
+        <v>7.665452721969948</v>
       </c>
       <c r="K7" t="n">
-        <v>5.578992447078197</v>
+        <v>5.578992447078204</v>
       </c>
       <c r="L7" t="n">
-        <v>5.141648037414084</v>
+        <v>5.141648037414089</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.772133968423943</v>
+        <v>4.772133968423932</v>
       </c>
       <c r="C8" t="n">
-        <v>5.941003158680562</v>
+        <v>5.941003158680566</v>
       </c>
       <c r="D8" t="n">
-        <v>7.6882741460458</v>
+        <v>7.688274146045804</v>
       </c>
       <c r="E8" t="n">
-        <v>6.601194883396872</v>
+        <v>6.60119488339687</v>
       </c>
       <c r="F8" t="n">
-        <v>5.764471284214405</v>
+        <v>5.764471284214406</v>
       </c>
       <c r="G8" t="n">
-        <v>7.37420662909419</v>
+        <v>7.374206629094184</v>
       </c>
       <c r="H8" t="n">
-        <v>8.966943337781515</v>
+        <v>8.966943337781519</v>
       </c>
       <c r="I8" t="n">
-        <v>6.929802592802313</v>
+        <v>6.929802592802307</v>
       </c>
       <c r="J8" t="n">
-        <v>9.321263868518752</v>
+        <v>9.321263868518765</v>
       </c>
       <c r="K8" t="n">
-        <v>6.008385216716846</v>
+        <v>6.008385216716845</v>
       </c>
       <c r="L8" t="n">
-        <v>8.054713475558817</v>
+        <v>8.054713475558797</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.934511713944657</v>
+        <v>6.93451171394466</v>
       </c>
       <c r="C9" t="n">
-        <v>8.021004993924862</v>
+        <v>8.02100499392488</v>
       </c>
       <c r="D9" t="n">
-        <v>9.519195286788678</v>
+        <v>9.51919528678869</v>
       </c>
       <c r="E9" t="n">
-        <v>10.30522054650621</v>
+        <v>10.3052205465062</v>
       </c>
       <c r="F9" t="n">
-        <v>9.010475704585122</v>
+        <v>9.010475704585126</v>
       </c>
       <c r="G9" t="n">
-        <v>9.454746918790576</v>
+        <v>9.454746918790589</v>
       </c>
       <c r="H9" t="n">
         <v>11.04748362747302</v>
       </c>
       <c r="I9" t="n">
-        <v>9.01034288249871</v>
+        <v>9.010342882498708</v>
       </c>
       <c r="J9" t="n">
-        <v>11.40156757491911</v>
+        <v>11.40156757491912</v>
       </c>
       <c r="K9" t="n">
-        <v>8.665026425521237</v>
+        <v>8.665026425521239</v>
       </c>
       <c r="L9" t="n">
-        <v>8.877762890363259</v>
+        <v>8.877762890363252</v>
       </c>
     </row>
   </sheetData>
@@ -1709,7 +1709,7 @@
         <v>40.56076130789975</v>
       </c>
       <c r="D2" t="n">
-        <v>41.5153534257341</v>
+        <v>41.51535342573409</v>
       </c>
       <c r="E2" t="n">
         <v>40.58282179528175</v>
@@ -1718,22 +1718,22 @@
         <v>40.58282054736654</v>
       </c>
       <c r="G2" t="n">
-        <v>41.48450271306984</v>
+        <v>41.48450271306985</v>
       </c>
       <c r="H2" t="n">
-        <v>41.53623126787917</v>
+        <v>41.53623126787918</v>
       </c>
       <c r="I2" t="n">
         <v>41.41968620515169</v>
       </c>
       <c r="J2" t="n">
-        <v>42.80263194231093</v>
+        <v>42.80263194231092</v>
       </c>
       <c r="K2" t="n">
-        <v>42.01561564008128</v>
+        <v>42.01561564008125</v>
       </c>
       <c r="L2" t="n">
-        <v>41.41562786092037</v>
+        <v>41.41562786092038</v>
       </c>
     </row>
     <row r="3">
@@ -1743,34 +1743,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.9165715392181</v>
+        <v>41.91657153921813</v>
       </c>
       <c r="C3" t="n">
-        <v>40.69616933004057</v>
+        <v>40.69616933004058</v>
       </c>
       <c r="D3" t="n">
-        <v>42.88744779644043</v>
+        <v>42.88744779644045</v>
       </c>
       <c r="E3" t="n">
-        <v>40.82511241515169</v>
+        <v>40.82511241515165</v>
       </c>
       <c r="F3" t="n">
-        <v>40.82511116723645</v>
+        <v>40.82511116723649</v>
       </c>
       <c r="G3" t="n">
         <v>42.66973561940192</v>
       </c>
       <c r="H3" t="n">
-        <v>43.05493256316469</v>
+        <v>43.0549325631647</v>
       </c>
       <c r="I3" t="n">
         <v>42.20655146173947</v>
       </c>
       <c r="J3" t="n">
-        <v>45.70131636440535</v>
+        <v>45.70131636440538</v>
       </c>
       <c r="K3" t="n">
-        <v>43.2464692718999</v>
+        <v>43.24646927189988</v>
       </c>
       <c r="L3" t="n">
         <v>42.19526784877328</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.126787786971164</v>
+        <v>2.126787786971171</v>
       </c>
       <c r="C4" t="n">
-        <v>2.331465242233455</v>
+        <v>2.331465242233454</v>
       </c>
       <c r="D4" t="n">
-        <v>3.668207748909381</v>
+        <v>3.668207748909357</v>
       </c>
       <c r="E4" t="n">
-        <v>2.560584729409121</v>
+        <v>2.560584729409122</v>
       </c>
       <c r="F4" t="n">
-        <v>2.56058472940912</v>
+        <v>2.560584729409122</v>
       </c>
       <c r="G4" t="n">
-        <v>3.318217563211358</v>
+        <v>3.318217563211363</v>
       </c>
       <c r="H4" t="n">
-        <v>3.917785442315348</v>
+        <v>3.917785442315343</v>
       </c>
       <c r="I4" t="n">
-        <v>2.577211360711126</v>
+        <v>2.577211360711127</v>
       </c>
       <c r="J4" t="n">
-        <v>5.077323763837854</v>
+        <v>5.077323763837857</v>
       </c>
       <c r="K4" t="n">
-        <v>2.70419703470539</v>
+        <v>2.704197034705397</v>
       </c>
       <c r="L4" t="n">
-        <v>2.562704122317586</v>
+        <v>2.562704122317566</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.70608169825508</v>
+        <v>17.70608169825511</v>
       </c>
       <c r="C5" t="n">
-        <v>22.17461559279452</v>
+        <v>22.17461559279456</v>
       </c>
       <c r="D5" t="n">
-        <v>43.37676541258674</v>
+        <v>43.37676541258685</v>
       </c>
       <c r="E5" t="n">
-        <v>25.23134145918819</v>
+        <v>25.23134145918822</v>
       </c>
       <c r="F5" t="n">
-        <v>25.23134145918819</v>
+        <v>25.23134145918822</v>
       </c>
       <c r="G5" t="n">
-        <v>38.4924082496464</v>
+        <v>38.49240824964635</v>
       </c>
       <c r="H5" t="n">
-        <v>53.4947265761697</v>
+        <v>53.49472657616965</v>
       </c>
       <c r="I5" t="n">
         <v>25.23114151761409</v>
       </c>
       <c r="J5" t="n">
-        <v>70.65820134778301</v>
+        <v>70.65820134778302</v>
       </c>
       <c r="K5" t="n">
-        <v>27.09409683673648</v>
+        <v>27.09409683673652</v>
       </c>
       <c r="L5" t="n">
-        <v>28.06728019748337</v>
+        <v>28.0672801974834</v>
       </c>
     </row>
     <row r="6">
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>135.3068493342829</v>
+        <v>135.306849334283</v>
       </c>
       <c r="C6" t="n">
-        <v>113.526687974328</v>
+        <v>113.5266879743281</v>
       </c>
       <c r="D6" t="n">
-        <v>136.8849891250599</v>
+        <v>136.8849891250598</v>
       </c>
       <c r="E6" t="n">
-        <v>102.6676886842213</v>
+        <v>102.6676886842214</v>
       </c>
       <c r="F6" t="n">
         <v>113.7479417662453</v>
@@ -1887,13 +1887,13 @@
         <v>113.7473273747328</v>
       </c>
       <c r="J6" t="n">
-        <v>121.9284216303427</v>
+        <v>121.9284216303428</v>
       </c>
       <c r="K6" t="n">
         <v>113.8628331084323</v>
       </c>
       <c r="L6" t="n">
-        <v>113.7358931191763</v>
+        <v>113.7358931191764</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.082439752560047</v>
+        <v>3.082439752560036</v>
       </c>
       <c r="C7" t="n">
-        <v>3.342914000526056</v>
+        <v>3.342914000526055</v>
       </c>
       <c r="D7" t="n">
-        <v>4.62385908910105</v>
+        <v>4.623859089101044</v>
       </c>
       <c r="E7" t="n">
-        <v>3.531934971393492</v>
+        <v>3.531934971393496</v>
       </c>
       <c r="F7" t="n">
-        <v>3.531934971393492</v>
+        <v>3.531934971393496</v>
       </c>
       <c r="G7" t="n">
-        <v>4.273869528800248</v>
+        <v>4.273869528800232</v>
       </c>
       <c r="H7" t="n">
-        <v>4.873437407904235</v>
+        <v>4.873437407904212</v>
       </c>
       <c r="I7" t="n">
-        <v>3.532863326300007</v>
+        <v>3.532863326300009</v>
       </c>
       <c r="J7" t="n">
         <v>6.032975729426734</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65984900029427</v>
+        <v>3.65984900029426</v>
       </c>
       <c r="L7" t="n">
-        <v>3.518356087906469</v>
+        <v>3.518356087906465</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.426215568189613</v>
+        <v>3.426215568189645</v>
       </c>
       <c r="C8" t="n">
-        <v>4.672689852059539</v>
+        <v>4.672689852059516</v>
       </c>
       <c r="D8" t="n">
-        <v>6.159170208530192</v>
+        <v>6.159170208530191</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5930372370129</v>
+        <v>4.593037237012926</v>
       </c>
       <c r="F8" t="n">
-        <v>3.907449436511162</v>
+        <v>3.907449436511166</v>
       </c>
       <c r="G8" t="n">
-        <v>5.604540817557107</v>
+        <v>5.604540817557101</v>
       </c>
       <c r="H8" t="n">
-        <v>6.204108696664598</v>
+        <v>6.204108696664583</v>
       </c>
       <c r="I8" t="n">
-        <v>4.863534615056866</v>
+        <v>4.863534615056849</v>
       </c>
       <c r="J8" t="n">
-        <v>7.363840969879581</v>
+        <v>7.363840969879564</v>
       </c>
       <c r="K8" t="n">
-        <v>3.985292725977244</v>
+        <v>3.985292725977234</v>
       </c>
       <c r="L8" t="n">
-        <v>5.879922219771718</v>
+        <v>5.879922219771712</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.899306418040782</v>
+        <v>4.899306418040762</v>
       </c>
       <c r="C9" t="n">
-        <v>5.996720454476503</v>
+        <v>5.996720454476508</v>
       </c>
       <c r="D9" t="n">
-        <v>7.277666898157119</v>
+        <v>7.277666898157108</v>
       </c>
       <c r="E9" t="n">
-        <v>7.152680484131347</v>
+        <v>7.15268048413134</v>
       </c>
       <c r="F9" t="n">
-        <v>6.186869188034015</v>
+        <v>6.186869188034006</v>
       </c>
       <c r="G9" t="n">
-        <v>6.927675982750695</v>
+        <v>6.927675982750685</v>
       </c>
       <c r="H9" t="n">
-        <v>7.527243861854688</v>
+        <v>7.527243861854673</v>
       </c>
       <c r="I9" t="n">
-        <v>6.186669780250456</v>
+        <v>6.186669780250451</v>
       </c>
       <c r="J9" t="n">
-        <v>8.686782183377192</v>
+        <v>8.68678218337719</v>
       </c>
       <c r="K9" t="n">
-        <v>5.82872956080169</v>
+        <v>5.828729560801683</v>
       </c>
       <c r="L9" t="n">
-        <v>6.17216254185693</v>
+        <v>6.172162541856919</v>
       </c>
     </row>
   </sheetData>
@@ -2102,34 +2102,34 @@
         <v>41.2460699385739</v>
       </c>
       <c r="C2" t="n">
-        <v>40.38836854980381</v>
+        <v>40.38836854980379</v>
       </c>
       <c r="D2" t="n">
         <v>41.3817478899368</v>
       </c>
       <c r="E2" t="n">
-        <v>40.36141218606083</v>
+        <v>40.36141218606084</v>
       </c>
       <c r="F2" t="n">
-        <v>40.3614097330695</v>
+        <v>40.36140973306954</v>
       </c>
       <c r="G2" t="n">
         <v>41.33598756670268</v>
       </c>
       <c r="H2" t="n">
-        <v>41.35477654470904</v>
+        <v>41.35477654470905</v>
       </c>
       <c r="I2" t="n">
-        <v>41.25264667647166</v>
+        <v>41.25264667647168</v>
       </c>
       <c r="J2" t="n">
-        <v>42.51726525827617</v>
+        <v>42.51726525827615</v>
       </c>
       <c r="K2" t="n">
-        <v>41.83031544108881</v>
+        <v>41.83031544108883</v>
       </c>
       <c r="L2" t="n">
-        <v>41.26562953415561</v>
+        <v>41.26562953415562</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.52820581922867</v>
+        <v>41.52820581922865</v>
       </c>
       <c r="C3" t="n">
-        <v>40.29191057797387</v>
+        <v>40.29191057797384</v>
       </c>
       <c r="D3" t="n">
-        <v>42.49401485975861</v>
+        <v>42.49401485975864</v>
       </c>
       <c r="E3" t="n">
-        <v>40.10352317913296</v>
+        <v>40.10352317913291</v>
       </c>
       <c r="F3" t="n">
-        <v>40.10352072614158</v>
+        <v>40.10352072614164</v>
       </c>
       <c r="G3" t="n">
-        <v>42.16944366435347</v>
+        <v>42.16944366435352</v>
       </c>
       <c r="H3" t="n">
         <v>42.31610221270574</v>
       </c>
       <c r="I3" t="n">
-        <v>41.57470554332495</v>
+        <v>41.57470554332496</v>
       </c>
       <c r="J3" t="n">
-        <v>44.85493333314216</v>
+        <v>44.85493333314221</v>
       </c>
       <c r="K3" t="n">
-        <v>42.59709166806486</v>
+        <v>42.59709166806493</v>
       </c>
       <c r="L3" t="n">
-        <v>41.68003431162788</v>
+        <v>41.68003431162789</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.404396318169562</v>
+        <v>1.404396318169564</v>
       </c>
       <c r="C4" t="n">
-        <v>1.727283214050158</v>
+        <v>1.727283214050161</v>
       </c>
       <c r="D4" t="n">
-        <v>2.936941193754655</v>
+        <v>2.936941193754651</v>
       </c>
       <c r="E4" t="n">
-        <v>1.441289755780093</v>
+        <v>1.441289755780095</v>
       </c>
       <c r="F4" t="n">
-        <v>1.441289755780094</v>
+        <v>1.441289755780095</v>
       </c>
       <c r="G4" t="n">
-        <v>2.418423502985684</v>
+        <v>2.418423502985683</v>
       </c>
       <c r="H4" t="n">
-        <v>2.645853157865109</v>
+        <v>2.645853157865113</v>
       </c>
       <c r="I4" t="n">
-        <v>1.467475690016822</v>
+        <v>1.467475690016826</v>
       </c>
       <c r="J4" t="n">
-        <v>3.931406135070428</v>
+        <v>3.931406135070431</v>
       </c>
       <c r="K4" t="n">
-        <v>1.620946900252223</v>
+        <v>1.620946900252222</v>
       </c>
       <c r="L4" t="n">
-        <v>1.643553409361677</v>
+        <v>1.643553409361678</v>
       </c>
     </row>
     <row r="5">
@@ -2219,34 +2219,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.069407099502662</v>
+        <v>8.069407099502671</v>
       </c>
       <c r="C5" t="n">
-        <v>14.36922459481774</v>
+        <v>14.36922459481777</v>
       </c>
       <c r="D5" t="n">
-        <v>33.86322960671388</v>
+        <v>33.86322960671381</v>
       </c>
       <c r="E5" t="n">
-        <v>9.144951426994464</v>
+        <v>9.144951426994476</v>
       </c>
       <c r="F5" t="n">
-        <v>9.144951426994464</v>
+        <v>9.144951426994476</v>
       </c>
       <c r="G5" t="n">
-        <v>25.76776711265529</v>
+        <v>25.76776711265528</v>
       </c>
       <c r="H5" t="n">
-        <v>32.45263733916728</v>
+        <v>32.45263733916736</v>
       </c>
       <c r="I5" t="n">
-        <v>9.144704593585594</v>
+        <v>9.144704593585598</v>
       </c>
       <c r="J5" t="n">
         <v>53.27266517306207</v>
       </c>
       <c r="K5" t="n">
-        <v>11.53668788540248</v>
+        <v>11.53668788540251</v>
       </c>
       <c r="L5" t="n">
         <v>13.50678699381556</v>
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.5132876934122</v>
+        <v>112.5132876934123</v>
       </c>
       <c r="C6" t="n">
-        <v>112.8577487748116</v>
+        <v>112.8577487748117</v>
       </c>
       <c r="D6" t="n">
-        <v>114.0726415891649</v>
+        <v>114.0726415891651</v>
       </c>
       <c r="E6" t="n">
-        <v>101.4944914869267</v>
+        <v>101.4944914869269</v>
       </c>
       <c r="F6" t="n">
-        <v>112.5739687106238</v>
+        <v>112.5739687106239</v>
       </c>
       <c r="G6" t="n">
-        <v>135.4549969249881</v>
+        <v>135.4549969249882</v>
       </c>
       <c r="H6" t="n">
         <v>135.7956452785585</v>
       </c>
       <c r="I6" t="n">
-        <v>134.5040491120194</v>
+        <v>134.5040491120193</v>
       </c>
       <c r="J6" t="n">
-        <v>137.0269085587977</v>
+        <v>137.0269085587978</v>
       </c>
       <c r="K6" t="n">
-        <v>112.7122517051722</v>
+        <v>112.7122517051723</v>
       </c>
       <c r="L6" t="n">
-        <v>112.7549947558273</v>
+        <v>112.7549947558274</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.277613182307954</v>
+        <v>2.277613182307958</v>
       </c>
       <c r="C7" t="n">
-        <v>2.641491866728491</v>
+        <v>2.641491866728492</v>
       </c>
       <c r="D7" t="n">
         <v>3.810156586586329</v>
       </c>
       <c r="E7" t="n">
-        <v>2.337574103390425</v>
+        <v>2.33757410339043</v>
       </c>
       <c r="F7" t="n">
-        <v>2.337574103390425</v>
+        <v>2.33757410339043</v>
       </c>
       <c r="G7" t="n">
-        <v>3.291640367124078</v>
+        <v>3.291640367124079</v>
       </c>
       <c r="H7" t="n">
-        <v>3.519070022003506</v>
+        <v>3.519070022003507</v>
       </c>
       <c r="I7" t="n">
-        <v>2.340692554155217</v>
+        <v>2.340692554155221</v>
       </c>
       <c r="J7" t="n">
-        <v>4.804622999208824</v>
+        <v>4.804622999208826</v>
       </c>
       <c r="K7" t="n">
         <v>2.494163764390617</v>
       </c>
       <c r="L7" t="n">
-        <v>2.516770273500069</v>
+        <v>2.516770273500073</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.554987816636188</v>
+        <v>2.554987816636189</v>
       </c>
       <c r="C8" t="n">
-        <v>3.782485707282038</v>
+        <v>3.782485707282043</v>
       </c>
       <c r="D8" t="n">
-        <v>5.133918452578223</v>
+        <v>5.133918452578219</v>
       </c>
       <c r="E8" t="n">
-        <v>3.245238403921556</v>
+        <v>3.245238403921565</v>
       </c>
       <c r="F8" t="n">
-        <v>2.643779605645741</v>
+        <v>2.643779605645747</v>
       </c>
       <c r="G8" t="n">
-        <v>4.435690045623581</v>
+        <v>4.435690045623589</v>
       </c>
       <c r="H8" t="n">
-        <v>4.663119700504786</v>
+        <v>4.663119700504788</v>
       </c>
       <c r="I8" t="n">
-        <v>3.484742232654729</v>
+        <v>3.48474223265473</v>
       </c>
       <c r="J8" t="n">
-        <v>5.948843002940871</v>
+        <v>5.948843002940873</v>
       </c>
       <c r="K8" t="n">
-        <v>2.755439464934907</v>
+        <v>2.75543946493491</v>
       </c>
       <c r="L8" t="n">
-        <v>4.566134504668451</v>
+        <v>4.566134504668455</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.670339827454671</v>
+        <v>3.670339827454674</v>
       </c>
       <c r="C9" t="n">
-        <v>4.719897558429659</v>
+        <v>4.719897558429667</v>
       </c>
       <c r="D9" t="n">
-        <v>5.88856435981262</v>
+        <v>5.888564359812621</v>
       </c>
       <c r="E9" t="n">
-        <v>5.2106041699912</v>
+        <v>5.210604169991206</v>
       </c>
       <c r="F9" t="n">
-        <v>4.419344645762736</v>
+        <v>4.41934464576274</v>
       </c>
       <c r="G9" t="n">
         <v>5.37004605882525</v>
       </c>
       <c r="H9" t="n">
-        <v>5.597475713704679</v>
+        <v>5.59747571370468</v>
       </c>
       <c r="I9" t="n">
-        <v>4.419098245856385</v>
+        <v>4.419098245856392</v>
       </c>
       <c r="J9" t="n">
-        <v>6.883028690909995</v>
+        <v>6.88302869091</v>
       </c>
       <c r="K9" t="n">
-        <v>4.159166206290248</v>
+        <v>4.15916620629025</v>
       </c>
       <c r="L9" t="n">
-        <v>4.59517596520124</v>
+        <v>4.595175965201247</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.23730920896681</v>
+        <v>41.23730920896679</v>
       </c>
       <c r="C2" t="n">
         <v>40.41349646573113</v>
       </c>
       <c r="D2" t="n">
-        <v>41.3489725231013</v>
+        <v>41.34897252310127</v>
       </c>
       <c r="E2" t="n">
-        <v>40.59233136895633</v>
+        <v>40.59233136895634</v>
       </c>
       <c r="F2" t="n">
-        <v>40.59233082113058</v>
+        <v>40.59233082113059</v>
       </c>
       <c r="G2" t="n">
-        <v>41.35779124592228</v>
+        <v>41.35779124592226</v>
       </c>
       <c r="H2" t="n">
-        <v>41.53004316305198</v>
+        <v>41.530043163052</v>
       </c>
       <c r="I2" t="n">
-        <v>41.31603155521825</v>
+        <v>41.31603155521827</v>
       </c>
       <c r="J2" t="n">
-        <v>42.89533167303797</v>
+        <v>42.895331673038</v>
       </c>
       <c r="K2" t="n">
-        <v>42.03313083330244</v>
+        <v>42.03313083330242</v>
       </c>
       <c r="L2" t="n">
-        <v>41.32441588522249</v>
+        <v>41.3244158852225</v>
       </c>
     </row>
     <row r="3">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.74236337287607</v>
+        <v>41.74236337287608</v>
       </c>
       <c r="C3" t="n">
         <v>40.11973815815449</v>
@@ -2544,25 +2544,25 @@
         <v>42.53665444395484</v>
       </c>
       <c r="E3" t="n">
-        <v>41.10797653738754</v>
+        <v>41.10797653738755</v>
       </c>
       <c r="F3" t="n">
-        <v>41.10797598956178</v>
+        <v>41.10797598956183</v>
       </c>
       <c r="G3" t="n">
-        <v>42.60158921893041</v>
+        <v>42.60158921893039</v>
       </c>
       <c r="H3" t="n">
-        <v>43.84335823003386</v>
+        <v>43.84335823003389</v>
       </c>
       <c r="I3" t="n">
-        <v>42.30262006083346</v>
+        <v>42.30262006083347</v>
       </c>
       <c r="J3" t="n">
-        <v>46.33627464307374</v>
+        <v>46.33627464307376</v>
       </c>
       <c r="K3" t="n">
-        <v>43.69231786279175</v>
+        <v>43.69231786279177</v>
       </c>
       <c r="L3" t="n">
         <v>42.37964775759337</v>
@@ -2578,34 +2578,34 @@
         <v>2.16590987837429</v>
       </c>
       <c r="C4" t="n">
-        <v>1.536407182503502</v>
+        <v>1.536407182503505</v>
       </c>
       <c r="D4" t="n">
-        <v>3.42719837918571</v>
+        <v>3.427198379185708</v>
       </c>
       <c r="E4" t="n">
-        <v>3.031107598009075</v>
+        <v>3.031107598009081</v>
       </c>
       <c r="F4" t="n">
-        <v>3.031107598009075</v>
+        <v>3.031107598009081</v>
       </c>
       <c r="G4" t="n">
-        <v>3.525491275020541</v>
+        <v>3.525491275020546</v>
       </c>
       <c r="H4" t="n">
-        <v>5.471875088448229</v>
+        <v>5.47187508844824</v>
       </c>
       <c r="I4" t="n">
-        <v>3.046089780765816</v>
+        <v>3.046089780765822</v>
       </c>
       <c r="J4" t="n">
-        <v>5.985659771109654</v>
+        <v>5.98565977110966</v>
       </c>
       <c r="K4" t="n">
-        <v>3.480966867013052</v>
+        <v>3.480966867013056</v>
       </c>
       <c r="L4" t="n">
-        <v>3.165742403779588</v>
+        <v>3.165742403779586</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.90088610746994</v>
+        <v>17.90088610746998</v>
       </c>
       <c r="C5" t="n">
-        <v>7.718577332692728</v>
+        <v>7.718577332692735</v>
       </c>
       <c r="D5" t="n">
-        <v>39.92968146768204</v>
+        <v>39.92968146768202</v>
       </c>
       <c r="E5" t="n">
-        <v>33.57738121416598</v>
+        <v>33.57738121416608</v>
       </c>
       <c r="F5" t="n">
-        <v>33.57738121416598</v>
+        <v>33.57738121416608</v>
       </c>
       <c r="G5" t="n">
-        <v>42.87443192398785</v>
+        <v>42.87443192398793</v>
       </c>
       <c r="H5" t="n">
         <v>86.04925037617257</v>
       </c>
       <c r="I5" t="n">
-        <v>33.57724033404389</v>
+        <v>33.57724033404403</v>
       </c>
       <c r="J5" t="n">
-        <v>89.96306698312682</v>
+        <v>89.96306698312689</v>
       </c>
       <c r="K5" t="n">
-        <v>41.05038885317887</v>
+        <v>41.05038885317884</v>
       </c>
       <c r="L5" t="n">
-        <v>40.316807181786</v>
+        <v>40.31680718178603</v>
       </c>
     </row>
     <row r="6">
@@ -2655,22 +2655,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119.5458353698725</v>
+        <v>119.5458353698728</v>
       </c>
       <c r="C6" t="n">
-        <v>118.9272814870454</v>
+        <v>118.9272814870456</v>
       </c>
       <c r="D6" t="n">
-        <v>120.8127953798546</v>
+        <v>120.8127953798545</v>
       </c>
       <c r="E6" t="n">
         <v>108.7337841409256</v>
       </c>
       <c r="F6" t="n">
-        <v>120.4297301733839</v>
+        <v>120.429730173384</v>
       </c>
       <c r="G6" t="n">
-        <v>120.9054167665188</v>
+        <v>120.9054167665191</v>
       </c>
       <c r="H6" t="n">
         <v>146.2864435798573</v>
@@ -2682,7 +2682,7 @@
         <v>129.3704527068454</v>
       </c>
       <c r="K6" t="n">
-        <v>120.8680385075915</v>
+        <v>120.8680385075916</v>
       </c>
       <c r="L6" t="n">
         <v>120.551682770953</v>
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.208498406084247</v>
+        <v>3.208498406084254</v>
       </c>
       <c r="C7" t="n">
-        <v>2.657810417125378</v>
+        <v>2.657810417125386</v>
       </c>
       <c r="D7" t="n">
-        <v>4.469788017186667</v>
+        <v>4.46978801718667</v>
       </c>
       <c r="E7" t="n">
-        <v>4.087786099801953</v>
+        <v>4.087786099801963</v>
       </c>
       <c r="F7" t="n">
-        <v>4.087786099801953</v>
+        <v>4.087786099801963</v>
       </c>
       <c r="G7" t="n">
-        <v>4.568079802730502</v>
+        <v>4.568079802730507</v>
       </c>
       <c r="H7" t="n">
-        <v>6.514463616158185</v>
+        <v>6.514463616158202</v>
       </c>
       <c r="I7" t="n">
-        <v>4.088678308475774</v>
+        <v>4.088678308475783</v>
       </c>
       <c r="J7" t="n">
-        <v>7.028248298819612</v>
+        <v>7.028248298819623</v>
       </c>
       <c r="K7" t="n">
-        <v>4.523555394723011</v>
+        <v>4.523555394723015</v>
       </c>
       <c r="L7" t="n">
-        <v>4.208330931489545</v>
+        <v>4.20833093148955</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.60340598104387</v>
+        <v>3.603405981043877</v>
       </c>
       <c r="C8" t="n">
-        <v>4.151548512030828</v>
+        <v>4.151548512030839</v>
       </c>
       <c r="D8" t="n">
-        <v>6.192322877188987</v>
+        <v>6.192322877189</v>
       </c>
       <c r="E8" t="n">
-        <v>5.281917034112332</v>
+        <v>5.281917034112341</v>
       </c>
       <c r="F8" t="n">
-        <v>4.51796594017606</v>
+        <v>4.517965940176069</v>
       </c>
       <c r="G8" t="n">
-        <v>6.062603257200205</v>
+        <v>6.062603257200219</v>
       </c>
       <c r="H8" t="n">
-        <v>8.00898707063277</v>
+        <v>8.008987070632788</v>
       </c>
       <c r="I8" t="n">
-        <v>5.583201762945481</v>
+        <v>5.583201762945494</v>
       </c>
       <c r="J8" t="n">
-        <v>8.522987857430701</v>
+        <v>8.522987857430714</v>
       </c>
       <c r="K8" t="n">
-        <v>4.898037040342923</v>
+        <v>4.898037040342932</v>
       </c>
       <c r="L8" t="n">
-        <v>6.851495118742366</v>
+        <v>6.851495118742381</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.442003597945633</v>
+        <v>5.442003597945648</v>
       </c>
       <c r="C9" t="n">
-        <v>5.878400236186013</v>
+        <v>5.878400236186032</v>
       </c>
       <c r="D9" t="n">
-        <v>7.690377326763683</v>
+        <v>7.690377326763711</v>
       </c>
       <c r="E9" t="n">
-        <v>8.448483347735294</v>
+        <v>8.448483347735317</v>
       </c>
       <c r="F9" t="n">
-        <v>7.309408261055763</v>
+        <v>7.309408261055786</v>
       </c>
       <c r="G9" t="n">
-        <v>7.788669621791136</v>
+        <v>7.788669621791156</v>
       </c>
       <c r="H9" t="n">
-        <v>9.735053435218827</v>
+        <v>9.735053435218845</v>
       </c>
       <c r="I9" t="n">
-        <v>7.309268127536411</v>
+        <v>7.30926812753643</v>
       </c>
       <c r="J9" t="n">
-        <v>10.24883811788025</v>
+        <v>10.24883811788026</v>
       </c>
       <c r="K9" t="n">
-        <v>7.172224756901184</v>
+        <v>7.172224756901195</v>
       </c>
       <c r="L9" t="n">
-        <v>7.428920750550183</v>
+        <v>7.428920750550198</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.86202786548662</v>
+        <v>40.86202786548665</v>
       </c>
       <c r="C2" t="n">
-        <v>40.13634422690648</v>
+        <v>40.13634422690645</v>
       </c>
       <c r="D2" t="n">
-        <v>40.91235761709054</v>
+        <v>40.91235761709056</v>
       </c>
       <c r="E2" t="n">
-        <v>40.17172710214477</v>
+        <v>40.17172710214481</v>
       </c>
       <c r="F2" t="n">
-        <v>40.17172518188841</v>
+        <v>40.17172518188845</v>
       </c>
       <c r="G2" t="n">
-        <v>40.90531027902679</v>
+        <v>40.9053102790268</v>
       </c>
       <c r="H2" t="n">
-        <v>40.98240275124753</v>
+        <v>40.98240275124756</v>
       </c>
       <c r="I2" t="n">
-        <v>40.88959905615865</v>
+        <v>40.88959905615867</v>
       </c>
       <c r="J2" t="n">
-        <v>42.3178464003548</v>
+        <v>42.31784640035478</v>
       </c>
       <c r="K2" t="n">
-        <v>41.51149137960066</v>
+        <v>41.51149137960068</v>
       </c>
       <c r="L2" t="n">
-        <v>40.86398065162833</v>
+        <v>40.86398065162838</v>
       </c>
     </row>
     <row r="3">
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.11355974841658</v>
+        <v>41.11355974841659</v>
       </c>
       <c r="C3" t="n">
         <v>39.80113308070288</v>
       </c>
       <c r="D3" t="n">
-        <v>41.4715314763522</v>
+        <v>41.47153147635219</v>
       </c>
       <c r="E3" t="n">
-        <v>40.12464463984642</v>
+        <v>40.12464463984639</v>
       </c>
       <c r="F3" t="n">
         <v>40.12464271959004</v>
@@ -2949,19 +2949,19 @@
         <v>41.42215280059364</v>
       </c>
       <c r="H3" t="n">
-        <v>41.97947633125951</v>
+        <v>41.97947633125953</v>
       </c>
       <c r="I3" t="n">
         <v>41.30966308939077</v>
       </c>
       <c r="J3" t="n">
-        <v>44.40055890646345</v>
+        <v>44.40055890646342</v>
       </c>
       <c r="K3" t="n">
         <v>42.29729728328305</v>
       </c>
       <c r="L3" t="n">
-        <v>41.13538844787261</v>
+        <v>41.13538844787264</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.37225789712999</v>
+        <v>1.372257897130002</v>
       </c>
       <c r="C4" t="n">
-        <v>1.067611800155217</v>
+        <v>1.067611800155213</v>
       </c>
       <c r="D4" t="n">
-        <v>1.940755594325708</v>
+        <v>1.940755594325717</v>
       </c>
       <c r="E4" t="n">
-        <v>1.661957453036494</v>
+        <v>1.66195745303649</v>
       </c>
       <c r="F4" t="n">
-        <v>1.661957453036494</v>
+        <v>1.661957453036491</v>
       </c>
       <c r="G4" t="n">
-        <v>1.860041042714721</v>
+        <v>1.86004104271468</v>
       </c>
       <c r="H4" t="n">
-        <v>2.735426752396442</v>
+        <v>2.73542675239645</v>
       </c>
       <c r="I4" t="n">
-        <v>1.67602844900801</v>
+        <v>1.676028449008006</v>
       </c>
       <c r="J4" t="n">
-        <v>3.190579002991822</v>
+        <v>3.190579002991819</v>
       </c>
       <c r="K4" t="n">
-        <v>1.603640396540361</v>
+        <v>1.603640396540355</v>
       </c>
       <c r="L4" t="n">
-        <v>1.406137588419983</v>
+        <v>1.406137588419976</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.494104533049576</v>
+        <v>7.494104533049541</v>
       </c>
       <c r="C5" t="n">
-        <v>3.222705943293238</v>
+        <v>3.222705943293221</v>
       </c>
       <c r="D5" t="n">
-        <v>16.90932202341599</v>
+        <v>16.90932202341595</v>
       </c>
       <c r="E5" t="n">
-        <v>12.64557071748264</v>
+        <v>12.64557071748265</v>
       </c>
       <c r="F5" t="n">
-        <v>12.64557071748264</v>
+        <v>12.64557071748265</v>
       </c>
       <c r="G5" t="n">
-        <v>15.97630483443813</v>
+        <v>15.97630483443822</v>
       </c>
       <c r="H5" t="n">
         <v>34.14574872043301</v>
       </c>
       <c r="I5" t="n">
-        <v>12.64549936368542</v>
+        <v>12.6454993636854</v>
       </c>
       <c r="J5" t="n">
-        <v>40.02699418661097</v>
+        <v>40.02699418661096</v>
       </c>
       <c r="K5" t="n">
-        <v>11.22026276985199</v>
+        <v>11.2202627698517</v>
       </c>
       <c r="L5" t="n">
-        <v>8.854282811165179</v>
+        <v>8.854282811165209</v>
       </c>
     </row>
     <row r="6">
@@ -3051,16 +3051,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.4783849016422</v>
+        <v>112.478384901642</v>
       </c>
       <c r="C6" t="n">
-        <v>112.2053963614667</v>
+        <v>112.2053963614666</v>
       </c>
       <c r="D6" t="n">
         <v>134.9892491112798</v>
       </c>
       <c r="E6" t="n">
-        <v>101.7165208968201</v>
+        <v>101.7165208968203</v>
       </c>
       <c r="F6" t="n">
         <v>112.7830361716032</v>
@@ -3069,19 +3069,19 @@
         <v>112.9661680472268</v>
       </c>
       <c r="H6" t="n">
-        <v>135.8974596637213</v>
+        <v>135.8974596637214</v>
       </c>
       <c r="I6" t="n">
         <v>134.690981032502</v>
       </c>
       <c r="J6" t="n">
-        <v>136.2699076002103</v>
+        <v>136.2699076002102</v>
       </c>
       <c r="K6" t="n">
-        <v>112.7038909996829</v>
+        <v>112.7038909996736</v>
       </c>
       <c r="L6" t="n">
-        <v>112.5127172897129</v>
+        <v>112.512717289713</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.218740945294163</v>
+        <v>2.218740945294094</v>
       </c>
       <c r="C7" t="n">
-        <v>1.977375937982242</v>
+        <v>1.977375937982227</v>
       </c>
       <c r="D7" t="n">
-        <v>2.787241907935533</v>
+        <v>2.787241907935515</v>
       </c>
       <c r="E7" t="n">
-        <v>2.520924023310785</v>
+        <v>2.520924023310779</v>
       </c>
       <c r="F7" t="n">
-        <v>2.520924023310785</v>
+        <v>2.520924023310779</v>
       </c>
       <c r="G7" t="n">
-        <v>2.706524090878905</v>
+        <v>2.706524090878855</v>
       </c>
       <c r="H7" t="n">
-        <v>3.581909800560613</v>
+        <v>3.581909800560547</v>
       </c>
       <c r="I7" t="n">
-        <v>2.522511497172189</v>
+        <v>2.522511497172183</v>
       </c>
       <c r="J7" t="n">
-        <v>4.037062051155994</v>
+        <v>4.03706205115592</v>
       </c>
       <c r="K7" t="n">
-        <v>2.450123444704535</v>
+        <v>2.450123444704461</v>
       </c>
       <c r="L7" t="n">
-        <v>2.25262063658416</v>
+        <v>2.252620636584201</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.485710849693348</v>
+        <v>2.485710849693302</v>
       </c>
       <c r="C8" t="n">
-        <v>3.096064288218387</v>
+        <v>3.096064288218354</v>
       </c>
       <c r="D8" t="n">
-        <v>4.084268564033028</v>
+        <v>4.084268564032994</v>
       </c>
       <c r="E8" t="n">
-        <v>3.408105570753552</v>
+        <v>3.408105570753558</v>
       </c>
       <c r="F8" t="n">
-        <v>2.815604874756687</v>
+        <v>2.815604874756689</v>
       </c>
       <c r="G8" t="n">
-        <v>3.826647148449035</v>
+        <v>3.826647148449007</v>
       </c>
       <c r="H8" t="n">
-        <v>4.702032858136784</v>
+        <v>4.702032858136762</v>
       </c>
       <c r="I8" t="n">
-        <v>3.642634554742326</v>
+        <v>3.642634554742309</v>
       </c>
       <c r="J8" t="n">
-        <v>5.157352776074067</v>
+        <v>5.157352776073996</v>
       </c>
       <c r="K8" t="n">
-        <v>2.701245591425517</v>
+        <v>2.701245591425513</v>
       </c>
       <c r="L8" t="n">
-        <v>4.263933500571723</v>
+        <v>4.263933500571719</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.632605728476192</v>
+        <v>3.632605728476207</v>
       </c>
       <c r="C9" t="n">
-        <v>4.07975788160393</v>
+        <v>4.079757881603914</v>
       </c>
       <c r="D9" t="n">
-        <v>4.889620971512564</v>
+        <v>4.889620971512544</v>
       </c>
       <c r="E9" t="n">
-        <v>5.419498908908245</v>
+        <v>5.419498908908232</v>
       </c>
       <c r="F9" t="n">
-        <v>4.624964443949082</v>
+        <v>4.624964443949073</v>
       </c>
       <c r="G9" t="n">
-        <v>4.808906034500608</v>
+        <v>4.808906034500554</v>
       </c>
       <c r="H9" t="n">
-        <v>5.684291744182318</v>
+        <v>5.684291744182364</v>
       </c>
       <c r="I9" t="n">
-        <v>4.624893440793897</v>
+        <v>4.624893440793879</v>
       </c>
       <c r="J9" t="n">
-        <v>6.139443994777697</v>
+        <v>6.139443994777724</v>
       </c>
       <c r="K9" t="n">
-        <v>4.153576003650089</v>
+        <v>4.153576003650036</v>
       </c>
       <c r="L9" t="n">
-        <v>4.355002580205863</v>
+        <v>4.355002580205832</v>
       </c>
     </row>
   </sheetData>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.77280998630033</v>
+        <v>40.77280998630035</v>
       </c>
       <c r="C2" t="n">
-        <v>40.03936330144668</v>
+        <v>40.03936330144667</v>
       </c>
       <c r="D2" t="n">
-        <v>40.82966361828824</v>
+        <v>40.82966361828825</v>
       </c>
       <c r="E2" t="n">
-        <v>40.04236045150699</v>
+        <v>40.042360451507</v>
       </c>
       <c r="F2" t="n">
-        <v>40.04235749866795</v>
+        <v>40.04235749866798</v>
       </c>
       <c r="G2" t="n">
-        <v>40.7956467375101</v>
+        <v>40.79564673751006</v>
       </c>
       <c r="H2" t="n">
-        <v>40.86071675155624</v>
+        <v>40.86071675155626</v>
       </c>
       <c r="I2" t="n">
-        <v>40.77850992687081</v>
+        <v>40.7785099268708</v>
       </c>
       <c r="J2" t="n">
-        <v>42.00978458888304</v>
+        <v>42.00978458888306</v>
       </c>
       <c r="K2" t="n">
-        <v>41.44414419994202</v>
+        <v>41.44414419994201</v>
       </c>
       <c r="L2" t="n">
         <v>40.76400605172694</v>
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.96312274504498</v>
+        <v>40.96312274504499</v>
       </c>
       <c r="C3" t="n">
-        <v>39.7078146057607</v>
+        <v>39.70781460576071</v>
       </c>
       <c r="D3" t="n">
-        <v>41.36773309463089</v>
+        <v>41.36773309463091</v>
       </c>
       <c r="E3" t="n">
-        <v>39.78831221085949</v>
+        <v>39.78831221085946</v>
       </c>
       <c r="F3" t="n">
-        <v>39.78830925802047</v>
+        <v>39.78830925802042</v>
       </c>
       <c r="G3" t="n">
-        <v>41.12588517280857</v>
+        <v>41.12588517280859</v>
       </c>
       <c r="H3" t="n">
-        <v>41.59492721040269</v>
+        <v>41.59492721040272</v>
       </c>
       <c r="I3" t="n">
         <v>41.00349551793991</v>
       </c>
       <c r="J3" t="n">
-        <v>43.30455388401612</v>
+        <v>43.30455388401613</v>
       </c>
       <c r="K3" t="n">
-        <v>42.05695488832086</v>
+        <v>42.05695488832087</v>
       </c>
       <c r="L3" t="n">
-        <v>40.90519268899493</v>
+        <v>40.90519268899494</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.044026760363056</v>
+        <v>1.044026760363009</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8907724971678058</v>
+        <v>0.8907724971677952</v>
       </c>
       <c r="D4" t="n">
-        <v>1.686214687629467</v>
+        <v>1.686214687629437</v>
       </c>
       <c r="E4" t="n">
         <v>1.080276484003171</v>
       </c>
       <c r="F4" t="n">
-        <v>1.080276484003171</v>
+        <v>1.08027648400317</v>
       </c>
       <c r="G4" t="n">
-        <v>1.30087450866896</v>
+        <v>1.300874508668783</v>
       </c>
       <c r="H4" t="n">
-        <v>2.039069060142809</v>
+        <v>2.039069060142844</v>
       </c>
       <c r="I4" t="n">
-        <v>1.100774013766608</v>
+        <v>1.100774013766647</v>
       </c>
       <c r="J4" t="n">
-        <v>1.660384142964324</v>
+        <v>1.660384142964299</v>
       </c>
       <c r="K4" t="n">
-        <v>1.015029684430749</v>
+        <v>1.015029684430745</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9530633027969133</v>
+        <v>0.9530633027969454</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.104435651046057</v>
+        <v>4.104435651046046</v>
       </c>
       <c r="C5" t="n">
-        <v>2.374384213529016</v>
+        <v>2.374384213529017</v>
       </c>
       <c r="D5" t="n">
-        <v>14.8630774191552</v>
+        <v>14.86307741915519</v>
       </c>
       <c r="E5" t="n">
-        <v>5.075995043185731</v>
+        <v>5.075995043185702</v>
       </c>
       <c r="F5" t="n">
-        <v>5.075995043185731</v>
+        <v>5.075995043185696</v>
       </c>
       <c r="G5" t="n">
-        <v>8.54923629609879</v>
+        <v>8.549236296098545</v>
       </c>
       <c r="H5" t="n">
-        <v>23.39865488584779</v>
+        <v>23.39865488584777</v>
       </c>
       <c r="I5" t="n">
-        <v>5.0759205071839</v>
+        <v>5.075920507183881</v>
       </c>
       <c r="J5" t="n">
-        <v>15.11170590937949</v>
+        <v>15.11170590937954</v>
       </c>
       <c r="K5" t="n">
-        <v>3.465344191408824</v>
+        <v>3.465344191408844</v>
       </c>
       <c r="L5" t="n">
-        <v>2.64906821919035</v>
+        <v>2.649068219190339</v>
       </c>
     </row>
     <row r="6">
@@ -3450,16 +3450,16 @@
         <v>133.9556819852595</v>
       </c>
       <c r="C6" t="n">
-        <v>111.9951605313703</v>
+        <v>111.9951605313702</v>
       </c>
       <c r="D6" t="n">
         <v>112.7688640547267</v>
       </c>
       <c r="E6" t="n">
-        <v>101.1049770493579</v>
+        <v>101.104977049358</v>
       </c>
       <c r="F6" t="n">
-        <v>112.1671613269655</v>
+        <v>112.1671613269656</v>
       </c>
       <c r="G6" t="n">
         <v>134.2125297335654</v>
@@ -3468,10 +3468,10 @@
         <v>113.1131714127543</v>
       </c>
       <c r="I6" t="n">
-        <v>134.0124292386633</v>
+        <v>134.0124292386634</v>
       </c>
       <c r="J6" t="n">
-        <v>118.3882989049781</v>
+        <v>118.3882989049782</v>
       </c>
       <c r="K6" t="n">
         <v>112.073231062317</v>
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.816508525136093</v>
+        <v>1.816508525136101</v>
       </c>
       <c r="C7" t="n">
-        <v>1.720613191452664</v>
+        <v>1.720613191452657</v>
       </c>
       <c r="D7" t="n">
-        <v>2.458700590107799</v>
+        <v>2.458700590107827</v>
       </c>
       <c r="E7" t="n">
-        <v>1.869651882274335</v>
+        <v>1.869651882274333</v>
       </c>
       <c r="F7" t="n">
         <v>1.869651882274335</v>
       </c>
       <c r="G7" t="n">
-        <v>2.07335627344187</v>
+        <v>2.073356273441862</v>
       </c>
       <c r="H7" t="n">
-        <v>2.811550824915906</v>
+        <v>2.811550824915935</v>
       </c>
       <c r="I7" t="n">
         <v>1.873255778539736</v>
       </c>
       <c r="J7" t="n">
-        <v>2.432865907737384</v>
+        <v>2.432865907737387</v>
       </c>
       <c r="K7" t="n">
-        <v>1.787511449203785</v>
+        <v>1.787511449203836</v>
       </c>
       <c r="L7" t="n">
-        <v>1.725545067570003</v>
+        <v>1.725545067570036</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.01828340723393</v>
+        <v>2.018283407233951</v>
       </c>
       <c r="C8" t="n">
-        <v>2.656914674022894</v>
+        <v>2.656914674022892</v>
       </c>
       <c r="D8" t="n">
-        <v>3.551400053728559</v>
+        <v>3.551400053728578</v>
       </c>
       <c r="E8" t="n">
-        <v>2.608190476682011</v>
+        <v>2.608190476682015</v>
       </c>
       <c r="F8" t="n">
-        <v>2.096299190536484</v>
+        <v>2.096299190536486</v>
       </c>
       <c r="G8" t="n">
-        <v>3.013048008346401</v>
+        <v>3.013048008346431</v>
       </c>
       <c r="H8" t="n">
-        <v>3.751242559826545</v>
+        <v>3.751242559826554</v>
       </c>
       <c r="I8" t="n">
-        <v>2.812947513444291</v>
+        <v>2.81294751344429</v>
       </c>
       <c r="J8" t="n">
-        <v>3.372702663070113</v>
+        <v>3.372702663070167</v>
       </c>
       <c r="K8" t="n">
-        <v>1.975579147039521</v>
+        <v>1.975579147039564</v>
       </c>
       <c r="L8" t="n">
-        <v>3.436052657540561</v>
+        <v>3.436052657540591</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.960519365136161</v>
+        <v>2.960519365136173</v>
       </c>
       <c r="C9" t="n">
-        <v>3.446384848660216</v>
+        <v>3.44638484866022</v>
       </c>
       <c r="D9" t="n">
-        <v>4.184468365046401</v>
+        <v>4.184468365046469</v>
       </c>
       <c r="E9" t="n">
-        <v>4.270441457280725</v>
+        <v>4.270441457280739</v>
       </c>
       <c r="F9" t="n">
-        <v>3.599101657258718</v>
+        <v>3.599101657258729</v>
       </c>
       <c r="G9" t="n">
-        <v>3.799127930649395</v>
+        <v>3.799127930649433</v>
       </c>
       <c r="H9" t="n">
-        <v>4.537322482123487</v>
+        <v>4.537322482123489</v>
       </c>
       <c r="I9" t="n">
-        <v>3.599027435747292</v>
+        <v>3.599027435747298</v>
       </c>
       <c r="J9" t="n">
-        <v>4.158637564944925</v>
+        <v>4.158637564944948</v>
       </c>
       <c r="K9" t="n">
         <v>3.176208711605879</v>
       </c>
       <c r="L9" t="n">
-        <v>3.451316724777572</v>
+        <v>3.451316724777592</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.95300181189385</v>
+        <v>40.95300181189383</v>
       </c>
       <c r="C2" t="n">
         <v>40.15984031007255</v>
       </c>
       <c r="D2" t="n">
-        <v>41.00036521328288</v>
+        <v>41.00036521328285</v>
       </c>
       <c r="E2" t="n">
         <v>40.39854636384089</v>
       </c>
       <c r="F2" t="n">
-        <v>40.39854512202128</v>
+        <v>40.39854512202125</v>
       </c>
       <c r="G2" t="n">
-        <v>41.02696559546965</v>
+        <v>41.02696559546958</v>
       </c>
       <c r="H2" t="n">
-        <v>41.20722559716969</v>
+        <v>41.20722559716965</v>
       </c>
       <c r="I2" t="n">
-        <v>41.01987358667562</v>
+        <v>41.01987358667558</v>
       </c>
       <c r="J2" t="n">
-        <v>42.57185580066095</v>
+        <v>42.57185580066093</v>
       </c>
       <c r="K2" t="n">
-        <v>41.72718472091655</v>
+        <v>41.7271847209165</v>
       </c>
       <c r="L2" t="n">
-        <v>41.01597968414225</v>
+        <v>41.01597968414218</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.35901033519236</v>
+        <v>41.35901033519237</v>
       </c>
       <c r="C3" t="n">
-        <v>39.78737270151247</v>
+        <v>39.78737270151248</v>
       </c>
       <c r="D3" t="n">
         <v>41.69548394760621</v>
       </c>
       <c r="E3" t="n">
-        <v>40.80924902203168</v>
+        <v>40.80924902203162</v>
       </c>
       <c r="F3" t="n">
-        <v>40.809247780212</v>
+        <v>40.80924778021195</v>
       </c>
       <c r="G3" t="n">
-        <v>41.88643105250867</v>
+        <v>41.8864310525087</v>
       </c>
       <c r="H3" t="n">
-        <v>43.1808032084664</v>
+        <v>43.18080320846646</v>
       </c>
       <c r="I3" t="n">
-        <v>41.83490598682354</v>
+        <v>41.83490598682359</v>
       </c>
       <c r="J3" t="n">
-        <v>45.19189847423817</v>
+        <v>45.1918984742383</v>
       </c>
       <c r="K3" t="n">
-        <v>42.99569785866356</v>
+        <v>42.99569785866359</v>
       </c>
       <c r="L3" t="n">
-        <v>41.81918325648097</v>
+        <v>41.81918325648098</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.928891202962567</v>
+        <v>1.928891202962553</v>
       </c>
       <c r="C4" t="n">
-        <v>1.309864388199968</v>
+        <v>1.309864388199965</v>
       </c>
       <c r="D4" t="n">
-        <v>2.463882609892888</v>
+        <v>2.463882609892964</v>
       </c>
       <c r="E4" t="n">
-        <v>2.665272345805399</v>
+        <v>2.665272345805427</v>
       </c>
       <c r="F4" t="n">
-        <v>2.665272345805417</v>
+        <v>2.665272345805424</v>
       </c>
       <c r="G4" t="n">
-        <v>2.763297196019937</v>
+        <v>2.763297196019896</v>
       </c>
       <c r="H4" t="n">
-        <v>4.795013138963717</v>
+        <v>4.795013138963697</v>
       </c>
       <c r="I4" t="n">
-        <v>2.677024545666665</v>
+        <v>2.677024545666679</v>
       </c>
       <c r="J4" t="n">
-        <v>4.316113259489087</v>
+        <v>4.316113259489093</v>
       </c>
       <c r="K4" t="n">
-        <v>2.670885303388073</v>
+        <v>2.670885303388129</v>
       </c>
       <c r="L4" t="n">
-        <v>2.650035479056408</v>
+        <v>2.650035479056435</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.10893547011892</v>
+        <v>15.10893547011889</v>
       </c>
       <c r="C5" t="n">
-        <v>4.969977861367576</v>
+        <v>4.969977861367603</v>
       </c>
       <c r="D5" t="n">
         <v>24.21475334861046</v>
       </c>
       <c r="E5" t="n">
-        <v>28.4138612834184</v>
+        <v>28.41386128341862</v>
       </c>
       <c r="F5" t="n">
-        <v>28.4138612834184</v>
+        <v>28.41386128341862</v>
       </c>
       <c r="G5" t="n">
-        <v>30.40871953713803</v>
+        <v>30.40871953713718</v>
       </c>
       <c r="H5" t="n">
-        <v>74.12967865245787</v>
+        <v>74.12967865245786</v>
       </c>
       <c r="I5" t="n">
-        <v>28.41381085432477</v>
+        <v>28.41381085432479</v>
       </c>
       <c r="J5" t="n">
-        <v>60.19001863483538</v>
+        <v>60.19001863483339</v>
       </c>
       <c r="K5" t="n">
-        <v>28.02539566686542</v>
+        <v>28.02539566686417</v>
       </c>
       <c r="L5" t="n">
-        <v>31.47978691622559</v>
+        <v>31.4797869162256</v>
       </c>
     </row>
     <row r="6">
@@ -3843,34 +3843,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119.2699508759977</v>
+        <v>119.2699508759979</v>
       </c>
       <c r="C6" t="n">
-        <v>118.6684619537065</v>
+        <v>118.6684619537068</v>
       </c>
       <c r="D6" t="n">
-        <v>119.7990605594277</v>
+        <v>119.7990605594278</v>
       </c>
       <c r="E6" t="n">
-        <v>108.3376887745413</v>
+        <v>108.3376887745414</v>
       </c>
       <c r="F6" t="n">
-        <v>120.0218991868906</v>
+        <v>120.0218991868907</v>
       </c>
       <c r="G6" t="n">
-        <v>120.1043568690551</v>
+        <v>120.1043568690552</v>
       </c>
       <c r="H6" t="n">
-        <v>145.5125608558375</v>
+        <v>145.5125608558374</v>
       </c>
       <c r="I6" t="n">
         <v>120.018084218702</v>
       </c>
       <c r="J6" t="n">
-        <v>127.6508346782989</v>
+        <v>127.6508346782991</v>
       </c>
       <c r="K6" t="n">
-        <v>120.0124119469881</v>
+        <v>120.0124119470011</v>
       </c>
       <c r="L6" t="n">
         <v>119.995519747676</v>
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.908697903249965</v>
+        <v>2.908697903249946</v>
       </c>
       <c r="C7" t="n">
-        <v>2.360689467507488</v>
+        <v>2.360689467507499</v>
       </c>
       <c r="D7" t="n">
-        <v>3.443690579381181</v>
+        <v>3.443690579381212</v>
       </c>
       <c r="E7" t="n">
-        <v>3.655725785327781</v>
+        <v>3.655725785327789</v>
       </c>
       <c r="F7" t="n">
-        <v>3.655725785327782</v>
+        <v>3.655725785327789</v>
       </c>
       <c r="G7" t="n">
-        <v>3.743103896307219</v>
+        <v>3.74310389630728</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7748198392511</v>
+        <v>5.774819839251087</v>
       </c>
       <c r="I7" t="n">
         <v>3.656831245954074</v>
       </c>
       <c r="J7" t="n">
-        <v>5.295919959776249</v>
+        <v>5.295919959776477</v>
       </c>
       <c r="K7" t="n">
-        <v>3.650692003675338</v>
+        <v>3.650692003675478</v>
       </c>
       <c r="L7" t="n">
-        <v>3.629842179343814</v>
+        <v>3.62984217934383</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.255864252911189</v>
+        <v>3.255864252911199</v>
       </c>
       <c r="C8" t="n">
         <v>3.723407692439046</v>
       </c>
       <c r="D8" t="n">
-        <v>5.01809819567606</v>
+        <v>5.018098195676068</v>
       </c>
       <c r="E8" t="n">
-        <v>4.741712852789242</v>
+        <v>4.741712852789251</v>
       </c>
       <c r="F8" t="n">
-        <v>4.035578276376407</v>
+        <v>4.035578276376439</v>
       </c>
       <c r="G8" t="n">
-        <v>5.106740958078072</v>
+        <v>5.10674095807813</v>
       </c>
       <c r="H8" t="n">
-        <v>7.138456901027014</v>
+        <v>7.138456901027033</v>
       </c>
       <c r="I8" t="n">
-        <v>5.020468307724878</v>
+        <v>5.020468307724923</v>
       </c>
       <c r="J8" t="n">
-        <v>6.659756785314768</v>
+        <v>6.65975678531485</v>
       </c>
       <c r="K8" t="n">
-        <v>3.978976888165057</v>
+        <v>3.978976888165334</v>
       </c>
       <c r="L8" t="n">
-        <v>6.055267894094052</v>
+        <v>6.055267894094056</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.898318971859066</v>
+        <v>4.898318971859065</v>
       </c>
       <c r="C9" t="n">
-        <v>5.246961863093026</v>
+        <v>5.246961863093049</v>
       </c>
       <c r="D9" t="n">
-        <v>6.329962062726083</v>
+        <v>6.329962062726256</v>
       </c>
       <c r="E9" t="n">
-        <v>7.577870178349376</v>
+        <v>7.577870178349365</v>
       </c>
       <c r="F9" t="n">
-        <v>6.54315340325728</v>
+        <v>6.54315340325726</v>
       </c>
       <c r="G9" t="n">
-        <v>6.629376291892831</v>
+        <v>6.629376291892862</v>
       </c>
       <c r="H9" t="n">
-        <v>8.661092234836623</v>
+        <v>8.661092234836651</v>
       </c>
       <c r="I9" t="n">
-        <v>6.543103641539637</v>
+        <v>6.543103641539653</v>
       </c>
       <c r="J9" t="n">
-        <v>8.182192355361913</v>
+        <v>8.182192355362089</v>
       </c>
       <c r="K9" t="n">
-        <v>6.017441249125526</v>
+        <v>6.017441249125356</v>
       </c>
       <c r="L9" t="n">
-        <v>6.516114574929404</v>
+        <v>6.516114574929418</v>
       </c>
     </row>
   </sheetData>
@@ -4079,19 +4079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.29329471757915</v>
+        <v>40.29329471757917</v>
       </c>
       <c r="C2" t="n">
         <v>39.695493205646</v>
       </c>
       <c r="D2" t="n">
-        <v>40.35090761744907</v>
+        <v>40.35090761744906</v>
       </c>
       <c r="E2" t="n">
-        <v>39.77171666359668</v>
+        <v>39.77171666359667</v>
       </c>
       <c r="F2" t="n">
-        <v>39.77171434026809</v>
+        <v>39.77171434026807</v>
       </c>
       <c r="G2" t="n">
         <v>40.32321557938975</v>
@@ -4100,16 +4100,16 @@
         <v>40.38930112626841</v>
       </c>
       <c r="I2" t="n">
-        <v>40.31512172925132</v>
+        <v>40.31512172925133</v>
       </c>
       <c r="J2" t="n">
         <v>41.9176186531845</v>
       </c>
       <c r="K2" t="n">
-        <v>40.94407746439011</v>
+        <v>40.94407746439015</v>
       </c>
       <c r="L2" t="n">
-        <v>40.2721538564108</v>
+        <v>40.27215385641082</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.5382147776027</v>
+        <v>40.53821477760268</v>
       </c>
       <c r="C3" t="n">
-        <v>39.44710209735113</v>
+        <v>39.44710209735116</v>
       </c>
       <c r="D3" t="n">
-        <v>40.94807885824033</v>
+        <v>40.94807885824029</v>
       </c>
       <c r="E3" t="n">
-        <v>39.79637240752051</v>
+        <v>39.79637240752047</v>
       </c>
       <c r="F3" t="n">
-        <v>39.79637008419191</v>
+        <v>39.79637008419193</v>
       </c>
       <c r="G3" t="n">
         <v>40.75149908566149</v>
       </c>
       <c r="H3" t="n">
-        <v>41.22929671574026</v>
+        <v>41.22929671574027</v>
       </c>
       <c r="I3" t="n">
-        <v>40.69339929514658</v>
+        <v>40.69339929514655</v>
       </c>
       <c r="J3" t="n">
-        <v>43.58554803094378</v>
+        <v>43.58554803094376</v>
       </c>
       <c r="K3" t="n">
-        <v>41.659422050425</v>
+        <v>41.65942205042501</v>
       </c>
       <c r="L3" t="n">
-        <v>40.39464007857248</v>
+        <v>40.39464007857249</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.285421191396932</v>
+        <v>1.285421191396931</v>
       </c>
       <c r="C4" t="n">
-        <v>1.009205167407759</v>
+        <v>1.00920516740773</v>
       </c>
       <c r="D4" t="n">
-        <v>1.93618539867069</v>
+        <v>1.936185398670685</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5102455822855</v>
+        <v>1.51024558228549</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5102455822855</v>
+        <v>1.51024558228549</v>
       </c>
       <c r="G4" t="n">
-        <v>1.622490658400055</v>
+        <v>1.622490658400069</v>
       </c>
       <c r="H4" t="n">
-        <v>2.373261211993842</v>
+        <v>2.37326121199385</v>
       </c>
       <c r="I4" t="n">
-        <v>1.525708734624349</v>
+        <v>1.525708734624343</v>
       </c>
       <c r="J4" t="n">
-        <v>2.038405605747447</v>
+        <v>2.038405605747435</v>
       </c>
       <c r="K4" t="n">
-        <v>1.383215444511715</v>
+        <v>1.383215444511693</v>
       </c>
       <c r="L4" t="n">
-        <v>1.059282525044758</v>
+        <v>1.05928252504475</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.93328109074109</v>
+        <v>6.933281090741085</v>
       </c>
       <c r="C5" t="n">
-        <v>3.040501090650367</v>
+        <v>3.040501090650314</v>
       </c>
       <c r="D5" t="n">
-        <v>17.75799693903181</v>
+        <v>17.75799693903144</v>
       </c>
       <c r="E5" t="n">
-        <v>10.97881213831142</v>
+        <v>10.97881213831127</v>
       </c>
       <c r="F5" t="n">
-        <v>10.97881213831142</v>
+        <v>10.97881213831127</v>
       </c>
       <c r="G5" t="n">
-        <v>12.77396717198526</v>
+        <v>12.77396717198527</v>
       </c>
       <c r="H5" t="n">
-        <v>28.26209681534317</v>
+        <v>28.26209681534308</v>
       </c>
       <c r="I5" t="n">
-        <v>10.97876029207244</v>
+        <v>10.97876029207221</v>
       </c>
       <c r="J5" t="n">
-        <v>20.43445959380189</v>
+        <v>20.43445959380141</v>
       </c>
       <c r="K5" t="n">
-        <v>8.388865738836374</v>
+        <v>8.388865738836376</v>
       </c>
       <c r="L5" t="n">
-        <v>3.157431927589277</v>
+        <v>3.157431927589257</v>
       </c>
     </row>
     <row r="6">
@@ -4239,19 +4239,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.250163674614</v>
+        <v>134.2501636746138</v>
       </c>
       <c r="C6" t="n">
-        <v>112.1242481449326</v>
+        <v>112.1242481449323</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0324698705199</v>
+        <v>113.0324698705198</v>
       </c>
       <c r="E6" t="n">
         <v>101.5489646395126</v>
       </c>
       <c r="F6" t="n">
-        <v>112.6108319231941</v>
+        <v>112.6108319231939</v>
       </c>
       <c r="G6" t="n">
         <v>112.7070484891232</v>
@@ -4260,10 +4260,10 @@
         <v>135.4814151624595</v>
       </c>
       <c r="I6" t="n">
-        <v>134.4904512178414</v>
+        <v>134.4904512178412</v>
       </c>
       <c r="J6" t="n">
-        <v>118.7858371266464</v>
+        <v>118.7858371266462</v>
       </c>
       <c r="K6" t="n">
         <v>112.4596546195753</v>
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.087667690990591</v>
+        <v>2.087667690990569</v>
       </c>
       <c r="C7" t="n">
-        <v>1.868133212991671</v>
+        <v>1.868133212991665</v>
       </c>
       <c r="D7" t="n">
-        <v>2.738434410014903</v>
+        <v>2.738434410014889</v>
       </c>
       <c r="E7" t="n">
-        <v>2.325612770512663</v>
+        <v>2.325612770512652</v>
       </c>
       <c r="F7" t="n">
-        <v>2.32561277051266</v>
+        <v>2.325612770512652</v>
       </c>
       <c r="G7" t="n">
-        <v>2.424737157993722</v>
+        <v>2.424737157993711</v>
       </c>
       <c r="H7" t="n">
-        <v>3.175507711587506</v>
+        <v>3.175507711587485</v>
       </c>
       <c r="I7" t="n">
-        <v>2.327955234218013</v>
+        <v>2.327955234218007</v>
       </c>
       <c r="J7" t="n">
-        <v>2.840652105341104</v>
+        <v>2.840652105341102</v>
       </c>
       <c r="K7" t="n">
-        <v>2.185461944105376</v>
+        <v>2.185461944105373</v>
       </c>
       <c r="L7" t="n">
-        <v>1.861529024638415</v>
+        <v>1.861529024638424</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.315709423635899</v>
+        <v>2.315709423635917</v>
       </c>
       <c r="C8" t="n">
-        <v>2.881046111289272</v>
+        <v>2.88104611128924</v>
       </c>
       <c r="D8" t="n">
-        <v>3.91668810753961</v>
+        <v>3.916688107539609</v>
       </c>
       <c r="E8" t="n">
-        <v>3.125916088598561</v>
+        <v>3.12591608859854</v>
       </c>
       <c r="F8" t="n">
-        <v>2.579566332068351</v>
+        <v>2.579566332068338</v>
       </c>
       <c r="G8" t="n">
-        <v>3.439799514129433</v>
+        <v>3.439799514129408</v>
       </c>
       <c r="H8" t="n">
-        <v>4.190570067730073</v>
+        <v>4.190570067730063</v>
       </c>
       <c r="I8" t="n">
-        <v>3.343017590353718</v>
+        <v>3.343017590353713</v>
       </c>
       <c r="J8" t="n">
-        <v>3.855869132026172</v>
+        <v>3.855869132026165</v>
       </c>
       <c r="K8" t="n">
-        <v>2.398884364753077</v>
+        <v>2.398884364753054</v>
       </c>
       <c r="L8" t="n">
-        <v>3.698700230154199</v>
+        <v>3.698700230154204</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.446309926223404</v>
+        <v>3.446309926223392</v>
       </c>
       <c r="C9" t="n">
-        <v>3.882001940172677</v>
+        <v>3.88200194017265</v>
       </c>
       <c r="D9" t="n">
-        <v>4.752300968096273</v>
+        <v>4.752300968096208</v>
       </c>
       <c r="E9" t="n">
-        <v>5.097993235293036</v>
+        <v>5.097993235293031</v>
       </c>
       <c r="F9" t="n">
-        <v>4.341875519032823</v>
+        <v>4.341875519032811</v>
       </c>
       <c r="G9" t="n">
-        <v>4.438605885174717</v>
+        <v>4.438605885174718</v>
       </c>
       <c r="H9" t="n">
-        <v>5.189376438768518</v>
+        <v>5.189376438768497</v>
       </c>
       <c r="I9" t="n">
-        <v>4.341823961399009</v>
+        <v>4.341823961399</v>
       </c>
       <c r="J9" t="n">
-        <v>4.854520832522152</v>
+        <v>4.854520832522097</v>
       </c>
       <c r="K9" t="n">
-        <v>3.374283471600739</v>
+        <v>3.374283471600701</v>
       </c>
       <c r="L9" t="n">
-        <v>3.875397751819414</v>
+        <v>3.875397751819427</v>
       </c>
     </row>
   </sheetData>
@@ -4478,31 +4478,31 @@
         <v>39.83272885727792</v>
       </c>
       <c r="C2" t="n">
-        <v>39.13179863280165</v>
+        <v>39.13179863280164</v>
       </c>
       <c r="D2" t="n">
-        <v>39.90441855044703</v>
+        <v>39.90441855044704</v>
       </c>
       <c r="E2" t="n">
-        <v>39.31943158422834</v>
+        <v>39.31943158422838</v>
       </c>
       <c r="F2" t="n">
-        <v>39.31942810564638</v>
+        <v>39.31942810564642</v>
       </c>
       <c r="G2" t="n">
         <v>39.85700716999681</v>
       </c>
       <c r="H2" t="n">
-        <v>39.9119735557859</v>
+        <v>39.91197355578591</v>
       </c>
       <c r="I2" t="n">
-        <v>39.83403654767768</v>
+        <v>39.8340365476777</v>
       </c>
       <c r="J2" t="n">
         <v>41.3010869509368</v>
       </c>
       <c r="K2" t="n">
-        <v>40.60732934797539</v>
+        <v>40.60732934797542</v>
       </c>
       <c r="L2" t="n">
         <v>39.82346873047887</v>
@@ -4521,13 +4521,13 @@
         <v>39.24401587116821</v>
       </c>
       <c r="D3" t="n">
-        <v>40.95658487983876</v>
+        <v>40.95658487983872</v>
       </c>
       <c r="E3" t="n">
-        <v>39.60590382332205</v>
+        <v>39.60590382332207</v>
       </c>
       <c r="F3" t="n">
-        <v>39.60590034474008</v>
+        <v>39.60590034474009</v>
       </c>
       <c r="G3" t="n">
         <v>40.61935499938603</v>
@@ -4536,13 +4536,13 @@
         <v>41.01640244555711</v>
       </c>
       <c r="I3" t="n">
-        <v>40.45538644262034</v>
+        <v>40.45538644262033</v>
       </c>
       <c r="J3" t="n">
-        <v>43.08831868094906</v>
+        <v>43.08831868094909</v>
       </c>
       <c r="K3" t="n">
-        <v>41.72446657825051</v>
+        <v>41.72446657825053</v>
       </c>
       <c r="L3" t="n">
         <v>40.38525685007791</v>
@@ -4555,19 +4555,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9914278991420322</v>
+        <v>0.9914278991420307</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8442664587094647</v>
+        <v>0.8442664587094635</v>
       </c>
       <c r="D4" t="n">
-        <v>1.801195962375155</v>
+        <v>1.801195962375153</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9848437061404625</v>
+        <v>0.9848437061404632</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9848437061404625</v>
+        <v>0.9848437061404631</v>
       </c>
       <c r="G4" t="n">
         <v>1.265212661325565</v>
@@ -4576,16 +4576,16 @@
         <v>1.889338816031694</v>
       </c>
       <c r="I4" t="n">
-        <v>1.002900301512833</v>
+        <v>1.002900301512834</v>
       </c>
       <c r="J4" t="n">
-        <v>1.440383335707759</v>
+        <v>1.440383335707756</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9910431371373779</v>
+        <v>0.9910431371373755</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8955968452610568</v>
+        <v>0.895596845261055</v>
       </c>
     </row>
     <row r="5">
@@ -4598,10 +4598,10 @@
         <v>4.050530243572216</v>
       </c>
       <c r="C5" t="n">
-        <v>2.301950455859012</v>
+        <v>2.301950455859008</v>
       </c>
       <c r="D5" t="n">
-        <v>17.65696320678111</v>
+        <v>17.65696320678114</v>
       </c>
       <c r="E5" t="n">
         <v>4.174069011930479</v>
@@ -4610,22 +4610,22 @@
         <v>4.174069011930479</v>
       </c>
       <c r="G5" t="n">
-        <v>8.779387820485724</v>
+        <v>8.77938782048583</v>
       </c>
       <c r="H5" t="n">
-        <v>21.48199811476283</v>
+        <v>21.48199811476285</v>
       </c>
       <c r="I5" t="n">
         <v>4.173979338426504</v>
       </c>
       <c r="J5" t="n">
-        <v>12.067648424304</v>
+        <v>12.06764842430401</v>
       </c>
       <c r="K5" t="n">
-        <v>3.898940007978041</v>
+        <v>3.898940007978049</v>
       </c>
       <c r="L5" t="n">
-        <v>2.496026403544096</v>
+        <v>2.496026403544086</v>
       </c>
     </row>
     <row r="6">
@@ -4653,19 +4653,19 @@
         <v>112.3184374619546</v>
       </c>
       <c r="H6" t="n">
-        <v>134.8850874094257</v>
+        <v>134.8850874094259</v>
       </c>
       <c r="I6" t="n">
-        <v>112.0561251021419</v>
+        <v>112.056125102142</v>
       </c>
       <c r="J6" t="n">
         <v>134.3688834784544</v>
       </c>
       <c r="K6" t="n">
-        <v>112.035104965764</v>
+        <v>112.0351049657641</v>
       </c>
       <c r="L6" t="n">
-        <v>111.9486489527913</v>
+        <v>111.9486489527915</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.729660748985007</v>
+        <v>1.729660748985003</v>
       </c>
       <c r="C7" t="n">
-        <v>1.632705519525312</v>
+        <v>1.632705519525324</v>
       </c>
       <c r="D7" t="n">
-        <v>2.539431072673912</v>
+        <v>2.539431072673909</v>
       </c>
       <c r="E7" t="n">
-        <v>1.738277579383209</v>
+        <v>1.738277579383211</v>
       </c>
       <c r="F7" t="n">
-        <v>1.738277579383209</v>
+        <v>1.738277579383211</v>
       </c>
       <c r="G7" t="n">
-        <v>2.003445511168538</v>
+        <v>2.003445511168536</v>
       </c>
       <c r="H7" t="n">
-        <v>2.627571665874668</v>
+        <v>2.627571665874664</v>
       </c>
       <c r="I7" t="n">
-        <v>1.741133151355805</v>
+        <v>1.741133151355806</v>
       </c>
       <c r="J7" t="n">
-        <v>2.178616185550732</v>
+        <v>2.17861618555073</v>
       </c>
       <c r="K7" t="n">
-        <v>1.72927598698035</v>
+        <v>1.729275986980346</v>
       </c>
       <c r="L7" t="n">
-        <v>1.633829695104029</v>
+        <v>1.633829695104026</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.895667902820573</v>
+        <v>1.895667902820569</v>
       </c>
       <c r="C8" t="n">
-        <v>2.474491874371281</v>
+        <v>2.474491874371286</v>
       </c>
       <c r="D8" t="n">
         <v>3.524599585480484</v>
       </c>
       <c r="E8" t="n">
-        <v>2.397749524836684</v>
+        <v>2.397749524836686</v>
       </c>
       <c r="F8" t="n">
         <v>1.92697832210596</v>
       </c>
       <c r="G8" t="n">
-        <v>2.847929659773983</v>
+        <v>2.847929659773984</v>
       </c>
       <c r="H8" t="n">
-        <v>3.472055814486698</v>
+        <v>3.472055814486692</v>
       </c>
       <c r="I8" t="n">
-        <v>2.58561729996125</v>
+        <v>2.585617299961251</v>
       </c>
       <c r="J8" t="n">
-        <v>3.023233673196987</v>
+        <v>3.023233673196985</v>
       </c>
       <c r="K8" t="n">
-        <v>1.882680082410818</v>
+        <v>1.88268008241081</v>
       </c>
       <c r="L8" t="n">
-        <v>3.187039797010422</v>
+        <v>3.187039797010423</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.865251270727545</v>
+        <v>2.865251270727549</v>
       </c>
       <c r="C9" t="n">
-        <v>3.331748503443484</v>
+        <v>3.331748503443489</v>
       </c>
       <c r="D9" t="n">
-        <v>4.238472062047169</v>
+        <v>4.238472062047175</v>
       </c>
       <c r="E9" t="n">
-        <v>4.090477890213781</v>
+        <v>4.090477890213791</v>
       </c>
       <c r="F9" t="n">
-        <v>3.440265526241503</v>
+        <v>3.44026552624151</v>
       </c>
       <c r="G9" t="n">
-        <v>3.702488495086709</v>
+        <v>3.702488495086711</v>
       </c>
       <c r="H9" t="n">
-        <v>4.326614649792837</v>
+        <v>4.326614649792842</v>
       </c>
       <c r="I9" t="n">
-        <v>3.440176135273974</v>
+        <v>3.440176135273985</v>
       </c>
       <c r="J9" t="n">
-        <v>3.877659169468899</v>
+        <v>3.877659169468906</v>
       </c>
       <c r="K9" t="n">
-        <v>3.088607345944734</v>
+        <v>3.088607345944738</v>
       </c>
       <c r="L9" t="n">
-        <v>3.332872679022197</v>
+        <v>3.332872679022202</v>
       </c>
     </row>
   </sheetData>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.72580994011476</v>
+        <v>39.72580994011474</v>
       </c>
       <c r="C2" t="n">
         <v>42.96124916834455</v>
@@ -4889,16 +4889,16 @@
         <v>39.85912829707512</v>
       </c>
       <c r="H2" t="n">
-        <v>40.18242547721953</v>
+        <v>40.18242547721952</v>
       </c>
       <c r="I2" t="n">
         <v>39.78455575458194</v>
       </c>
       <c r="J2" t="n">
-        <v>46.20144520049066</v>
+        <v>46.20144520049065</v>
       </c>
       <c r="K2" t="n">
-        <v>41.15735977728419</v>
+        <v>41.15735977728416</v>
       </c>
       <c r="L2" t="n">
         <v>40.11733093295646</v>
@@ -4911,34 +4911,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.93719722333537</v>
+        <v>40.93719722333523</v>
       </c>
       <c r="C3" t="n">
-        <v>46.60071116893666</v>
+        <v>46.60071116893659</v>
       </c>
       <c r="D3" t="n">
-        <v>41.85146775157067</v>
+        <v>41.85146775157069</v>
       </c>
       <c r="E3" t="n">
-        <v>49.1512350085736</v>
+        <v>49.15123500857356</v>
       </c>
       <c r="F3" t="n">
-        <v>43.42877034640717</v>
+        <v>43.42877034640713</v>
       </c>
       <c r="G3" t="n">
-        <v>41.89190439359093</v>
+        <v>41.89190439359085</v>
       </c>
       <c r="H3" t="n">
-        <v>44.21916330590751</v>
+        <v>44.21916330590749</v>
       </c>
       <c r="I3" t="n">
-        <v>41.3521266253388</v>
+        <v>41.35212662533878</v>
       </c>
       <c r="J3" t="n">
-        <v>53.73341970640298</v>
+        <v>53.73341970640293</v>
       </c>
       <c r="K3" t="n">
-        <v>43.83555928904402</v>
+        <v>43.83555928904403</v>
       </c>
       <c r="L3" t="n">
         <v>43.75534548155709</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.891162946555209</v>
+        <v>4.891162946555415</v>
       </c>
       <c r="C4" t="n">
-        <v>5.53218206793025</v>
+        <v>5.532182067930192</v>
       </c>
       <c r="D4" t="n">
-        <v>6.338444247821908</v>
+        <v>6.338444247821848</v>
       </c>
       <c r="E4" t="n">
-        <v>5.550393849309598</v>
+        <v>5.550393849309545</v>
       </c>
       <c r="F4" t="n">
-        <v>5.550393849309598</v>
+        <v>5.550393849309544</v>
       </c>
       <c r="G4" t="n">
-        <v>6.39733082502706</v>
+        <v>6.397330825026947</v>
       </c>
       <c r="H4" t="n">
-        <v>10.04225547056283</v>
+        <v>10.04225547056281</v>
       </c>
       <c r="I4" t="n">
-        <v>5.556285241547661</v>
+        <v>5.556285241547601</v>
       </c>
       <c r="J4" t="n">
-        <v>9.208985323271245</v>
+        <v>9.208985323271229</v>
       </c>
       <c r="K4" t="n">
-        <v>5.991885103101383</v>
+        <v>5.991885103101366</v>
       </c>
       <c r="L4" t="n">
-        <v>9.291784954554544</v>
+        <v>9.291784954554521</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.56672805631811</v>
+        <v>57.56672805631717</v>
       </c>
       <c r="C5" t="n">
-        <v>67.70002719829577</v>
+        <v>67.70002719829515</v>
       </c>
       <c r="D5" t="n">
-        <v>84.82284359322675</v>
+        <v>84.82284359322621</v>
       </c>
       <c r="E5" t="n">
-        <v>67.70002796419968</v>
+        <v>67.70002796419963</v>
       </c>
       <c r="F5" t="n">
-        <v>67.70002796419968</v>
+        <v>67.70002796419963</v>
       </c>
       <c r="G5" t="n">
-        <v>87.82407768000581</v>
+        <v>87.8240776800055</v>
       </c>
       <c r="H5" t="n">
-        <v>169.7894016808673</v>
+        <v>169.7894016808674</v>
       </c>
       <c r="I5" t="n">
-        <v>67.69979935008948</v>
+        <v>67.69979935008865</v>
       </c>
       <c r="J5" t="n">
         <v>144.6428627304201</v>
       </c>
       <c r="K5" t="n">
-        <v>78.76307964449067</v>
+        <v>78.76307964449069</v>
       </c>
       <c r="L5" t="n">
-        <v>57.18186871054759</v>
+        <v>57.18186871054788</v>
       </c>
     </row>
     <row r="6">
@@ -5031,25 +5031,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124.4248091530167</v>
+        <v>124.4248091530163</v>
       </c>
       <c r="C6" t="n">
-        <v>125.0677895145692</v>
+        <v>125.0677895145691</v>
       </c>
       <c r="D6" t="n">
-        <v>125.8813359884838</v>
+        <v>125.8813359884839</v>
       </c>
       <c r="E6" t="n">
-        <v>113.1880961315637</v>
+        <v>113.1880961315636</v>
       </c>
       <c r="F6" t="n">
-        <v>125.095666029927</v>
+        <v>125.0956660299269</v>
       </c>
       <c r="G6" t="n">
-        <v>125.9309770314885</v>
+        <v>125.9309770314887</v>
       </c>
       <c r="H6" t="n">
-        <v>153.5924013898978</v>
+        <v>153.5924013898979</v>
       </c>
       <c r="I6" t="n">
         <v>148.9761556571968</v>
@@ -5058,10 +5058,10 @@
         <v>134.8656897275702</v>
       </c>
       <c r="K6" t="n">
-        <v>125.528567213477</v>
+        <v>125.5285672134771</v>
       </c>
       <c r="L6" t="n">
-        <v>128.8558692014217</v>
+        <v>128.8558692014215</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.11254776877503</v>
+        <v>6.112547768775122</v>
       </c>
       <c r="C7" t="n">
-        <v>6.777897911973765</v>
+        <v>6.777897911973688</v>
       </c>
       <c r="D7" t="n">
-        <v>7.559815369204602</v>
+        <v>7.559815369204534</v>
       </c>
       <c r="E7" t="n">
-        <v>6.779075874870587</v>
+        <v>6.779075874870543</v>
       </c>
       <c r="F7" t="n">
-        <v>6.779075874870587</v>
+        <v>6.779075874870539</v>
       </c>
       <c r="G7" t="n">
-        <v>7.618715647246897</v>
+        <v>7.618715647246841</v>
       </c>
       <c r="H7" t="n">
         <v>11.26364029278266</v>
       </c>
       <c r="I7" t="n">
-        <v>6.777670063767503</v>
+        <v>6.777670063767443</v>
       </c>
       <c r="J7" t="n">
-        <v>10.43037014549109</v>
+        <v>10.43037014549108</v>
       </c>
       <c r="K7" t="n">
-        <v>7.213269925321231</v>
+        <v>7.21326992532121</v>
       </c>
       <c r="L7" t="n">
-        <v>10.51316977677436</v>
+        <v>10.51316977677437</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.621272944695887</v>
+        <v>6.621272944695454</v>
       </c>
       <c r="C8" t="n">
-        <v>8.596277268045673</v>
+        <v>8.596277268045618</v>
       </c>
       <c r="D8" t="n">
-        <v>9.648099004734103</v>
+        <v>9.64809900473408</v>
       </c>
       <c r="E8" t="n">
-        <v>8.23833974979344</v>
+        <v>8.238339749793377</v>
       </c>
       <c r="F8" t="n">
-        <v>7.328804328991092</v>
+        <v>7.328804328991021</v>
       </c>
       <c r="G8" t="n">
-        <v>9.435707884372105</v>
+        <v>9.435707884371936</v>
       </c>
       <c r="H8" t="n">
-        <v>13.08063252990908</v>
+        <v>13.08063252990906</v>
       </c>
       <c r="I8" t="n">
-        <v>8.594662300892709</v>
+        <v>8.594662300892645</v>
       </c>
       <c r="J8" t="n">
-        <v>12.24761949273707</v>
+        <v>12.247619492737</v>
       </c>
       <c r="K8" t="n">
-        <v>7.697693369075867</v>
+        <v>7.697693369075831</v>
       </c>
       <c r="L8" t="n">
-        <v>13.69675635312046</v>
+        <v>13.69675635312047</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.472729930505682</v>
+        <v>9.472729930505512</v>
       </c>
       <c r="C9" t="n">
-        <v>11.49609245284565</v>
+        <v>11.49609245284556</v>
       </c>
       <c r="D9" t="n">
-        <v>12.27802402932325</v>
+        <v>12.27802402932315</v>
       </c>
       <c r="E9" t="n">
-        <v>13.06320875087474</v>
+        <v>13.06320875087464</v>
       </c>
       <c r="F9" t="n">
-        <v>11.49609134905059</v>
+        <v>11.49609134905053</v>
       </c>
       <c r="G9" t="n">
-        <v>12.33691018811879</v>
+        <v>12.3369101881187</v>
       </c>
       <c r="H9" t="n">
-        <v>15.98183483365457</v>
+        <v>15.98183483365448</v>
       </c>
       <c r="I9" t="n">
-        <v>11.4958646046394</v>
+        <v>11.49586460463938</v>
       </c>
       <c r="J9" t="n">
-        <v>15.14856468636299</v>
+        <v>15.14856468636295</v>
       </c>
       <c r="K9" t="n">
-        <v>11.14462693637402</v>
+        <v>11.14462693637396</v>
       </c>
       <c r="L9" t="n">
-        <v>15.23136431764626</v>
+        <v>15.23136431764621</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.56059172854726</v>
+        <v>39.56059172854729</v>
       </c>
       <c r="C2" t="n">
-        <v>42.79459298774843</v>
+        <v>42.79459298774845</v>
       </c>
       <c r="D2" t="n">
-        <v>39.72019682492726</v>
+        <v>39.7201968249273</v>
       </c>
       <c r="E2" t="n">
-        <v>44.32755933398813</v>
+        <v>44.32755933398814</v>
       </c>
       <c r="F2" t="n">
-        <v>40.90302744512852</v>
+        <v>40.90302744512854</v>
       </c>
       <c r="G2" t="n">
-        <v>39.72128071052319</v>
+        <v>39.72128071052322</v>
       </c>
       <c r="H2" t="n">
-        <v>39.98941944988391</v>
+        <v>39.98941944988398</v>
       </c>
       <c r="I2" t="n">
-        <v>39.65778483380656</v>
+        <v>39.6577848338066</v>
       </c>
       <c r="J2" t="n">
-        <v>45.89161538539245</v>
+        <v>45.89161538539246</v>
       </c>
       <c r="K2" t="n">
-        <v>40.92156163048812</v>
+        <v>40.92156163048814</v>
       </c>
       <c r="L2" t="n">
-        <v>39.96068530185054</v>
+        <v>39.9606853018506</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.46416016637052</v>
+        <v>40.46416016637059</v>
       </c>
       <c r="C3" t="n">
-        <v>46.33192915151722</v>
+        <v>46.33192915151726</v>
       </c>
       <c r="D3" t="n">
-        <v>41.59835099161167</v>
+        <v>41.59835099161169</v>
       </c>
       <c r="E3" t="n">
-        <v>48.85784752860403</v>
+        <v>48.85784752860407</v>
       </c>
       <c r="F3" t="n">
-        <v>43.20503074781421</v>
+        <v>43.20503074781419</v>
       </c>
       <c r="G3" t="n">
-        <v>41.60973800974752</v>
+        <v>41.60973800974755</v>
       </c>
       <c r="H3" t="n">
-        <v>43.54577354642247</v>
+        <v>43.54577354642253</v>
       </c>
       <c r="I3" t="n">
-        <v>41.14957104621198</v>
+        <v>41.14957104621202</v>
       </c>
       <c r="J3" t="n">
-        <v>52.80782941283297</v>
+        <v>52.80782941283296</v>
       </c>
       <c r="K3" t="n">
-        <v>43.2415521094538</v>
+        <v>43.24155210945379</v>
       </c>
       <c r="L3" t="n">
-        <v>43.3405141259453</v>
+        <v>43.34051412594537</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.132126760314254</v>
+        <v>4.132126760314261</v>
       </c>
       <c r="C4" t="n">
-        <v>5.197526829456841</v>
+        <v>5.19752682945684</v>
       </c>
       <c r="D4" t="n">
-        <v>5.93493974589813</v>
+        <v>5.934939745898132</v>
       </c>
       <c r="E4" t="n">
-        <v>5.213740488255376</v>
+        <v>5.213740488255373</v>
       </c>
       <c r="F4" t="n">
-        <v>5.213740488255375</v>
+        <v>5.21374048825537</v>
       </c>
       <c r="G4" t="n">
-        <v>5.947518490618015</v>
+        <v>5.947518490618008</v>
       </c>
       <c r="H4" t="n">
-        <v>8.973970419542347</v>
+        <v>8.973970419542345</v>
       </c>
       <c r="I4" t="n">
-        <v>5.231933008968017</v>
+        <v>5.231933008968013</v>
       </c>
       <c r="J4" t="n">
-        <v>8.016055715210959</v>
+        <v>8.016055715210969</v>
       </c>
       <c r="K4" t="n">
-        <v>5.242035282656218</v>
+        <v>5.242035282656224</v>
       </c>
       <c r="L4" t="n">
-        <v>8.631270676171312</v>
+        <v>8.631270676171296</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.44439971983017</v>
+        <v>44.44439971983021</v>
       </c>
       <c r="C5" t="n">
-        <v>59.58255444769952</v>
+        <v>59.58255444769974</v>
       </c>
       <c r="D5" t="n">
-        <v>73.78112832144797</v>
+        <v>73.78112832144811</v>
       </c>
       <c r="E5" t="n">
-        <v>59.5825555861814</v>
+        <v>59.58255558618154</v>
       </c>
       <c r="F5" t="n">
-        <v>59.58255558618141</v>
+        <v>59.58255558618154</v>
       </c>
       <c r="G5" t="n">
-        <v>75.89018106623347</v>
+        <v>75.8901810662335</v>
       </c>
       <c r="H5" t="n">
-        <v>141.5409032739211</v>
+        <v>141.5409032739215</v>
       </c>
       <c r="I5" t="n">
-        <v>59.5823561178812</v>
+        <v>59.58235611788139</v>
       </c>
       <c r="J5" t="n">
         <v>116.5976230827672</v>
       </c>
       <c r="K5" t="n">
-        <v>59.80660294114999</v>
+        <v>59.80660294114978</v>
       </c>
       <c r="L5" t="n">
-        <v>59.85751201526708</v>
+        <v>59.85751201526693</v>
       </c>
     </row>
     <row r="6">
@@ -5433,16 +5433,16 @@
         <v>116.5674369459213</v>
       </c>
       <c r="D6" t="n">
-        <v>117.2992336016642</v>
+        <v>117.2992336016641</v>
       </c>
       <c r="E6" t="n">
-        <v>105.5013846649216</v>
+        <v>105.5013846649217</v>
       </c>
       <c r="F6" t="n">
-        <v>116.591032847633</v>
+        <v>116.5910328476331</v>
       </c>
       <c r="G6" t="n">
-        <v>117.3008042489507</v>
+        <v>117.3008042489508</v>
       </c>
       <c r="H6" t="n">
         <v>142.6429758217004</v>
@@ -5467,22 +5467,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.202089439632257</v>
+        <v>5.202089439632259</v>
       </c>
       <c r="C7" t="n">
-        <v>6.302094018104313</v>
+        <v>6.302094018104309</v>
       </c>
       <c r="D7" t="n">
-        <v>7.004894556280005</v>
+        <v>7.004894556280009</v>
       </c>
       <c r="E7" t="n">
-        <v>6.299174398026299</v>
+        <v>6.2991743980263</v>
       </c>
       <c r="F7" t="n">
-        <v>6.299174398026299</v>
+        <v>6.2991743980263</v>
       </c>
       <c r="G7" t="n">
-        <v>7.01748116993601</v>
+        <v>7.01748116993602</v>
       </c>
       <c r="H7" t="n">
         <v>10.04393309886034</v>
@@ -5491,13 +5491,13 @@
         <v>6.301895688286015</v>
       </c>
       <c r="J7" t="n">
-        <v>9.086018394528963</v>
+        <v>9.086018394528967</v>
       </c>
       <c r="K7" t="n">
-        <v>6.311997961974223</v>
+        <v>6.311997961974217</v>
       </c>
       <c r="L7" t="n">
-        <v>9.701233355489318</v>
+        <v>9.701233355489302</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.622648223118323</v>
+        <v>5.622648223118329</v>
       </c>
       <c r="C8" t="n">
-        <v>7.84088114004898</v>
+        <v>7.840881140048969</v>
       </c>
       <c r="D8" t="n">
-        <v>8.778671453189482</v>
+        <v>8.778671453189475</v>
       </c>
       <c r="E8" t="n">
-        <v>7.53463558112894</v>
+        <v>7.534635581128938</v>
       </c>
       <c r="F8" t="n">
-        <v>6.756444023205489</v>
+        <v>6.75644402320549</v>
       </c>
       <c r="G8" t="n">
-        <v>8.558844147102002</v>
+        <v>8.558844147102004</v>
       </c>
       <c r="H8" t="n">
         <v>11.58529607602867</v>
       </c>
       <c r="I8" t="n">
-        <v>7.843258665452005</v>
+        <v>7.843258665452004</v>
       </c>
       <c r="J8" t="n">
-        <v>10.62760164035214</v>
+        <v>10.62760164035215</v>
       </c>
       <c r="K8" t="n">
-        <v>6.711737232272517</v>
+        <v>6.711737232272519</v>
       </c>
       <c r="L8" t="n">
-        <v>12.41337003169282</v>
+        <v>12.41337003169279</v>
       </c>
     </row>
     <row r="9">
@@ -5547,34 +5547,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.882068879152076</v>
+        <v>7.882068879152082</v>
       </c>
       <c r="C9" t="n">
         <v>10.09476130319292</v>
       </c>
       <c r="D9" t="n">
-        <v>10.79757012977147</v>
+        <v>10.7975701297715</v>
       </c>
       <c r="E9" t="n">
-        <v>11.37877906856704</v>
+        <v>11.37877906856705</v>
       </c>
       <c r="F9" t="n">
         <v>10.09476089504279</v>
       </c>
       <c r="G9" t="n">
-        <v>10.81014845502461</v>
+        <v>10.81014845502463</v>
       </c>
       <c r="H9" t="n">
-        <v>13.83660038394894</v>
+        <v>13.83660038394896</v>
       </c>
       <c r="I9" t="n">
-        <v>10.09456297337461</v>
+        <v>10.09456297337463</v>
       </c>
       <c r="J9" t="n">
-        <v>12.87868567961756</v>
+        <v>12.87868567961757</v>
       </c>
       <c r="K9" t="n">
-        <v>9.459969715904023</v>
+        <v>9.459969715904032</v>
       </c>
       <c r="L9" t="n">
         <v>13.49390064057791</v>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.43729550887269</v>
+        <v>39.4372955088727</v>
       </c>
       <c r="C2" t="n">
-        <v>42.62335404244798</v>
+        <v>42.62335404244796</v>
       </c>
       <c r="D2" t="n">
         <v>39.58264658616771</v>
@@ -5675,25 +5675,25 @@
         <v>44.14729926229981</v>
       </c>
       <c r="F2" t="n">
-        <v>40.74742462307069</v>
+        <v>40.74742462307071</v>
       </c>
       <c r="G2" t="n">
-        <v>39.58294453588041</v>
+        <v>39.58294453588044</v>
       </c>
       <c r="H2" t="n">
         <v>39.81767239025582</v>
       </c>
       <c r="I2" t="n">
-        <v>39.51840122139517</v>
+        <v>39.51840122139519</v>
       </c>
       <c r="J2" t="n">
-        <v>45.67519399306963</v>
+        <v>45.67519399306965</v>
       </c>
       <c r="K2" t="n">
-        <v>40.64338812755108</v>
+        <v>40.64338812755113</v>
       </c>
       <c r="L2" t="n">
-        <v>39.79622319890691</v>
+        <v>39.7962231989069</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.27070041246533</v>
+        <v>40.27070041246539</v>
       </c>
       <c r="C3" t="n">
-        <v>45.97315084536039</v>
+        <v>45.97315084536041</v>
       </c>
       <c r="D3" t="n">
-        <v>41.3017367019465</v>
+        <v>41.30173670194651</v>
       </c>
       <c r="E3" t="n">
         <v>48.48449407366004</v>
       </c>
       <c r="F3" t="n">
-        <v>42.87237894257137</v>
+        <v>42.87237894257135</v>
       </c>
       <c r="G3" t="n">
-        <v>41.308293735683</v>
+        <v>41.30829373568299</v>
       </c>
       <c r="H3" t="n">
-        <v>42.99774028034812</v>
+        <v>42.99774028034808</v>
       </c>
       <c r="I3" t="n">
-        <v>40.84368718966</v>
+        <v>40.84368718965994</v>
       </c>
       <c r="J3" t="n">
-        <v>52.31735116476256</v>
+        <v>52.31735116476258</v>
       </c>
       <c r="K3" t="n">
-        <v>42.40499219046941</v>
+        <v>42.40499219046944</v>
       </c>
       <c r="L3" t="n">
-        <v>42.85080386502624</v>
+        <v>42.85080386502626</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.847579065560785</v>
+        <v>3.847579065560826</v>
       </c>
       <c r="C4" t="n">
         <v>4.711569147764361</v>
       </c>
       <c r="D4" t="n">
-        <v>5.489386348406907</v>
+        <v>5.489386348406941</v>
       </c>
       <c r="E4" t="n">
-        <v>4.728257476038746</v>
+        <v>4.728257476038742</v>
       </c>
       <c r="F4" t="n">
-        <v>4.728257476038744</v>
+        <v>4.728257476038743</v>
       </c>
       <c r="G4" t="n">
-        <v>5.493074259430854</v>
+        <v>5.493074259430851</v>
       </c>
       <c r="H4" t="n">
-        <v>8.144004365572389</v>
+        <v>8.144004365572426</v>
       </c>
       <c r="I4" t="n">
         <v>4.765584488568575</v>
       </c>
       <c r="J4" t="n">
-        <v>7.431981994121788</v>
+        <v>7.431981994121815</v>
       </c>
       <c r="K4" t="n">
-        <v>4.156868729617053</v>
+        <v>4.156868729617099</v>
       </c>
       <c r="L4" t="n">
-        <v>7.884468885298336</v>
+        <v>7.884468885298375</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>40.12016053191343</v>
       </c>
       <c r="C5" t="n">
-        <v>53.28412173395334</v>
+        <v>53.28412173395343</v>
       </c>
       <c r="D5" t="n">
-        <v>65.87186039093389</v>
+        <v>65.87186039093385</v>
       </c>
       <c r="E5" t="n">
-        <v>53.28412344214254</v>
+        <v>53.28412344214261</v>
       </c>
       <c r="F5" t="n">
-        <v>53.28412344214254</v>
+        <v>53.28412344214261</v>
       </c>
       <c r="G5" t="n">
-        <v>68.22772814467244</v>
+        <v>68.22772814467248</v>
       </c>
       <c r="H5" t="n">
         <v>122.4987224325463</v>
       </c>
       <c r="I5" t="n">
-        <v>53.28392155326095</v>
+        <v>53.28392155326102</v>
       </c>
       <c r="J5" t="n">
         <v>108.1084734283548</v>
       </c>
       <c r="K5" t="n">
-        <v>42.06066965118417</v>
+        <v>42.0606696511843</v>
       </c>
       <c r="L5" t="n">
-        <v>45.73637319761381</v>
+        <v>45.73637319761382</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>115.1638220920294</v>
       </c>
       <c r="C6" t="n">
-        <v>116.0653852494731</v>
+        <v>116.0653852494732</v>
       </c>
       <c r="D6" t="n">
-        <v>116.8220727077537</v>
+        <v>116.8220727077538</v>
       </c>
       <c r="E6" t="n">
-        <v>105.0024933605676</v>
+        <v>105.0024933605674</v>
       </c>
       <c r="F6" t="n">
         <v>116.0898436638981</v>
       </c>
       <c r="G6" t="n">
-        <v>138.95547693064</v>
+        <v>138.9554769306402</v>
       </c>
       <c r="H6" t="n">
         <v>141.7283405924986</v>
       </c>
       <c r="I6" t="n">
-        <v>116.0818275150373</v>
+        <v>116.0818275150371</v>
       </c>
       <c r="J6" t="n">
-        <v>140.958761687564</v>
+        <v>140.9587616875641</v>
       </c>
       <c r="K6" t="n">
-        <v>115.4528214313737</v>
+        <v>115.4528214313738</v>
       </c>
       <c r="L6" t="n">
-        <v>119.2309787696336</v>
+        <v>119.2309787696337</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.870415062437925</v>
+        <v>4.870415062437932</v>
       </c>
       <c r="C7" t="n">
-        <v>5.7886206661381</v>
+        <v>5.788620666138106</v>
       </c>
       <c r="D7" t="n">
-        <v>6.512219291200057</v>
+        <v>6.512219291200182</v>
       </c>
       <c r="E7" t="n">
-        <v>5.780227011612938</v>
+        <v>5.780227011612936</v>
       </c>
       <c r="F7" t="n">
-        <v>5.780227011612937</v>
+        <v>5.780227011612936</v>
       </c>
       <c r="G7" t="n">
-        <v>6.515910256308005</v>
+        <v>6.515910256308056</v>
       </c>
       <c r="H7" t="n">
-        <v>9.166840362449516</v>
+        <v>9.166840362449534</v>
       </c>
       <c r="I7" t="n">
-        <v>5.788420485445739</v>
+        <v>5.788420485445743</v>
       </c>
       <c r="J7" t="n">
-        <v>8.454817990998913</v>
+        <v>8.454817990998936</v>
       </c>
       <c r="K7" t="n">
-        <v>5.179704726494178</v>
+        <v>5.179704726494207</v>
       </c>
       <c r="L7" t="n">
-        <v>8.907304882175451</v>
+        <v>8.907304882175481</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.252449914627996</v>
+        <v>5.25244991462795</v>
       </c>
       <c r="C8" t="n">
-        <v>7.216170720595987</v>
+        <v>7.216170720595995</v>
       </c>
       <c r="D8" t="n">
-        <v>8.166021441811475</v>
+        <v>8.166021441811505</v>
       </c>
       <c r="E8" t="n">
-        <v>6.928934397572486</v>
+        <v>6.928934397572489</v>
       </c>
       <c r="F8" t="n">
-        <v>6.199040251929111</v>
+        <v>6.199040251929116</v>
       </c>
       <c r="G8" t="n">
-        <v>7.951291182567023</v>
+        <v>7.951291182567024</v>
       </c>
       <c r="H8" t="n">
-        <v>10.60222128871134</v>
+        <v>10.60222128871138</v>
       </c>
       <c r="I8" t="n">
-        <v>7.223801411704725</v>
+        <v>7.223801411704728</v>
       </c>
       <c r="J8" t="n">
-        <v>9.890405928609859</v>
+        <v>9.890405928609868</v>
       </c>
       <c r="K8" t="n">
-        <v>5.542173134687163</v>
+        <v>5.542173134687221</v>
       </c>
       <c r="L8" t="n">
-        <v>11.44299386092344</v>
+        <v>11.4429938609235</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.174900010684919</v>
+        <v>7.17490001068499</v>
       </c>
       <c r="C9" t="n">
-        <v>9.083241162235822</v>
+        <v>9.083241162235833</v>
       </c>
       <c r="D9" t="n">
-        <v>9.806843252987145</v>
+        <v>9.806843252987141</v>
       </c>
       <c r="E9" t="n">
-        <v>10.22583689853581</v>
+        <v>10.22583689853582</v>
       </c>
       <c r="F9" t="n">
         <v>9.083241452883671</v>
       </c>
       <c r="G9" t="n">
-        <v>9.810530752405722</v>
+        <v>9.810530752405777</v>
       </c>
       <c r="H9" t="n">
         <v>12.4614608585473</v>
       </c>
       <c r="I9" t="n">
-        <v>9.08304098154346</v>
+        <v>9.083040981543473</v>
       </c>
       <c r="J9" t="n">
-        <v>11.74943848709669</v>
+        <v>11.7494384870967</v>
       </c>
       <c r="K9" t="n">
-        <v>7.900636970724527</v>
+        <v>7.900636970724623</v>
       </c>
       <c r="L9" t="n">
-        <v>12.20192537827324</v>
+        <v>12.20192537827325</v>
       </c>
     </row>
   </sheetData>
@@ -6059,19 +6059,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.15454063994349</v>
+        <v>39.1545406399435</v>
       </c>
       <c r="C2" t="n">
-        <v>42.51748204483947</v>
+        <v>42.51748204483946</v>
       </c>
       <c r="D2" t="n">
         <v>39.32047024428478</v>
       </c>
       <c r="E2" t="n">
-        <v>44.04655005423509</v>
+        <v>44.04655005423506</v>
       </c>
       <c r="F2" t="n">
-        <v>40.63247995975872</v>
+        <v>40.6324799597587</v>
       </c>
       <c r="G2" t="n">
         <v>39.3554226721101</v>
@@ -6080,16 +6080,16 @@
         <v>39.43162647903551</v>
       </c>
       <c r="I2" t="n">
-        <v>39.37842408545998</v>
+        <v>39.37842408545996</v>
       </c>
       <c r="J2" t="n">
-        <v>45.78567807371423</v>
+        <v>45.78567807371425</v>
       </c>
       <c r="K2" t="n">
         <v>40.58290402803306</v>
       </c>
       <c r="L2" t="n">
-        <v>39.50402534619136</v>
+        <v>39.50402534619135</v>
       </c>
     </row>
     <row r="3">
@@ -6099,34 +6099,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.10365311102804</v>
+        <v>39.10365311102801</v>
       </c>
       <c r="C3" t="n">
         <v>45.87675208383347</v>
       </c>
       <c r="D3" t="n">
-        <v>40.27770926165003</v>
+        <v>40.27770926165002</v>
       </c>
       <c r="E3" t="n">
-        <v>48.39769921582934</v>
+        <v>48.39769921582932</v>
       </c>
       <c r="F3" t="n">
-        <v>42.76215246419557</v>
+        <v>42.76215246419554</v>
       </c>
       <c r="G3" t="n">
-        <v>40.53041174013801</v>
+        <v>40.53041174013799</v>
       </c>
       <c r="H3" t="n">
-        <v>41.08613539042383</v>
+        <v>41.08613539042381</v>
       </c>
       <c r="I3" t="n">
-        <v>40.69214185982189</v>
+        <v>40.69214185982185</v>
       </c>
       <c r="J3" t="n">
-        <v>53.57354443914116</v>
+        <v>53.57354443914121</v>
       </c>
       <c r="K3" t="n">
-        <v>42.55218234369272</v>
+        <v>42.55218234369273</v>
       </c>
       <c r="L3" t="n">
         <v>41.60381409650373</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.131680178643245</v>
+        <v>2.131680178643242</v>
       </c>
       <c r="C4" t="n">
         <v>4.632793112584867</v>
       </c>
       <c r="D4" t="n">
-        <v>4.005931391067454</v>
+        <v>4.00593139106746</v>
       </c>
       <c r="E4" t="n">
-        <v>4.650078328129811</v>
+        <v>4.650078328129812</v>
       </c>
       <c r="F4" t="n">
         <v>4.650078328129808</v>
       </c>
       <c r="G4" t="n">
-        <v>4.401698778735674</v>
+        <v>4.401698778735675</v>
       </c>
       <c r="H4" t="n">
-        <v>5.276006948393881</v>
+        <v>5.276006948393877</v>
       </c>
       <c r="I4" t="n">
-        <v>4.666745330017952</v>
+        <v>4.66674533001795</v>
       </c>
       <c r="J4" t="n">
-        <v>9.38040885510442</v>
+        <v>9.380408855104429</v>
       </c>
       <c r="K4" t="n">
-        <v>4.396550546842331</v>
+        <v>4.396550546842329</v>
       </c>
       <c r="L4" t="n">
-        <v>6.068487055280591</v>
+        <v>6.068487055280592</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.02606300599906</v>
+        <v>14.02606300599897</v>
       </c>
       <c r="C5" t="n">
-        <v>56.63189176202176</v>
+        <v>56.63189176202182</v>
       </c>
       <c r="D5" t="n">
-        <v>43.79608488908548</v>
+        <v>43.79608488908545</v>
       </c>
       <c r="E5" t="n">
-        <v>56.63189303989199</v>
+        <v>56.63189303989196</v>
       </c>
       <c r="F5" t="n">
-        <v>56.63189303989201</v>
+        <v>56.63189303989196</v>
       </c>
       <c r="G5" t="n">
-        <v>53.06681805905457</v>
+        <v>53.06681805905482</v>
       </c>
       <c r="H5" t="n">
-        <v>71.82173617989419</v>
+        <v>71.8217361798941</v>
       </c>
       <c r="I5" t="n">
-        <v>56.63191923897291</v>
+        <v>56.631919238973</v>
       </c>
       <c r="J5" t="n">
-        <v>152.849364373216</v>
+        <v>152.8493643732161</v>
       </c>
       <c r="K5" t="n">
-        <v>51.66332846511003</v>
+        <v>51.66332846510998</v>
       </c>
       <c r="L5" t="n">
-        <v>94.98660219687575</v>
+        <v>94.98660219687567</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>145.2421160683528</v>
+        <v>145.242116068353</v>
       </c>
       <c r="C6" t="n">
-        <v>124.1231633150651</v>
+        <v>124.1231633150653</v>
       </c>
       <c r="D6" t="n">
         <v>147.1479256271488</v>
       </c>
       <c r="E6" t="n">
-        <v>112.2487808992788</v>
+        <v>112.2487808992789</v>
       </c>
       <c r="F6" t="n">
-        <v>124.1268085438256</v>
+        <v>124.1268085438257</v>
       </c>
       <c r="G6" t="n">
-        <v>147.5121346684452</v>
+        <v>147.5121346684453</v>
       </c>
       <c r="H6" t="n">
-        <v>124.7410378836388</v>
+        <v>124.7410378836389</v>
       </c>
       <c r="I6" t="n">
         <v>147.7771812197274</v>
       </c>
       <c r="J6" t="n">
-        <v>152.5627625588106</v>
+        <v>152.5627625588107</v>
       </c>
       <c r="K6" t="n">
-        <v>123.8537661102587</v>
+        <v>123.8537661102588</v>
       </c>
       <c r="L6" t="n">
-        <v>125.5387140378237</v>
+        <v>125.5387140378238</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.161711798712982</v>
+        <v>3.161711798712986</v>
       </c>
       <c r="C7" t="n">
-        <v>5.696749473136529</v>
+        <v>5.696749473136534</v>
       </c>
       <c r="D7" t="n">
-        <v>5.035957800322066</v>
+        <v>5.035957800322071</v>
       </c>
       <c r="E7" t="n">
-        <v>5.691789859358074</v>
+        <v>5.691789859358078</v>
       </c>
       <c r="F7" t="n">
-        <v>5.691789859358076</v>
+        <v>5.691789859358078</v>
       </c>
       <c r="G7" t="n">
-        <v>5.431730398805415</v>
+        <v>5.431730398805419</v>
       </c>
       <c r="H7" t="n">
-        <v>6.306038568463624</v>
+        <v>6.306038568463625</v>
       </c>
       <c r="I7" t="n">
-        <v>5.696776950087694</v>
+        <v>5.696776950087692</v>
       </c>
       <c r="J7" t="n">
-        <v>10.41044047517416</v>
+        <v>10.41044047517417</v>
       </c>
       <c r="K7" t="n">
-        <v>5.426582166912064</v>
+        <v>5.426582166912072</v>
       </c>
       <c r="L7" t="n">
-        <v>7.09851867535034</v>
+        <v>7.098518675350336</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.507435481882583</v>
+        <v>3.507435481882585</v>
       </c>
       <c r="C8" t="n">
-        <v>7.077125074219843</v>
+        <v>7.077125074219847</v>
       </c>
       <c r="D8" t="n">
-        <v>6.636369831785793</v>
+        <v>6.636369831785798</v>
       </c>
       <c r="E8" t="n">
-        <v>6.793408356132309</v>
+        <v>6.793408356132312</v>
       </c>
       <c r="F8" t="n">
-        <v>6.072459120305208</v>
+        <v>6.072459120305214</v>
       </c>
       <c r="G8" t="n">
-        <v>6.816652630740161</v>
+        <v>6.816652630740164</v>
       </c>
       <c r="H8" t="n">
-        <v>7.690960800399887</v>
+        <v>7.690960800399893</v>
       </c>
       <c r="I8" t="n">
-        <v>7.081699182022437</v>
+        <v>7.081699182022442</v>
       </c>
       <c r="J8" t="n">
-        <v>11.79556693783108</v>
+        <v>11.7955669378311</v>
       </c>
       <c r="K8" t="n">
-        <v>5.753002203645058</v>
+        <v>5.753002203645057</v>
       </c>
       <c r="L8" t="n">
-        <v>9.568970686384759</v>
+        <v>9.56897068638477</v>
       </c>
     </row>
     <row r="9">
@@ -6339,34 +6339,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.892969948846417</v>
+        <v>5.892969948846418</v>
       </c>
       <c r="C9" t="n">
-        <v>9.540053514437506</v>
+        <v>9.540053514437503</v>
       </c>
       <c r="D9" t="n">
         <v>8.879267693716294</v>
       </c>
       <c r="E9" t="n">
-        <v>10.82333182679844</v>
+        <v>10.82333182679843</v>
       </c>
       <c r="F9" t="n">
         <v>9.540054052758279</v>
       </c>
       <c r="G9" t="n">
-        <v>9.275034440106385</v>
+        <v>9.275034440106388</v>
       </c>
       <c r="H9" t="n">
         <v>10.1493426097646</v>
       </c>
       <c r="I9" t="n">
-        <v>9.54008099138867</v>
+        <v>9.540080991388663</v>
       </c>
       <c r="J9" t="n">
         <v>14.25374451647514</v>
       </c>
       <c r="K9" t="n">
-        <v>8.625562721248437</v>
+        <v>8.62556272124843</v>
       </c>
       <c r="L9" t="n">
         <v>10.94182271665131</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.88242261075715</v>
+        <v>38.8824226107571</v>
       </c>
       <c r="C2" t="n">
-        <v>42.14628692162066</v>
+        <v>42.14628692162065</v>
       </c>
       <c r="D2" t="n">
-        <v>39.056135327855</v>
+        <v>39.05613532785499</v>
       </c>
       <c r="E2" t="n">
-        <v>43.65221337099769</v>
+        <v>43.65221337099768</v>
       </c>
       <c r="F2" t="n">
-        <v>40.30121220790645</v>
+        <v>40.30121220790647</v>
       </c>
       <c r="G2" t="n">
-        <v>39.05510520899119</v>
+        <v>39.05510520899117</v>
       </c>
       <c r="H2" t="n">
-        <v>38.99002661962634</v>
+        <v>38.99002661962631</v>
       </c>
       <c r="I2" t="n">
-        <v>39.07776872374773</v>
+        <v>39.07776872374772</v>
       </c>
       <c r="J2" t="n">
-        <v>45.12704792442422</v>
+        <v>45.12704792442423</v>
       </c>
       <c r="K2" t="n">
         <v>40.08976972781336</v>
       </c>
       <c r="L2" t="n">
-        <v>39.13107138397531</v>
+        <v>39.1310713839753</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.6024532478198</v>
+        <v>38.60245324781979</v>
       </c>
       <c r="C3" t="n">
         <v>45.05427019096024</v>
       </c>
       <c r="D3" t="n">
-        <v>39.83062474417351</v>
+        <v>39.83062474417346</v>
       </c>
       <c r="E3" t="n">
-        <v>47.53776171275797</v>
+        <v>47.537761712758</v>
       </c>
       <c r="F3" t="n">
-        <v>42.00632268926584</v>
+        <v>42.00632268926582</v>
       </c>
       <c r="G3" t="n">
-        <v>39.82708272174188</v>
+        <v>39.82708272174191</v>
       </c>
       <c r="H3" t="n">
-        <v>39.38131104656533</v>
+        <v>39.38131104656532</v>
       </c>
       <c r="I3" t="n">
-        <v>39.98683825681401</v>
+        <v>39.98683825681397</v>
       </c>
       <c r="J3" t="n">
-        <v>51.23345737272905</v>
+        <v>51.23345737272902</v>
       </c>
       <c r="K3" t="n">
         <v>41.15646547751039</v>
       </c>
       <c r="L3" t="n">
-        <v>40.37786846780985</v>
+        <v>40.37786846780992</v>
       </c>
     </row>
     <row r="4">
@@ -6538,34 +6538,34 @@
         <v>1.387092018350145</v>
       </c>
       <c r="C4" t="n">
-        <v>3.568702594083762</v>
+        <v>3.568702594083757</v>
       </c>
       <c r="D4" t="n">
         <v>3.349257069768677</v>
       </c>
       <c r="E4" t="n">
-        <v>3.581823095155437</v>
+        <v>3.58182309515543</v>
       </c>
       <c r="F4" t="n">
-        <v>3.581823095155437</v>
+        <v>3.58182309515543</v>
       </c>
       <c r="G4" t="n">
-        <v>3.338590011066218</v>
+        <v>3.338590011066213</v>
       </c>
       <c r="H4" t="n">
         <v>2.629797879856611</v>
       </c>
       <c r="I4" t="n">
-        <v>3.599815624403249</v>
+        <v>3.599815624403243</v>
       </c>
       <c r="J4" t="n">
-        <v>6.188617851699131</v>
+        <v>6.188617851699137</v>
       </c>
       <c r="K4" t="n">
-        <v>2.552845322768979</v>
+        <v>2.55284532276898</v>
       </c>
       <c r="L4" t="n">
-        <v>4.193226272359313</v>
+        <v>4.193226272359311</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.683900907360269</v>
+        <v>4.683900907360271</v>
       </c>
       <c r="C5" t="n">
-        <v>38.63234221059546</v>
+        <v>38.63234221059543</v>
       </c>
       <c r="D5" t="n">
-        <v>33.36375622354797</v>
+        <v>33.36375622354794</v>
       </c>
       <c r="E5" t="n">
-        <v>38.63234345465679</v>
+        <v>38.63234345465678</v>
       </c>
       <c r="F5" t="n">
-        <v>38.63234345465679</v>
+        <v>38.63234345465678</v>
       </c>
       <c r="G5" t="n">
-        <v>35.13335828679337</v>
+        <v>35.13335828679328</v>
       </c>
       <c r="H5" t="n">
-        <v>24.62491552959475</v>
+        <v>24.62491552959474</v>
       </c>
       <c r="I5" t="n">
-        <v>38.63237015055202</v>
+        <v>38.63237015055201</v>
       </c>
       <c r="J5" t="n">
-        <v>84.91010932442173</v>
+        <v>84.91010932442163</v>
       </c>
       <c r="K5" t="n">
-        <v>22.62901353672825</v>
+        <v>22.62901353672827</v>
       </c>
       <c r="L5" t="n">
-        <v>10.95393818781959</v>
+        <v>10.9539381878196</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.5465979929793</v>
+        <v>134.5465979929792</v>
       </c>
       <c r="C6" t="n">
-        <v>114.8186394239843</v>
+        <v>114.8186394239844</v>
       </c>
       <c r="D6" t="n">
-        <v>114.5653374237374</v>
+        <v>114.5653374237375</v>
       </c>
       <c r="E6" t="n">
-        <v>103.7618891176364</v>
+        <v>103.7618891176365</v>
       </c>
       <c r="F6" t="n">
-        <v>114.8196401868913</v>
+        <v>114.8196401868912</v>
       </c>
       <c r="G6" t="n">
         <v>136.4980959856953</v>
       </c>
       <c r="H6" t="n">
-        <v>135.8802623936428</v>
+        <v>135.8802623936427</v>
       </c>
       <c r="I6" t="n">
-        <v>136.7593215990322</v>
+        <v>136.7593215990323</v>
       </c>
       <c r="J6" t="n">
-        <v>123.0892612688459</v>
+        <v>123.0892612688458</v>
       </c>
       <c r="K6" t="n">
         <v>113.7443757532144</v>
       </c>
       <c r="L6" t="n">
-        <v>115.4188589286664</v>
+        <v>115.4188589286663</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.244412328213632</v>
+        <v>2.244412328213634</v>
       </c>
       <c r="C7" t="n">
-        <v>4.457107994310157</v>
+        <v>4.457107994310149</v>
       </c>
       <c r="D7" t="n">
-        <v>4.206574210922282</v>
+        <v>4.20657421092228</v>
       </c>
       <c r="E7" t="n">
-        <v>4.451752747955426</v>
+        <v>4.451752747955417</v>
       </c>
       <c r="F7" t="n">
-        <v>4.451752747955425</v>
+        <v>4.451752747955417</v>
       </c>
       <c r="G7" t="n">
-        <v>4.195910320929708</v>
+        <v>4.195910320929702</v>
       </c>
       <c r="H7" t="n">
-        <v>3.487118189720097</v>
+        <v>3.487118189720096</v>
       </c>
       <c r="I7" t="n">
-        <v>4.457135934266735</v>
+        <v>4.457135934266729</v>
       </c>
       <c r="J7" t="n">
-        <v>7.04593816156262</v>
+        <v>7.045938161562618</v>
       </c>
       <c r="K7" t="n">
-        <v>3.410165632632466</v>
+        <v>3.410165632632465</v>
       </c>
       <c r="L7" t="n">
-        <v>5.0505465822228</v>
+        <v>5.050546582222797</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.470490776510912</v>
+        <v>2.470490776510907</v>
       </c>
       <c r="C8" t="n">
-        <v>5.489658000376139</v>
+        <v>5.489658000376131</v>
       </c>
       <c r="D8" t="n">
-        <v>5.41235748249814</v>
+        <v>5.412357482498135</v>
       </c>
       <c r="E8" t="n">
-        <v>5.268275590932495</v>
+        <v>5.268275590932484</v>
       </c>
       <c r="F8" t="n">
-        <v>4.705715678640759</v>
+        <v>4.705715678640754</v>
       </c>
       <c r="G8" t="n">
-        <v>5.233432317984344</v>
+        <v>5.233432317984339</v>
       </c>
       <c r="H8" t="n">
-        <v>4.524640186774389</v>
+        <v>4.524640186774383</v>
       </c>
       <c r="I8" t="n">
-        <v>5.494657931321376</v>
+        <v>5.494657931321367</v>
       </c>
       <c r="J8" t="n">
         <v>8.083619629391542</v>
       </c>
       <c r="K8" t="n">
-        <v>3.621171100513124</v>
+        <v>3.621171100513123</v>
       </c>
       <c r="L8" t="n">
-        <v>6.935689216708099</v>
+        <v>6.935689216708094</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.212337931874144</v>
+        <v>4.212337931874133</v>
       </c>
       <c r="C9" t="n">
-        <v>7.259933192791879</v>
+        <v>7.259933192791852</v>
       </c>
       <c r="D9" t="n">
-        <v>7.009403347993877</v>
+        <v>7.009403347993862</v>
       </c>
       <c r="E9" t="n">
-        <v>8.223391317085897</v>
+        <v>8.223391317085877</v>
       </c>
       <c r="F9" t="n">
-        <v>7.25993424052103</v>
+        <v>7.259934240521018</v>
       </c>
       <c r="G9" t="n">
-        <v>6.998735519411424</v>
+        <v>6.998735519411404</v>
       </c>
       <c r="H9" t="n">
-        <v>6.289943388201817</v>
+        <v>6.289943388201803</v>
       </c>
       <c r="I9" t="n">
-        <v>7.259961132748459</v>
+        <v>7.259961132748438</v>
       </c>
       <c r="J9" t="n">
-        <v>9.848763360044344</v>
+        <v>9.848763360044334</v>
       </c>
       <c r="K9" t="n">
-        <v>5.729247050779565</v>
+        <v>5.729247050779552</v>
       </c>
       <c r="L9" t="n">
-        <v>7.85337178070452</v>
+        <v>7.853371780704506</v>
       </c>
     </row>
   </sheetData>
@@ -6851,34 +6851,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.73537705002167</v>
+        <v>38.73537705002166</v>
       </c>
       <c r="C2" t="n">
         <v>41.88960113106351</v>
       </c>
       <c r="D2" t="n">
-        <v>38.8307632092232</v>
+        <v>38.83076320922319</v>
       </c>
       <c r="E2" t="n">
-        <v>43.38387655253985</v>
+        <v>43.38387655253984</v>
       </c>
       <c r="F2" t="n">
-        <v>40.06345987444439</v>
+        <v>40.0634598744444</v>
       </c>
       <c r="G2" t="n">
-        <v>38.85341202708239</v>
+        <v>38.85341202708241</v>
       </c>
       <c r="H2" t="n">
-        <v>38.83979491240937</v>
+        <v>38.83979491240936</v>
       </c>
       <c r="I2" t="n">
-        <v>38.86417689808324</v>
+        <v>38.86417689808323</v>
       </c>
       <c r="J2" t="n">
-        <v>44.71149968772895</v>
+        <v>44.71149968772892</v>
       </c>
       <c r="K2" t="n">
-        <v>39.82746796772503</v>
+        <v>39.82746796772497</v>
       </c>
       <c r="L2" t="n">
         <v>38.94563449483029</v>
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.47589530418091</v>
+        <v>38.47589530418092</v>
       </c>
       <c r="C3" t="n">
-        <v>44.38571219559084</v>
+        <v>44.38571219559086</v>
       </c>
       <c r="D3" t="n">
-        <v>39.15205464619196</v>
+        <v>39.15205464619193</v>
       </c>
       <c r="E3" t="n">
-        <v>46.85044685894856</v>
+        <v>46.85044685894857</v>
       </c>
       <c r="F3" t="n">
         <v>41.36949360754261</v>
@@ -6909,19 +6909,19 @@
         <v>39.31433015402379</v>
       </c>
       <c r="H3" t="n">
-        <v>39.23022891739446</v>
+        <v>39.23022891739448</v>
       </c>
       <c r="I3" t="n">
-        <v>39.38988785651635</v>
+        <v>39.38988785651634</v>
       </c>
       <c r="J3" t="n">
-        <v>49.69464166539549</v>
+        <v>49.69464166539552</v>
       </c>
       <c r="K3" t="n">
         <v>40.49980389767989</v>
       </c>
       <c r="L3" t="n">
-        <v>39.97814520938575</v>
+        <v>39.9781452093857</v>
       </c>
     </row>
     <row r="4">
@@ -6931,34 +6931,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.236863249124559</v>
+        <v>1.236863249124555</v>
       </c>
       <c r="C4" t="n">
         <v>2.664243267941179</v>
       </c>
       <c r="D4" t="n">
-        <v>2.314293797107067</v>
+        <v>2.314293797107065</v>
       </c>
       <c r="E4" t="n">
-        <v>2.676184797679037</v>
+        <v>2.676184797679034</v>
       </c>
       <c r="F4" t="n">
-        <v>2.676184797679037</v>
+        <v>2.676184797679034</v>
       </c>
       <c r="G4" t="n">
-        <v>2.571010893891048</v>
+        <v>2.571010893891053</v>
       </c>
       <c r="H4" t="n">
-        <v>2.433181076270236</v>
+        <v>2.433181076270235</v>
       </c>
       <c r="I4" t="n">
-        <v>2.697359298994122</v>
+        <v>2.697359298994123</v>
       </c>
       <c r="J4" t="n">
-        <v>4.031410477847092</v>
+        <v>4.031410477847091</v>
       </c>
       <c r="K4" t="n">
-        <v>1.697361280127093</v>
+        <v>1.69736128012709</v>
       </c>
       <c r="L4" t="n">
         <v>3.604355844599808</v>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.324372068760545</v>
+        <v>4.324372068760542</v>
       </c>
       <c r="C5" t="n">
         <v>27.33647751804329</v>
       </c>
       <c r="D5" t="n">
-        <v>20.98816053715341</v>
+        <v>20.98816053715334</v>
       </c>
       <c r="E5" t="n">
-        <v>27.33647877373495</v>
+        <v>27.33647877373496</v>
       </c>
       <c r="F5" t="n">
-        <v>27.33647877373495</v>
+        <v>27.33647877373496</v>
       </c>
       <c r="G5" t="n">
-        <v>25.84016370946691</v>
+        <v>25.84016370946693</v>
       </c>
       <c r="H5" t="n">
-        <v>25.44814037099825</v>
+        <v>25.44814037099823</v>
       </c>
       <c r="I5" t="n">
-        <v>27.33647558488415</v>
+        <v>27.33647558488417</v>
       </c>
       <c r="J5" t="n">
-        <v>52.04573072683232</v>
+        <v>52.04573072683247</v>
       </c>
       <c r="K5" t="n">
-        <v>11.19530180254607</v>
+        <v>11.19530180254609</v>
       </c>
       <c r="L5" t="n">
-        <v>14.924322307935</v>
+        <v>14.92432230793501</v>
       </c>
     </row>
     <row r="6">
@@ -7011,34 +7011,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.3838622620219</v>
+        <v>112.383862262022</v>
       </c>
       <c r="C6" t="n">
-        <v>113.847395670388</v>
+        <v>113.8473956703879</v>
       </c>
       <c r="D6" t="n">
-        <v>113.4584232177803</v>
+        <v>113.4584232177804</v>
       </c>
       <c r="E6" t="n">
         <v>102.7954782596945</v>
       </c>
       <c r="F6" t="n">
-        <v>113.8511599707137</v>
+        <v>113.8511599707136</v>
       </c>
       <c r="G6" t="n">
-        <v>113.7180099067884</v>
+        <v>113.7180099067883</v>
       </c>
       <c r="H6" t="n">
-        <v>135.557048475883</v>
+        <v>135.5570484758829</v>
       </c>
       <c r="I6" t="n">
-        <v>113.8443583118914</v>
+        <v>113.8443583118916</v>
       </c>
       <c r="J6" t="n">
-        <v>120.8554730336598</v>
+        <v>120.8554730336597</v>
       </c>
       <c r="K6" t="n">
-        <v>112.8218443311953</v>
+        <v>112.8218443311952</v>
       </c>
       <c r="L6" t="n">
         <v>114.7662280614021</v>
@@ -7051,34 +7051,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.035933076104913</v>
+        <v>2.03593307610491</v>
       </c>
       <c r="C7" t="n">
-        <v>3.496431059133626</v>
+        <v>3.496431059133627</v>
       </c>
       <c r="D7" t="n">
-        <v>3.11336206603779</v>
+        <v>3.113362066037789</v>
       </c>
       <c r="E7" t="n">
-        <v>3.490661226028442</v>
+        <v>3.490661226028438</v>
       </c>
       <c r="F7" t="n">
-        <v>3.490661226028442</v>
+        <v>3.490661226028438</v>
       </c>
       <c r="G7" t="n">
-        <v>3.370080720871414</v>
+        <v>3.370080720871408</v>
       </c>
       <c r="H7" t="n">
-        <v>3.232250903250592</v>
+        <v>3.23225090325059</v>
       </c>
       <c r="I7" t="n">
-        <v>3.49642912597448</v>
+        <v>3.496429125974476</v>
       </c>
       <c r="J7" t="n">
         <v>4.830480304827447</v>
       </c>
       <c r="K7" t="n">
-        <v>2.496431107107445</v>
+        <v>2.496431107107447</v>
       </c>
       <c r="L7" t="n">
         <v>4.403425671580163</v>
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.210563727100496</v>
+        <v>2.210563727100495</v>
       </c>
       <c r="C8" t="n">
-        <v>4.39180480176054</v>
+        <v>4.391804801760541</v>
       </c>
       <c r="D8" t="n">
-        <v>4.164692510274152</v>
+        <v>4.164692510274149</v>
       </c>
       <c r="E8" t="n">
         <v>4.193799306014427</v>
       </c>
       <c r="F8" t="n">
-        <v>3.690638372836973</v>
+        <v>3.690638372836969</v>
       </c>
       <c r="G8" t="n">
-        <v>4.270841744141195</v>
+        <v>4.270841744141213</v>
       </c>
       <c r="H8" t="n">
-        <v>4.133011926519124</v>
+        <v>4.133011926519123</v>
       </c>
       <c r="I8" t="n">
-        <v>4.397190149244294</v>
+        <v>4.39719014924428</v>
       </c>
       <c r="J8" t="n">
-        <v>5.73138403255321</v>
+        <v>5.731384032553219</v>
       </c>
       <c r="K8" t="n">
-        <v>2.657573513724615</v>
+        <v>2.657573513724612</v>
       </c>
       <c r="L8" t="n">
-        <v>6.062690585828164</v>
+        <v>6.062690585828161</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.611660232204686</v>
+        <v>3.611660232204684</v>
       </c>
       <c r="C9" t="n">
-        <v>5.775688899559899</v>
+        <v>5.7756888995599</v>
       </c>
       <c r="D9" t="n">
         <v>5.392621959133157</v>
       </c>
       <c r="E9" t="n">
-        <v>6.587549759747735</v>
+        <v>6.587549759747742</v>
       </c>
       <c r="F9" t="n">
-        <v>5.775689887185959</v>
+        <v>5.77568988718596</v>
       </c>
       <c r="G9" t="n">
-        <v>5.649338561297689</v>
+        <v>5.649338561297695</v>
       </c>
       <c r="H9" t="n">
-        <v>5.511508743676876</v>
+        <v>5.511508743676873</v>
       </c>
       <c r="I9" t="n">
-        <v>5.775686966400761</v>
+        <v>5.775686966400754</v>
       </c>
       <c r="J9" t="n">
-        <v>7.109738145253722</v>
+        <v>7.109738145253733</v>
       </c>
       <c r="K9" t="n">
-        <v>4.35152270168213</v>
+        <v>4.351522701682139</v>
       </c>
       <c r="L9" t="n">
-        <v>6.682683512006439</v>
+        <v>6.682683512006449</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.53065265210493</v>
+        <v>39.53065265210489</v>
       </c>
       <c r="C2" t="n">
-        <v>42.82822308126441</v>
+        <v>42.82822308126437</v>
       </c>
       <c r="D2" t="n">
-        <v>39.73705224428787</v>
+        <v>39.73705224428783</v>
       </c>
       <c r="E2" t="n">
-        <v>44.36814283513358</v>
+        <v>44.36814283513356</v>
       </c>
       <c r="F2" t="n">
-        <v>40.92449498684181</v>
+        <v>40.92449498684179</v>
       </c>
       <c r="G2" t="n">
-        <v>39.71437889808684</v>
+        <v>39.7143788980868</v>
       </c>
       <c r="H2" t="n">
-        <v>40.06040995392646</v>
+        <v>40.06040995392642</v>
       </c>
       <c r="I2" t="n">
-        <v>39.66923953350296</v>
+        <v>39.66923953350292</v>
       </c>
       <c r="J2" t="n">
-        <v>46.05204684694939</v>
+        <v>46.05204684694936</v>
       </c>
       <c r="K2" t="n">
-        <v>40.97548752789438</v>
+        <v>40.97548752789437</v>
       </c>
       <c r="L2" t="n">
-        <v>39.94899396491952</v>
+        <v>39.94899396491947</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.21739230859985</v>
+        <v>40.21739230859983</v>
       </c>
       <c r="C3" t="n">
-        <v>46.41848917186226</v>
+        <v>46.41848917186225</v>
       </c>
       <c r="D3" t="n">
         <v>41.68200574264366</v>
       </c>
       <c r="E3" t="n">
-        <v>48.95606285676036</v>
+        <v>48.9560628567604</v>
       </c>
       <c r="F3" t="n">
-        <v>43.27169158167909</v>
+        <v>43.27169158167911</v>
       </c>
       <c r="G3" t="n">
-        <v>41.52607901887318</v>
+        <v>41.52607901887317</v>
       </c>
       <c r="H3" t="n">
-        <v>43.99210751074573</v>
+        <v>43.99210751074568</v>
       </c>
       <c r="I3" t="n">
-        <v>41.19970733647136</v>
+        <v>41.19970733647132</v>
       </c>
       <c r="J3" t="n">
         <v>53.60630393486804</v>
       </c>
       <c r="K3" t="n">
-        <v>43.42798864181739</v>
+        <v>43.42798864181738</v>
       </c>
       <c r="L3" t="n">
-        <v>43.22218976774576</v>
+        <v>43.22218976774579</v>
       </c>
     </row>
     <row r="4">
@@ -7330,34 +7330,34 @@
         <v>3.791501674366591</v>
       </c>
       <c r="C4" t="n">
-        <v>5.330832834053775</v>
+        <v>5.33083283405378</v>
       </c>
       <c r="D4" t="n">
-        <v>6.122880016576075</v>
+        <v>6.122880016576073</v>
       </c>
       <c r="E4" t="n">
-        <v>5.348996098173211</v>
+        <v>5.348996098173214</v>
       </c>
       <c r="F4" t="n">
-        <v>5.348996098173211</v>
+        <v>5.348996098173214</v>
       </c>
       <c r="G4" t="n">
-        <v>5.867246442941773</v>
+        <v>5.867246442941796</v>
       </c>
       <c r="H4" t="n">
-        <v>9.762808368881077</v>
+        <v>9.762808368881091</v>
       </c>
       <c r="I4" t="n">
-        <v>5.359792983243748</v>
+        <v>5.35979298324375</v>
       </c>
       <c r="J4" t="n">
-        <v>9.179079524747685</v>
+        <v>9.179079524747687</v>
       </c>
       <c r="K4" t="n">
-        <v>5.499479230281777</v>
+        <v>5.499479230281785</v>
       </c>
       <c r="L4" t="n">
-        <v>8.497161824330979</v>
+        <v>8.497161824330975</v>
       </c>
     </row>
     <row r="5">
@@ -7370,34 +7370,34 @@
         <v>39.54403898228888</v>
       </c>
       <c r="C5" t="n">
-        <v>65.37125969559884</v>
+        <v>65.37125969559877</v>
       </c>
       <c r="D5" t="n">
-        <v>78.91449425705075</v>
+        <v>78.91449425705088</v>
       </c>
       <c r="E5" t="n">
-        <v>65.37126066794788</v>
+        <v>65.37126066794777</v>
       </c>
       <c r="F5" t="n">
-        <v>65.37126066794788</v>
+        <v>65.37126066794777</v>
       </c>
       <c r="G5" t="n">
-        <v>77.35054608116599</v>
+        <v>77.35054608116606</v>
       </c>
       <c r="H5" t="n">
-        <v>152.7977968016694</v>
+        <v>152.7977968016693</v>
       </c>
       <c r="I5" t="n">
-        <v>65.37110879489309</v>
+        <v>65.371108794893</v>
       </c>
       <c r="J5" t="n">
-        <v>145.4900426867858</v>
+        <v>145.4900426867859</v>
       </c>
       <c r="K5" t="n">
-        <v>69.63745022151355</v>
+        <v>69.63745022151362</v>
       </c>
       <c r="L5" t="n">
-        <v>46.06276198936966</v>
+        <v>46.06276198936992</v>
       </c>
     </row>
     <row r="6">
@@ -7407,22 +7407,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.3069211714075</v>
+        <v>123.3069211714076</v>
       </c>
       <c r="C6" t="n">
-        <v>124.8619119677834</v>
+        <v>124.8619119677835</v>
       </c>
       <c r="D6" t="n">
-        <v>125.6555210801151</v>
+        <v>125.6555210801152</v>
       </c>
       <c r="E6" t="n">
-        <v>112.9837772769435</v>
+        <v>112.9837772769436</v>
       </c>
       <c r="F6" t="n">
         <v>124.8825739572462</v>
       </c>
       <c r="G6" t="n">
-        <v>149.2032200211463</v>
+        <v>149.2032200211464</v>
       </c>
       <c r="H6" t="n">
         <v>153.232899426041</v>
@@ -7431,10 +7431,10 @@
         <v>148.6957665614482</v>
       </c>
       <c r="J6" t="n">
-        <v>152.5833293003563</v>
+        <v>152.5833293003562</v>
       </c>
       <c r="K6" t="n">
-        <v>125.0170311504757</v>
+        <v>125.0170311504759</v>
       </c>
       <c r="L6" t="n">
         <v>128.040959333035</v>
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.941952722905322</v>
+        <v>4.941952722905333</v>
       </c>
       <c r="C7" t="n">
-        <v>6.510394932488287</v>
+        <v>6.510394932488291</v>
       </c>
       <c r="D7" t="n">
-        <v>7.273320471896435</v>
+        <v>7.273320471896459</v>
       </c>
       <c r="E7" t="n">
-        <v>6.509270713601472</v>
+        <v>6.509270713601475</v>
       </c>
       <c r="F7" t="n">
-        <v>6.509270713601472</v>
+        <v>6.509270713601474</v>
       </c>
       <c r="G7" t="n">
-        <v>7.017697491480523</v>
+        <v>7.017697491480532</v>
       </c>
       <c r="H7" t="n">
-        <v>10.91325941741982</v>
+        <v>10.91325941741984</v>
       </c>
       <c r="I7" t="n">
-        <v>6.510244031782495</v>
+        <v>6.510244031782493</v>
       </c>
       <c r="J7" t="n">
-        <v>10.32953057328641</v>
+        <v>10.32953057328643</v>
       </c>
       <c r="K7" t="n">
-        <v>6.649930278820509</v>
+        <v>6.649930278820524</v>
       </c>
       <c r="L7" t="n">
-        <v>9.647612872869697</v>
+        <v>9.647612872869724</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.392495918721503</v>
+        <v>5.392495918721519</v>
       </c>
       <c r="C8" t="n">
         <v>8.171177798285864</v>
       </c>
       <c r="D8" t="n">
-        <v>9.186076509849569</v>
+        <v>9.186076509849572</v>
       </c>
       <c r="E8" t="n">
-        <v>7.840058091111795</v>
+        <v>7.840058091111797</v>
       </c>
       <c r="F8" t="n">
-        <v>6.998663475030498</v>
+        <v>6.998663475030497</v>
       </c>
       <c r="G8" t="n">
-        <v>8.679318137596688</v>
+        <v>8.679318137596701</v>
       </c>
       <c r="H8" t="n">
-        <v>12.57488006353693</v>
+        <v>12.57488006353696</v>
       </c>
       <c r="I8" t="n">
-        <v>8.171864677898666</v>
+        <v>8.171864677898668</v>
       </c>
       <c r="J8" t="n">
-        <v>11.99138922904706</v>
+        <v>11.99138922904709</v>
       </c>
       <c r="K8" t="n">
-        <v>7.077977089383133</v>
+        <v>7.077977089383162</v>
       </c>
       <c r="L8" t="n">
-        <v>12.57430518281901</v>
+        <v>12.57430518281905</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.149904778543906</v>
+        <v>8.149904778543924</v>
       </c>
       <c r="C9" t="n">
-        <v>11.0080479401402</v>
+        <v>11.00804794014021</v>
       </c>
       <c r="D9" t="n">
-        <v>11.77098430773746</v>
+        <v>11.77098430773749</v>
       </c>
       <c r="E9" t="n">
-        <v>12.49633444511754</v>
+        <v>12.49633444511756</v>
       </c>
       <c r="F9" t="n">
         <v>11.0080471266282</v>
       </c>
       <c r="G9" t="n">
-        <v>11.51535049913243</v>
+        <v>11.51535049913246</v>
       </c>
       <c r="H9" t="n">
-        <v>15.41091242507174</v>
+        <v>15.41091242507175</v>
       </c>
       <c r="I9" t="n">
         <v>11.00789703943441</v>
       </c>
       <c r="J9" t="n">
-        <v>14.82718358093832</v>
+        <v>14.82718358093835</v>
       </c>
       <c r="K9" t="n">
-        <v>10.40032558865725</v>
+        <v>10.40032558865726</v>
       </c>
       <c r="L9" t="n">
-        <v>14.14526588052163</v>
+        <v>14.14526588052165</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.04493957255399</v>
+        <v>39.04493957255402</v>
       </c>
       <c r="C2" t="n">
-        <v>42.32270411766963</v>
+        <v>42.32270411766964</v>
       </c>
       <c r="D2" t="n">
-        <v>39.37166287298752</v>
+        <v>39.37166287298755</v>
       </c>
       <c r="E2" t="n">
         <v>43.84253650176903</v>
       </c>
       <c r="F2" t="n">
-        <v>40.45338141098799</v>
+        <v>40.45338141098801</v>
       </c>
       <c r="G2" t="n">
-        <v>39.28418902902357</v>
+        <v>39.28418902902362</v>
       </c>
       <c r="H2" t="n">
-        <v>39.26378152757619</v>
+        <v>39.26378152757621</v>
       </c>
       <c r="I2" t="n">
-        <v>39.23838145905376</v>
+        <v>39.23838145905378</v>
       </c>
       <c r="J2" t="n">
-        <v>45.42319877244569</v>
+        <v>45.42319877244574</v>
       </c>
       <c r="K2" t="n">
-        <v>40.31129174019638</v>
+        <v>40.3112917401964</v>
       </c>
       <c r="L2" t="n">
-        <v>39.50038795146245</v>
+        <v>39.50038795146247</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.76962952449717</v>
+        <v>38.76962952449721</v>
       </c>
       <c r="C3" t="n">
-        <v>45.23574282110591</v>
+        <v>45.23574282110592</v>
       </c>
       <c r="D3" t="n">
-        <v>41.08426258504394</v>
+        <v>41.08426258504398</v>
       </c>
       <c r="E3" t="n">
-        <v>47.74120825172405</v>
+        <v>47.74120825172402</v>
       </c>
       <c r="F3" t="n">
-        <v>42.14678839976361</v>
+        <v>42.14678839976366</v>
       </c>
       <c r="G3" t="n">
-        <v>40.46889365936865</v>
+        <v>40.4688936593687</v>
       </c>
       <c r="H3" t="n">
-        <v>40.34307463746584</v>
+        <v>40.34307463746591</v>
       </c>
       <c r="I3" t="n">
-        <v>40.14124496868283</v>
+        <v>40.14124496868287</v>
       </c>
       <c r="J3" t="n">
-        <v>51.95265467220104</v>
+        <v>51.95265467220109</v>
       </c>
       <c r="K3" t="n">
         <v>41.5564481244603</v>
       </c>
       <c r="L3" t="n">
-        <v>42.02269796755363</v>
+        <v>42.02269796755368</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.564543215159968</v>
+        <v>1.564543215159969</v>
       </c>
       <c r="C4" t="n">
         <v>3.717657462514984</v>
       </c>
       <c r="D4" t="n">
-        <v>5.255033193700681</v>
+        <v>5.255033193700672</v>
       </c>
       <c r="E4" t="n">
-        <v>3.732243351947479</v>
+        <v>3.73224335194748</v>
       </c>
       <c r="F4" t="n">
-        <v>3.73224335194748</v>
+        <v>3.732243351947481</v>
       </c>
       <c r="G4" t="n">
-        <v>4.267477306830321</v>
+        <v>4.267477306830317</v>
       </c>
       <c r="H4" t="n">
-        <v>4.062913689053914</v>
+        <v>4.062913689053925</v>
       </c>
       <c r="I4" t="n">
-        <v>3.752612291270802</v>
+        <v>3.752612291270804</v>
       </c>
       <c r="J4" t="n">
-        <v>7.0266201104193</v>
+        <v>7.02662011041931</v>
       </c>
       <c r="K4" t="n">
-        <v>3.011388245948335</v>
+        <v>3.011388245948342</v>
       </c>
       <c r="L4" t="n">
         <v>6.687221316634373</v>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.917416326301149</v>
+        <v>5.917416326301136</v>
       </c>
       <c r="C5" t="n">
-        <v>39.90792598027414</v>
+        <v>39.90792598027416</v>
       </c>
       <c r="D5" t="n">
-        <v>62.27251043392864</v>
+        <v>62.2725104339286</v>
       </c>
       <c r="E5" t="n">
         <v>39.90792715075636</v>
@@ -7778,22 +7778,22 @@
         <v>39.90792715075636</v>
       </c>
       <c r="G5" t="n">
-        <v>49.42857811603667</v>
+        <v>49.42857811603661</v>
       </c>
       <c r="H5" t="n">
         <v>48.64817963423658</v>
       </c>
       <c r="I5" t="n">
-        <v>39.90777563339501</v>
+        <v>39.90777563339505</v>
       </c>
       <c r="J5" t="n">
-        <v>103.3170023307412</v>
+        <v>103.3170023307413</v>
       </c>
       <c r="K5" t="n">
-        <v>28.25236844656077</v>
+        <v>28.2523684465608</v>
       </c>
       <c r="L5" t="n">
-        <v>103.9654368604552</v>
+        <v>103.965436860455</v>
       </c>
     </row>
     <row r="6">
@@ -7812,16 +7812,16 @@
         <v>116.5519179537493</v>
       </c>
       <c r="E6" t="n">
-        <v>103.9354233056241</v>
+        <v>103.935423305624</v>
       </c>
       <c r="F6" t="n">
         <v>115.0130217570188</v>
       </c>
       <c r="G6" t="n">
-        <v>137.5654534269977</v>
+        <v>137.5654534269976</v>
       </c>
       <c r="H6" t="n">
-        <v>137.4678211124944</v>
+        <v>137.4678211124943</v>
       </c>
       <c r="I6" t="n">
         <v>137.050588411438</v>
@@ -7833,7 +7833,7 @@
         <v>114.2412205570437</v>
       </c>
       <c r="L6" t="n">
-        <v>117.9673457580297</v>
+        <v>117.9673457580296</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.494779852483951</v>
+        <v>2.494779852483946</v>
       </c>
       <c r="C7" t="n">
         <v>4.682999275473865</v>
       </c>
       <c r="D7" t="n">
-        <v>6.185265058024383</v>
+        <v>6.185265058024379</v>
       </c>
       <c r="E7" t="n">
-        <v>4.679115399712323</v>
+        <v>4.679115399712325</v>
       </c>
       <c r="F7" t="n">
-        <v>4.679115399712323</v>
+        <v>4.679115399712327</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1977139441543</v>
+        <v>5.197713944154291</v>
       </c>
       <c r="H7" t="n">
-        <v>4.993150326377897</v>
+        <v>4.993150326377899</v>
       </c>
       <c r="I7" t="n">
-        <v>4.68284892859478</v>
+        <v>4.682848928594783</v>
       </c>
       <c r="J7" t="n">
-        <v>7.956856747743284</v>
+        <v>7.956856747743283</v>
       </c>
       <c r="K7" t="n">
-        <v>3.941624883272322</v>
+        <v>3.941624883272317</v>
       </c>
       <c r="L7" t="n">
-        <v>7.617457953958359</v>
+        <v>7.61745795395835</v>
       </c>
     </row>
     <row r="8">
@@ -7886,34 +7886,34 @@
         <v>2.800960802713448</v>
       </c>
       <c r="C8" t="n">
-        <v>5.915104862452596</v>
+        <v>5.915104862452605</v>
       </c>
       <c r="D8" t="n">
-        <v>7.613645253783449</v>
+        <v>7.613645253783453</v>
       </c>
       <c r="E8" t="n">
-        <v>5.661292142592321</v>
+        <v>5.661292142592324</v>
       </c>
       <c r="F8" t="n">
-        <v>5.016329200750484</v>
+        <v>5.016329200750492</v>
       </c>
       <c r="G8" t="n">
-        <v>6.433358941871626</v>
+        <v>6.433358941871629</v>
       </c>
       <c r="H8" t="n">
-        <v>6.228795324096664</v>
+        <v>6.228795324096678</v>
       </c>
       <c r="I8" t="n">
-        <v>5.918493926312106</v>
+        <v>5.918493926312117</v>
       </c>
       <c r="J8" t="n">
-        <v>9.192684410460265</v>
+        <v>9.192684410460268</v>
       </c>
       <c r="K8" t="n">
-        <v>4.230540561748031</v>
+        <v>4.230540561748036</v>
       </c>
       <c r="L8" t="n">
-        <v>9.824005868568433</v>
+        <v>9.824005868568438</v>
       </c>
     </row>
     <row r="9">
@@ -7926,34 +7926,34 @@
         <v>4.703595021681753</v>
       </c>
       <c r="C9" t="n">
-        <v>7.822549238734277</v>
+        <v>7.822549238734274</v>
       </c>
       <c r="D9" t="n">
         <v>9.324820685519409</v>
       </c>
       <c r="E9" t="n">
-        <v>8.896598773817859</v>
+        <v>8.89659877381785</v>
       </c>
       <c r="F9" t="n">
-        <v>7.822549882305733</v>
+        <v>7.822549882305729</v>
       </c>
       <c r="G9" t="n">
-        <v>8.337263907414718</v>
+        <v>8.337263907414712</v>
       </c>
       <c r="H9" t="n">
-        <v>8.132700289638315</v>
+        <v>8.132700289638308</v>
       </c>
       <c r="I9" t="n">
-        <v>7.822398891855189</v>
+        <v>7.822398891855192</v>
       </c>
       <c r="J9" t="n">
         <v>11.0964067110037</v>
       </c>
       <c r="K9" t="n">
-        <v>6.541903826424965</v>
+        <v>6.54190382642495</v>
       </c>
       <c r="L9" t="n">
-        <v>10.75700791721877</v>
+        <v>10.75700791721876</v>
       </c>
     </row>
   </sheetData>
